--- a/projetos/gestao-ia-planilhas/produto/kit-medicos/15-orcamentos.xlsx
+++ b/projetos/gestao-ia-planilhas/produto/kit-medicos/15-orcamentos.xlsx
@@ -895,7 +895,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Ao decidir, mude a etapa para Aprovado, Recusado ou Sem retorno e preencha a data. Se recusado, anote o motivo: é a parte mais valiosa da planilha. Aprovado vira horário na agenda (01) e, se for a prazo, parcela na 14.</t>
+          <t>Ao decidir, mude a etapa para Aprovado, Recusado ou Sem retorno e preencha a data — que é sempre igual ou posterior à da apresentação. Se recusado, anote o motivo: é a parte mais valiosa da planilha. Aprovado vira horário na agenda (01) e, se for a prazo, parcela na 14 — e a prazo só para quem não tem parcela vencida em aberto.</t>
         </is>
       </c>
     </row>
@@ -919,7 +919,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Sexta-feira, 10 minutos: atualizar etapas, retomar os parados. Dia 1 do mês: comparar o aprovado com a meta e olhar os motivos de recusa. O Painel da clínica (17) copia "Em aberto" e "Aprovado no mês" daqui.</t>
+          <t>Sexta-feira, 3 minutos (rotina da semana, planilha 03): atualizar as etapas e retomar os parados. Dia 1 do mês: comparar o aprovado com a meta e olhar os motivos de recusa. O Painel da clínica (17) copia "Em aberto" e "Aprovado no mês" daqui.</t>
         </is>
       </c>
     </row>
@@ -1125,22 +1125,22 @@
       <c r="D5" s="10" t="n"/>
       <c r="E5" s="15">
         <f>SUMIFS(Orçamentos!$F$5:$F$304,Orçamentos!$G$5:$G$304,"Aprovado",Orçamentos!$H$5:$H$304,"&gt;="&amp;DATE(YEAR(Config!$B$5),3*INT((MONTH(Config!$B$5)-1)/3)+1,1))</f>
-        <v>8510</v>
+        <v>8960</v>
       </c>
       <c r="F5" s="12" t="n"/>
       <c r="G5" s="16">
         <f>IFERROR(E5/Config!$B$6,0)</f>
-        <v>0.472777777777778</v>
+        <v>0.497777777777778</v>
       </c>
       <c r="H5" s="12" t="n"/>
       <c r="I5" s="17">
         <f>IFERROR(COUNTIFS(Orçamentos!$G$5:$G$304,"Aprovado")/(COUNTIFS(Orçamentos!$G$5:$G$304,"Aprovado")+COUNTIFS(Orçamentos!$G$5:$G$304,"Recusado")+COUNTIFS(Orçamentos!$G$5:$G$304,"Sem retorno")),0)</f>
-        <v>0.724137931034483</v>
+        <v>0.733333333333333</v>
       </c>
       <c r="J5" s="8" t="n"/>
       <c r="K5" s="18">
         <f>IFERROR(AVERAGEIFS(Orçamentos!$N$5:$N$304,Orçamentos!$G$5:$G$304,"Aprovado"),0)</f>
-        <v>5.90476190476191</v>
+        <v>11.3636363636364</v>
       </c>
       <c r="L5" s="8" t="n"/>
     </row>
@@ -1248,11 +1248,11 @@
       </c>
       <c r="B13" s="25">
         <f>COUNTIFS(Orçamentos!$G$5:$G$304,"Aprovado")</f>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C13" s="26">
         <f>SUMIFS(Orçamentos!$F$5:$F$304,Orçamentos!$G$5:$G$304,"Aprovado")</f>
-        <v>8510</v>
+        <v>8960</v>
       </c>
       <c r="E13" s="27" t="str">
         <f>REPT("█",ROUND(IFERROR(C13/MAX($C$11:$C$15),0)*30,0))</f>
@@ -1278,7 +1278,7 @@
       </c>
       <c r="E14" s="28" t="str">
         <f>REPT("█",ROUND(IFERROR(C14/MAX($C$11:$C$15),0)*30,0))</f>
-        <v>███████</v>
+        <v>██████</v>
       </c>
       <c r="F14" s="22" t="n"/>
       <c r="G14" s="22" t="n"/>
@@ -1314,7 +1314,7 @@
       </c>
       <c r="B16" s="26">
         <f>IFERROR(C13/B13,0)</f>
-        <v>405.238095238095</v>
+        <v>407.272727272727</v>
       </c>
     </row>
     <row r="17"/>
@@ -1720,11 +1720,11 @@
       </c>
       <c r="B33" s="25">
         <f>IF(Config!$A$19="","",COUNTIFS(Orçamentos!$D$5:$D$304,Config!$A$19))</f>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C33" s="25">
         <f>IF(Config!$A$19="","",COUNTIFS(Orçamentos!$D$5:$D$304,Config!$A$19,Orçamentos!$G$5:$G$304,"Aprovado"))</f>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D33" s="25">
         <f>IF(Config!$A$19="","",COUNTIFS(Orçamentos!$D$5:$D$304,Config!$A$19,Orçamentos!$G$5:$G$304,"Recusado")+COUNTIFS(Orçamentos!$D$5:$D$304,Config!$A$19,Orçamentos!$G$5:$G$304,"Sem retorno"))</f>
@@ -1732,11 +1732,11 @@
       </c>
       <c r="E33" s="30">
         <f>IF(Config!$A$19="","",IFERROR(C33/(C33+D33),0))</f>
-        <v>0.833333333333333</v>
+        <v>0.84</v>
       </c>
       <c r="F33" s="26">
         <f>IF(Config!$A$19="","",SUMIFS(Orçamentos!$F$5:$F$304,Orçamentos!$D$5:$D$304,Config!$A$19,Orçamentos!$G$5:$G$304,"Aprovado"))</f>
-        <v>7550</v>
+        <v>8000</v>
       </c>
       <c r="G33" s="26">
         <f>IF(Config!$A$19="","",SUMIFS(Orçamentos!$F$5:$F$304,Orçamentos!$D$5:$D$304,Config!$A$19,Orçamentos!$G$5:$G$304,"&lt;&gt;Aprovado",Orçamentos!$G$5:$G$304,"&lt;&gt;Recusado",Orçamentos!$G$5:$G$304,"&lt;&gt;Sem retorno",Orçamentos!$G$5:$G$304,"&lt;&gt;"))</f>
@@ -2099,19 +2099,19 @@
       </c>
       <c r="G46" s="25">
         <f>IF(Config!$E$19="","",COUNTIFS(Orçamentos!$C$5:$C$304,Config!$E$19))</f>
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H46" s="25">
         <f>IF(Config!$E$19="","",COUNTIFS(Orçamentos!$C$5:$C$304,Config!$E$19,Orçamentos!$G$5:$G$304,"Aprovado"))</f>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I46" s="30">
         <f>IF(Config!$E$19="","",IFERROR(H46/(H46+COUNTIFS(Orçamentos!$C$5:$C$304,Config!$E$19,Orçamentos!$G$5:$G$304,"Recusado")+COUNTIFS(Orçamentos!$C$5:$C$304,Config!$E$19,Orçamentos!$G$5:$G$304,"Sem retorno")),0))</f>
-        <v>0.807692307692308</v>
+        <v>0.814814814814815</v>
       </c>
       <c r="J46" s="26">
         <f>IF(Config!$E$19="","",SUMIFS(Orçamentos!$F$5:$F$304,Orçamentos!$C$5:$C$304,Config!$E$19,Orçamentos!$G$5:$G$304,"Aprovado"))</f>
-        <v>8510</v>
+        <v>8960</v>
       </c>
     </row>
     <row r="47">
@@ -2802,7 +2802,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q306"/>
+  <dimension ref="A1:Q308"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -2922,11 +2922,11 @@
     </row>
     <row r="5">
       <c r="A5" s="37" t="n">
-        <v>46206</v>
+        <v>46198</v>
       </c>
       <c r="B5" s="32" t="inlineStr">
         <is>
-          <t>Gustavo Ferreira</t>
+          <t>Helena Moreira</t>
         </is>
       </c>
       <c r="C5" s="35" t="inlineStr">
@@ -2941,11 +2941,11 @@
       </c>
       <c r="E5" s="32" t="inlineStr">
         <is>
-          <t>Holter</t>
+          <t>MAPA</t>
         </is>
       </c>
       <c r="F5" s="38" t="n">
-        <v>350</v>
+        <v>300</v>
       </c>
       <c r="G5" s="35" t="inlineStr">
         <is>
@@ -2953,12 +2953,12 @@
         </is>
       </c>
       <c r="H5" s="37" t="n">
-        <v>46212</v>
+        <v>46216</v>
       </c>
       <c r="I5" s="35" t="n"/>
       <c r="J5" s="32" t="inlineStr">
         <is>
-          <t>Agendado para 09/07</t>
+          <t>Agendado para 14/07</t>
         </is>
       </c>
       <c r="K5" s="30">
@@ -2967,15 +2967,15 @@
       </c>
       <c r="L5" s="26">
         <f>IF(OR(G5="",F5=""),"",F5*K5)</f>
-        <v>350</v>
+        <v>300</v>
       </c>
       <c r="M5" s="29">
         <f>IF(OR(G5="",G5="Aprovado",G5="Recusado",G5="Sem retorno",A5=""),"",Config!$B$5-A5)</f>
         <v/>
       </c>
       <c r="N5" s="29">
-        <f>IF(AND(OR(G5="Aprovado",G5="Recusado"),H5&lt;&gt;"",A5&lt;&gt;""),H5-A5,"")</f>
-        <v>6</v>
+        <f>IF(AND(OR(G5="Aprovado",G5="Recusado"),H5&lt;&gt;"",A5&lt;&gt;"",H5&gt;=A5),H5-A5,"")</f>
+        <v>18</v>
       </c>
       <c r="O5" s="25" t="str">
         <f>IF(G5="","",IF(OR(G5="Aprovado",G5="Recusado",G5="Sem retorno"),G5,IF(AND(M5&lt;&gt;"",M5&gt;Config!$B$7),"Parado","Ativo")))</f>
@@ -2983,7 +2983,7 @@
       </c>
       <c r="P5" s="39">
         <f>IF(A5="","",DATE(YEAR(A5),MONTH(A5),1))</f>
-        <v>46204.0</v>
+        <v>46174.0</v>
       </c>
       <c r="Q5" s="40">
         <f>IF(OR(G5="",O5="Aprovado",O5="Recusado",O5="Sem retorno"),0,IF(O5="Parado",2000,1000)+MIN(N(M5),500)+N(F5)/1000000-ROW()/100000)</f>
@@ -2991,137 +2991,137 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="37">
+      <c r="A6" s="37" t="n">
+        <v>46199</v>
+      </c>
+      <c r="B6" s="32" t="inlineStr">
+        <is>
+          <t>Gustavo Ferreira</t>
+        </is>
+      </c>
+      <c r="C6" s="35" t="inlineStr">
+        <is>
+          <t>Dr. Paulo Andrade</t>
+        </is>
+      </c>
+      <c r="D6" s="35" t="inlineStr">
+        <is>
+          <t>Exame cardiológico</t>
+        </is>
+      </c>
+      <c r="E6" s="32" t="inlineStr">
+        <is>
+          <t>Holter</t>
+        </is>
+      </c>
+      <c r="F6" s="38" t="n">
+        <v>350</v>
+      </c>
+      <c r="G6" s="35" t="inlineStr">
+        <is>
+          <t>Aprovado</t>
+        </is>
+      </c>
+      <c r="H6" s="37" t="n">
+        <v>46211</v>
+      </c>
+      <c r="I6" s="35" t="n"/>
+      <c r="J6" s="32" t="inlineStr">
+        <is>
+          <t>Agendado para 09/07</t>
+        </is>
+      </c>
+      <c r="K6" s="30">
+        <f>IF(G6="","",IFERROR(INDEX(Config!$B$10:$B$14,MATCH(G6,Config!$A$10:$A$14,0)),0))</f>
+        <v>1</v>
+      </c>
+      <c r="L6" s="26">
+        <f>IF(OR(G6="",F6=""),"",F6*K6)</f>
+        <v>350</v>
+      </c>
+      <c r="M6" s="29">
+        <f>IF(OR(G6="",G6="Aprovado",G6="Recusado",G6="Sem retorno",A6=""),"",Config!$B$5-A6)</f>
+        <v/>
+      </c>
+      <c r="N6" s="29">
+        <f>IF(AND(OR(G6="Aprovado",G6="Recusado"),H6&lt;&gt;"",A6&lt;&gt;"",H6&gt;=A6),H6-A6,"")</f>
+        <v>12</v>
+      </c>
+      <c r="O6" s="25" t="str">
+        <f>IF(G6="","",IF(OR(G6="Aprovado",G6="Recusado",G6="Sem retorno"),G6,IF(AND(M6&lt;&gt;"",M6&gt;Config!$B$7),"Parado","Ativo")))</f>
+        <v>Aprovado</v>
+      </c>
+      <c r="P6" s="39">
+        <f>IF(A6="","",DATE(YEAR(A6),MONTH(A6),1))</f>
+        <v>46174.0</v>
+      </c>
+      <c r="Q6" s="40">
+        <f>IF(OR(G6="",O6="Aprovado",O6="Recusado",O6="Sem retorno"),0,IF(O6="Parado",2000,1000)+MIN(N(M6),500)+N(F6)/1000000-ROW()/100000)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="37">
         <f>TODAY()-70</f>
         <v>46209.0</v>
       </c>
-      <c r="B6" s="32" t="inlineStr">
+      <c r="B7" s="32" t="inlineStr">
         <is>
           <t>Ana Costa</t>
         </is>
       </c>
-      <c r="C6" s="35" t="inlineStr">
+      <c r="C7" s="35" t="inlineStr">
         <is>
           <t>Dr. Paulo Andrade</t>
         </is>
       </c>
-      <c r="D6" s="35" t="inlineStr">
+      <c r="D7" s="35" t="inlineStr">
         <is>
           <t>Exame cardiológico</t>
         </is>
       </c>
-      <c r="E6" s="32" t="inlineStr">
+      <c r="E7" s="32" t="inlineStr">
         <is>
           <t>MAPA</t>
         </is>
       </c>
-      <c r="F6" s="38" t="n">
+      <c r="F7" s="38" t="n">
         <v>300</v>
       </c>
-      <c r="G6" s="35" t="inlineStr">
+      <c r="G7" s="35" t="inlineStr">
         <is>
           <t>Recusado</t>
         </is>
       </c>
-      <c r="H6" s="37">
-        <f>TODAY()-61</f>
-        <v>46218.0</v>
-      </c>
-      <c r="I6" s="35" t="inlineStr">
+      <c r="H7" s="37">
+        <f>TODAY()-65</f>
+        <v>46214.0</v>
+      </c>
+      <c r="I7" s="35" t="inlineStr">
         <is>
           <t>Preço</t>
         </is>
       </c>
-      <c r="J6" s="32" t="n"/>
-      <c r="K6" s="30">
-        <f>IF(G6="","",IFERROR(INDEX(Config!$B$10:$B$14,MATCH(G6,Config!$A$10:$A$14,0)),0))</f>
-        <v>0</v>
-      </c>
-      <c r="L6" s="26">
-        <f>IF(OR(G6="",F6=""),"",F6*K6)</f>
-        <v>0</v>
-      </c>
-      <c r="M6" s="29">
-        <f>IF(OR(G6="",G6="Aprovado",G6="Recusado",G6="Sem retorno",A6=""),"",Config!$B$5-A6)</f>
-        <v/>
-      </c>
-      <c r="N6" s="29">
-        <f>IF(AND(OR(G6="Aprovado",G6="Recusado"),H6&lt;&gt;"",A6&lt;&gt;""),H6-A6,"")</f>
-        <v>9</v>
-      </c>
-      <c r="O6" s="25" t="str">
-        <f>IF(G6="","",IF(OR(G6="Aprovado",G6="Recusado",G6="Sem retorno"),G6,IF(AND(M6&lt;&gt;"",M6&gt;Config!$B$7),"Parado","Ativo")))</f>
-        <v>Recusado</v>
-      </c>
-      <c r="P6" s="39">
-        <f>IF(A6="","",DATE(YEAR(A6),MONTH(A6),1))</f>
-        <v>46204.0</v>
-      </c>
-      <c r="Q6" s="40">
-        <f>IF(OR(G6="",O6="Aprovado",O6="Recusado",O6="Sem retorno"),0,IF(O6="Parado",2000,1000)+MIN(N(M6),500)+N(F6)/1000000-ROW()/100000)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="37" t="n">
-        <v>46213</v>
-      </c>
-      <c r="B7" s="32" t="inlineStr">
-        <is>
-          <t>Lucas Lopes</t>
-        </is>
-      </c>
-      <c r="C7" s="35" t="inlineStr">
-        <is>
-          <t>Dr. Paulo Andrade</t>
-        </is>
-      </c>
-      <c r="D7" s="35" t="inlineStr">
-        <is>
-          <t>Exame cardiológico</t>
-        </is>
-      </c>
-      <c r="E7" s="32" t="inlineStr">
-        <is>
-          <t>Teste ergométrico</t>
-        </is>
-      </c>
-      <c r="F7" s="38" t="n">
-        <v>450</v>
-      </c>
-      <c r="G7" s="35" t="inlineStr">
-        <is>
-          <t>Aprovado</t>
-        </is>
-      </c>
-      <c r="H7" s="37" t="n">
-        <v>46226</v>
-      </c>
-      <c r="I7" s="35" t="n"/>
-      <c r="J7" s="32" t="inlineStr">
-        <is>
-          <t>Agendado para 24/07</t>
-        </is>
-      </c>
+      <c r="J7" s="32" t="n"/>
       <c r="K7" s="30">
         <f>IF(G7="","",IFERROR(INDEX(Config!$B$10:$B$14,MATCH(G7,Config!$A$10:$A$14,0)),0))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L7" s="26">
         <f>IF(OR(G7="",F7=""),"",F7*K7)</f>
-        <v>450</v>
+        <v>0</v>
       </c>
       <c r="M7" s="29">
         <f>IF(OR(G7="",G7="Aprovado",G7="Recusado",G7="Sem retorno",A7=""),"",Config!$B$5-A7)</f>
         <v/>
       </c>
       <c r="N7" s="29">
-        <f>IF(AND(OR(G7="Aprovado",G7="Recusado"),H7&lt;&gt;"",A7&lt;&gt;""),H7-A7,"")</f>
-        <v>13</v>
+        <f>IF(AND(OR(G7="Aprovado",G7="Recusado"),H7&lt;&gt;"",A7&lt;&gt;"",H7&gt;=A7),H7-A7,"")</f>
+        <v>5</v>
       </c>
       <c r="O7" s="25" t="str">
         <f>IF(G7="","",IF(OR(G7="Aprovado",G7="Recusado",G7="Sem retorno"),G7,IF(AND(M7&lt;&gt;"",M7&gt;Config!$B$7),"Parado","Ativo")))</f>
-        <v>Aprovado</v>
+        <v>Recusado</v>
       </c>
       <c r="P7" s="39">
         <f>IF(A7="","",DATE(YEAR(A7),MONTH(A7),1))</f>
@@ -3134,11 +3134,11 @@
     </row>
     <row r="8">
       <c r="A8" s="37" t="n">
-        <v>46218</v>
+        <v>46216</v>
       </c>
       <c r="B8" s="32" t="inlineStr">
         <is>
-          <t>Eduardo Lima</t>
+          <t>Débora Ramos</t>
         </is>
       </c>
       <c r="C8" s="35" t="inlineStr">
@@ -3165,12 +3165,12 @@
         </is>
       </c>
       <c r="H8" s="37" t="n">
-        <v>46226</v>
+        <v>46220</v>
       </c>
       <c r="I8" s="35" t="n"/>
       <c r="J8" s="32" t="inlineStr">
         <is>
-          <t>Agendado para 24/07</t>
+          <t>Agendado para 20/07</t>
         </is>
       </c>
       <c r="K8" s="30">
@@ -3186,8 +3186,8 @@
         <v/>
       </c>
       <c r="N8" s="29">
-        <f>IF(AND(OR(G8="Aprovado",G8="Recusado"),H8&lt;&gt;"",A8&lt;&gt;""),H8-A8,"")</f>
-        <v>8</v>
+        <f>IF(AND(OR(G8="Aprovado",G8="Recusado"),H8&lt;&gt;"",A8&lt;&gt;"",H8&gt;=A8),H8-A8,"")</f>
+        <v>4</v>
       </c>
       <c r="O8" s="25" t="str">
         <f>IF(G8="","",IF(OR(G8="Aprovado",G8="Recusado",G8="Sem retorno"),G8,IF(AND(M8&lt;&gt;"",M8&gt;Config!$B$7),"Parado","Ativo")))</f>
@@ -3204,11 +3204,11 @@
     </row>
     <row r="9">
       <c r="A9" s="37" t="n">
-        <v>46219</v>
+        <v>46217</v>
       </c>
       <c r="B9" s="32" t="inlineStr">
         <is>
-          <t>Débora Ramos</t>
+          <t>Wagner Santos</t>
         </is>
       </c>
       <c r="C9" s="35" t="inlineStr">
@@ -3223,11 +3223,11 @@
       </c>
       <c r="E9" s="32" t="inlineStr">
         <is>
-          <t>Teste ergométrico</t>
+          <t>MAPA</t>
         </is>
       </c>
       <c r="F9" s="38" t="n">
-        <v>450</v>
+        <v>300</v>
       </c>
       <c r="G9" s="35" t="inlineStr">
         <is>
@@ -3235,12 +3235,12 @@
         </is>
       </c>
       <c r="H9" s="37" t="n">
-        <v>46223</v>
+        <v>46234</v>
       </c>
       <c r="I9" s="35" t="n"/>
       <c r="J9" s="32" t="inlineStr">
         <is>
-          <t>Agendado para 20/07</t>
+          <t>Agendado para 03/08</t>
         </is>
       </c>
       <c r="K9" s="30">
@@ -3249,15 +3249,15 @@
       </c>
       <c r="L9" s="26">
         <f>IF(OR(G9="",F9=""),"",F9*K9)</f>
-        <v>450</v>
+        <v>300</v>
       </c>
       <c r="M9" s="29">
         <f>IF(OR(G9="",G9="Aprovado",G9="Recusado",G9="Sem retorno",A9=""),"",Config!$B$5-A9)</f>
         <v/>
       </c>
       <c r="N9" s="29">
-        <f>IF(AND(OR(G9="Aprovado",G9="Recusado"),H9&lt;&gt;"",A9&lt;&gt;""),H9-A9,"")</f>
-        <v>4</v>
+        <f>IF(AND(OR(G9="Aprovado",G9="Recusado"),H9&lt;&gt;"",A9&lt;&gt;"",H9&gt;=A9),H9-A9,"")</f>
+        <v>17</v>
       </c>
       <c r="O9" s="25" t="str">
         <f>IF(G9="","",IF(OR(G9="Aprovado",G9="Recusado",G9="Sem retorno"),G9,IF(AND(M9&lt;&gt;"",M9&gt;Config!$B$7),"Parado","Ativo")))</f>
@@ -3274,11 +3274,11 @@
     </row>
     <row r="10">
       <c r="A10" s="37" t="n">
-        <v>46220</v>
+        <v>46218</v>
       </c>
       <c r="B10" s="32" t="inlineStr">
         <is>
-          <t>Otávio Nascimento</t>
+          <t>Lucas Lopes</t>
         </is>
       </c>
       <c r="C10" s="35" t="inlineStr">
@@ -3293,11 +3293,11 @@
       </c>
       <c r="E10" s="32" t="inlineStr">
         <is>
-          <t>Holter</t>
+          <t>Teste ergométrico</t>
         </is>
       </c>
       <c r="F10" s="38" t="n">
-        <v>350</v>
+        <v>450</v>
       </c>
       <c r="G10" s="35" t="inlineStr">
         <is>
@@ -3305,12 +3305,12 @@
         </is>
       </c>
       <c r="H10" s="37" t="n">
-        <v>46227</v>
+        <v>46224</v>
       </c>
       <c r="I10" s="35" t="n"/>
       <c r="J10" s="32" t="inlineStr">
         <is>
-          <t>Agendado para 28/07</t>
+          <t>Agendado para 24/07</t>
         </is>
       </c>
       <c r="K10" s="30">
@@ -3319,15 +3319,15 @@
       </c>
       <c r="L10" s="26">
         <f>IF(OR(G10="",F10=""),"",F10*K10)</f>
-        <v>350</v>
+        <v>450</v>
       </c>
       <c r="M10" s="29">
         <f>IF(OR(G10="",G10="Aprovado",G10="Recusado",G10="Sem retorno",A10=""),"",Config!$B$5-A10)</f>
         <v/>
       </c>
       <c r="N10" s="29">
-        <f>IF(AND(OR(G10="Aprovado",G10="Recusado"),H10&lt;&gt;"",A10&lt;&gt;""),H10-A10,"")</f>
-        <v>7</v>
+        <f>IF(AND(OR(G10="Aprovado",G10="Recusado"),H10&lt;&gt;"",A10&lt;&gt;"",H10&gt;=A10),H10-A10,"")</f>
+        <v>6</v>
       </c>
       <c r="O10" s="25" t="str">
         <f>IF(G10="","",IF(OR(G10="Aprovado",G10="Recusado",G10="Sem retorno"),G10,IF(AND(M10&lt;&gt;"",M10&gt;Config!$B$7),"Parado","Ativo")))</f>
@@ -3343,13 +3343,12 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="37">
-        <f>TODAY()-55</f>
-        <v>46224.0</v>
+      <c r="A11" s="37" t="n">
+        <v>46218</v>
       </c>
       <c r="B11" s="32" t="inlineStr">
         <is>
-          <t>Carlos Freitas</t>
+          <t>Eduardo Lima</t>
         </is>
       </c>
       <c r="C11" s="35" t="inlineStr">
@@ -3364,46 +3363,45 @@
       </c>
       <c r="E11" s="32" t="inlineStr">
         <is>
-          <t>Holter</t>
+          <t>Teste ergométrico</t>
         </is>
       </c>
       <c r="F11" s="38" t="n">
-        <v>350</v>
+        <v>450</v>
       </c>
       <c r="G11" s="35" t="inlineStr">
         <is>
-          <t>Recusado</t>
-        </is>
-      </c>
-      <c r="H11" s="37">
-        <f>TODAY()-46</f>
-        <v>46233.0</v>
-      </c>
-      <c r="I11" s="35" t="inlineStr">
-        <is>
-          <t>Vai fazer pelo convênio</t>
-        </is>
-      </c>
-      <c r="J11" s="32" t="n"/>
+          <t>Aprovado</t>
+        </is>
+      </c>
+      <c r="H11" s="37" t="n">
+        <v>46225</v>
+      </c>
+      <c r="I11" s="35" t="n"/>
+      <c r="J11" s="32" t="inlineStr">
+        <is>
+          <t>Agendado para 24/07</t>
+        </is>
+      </c>
       <c r="K11" s="30">
         <f>IF(G11="","",IFERROR(INDEX(Config!$B$10:$B$14,MATCH(G11,Config!$A$10:$A$14,0)),0))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L11" s="26">
         <f>IF(OR(G11="",F11=""),"",F11*K11)</f>
-        <v>0</v>
+        <v>450</v>
       </c>
       <c r="M11" s="29">
         <f>IF(OR(G11="",G11="Aprovado",G11="Recusado",G11="Sem retorno",A11=""),"",Config!$B$5-A11)</f>
         <v/>
       </c>
       <c r="N11" s="29">
-        <f>IF(AND(OR(G11="Aprovado",G11="Recusado"),H11&lt;&gt;"",A11&lt;&gt;""),H11-A11,"")</f>
-        <v>9</v>
+        <f>IF(AND(OR(G11="Aprovado",G11="Recusado"),H11&lt;&gt;"",A11&lt;&gt;"",H11&gt;=A11),H11-A11,"")</f>
+        <v>7</v>
       </c>
       <c r="O11" s="25" t="str">
         <f>IF(G11="","",IF(OR(G11="Aprovado",G11="Recusado",G11="Sem retorno"),G11,IF(AND(M11&lt;&gt;"",M11&gt;Config!$B$7),"Parado","Ativo")))</f>
-        <v>Recusado</v>
+        <v>Aprovado</v>
       </c>
       <c r="P11" s="39">
         <f>IF(A11="","",DATE(YEAR(A11),MONTH(A11),1))</f>
@@ -3416,11 +3414,11 @@
     </row>
     <row r="12">
       <c r="A12" s="37" t="n">
-        <v>46230</v>
+        <v>46219</v>
       </c>
       <c r="B12" s="32" t="inlineStr">
         <is>
-          <t>Wagner Santos</t>
+          <t>Otávio Nascimento</t>
         </is>
       </c>
       <c r="C12" s="35" t="inlineStr">
@@ -3435,11 +3433,11 @@
       </c>
       <c r="E12" s="32" t="inlineStr">
         <is>
-          <t>MAPA</t>
+          <t>Holter</t>
         </is>
       </c>
       <c r="F12" s="38" t="n">
-        <v>300</v>
+        <v>350</v>
       </c>
       <c r="G12" s="35" t="inlineStr">
         <is>
@@ -3447,12 +3445,12 @@
         </is>
       </c>
       <c r="H12" s="37" t="n">
-        <v>46234</v>
+        <v>46227</v>
       </c>
       <c r="I12" s="35" t="n"/>
       <c r="J12" s="32" t="inlineStr">
         <is>
-          <t>Agendado para 03/08</t>
+          <t>Agendado para 28/07</t>
         </is>
       </c>
       <c r="K12" s="30">
@@ -3461,15 +3459,15 @@
       </c>
       <c r="L12" s="26">
         <f>IF(OR(G12="",F12=""),"",F12*K12)</f>
-        <v>300</v>
+        <v>350</v>
       </c>
       <c r="M12" s="29">
         <f>IF(OR(G12="",G12="Aprovado",G12="Recusado",G12="Sem retorno",A12=""),"",Config!$B$5-A12)</f>
         <v/>
       </c>
       <c r="N12" s="29">
-        <f>IF(AND(OR(G12="Aprovado",G12="Recusado"),H12&lt;&gt;"",A12&lt;&gt;""),H12-A12,"")</f>
-        <v>4</v>
+        <f>IF(AND(OR(G12="Aprovado",G12="Recusado"),H12&lt;&gt;"",A12&lt;&gt;"",H12&gt;=A12),H12-A12,"")</f>
+        <v>8</v>
       </c>
       <c r="O12" s="25" t="str">
         <f>IF(G12="","",IF(OR(G12="Aprovado",G12="Recusado",G12="Sem retorno"),G12,IF(AND(M12&lt;&gt;"",M12&gt;Config!$B$7),"Parado","Ativo")))</f>
@@ -3485,12 +3483,13 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="37" t="n">
-        <v>46232</v>
+      <c r="A13" s="37">
+        <f>TODAY()-55</f>
+        <v>46224.0</v>
       </c>
       <c r="B13" s="32" t="inlineStr">
         <is>
-          <t>Marcelo Moreira</t>
+          <t>Carlos Freitas</t>
         </is>
       </c>
       <c r="C13" s="35" t="inlineStr">
@@ -3513,37 +3512,38 @@
       </c>
       <c r="G13" s="35" t="inlineStr">
         <is>
-          <t>Aprovado</t>
-        </is>
-      </c>
-      <c r="H13" s="37" t="n">
-        <v>46241</v>
-      </c>
-      <c r="I13" s="35" t="n"/>
-      <c r="J13" s="32" t="inlineStr">
-        <is>
-          <t>Agendado para 10/08</t>
-        </is>
-      </c>
+          <t>Recusado</t>
+        </is>
+      </c>
+      <c r="H13" s="37">
+        <f>TODAY()-51</f>
+        <v>46228.0</v>
+      </c>
+      <c r="I13" s="35" t="inlineStr">
+        <is>
+          <t>Vai fazer pelo convênio</t>
+        </is>
+      </c>
+      <c r="J13" s="32" t="n"/>
       <c r="K13" s="30">
         <f>IF(G13="","",IFERROR(INDEX(Config!$B$10:$B$14,MATCH(G13,Config!$A$10:$A$14,0)),0))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L13" s="26">
         <f>IF(OR(G13="",F13=""),"",F13*K13)</f>
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="M13" s="29">
         <f>IF(OR(G13="",G13="Aprovado",G13="Recusado",G13="Sem retorno",A13=""),"",Config!$B$5-A13)</f>
         <v/>
       </c>
       <c r="N13" s="29">
-        <f>IF(AND(OR(G13="Aprovado",G13="Recusado"),H13&lt;&gt;"",A13&lt;&gt;""),H13-A13,"")</f>
-        <v>9</v>
+        <f>IF(AND(OR(G13="Aprovado",G13="Recusado"),H13&lt;&gt;"",A13&lt;&gt;"",H13&gt;=A13),H13-A13,"")</f>
+        <v>4</v>
       </c>
       <c r="O13" s="25" t="str">
         <f>IF(G13="","",IF(OR(G13="Aprovado",G13="Recusado",G13="Sem retorno"),G13,IF(AND(M13&lt;&gt;"",M13&gt;Config!$B$7),"Parado","Ativo")))</f>
-        <v>Aprovado</v>
+        <v>Recusado</v>
       </c>
       <c r="P13" s="39">
         <f>IF(A13="","",DATE(YEAR(A13),MONTH(A13),1))</f>
@@ -3556,11 +3556,11 @@
     </row>
     <row r="14">
       <c r="A14" s="37" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="B14" s="32" t="inlineStr">
         <is>
-          <t>Otávio Cardoso</t>
+          <t>Regina Duarte</t>
         </is>
       </c>
       <c r="C14" s="35" t="inlineStr">
@@ -3587,12 +3587,12 @@
         </is>
       </c>
       <c r="H14" s="37" t="n">
-        <v>46238</v>
+        <v>46241</v>
       </c>
       <c r="I14" s="35" t="n"/>
       <c r="J14" s="32" t="inlineStr">
         <is>
-          <t>Agendado para 06/08</t>
+          <t>Agendado para 11/08</t>
         </is>
       </c>
       <c r="K14" s="30">
@@ -3608,8 +3608,8 @@
         <v/>
       </c>
       <c r="N14" s="29">
-        <f>IF(AND(OR(G14="Aprovado",G14="Recusado"),H14&lt;&gt;"",A14&lt;&gt;""),H14-A14,"")</f>
-        <v>5</v>
+        <f>IF(AND(OR(G14="Aprovado",G14="Recusado"),H14&lt;&gt;"",A14&lt;&gt;"",H14&gt;=A14),H14-A14,"")</f>
+        <v>7</v>
       </c>
       <c r="O14" s="25" t="str">
         <f>IF(G14="","",IF(OR(G14="Aprovado",G14="Recusado",G14="Sem retorno"),G14,IF(AND(M14&lt;&gt;"",M14&gt;Config!$B$7),"Parado","Ativo")))</f>
@@ -3625,65 +3625,67 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="37" t="n">
-        <v>46234</v>
+      <c r="A15" s="37">
+        <f>TODAY()-45</f>
+        <v>46234.0</v>
       </c>
       <c r="B15" s="32" t="inlineStr">
         <is>
-          <t>Regina Duarte</t>
+          <t>Cláudia Costa</t>
         </is>
       </c>
       <c r="C15" s="35" t="inlineStr">
         <is>
-          <t>Dr. Paulo Andrade</t>
+          <t>Dra. Carolina Mendes</t>
         </is>
       </c>
       <c r="D15" s="35" t="inlineStr">
         <is>
-          <t>Exame cardiológico</t>
+          <t>Pacote de consultas</t>
         </is>
       </c>
       <c r="E15" s="32" t="inlineStr">
         <is>
-          <t>Teste ergométrico</t>
+          <t>Consulta + 2 retornos (acompanhamento)</t>
         </is>
       </c>
       <c r="F15" s="38" t="n">
-        <v>450</v>
+        <v>380</v>
       </c>
       <c r="G15" s="35" t="inlineStr">
         <is>
-          <t>Aprovado</t>
-        </is>
-      </c>
-      <c r="H15" s="37" t="n">
-        <v>46241</v>
-      </c>
-      <c r="I15" s="35" t="n"/>
-      <c r="J15" s="32" t="inlineStr">
-        <is>
-          <t>Agendado para 11/08</t>
-        </is>
-      </c>
+          <t>Recusado</t>
+        </is>
+      </c>
+      <c r="H15" s="37">
+        <f>TODAY()-41</f>
+        <v>46238.0</v>
+      </c>
+      <c r="I15" s="35" t="inlineStr">
+        <is>
+          <t>Sem indicação no momento</t>
+        </is>
+      </c>
+      <c r="J15" s="32" t="n"/>
       <c r="K15" s="30">
         <f>IF(G15="","",IFERROR(INDEX(Config!$B$10:$B$14,MATCH(G15,Config!$A$10:$A$14,0)),0))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L15" s="26">
         <f>IF(OR(G15="",F15=""),"",F15*K15)</f>
-        <v>450</v>
+        <v>0</v>
       </c>
       <c r="M15" s="29">
         <f>IF(OR(G15="",G15="Aprovado",G15="Recusado",G15="Sem retorno",A15=""),"",Config!$B$5-A15)</f>
         <v/>
       </c>
       <c r="N15" s="29">
-        <f>IF(AND(OR(G15="Aprovado",G15="Recusado"),H15&lt;&gt;"",A15&lt;&gt;""),H15-A15,"")</f>
-        <v>7</v>
+        <f>IF(AND(OR(G15="Aprovado",G15="Recusado"),H15&lt;&gt;"",A15&lt;&gt;"",H15&gt;=A15),H15-A15,"")</f>
+        <v>4</v>
       </c>
       <c r="O15" s="25" t="str">
         <f>IF(G15="","",IF(OR(G15="Aprovado",G15="Recusado",G15="Sem retorno"),G15,IF(AND(M15&lt;&gt;"",M15&gt;Config!$B$7),"Parado","Ativo")))</f>
-        <v>Aprovado</v>
+        <v>Recusado</v>
       </c>
       <c r="P15" s="39">
         <f>IF(A15="","",DATE(YEAR(A15),MONTH(A15),1))</f>
@@ -3696,11 +3698,11 @@
     </row>
     <row r="16">
       <c r="A16" s="37" t="n">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="B16" s="32" t="inlineStr">
         <is>
-          <t>Regina Teixeira</t>
+          <t>Helena Moreira</t>
         </is>
       </c>
       <c r="C16" s="35" t="inlineStr">
@@ -3710,16 +3712,16 @@
       </c>
       <c r="D16" s="35" t="inlineStr">
         <is>
-          <t>Check-up cardiológico</t>
+          <t>Exame cardiológico</t>
         </is>
       </c>
       <c r="E16" s="32" t="inlineStr">
         <is>
-          <t>Consulta + ECG + teste ergométrico</t>
+          <t>MAPA</t>
         </is>
       </c>
       <c r="F16" s="38" t="n">
-        <v>960</v>
+        <v>300</v>
       </c>
       <c r="G16" s="35" t="inlineStr">
         <is>
@@ -3727,12 +3729,12 @@
         </is>
       </c>
       <c r="H16" s="37" t="n">
-        <v>46251</v>
+        <v>46248</v>
       </c>
       <c r="I16" s="35" t="n"/>
       <c r="J16" s="32" t="inlineStr">
         <is>
-          <t>Agendado para 20/08</t>
+          <t>Agendado para 17/08</t>
         </is>
       </c>
       <c r="K16" s="30">
@@ -3741,15 +3743,15 @@
       </c>
       <c r="L16" s="26">
         <f>IF(OR(G16="",F16=""),"",F16*K16)</f>
-        <v>960</v>
+        <v>300</v>
       </c>
       <c r="M16" s="29">
         <f>IF(OR(G16="",G16="Aprovado",G16="Recusado",G16="Sem retorno",A16=""),"",Config!$B$5-A16)</f>
         <v/>
       </c>
       <c r="N16" s="29">
-        <f>IF(AND(OR(G16="Aprovado",G16="Recusado"),H16&lt;&gt;"",A16&lt;&gt;""),H16-A16,"")</f>
-        <v>17</v>
+        <f>IF(AND(OR(G16="Aprovado",G16="Recusado"),H16&lt;&gt;"",A16&lt;&gt;"",H16&gt;=A16),H16-A16,"")</f>
+        <v>11</v>
       </c>
       <c r="O16" s="25" t="str">
         <f>IF(G16="","",IF(OR(G16="Aprovado",G16="Recusado",G16="Sem retorno"),G16,IF(AND(M16&lt;&gt;"",M16&gt;Config!$B$7),"Parado","Ativo")))</f>
@@ -3757,7 +3759,7 @@
       </c>
       <c r="P16" s="39">
         <f>IF(A16="","",DATE(YEAR(A16),MONTH(A16),1))</f>
-        <v>46204.0</v>
+        <v>46235.0</v>
       </c>
       <c r="Q16" s="40">
         <f>IF(OR(G16="",O16="Aprovado",O16="Recusado",O16="Sem retorno"),0,IF(O16="Parado",2000,1000)+MIN(N(M16),500)+N(F16)/1000000-ROW()/100000)</f>
@@ -3766,44 +3768,44 @@
     </row>
     <row r="17">
       <c r="A17" s="37">
-        <f>TODAY()-45</f>
-        <v>46234.0</v>
+        <f>TODAY()-40</f>
+        <v>46239.0</v>
       </c>
       <c r="B17" s="32" t="inlineStr">
         <is>
-          <t>Cláudia Costa</t>
+          <t>Eduardo Lima</t>
         </is>
       </c>
       <c r="C17" s="35" t="inlineStr">
         <is>
-          <t>Dra. Carolina Mendes</t>
+          <t>Dr. Paulo Andrade</t>
         </is>
       </c>
       <c r="D17" s="35" t="inlineStr">
         <is>
-          <t>Pacote de consultas</t>
+          <t>Check-up cardiológico</t>
         </is>
       </c>
       <c r="E17" s="32" t="inlineStr">
         <is>
-          <t>Consulta + 2 retornos (acompanhamento)</t>
+          <t>Consulta + ECG + teste ergométrico</t>
         </is>
       </c>
       <c r="F17" s="38" t="n">
-        <v>380</v>
+        <v>960</v>
       </c>
       <c r="G17" s="35" t="inlineStr">
         <is>
-          <t>Recusado</t>
+          <t>Sem retorno</t>
         </is>
       </c>
       <c r="H17" s="37">
-        <f>TODAY()-42</f>
-        <v>46237.0</v>
+        <f>TODAY()-30</f>
+        <v>46249.0</v>
       </c>
       <c r="I17" s="35" t="inlineStr">
         <is>
-          <t>Sem indicação no momento</t>
+          <t>Vai pensar / sem retorno</t>
         </is>
       </c>
       <c r="J17" s="32" t="n"/>
@@ -3820,16 +3822,16 @@
         <v/>
       </c>
       <c r="N17" s="29">
-        <f>IF(AND(OR(G17="Aprovado",G17="Recusado"),H17&lt;&gt;"",A17&lt;&gt;""),H17-A17,"")</f>
-        <v>3</v>
+        <f>IF(AND(OR(G17="Aprovado",G17="Recusado"),H17&lt;&gt;"",A17&lt;&gt;"",H17&gt;=A17),H17-A17,"")</f>
+        <v/>
       </c>
       <c r="O17" s="25" t="str">
         <f>IF(G17="","",IF(OR(G17="Aprovado",G17="Recusado",G17="Sem retorno"),G17,IF(AND(M17&lt;&gt;"",M17&gt;Config!$B$7),"Parado","Ativo")))</f>
-        <v>Recusado</v>
+        <v>Sem retorno</v>
       </c>
       <c r="P17" s="39">
         <f>IF(A17="","",DATE(YEAR(A17),MONTH(A17),1))</f>
-        <v>46204.0</v>
+        <v>46235.0</v>
       </c>
       <c r="Q17" s="40">
         <f>IF(OR(G17="",O17="Aprovado",O17="Recusado",O17="Sem retorno"),0,IF(O17="Parado",2000,1000)+MIN(N(M17),500)+N(F17)/1000000-ROW()/100000)</f>
@@ -3837,13 +3839,12 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="37">
-        <f>TODAY()-40</f>
-        <v>46239.0</v>
+      <c r="A18" s="37" t="n">
+        <v>46241</v>
       </c>
       <c r="B18" s="32" t="inlineStr">
         <is>
-          <t>Eduardo Lima</t>
+          <t>Regina Teixeira</t>
         </is>
       </c>
       <c r="C18" s="35" t="inlineStr">
@@ -3866,38 +3867,37 @@
       </c>
       <c r="G18" s="35" t="inlineStr">
         <is>
-          <t>Sem retorno</t>
-        </is>
-      </c>
-      <c r="H18" s="37">
-        <f>TODAY()-37</f>
-        <v>46242.0</v>
-      </c>
-      <c r="I18" s="35" t="inlineStr">
-        <is>
-          <t>Vai pensar / sem retorno</t>
-        </is>
-      </c>
-      <c r="J18" s="32" t="n"/>
+          <t>Aprovado</t>
+        </is>
+      </c>
+      <c r="H18" s="37" t="n">
+        <v>46252</v>
+      </c>
+      <c r="I18" s="35" t="n"/>
+      <c r="J18" s="32" t="inlineStr">
+        <is>
+          <t>Agendado para 20/08</t>
+        </is>
+      </c>
       <c r="K18" s="30">
         <f>IF(G18="","",IFERROR(INDEX(Config!$B$10:$B$14,MATCH(G18,Config!$A$10:$A$14,0)),0))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L18" s="26">
         <f>IF(OR(G18="",F18=""),"",F18*K18)</f>
-        <v>0</v>
+        <v>960</v>
       </c>
       <c r="M18" s="29">
         <f>IF(OR(G18="",G18="Aprovado",G18="Recusado",G18="Sem retorno",A18=""),"",Config!$B$5-A18)</f>
         <v/>
       </c>
       <c r="N18" s="29">
-        <f>IF(AND(OR(G18="Aprovado",G18="Recusado"),H18&lt;&gt;"",A18&lt;&gt;""),H18-A18,"")</f>
-        <v/>
+        <f>IF(AND(OR(G18="Aprovado",G18="Recusado"),H18&lt;&gt;"",A18&lt;&gt;"",H18&gt;=A18),H18-A18,"")</f>
+        <v>11</v>
       </c>
       <c r="O18" s="25" t="str">
         <f>IF(G18="","",IF(OR(G18="Aprovado",G18="Recusado",G18="Sem retorno"),G18,IF(AND(M18&lt;&gt;"",M18&gt;Config!$B$7),"Parado","Ativo")))</f>
-        <v>Sem retorno</v>
+        <v>Aprovado</v>
       </c>
       <c r="P18" s="39">
         <f>IF(A18="","",DATE(YEAR(A18),MONTH(A18),1))</f>
@@ -3914,7 +3914,7 @@
       </c>
       <c r="B19" s="32" t="inlineStr">
         <is>
-          <t>Paulo Reis</t>
+          <t>Sérgio Martins</t>
         </is>
       </c>
       <c r="C19" s="35" t="inlineStr">
@@ -3941,12 +3941,12 @@
         </is>
       </c>
       <c r="H19" s="37" t="n">
-        <v>46259</v>
+        <v>46255</v>
       </c>
       <c r="I19" s="35" t="n"/>
       <c r="J19" s="32" t="inlineStr">
         <is>
-          <t>Agendado para 25/08</t>
+          <t>Agendado para 24/08</t>
         </is>
       </c>
       <c r="K19" s="30">
@@ -3962,8 +3962,8 @@
         <v/>
       </c>
       <c r="N19" s="29">
-        <f>IF(AND(OR(G19="Aprovado",G19="Recusado"),H19&lt;&gt;"",A19&lt;&gt;""),H19-A19,"")</f>
-        <v>18</v>
+        <f>IF(AND(OR(G19="Aprovado",G19="Recusado"),H19&lt;&gt;"",A19&lt;&gt;"",H19&gt;=A19),H19-A19,"")</f>
+        <v>14</v>
       </c>
       <c r="O19" s="25" t="str">
         <f>IF(G19="","",IF(OR(G19="Aprovado",G19="Recusado",G19="Sem retorno"),G19,IF(AND(M19&lt;&gt;"",M19&gt;Config!$B$7),"Parado","Ativo")))</f>
@@ -3980,11 +3980,11 @@
     </row>
     <row r="20">
       <c r="A20" s="37" t="n">
-        <v>46245</v>
+        <v>46247</v>
       </c>
       <c r="B20" s="32" t="inlineStr">
         <is>
-          <t>Viviane Ribeiro</t>
+          <t>Roberta Araújo</t>
         </is>
       </c>
       <c r="C20" s="35" t="inlineStr">
@@ -3999,11 +3999,11 @@
       </c>
       <c r="E20" s="32" t="inlineStr">
         <is>
-          <t>Teste ergométrico</t>
+          <t>Holter</t>
         </is>
       </c>
       <c r="F20" s="38" t="n">
-        <v>450</v>
+        <v>350</v>
       </c>
       <c r="G20" s="35" t="inlineStr">
         <is>
@@ -4011,12 +4011,12 @@
         </is>
       </c>
       <c r="H20" s="37" t="n">
-        <v>46251</v>
+        <v>46258</v>
       </c>
       <c r="I20" s="35" t="n"/>
       <c r="J20" s="32" t="inlineStr">
         <is>
-          <t>Agendado para 20/08</t>
+          <t>Agendado para 25/08</t>
         </is>
       </c>
       <c r="K20" s="30">
@@ -4025,15 +4025,15 @@
       </c>
       <c r="L20" s="26">
         <f>IF(OR(G20="",F20=""),"",F20*K20)</f>
-        <v>450</v>
+        <v>350</v>
       </c>
       <c r="M20" s="29">
         <f>IF(OR(G20="",G20="Aprovado",G20="Recusado",G20="Sem retorno",A20=""),"",Config!$B$5-A20)</f>
         <v/>
       </c>
       <c r="N20" s="29">
-        <f>IF(AND(OR(G20="Aprovado",G20="Recusado"),H20&lt;&gt;"",A20&lt;&gt;""),H20-A20,"")</f>
-        <v>6</v>
+        <f>IF(AND(OR(G20="Aprovado",G20="Recusado"),H20&lt;&gt;"",A20&lt;&gt;"",H20&gt;=A20),H20-A20,"")</f>
+        <v>11</v>
       </c>
       <c r="O20" s="25" t="str">
         <f>IF(G20="","",IF(OR(G20="Aprovado",G20="Recusado",G20="Sem retorno"),G20,IF(AND(M20&lt;&gt;"",M20&gt;Config!$B$7),"Parado","Ativo")))</f>
@@ -4082,8 +4082,8 @@
         </is>
       </c>
       <c r="H21" s="37">
-        <f>TODAY()-25</f>
-        <v>46254.0</v>
+        <f>TODAY()-23</f>
+        <v>46256.0</v>
       </c>
       <c r="I21" s="35" t="inlineStr">
         <is>
@@ -4104,8 +4104,8 @@
         <v/>
       </c>
       <c r="N21" s="29">
-        <f>IF(AND(OR(G21="Aprovado",G21="Recusado"),H21&lt;&gt;"",A21&lt;&gt;""),H21-A21,"")</f>
-        <v>7</v>
+        <f>IF(AND(OR(G21="Aprovado",G21="Recusado"),H21&lt;&gt;"",A21&lt;&gt;"",H21&gt;=A21),H21-A21,"")</f>
+        <v>9</v>
       </c>
       <c r="O21" s="25" t="str">
         <f>IF(G21="","",IF(OR(G21="Aprovado",G21="Recusado",G21="Sem retorno"),G21,IF(AND(M21&lt;&gt;"",M21&gt;Config!$B$7),"Parado","Ativo")))</f>
@@ -4126,7 +4126,7 @@
       </c>
       <c r="B22" s="32" t="inlineStr">
         <is>
-          <t>Renato Dias</t>
+          <t>Rafael Barros</t>
         </is>
       </c>
       <c r="C22" s="35" t="inlineStr">
@@ -4141,11 +4141,11 @@
       </c>
       <c r="E22" s="32" t="inlineStr">
         <is>
-          <t>Holter</t>
+          <t>Teste ergométrico</t>
         </is>
       </c>
       <c r="F22" s="38" t="n">
-        <v>350</v>
+        <v>450</v>
       </c>
       <c r="G22" s="35" t="inlineStr">
         <is>
@@ -4153,12 +4153,12 @@
         </is>
       </c>
       <c r="H22" s="37" t="n">
-        <v>46261</v>
+        <v>46265</v>
       </c>
       <c r="I22" s="35" t="n"/>
       <c r="J22" s="32" t="inlineStr">
         <is>
-          <t>Agendado para 27/08</t>
+          <t>Agendado para 03/09</t>
         </is>
       </c>
       <c r="K22" s="30">
@@ -4167,15 +4167,15 @@
       </c>
       <c r="L22" s="26">
         <f>IF(OR(G22="",F22=""),"",F22*K22)</f>
-        <v>350</v>
+        <v>450</v>
       </c>
       <c r="M22" s="29">
         <f>IF(OR(G22="",G22="Aprovado",G22="Recusado",G22="Sem retorno",A22=""),"",Config!$B$5-A22)</f>
         <v/>
       </c>
       <c r="N22" s="29">
-        <f>IF(AND(OR(G22="Aprovado",G22="Recusado"),H22&lt;&gt;"",A22&lt;&gt;""),H22-A22,"")</f>
-        <v>13</v>
+        <f>IF(AND(OR(G22="Aprovado",G22="Recusado"),H22&lt;&gt;"",A22&lt;&gt;"",H22&gt;=A22),H22-A22,"")</f>
+        <v>17</v>
       </c>
       <c r="O22" s="25" t="str">
         <f>IF(G22="","",IF(OR(G22="Aprovado",G22="Recusado",G22="Sem retorno"),G22,IF(AND(M22&lt;&gt;"",M22&gt;Config!$B$7),"Parado","Ativo")))</f>
@@ -4192,11 +4192,11 @@
     </row>
     <row r="23">
       <c r="A23" s="37" t="n">
-        <v>46251</v>
+        <v>46248</v>
       </c>
       <c r="B23" s="32" t="inlineStr">
         <is>
-          <t>Fernanda Freitas</t>
+          <t>Rafael Dias</t>
         </is>
       </c>
       <c r="C23" s="35" t="inlineStr">
@@ -4211,11 +4211,11 @@
       </c>
       <c r="E23" s="32" t="inlineStr">
         <is>
-          <t>Teste ergométrico</t>
+          <t>MAPA</t>
         </is>
       </c>
       <c r="F23" s="38" t="n">
-        <v>450</v>
+        <v>300</v>
       </c>
       <c r="G23" s="35" t="inlineStr">
         <is>
@@ -4223,7 +4223,7 @@
         </is>
       </c>
       <c r="H23" s="37" t="n">
-        <v>46269</v>
+        <v>46268</v>
       </c>
       <c r="I23" s="35" t="n"/>
       <c r="J23" s="32" t="inlineStr">
@@ -4237,15 +4237,15 @@
       </c>
       <c r="L23" s="26">
         <f>IF(OR(G23="",F23=""),"",F23*K23)</f>
-        <v>450</v>
+        <v>300</v>
       </c>
       <c r="M23" s="29">
         <f>IF(OR(G23="",G23="Aprovado",G23="Recusado",G23="Sem retorno",A23=""),"",Config!$B$5-A23)</f>
         <v/>
       </c>
       <c r="N23" s="29">
-        <f>IF(AND(OR(G23="Aprovado",G23="Recusado"),H23&lt;&gt;"",A23&lt;&gt;""),H23-A23,"")</f>
-        <v>18</v>
+        <f>IF(AND(OR(G23="Aprovado",G23="Recusado"),H23&lt;&gt;"",A23&lt;&gt;"",H23&gt;=A23),H23-A23,"")</f>
+        <v>20</v>
       </c>
       <c r="O23" s="25" t="str">
         <f>IF(G23="","",IF(OR(G23="Aprovado",G23="Recusado",G23="Sem retorno"),G23,IF(AND(M23&lt;&gt;"",M23&gt;Config!$B$7),"Parado","Ativo")))</f>
@@ -4261,67 +4261,65 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="37">
-        <f>TODAY()-26</f>
-        <v>46253.0</v>
+      <c r="A24" s="37" t="n">
+        <v>46251</v>
       </c>
       <c r="B24" s="32" t="inlineStr">
         <is>
-          <t>Beatriz Gomes</t>
+          <t>Paulo Reis</t>
         </is>
       </c>
       <c r="C24" s="35" t="inlineStr">
         <is>
-          <t>Dra. Renata Sousa</t>
+          <t>Dr. Paulo Andrade</t>
         </is>
       </c>
       <c r="D24" s="35" t="inlineStr">
         <is>
-          <t>Avaliação endócrina</t>
+          <t>Exame cardiológico</t>
         </is>
       </c>
       <c r="E24" s="32" t="inlineStr">
         <is>
-          <t>Avaliação endócrina + retorno</t>
+          <t>Holter</t>
         </is>
       </c>
       <c r="F24" s="38" t="n">
-        <v>400</v>
+        <v>350</v>
       </c>
       <c r="G24" s="35" t="inlineStr">
         <is>
-          <t>Sem retorno</t>
-        </is>
-      </c>
-      <c r="H24" s="37">
-        <f>TODAY()-22</f>
-        <v>46257.0</v>
-      </c>
-      <c r="I24" s="35" t="inlineStr">
-        <is>
-          <t>Vai pensar / sem retorno</t>
-        </is>
-      </c>
-      <c r="J24" s="32" t="n"/>
+          <t>Aprovado</t>
+        </is>
+      </c>
+      <c r="H24" s="37" t="n">
+        <v>46258</v>
+      </c>
+      <c r="I24" s="35" t="n"/>
+      <c r="J24" s="32" t="inlineStr">
+        <is>
+          <t>Agendado para 25/08</t>
+        </is>
+      </c>
       <c r="K24" s="30">
         <f>IF(G24="","",IFERROR(INDEX(Config!$B$10:$B$14,MATCH(G24,Config!$A$10:$A$14,0)),0))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L24" s="26">
         <f>IF(OR(G24="",F24=""),"",F24*K24)</f>
-        <v>0</v>
+        <v>350</v>
       </c>
       <c r="M24" s="29">
         <f>IF(OR(G24="",G24="Aprovado",G24="Recusado",G24="Sem retorno",A24=""),"",Config!$B$5-A24)</f>
         <v/>
       </c>
       <c r="N24" s="29">
-        <f>IF(AND(OR(G24="Aprovado",G24="Recusado"),H24&lt;&gt;"",A24&lt;&gt;""),H24-A24,"")</f>
-        <v/>
+        <f>IF(AND(OR(G24="Aprovado",G24="Recusado"),H24&lt;&gt;"",A24&lt;&gt;"",H24&gt;=A24),H24-A24,"")</f>
+        <v>7</v>
       </c>
       <c r="O24" s="25" t="str">
         <f>IF(G24="","",IF(OR(G24="Aprovado",G24="Recusado",G24="Sem retorno"),G24,IF(AND(M24&lt;&gt;"",M24&gt;Config!$B$7),"Parado","Ativo")))</f>
-        <v>Sem retorno</v>
+        <v>Aprovado</v>
       </c>
       <c r="P24" s="39">
         <f>IF(A24="","",DATE(YEAR(A24),MONTH(A24),1))</f>
@@ -4333,65 +4331,67 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="37" t="n">
-        <v>46254</v>
+      <c r="A25" s="37">
+        <f>TODAY()-26</f>
+        <v>46253.0</v>
       </c>
       <c r="B25" s="32" t="inlineStr">
         <is>
-          <t>Roberta Araújo</t>
+          <t>Beatriz Gomes</t>
         </is>
       </c>
       <c r="C25" s="35" t="inlineStr">
         <is>
-          <t>Dr. Paulo Andrade</t>
+          <t>Dra. Renata Sousa</t>
         </is>
       </c>
       <c r="D25" s="35" t="inlineStr">
         <is>
-          <t>Exame cardiológico</t>
+          <t>Avaliação endócrina</t>
         </is>
       </c>
       <c r="E25" s="32" t="inlineStr">
         <is>
-          <t>Holter</t>
+          <t>Avaliação endócrina + retorno</t>
         </is>
       </c>
       <c r="F25" s="38" t="n">
-        <v>350</v>
+        <v>400</v>
       </c>
       <c r="G25" s="35" t="inlineStr">
         <is>
-          <t>Aprovado</t>
-        </is>
-      </c>
-      <c r="H25" s="37" t="n">
-        <v>46255</v>
-      </c>
-      <c r="I25" s="35" t="n"/>
-      <c r="J25" s="32" t="inlineStr">
-        <is>
-          <t>Agendado para 25/08</t>
-        </is>
-      </c>
+          <t>Sem retorno</t>
+        </is>
+      </c>
+      <c r="H25" s="37">
+        <f>TODAY()-17</f>
+        <v>46262.0</v>
+      </c>
+      <c r="I25" s="35" t="inlineStr">
+        <is>
+          <t>Vai pensar / sem retorno</t>
+        </is>
+      </c>
+      <c r="J25" s="32" t="n"/>
       <c r="K25" s="30">
         <f>IF(G25="","",IFERROR(INDEX(Config!$B$10:$B$14,MATCH(G25,Config!$A$10:$A$14,0)),0))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L25" s="26">
         <f>IF(OR(G25="",F25=""),"",F25*K25)</f>
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="M25" s="29">
         <f>IF(OR(G25="",G25="Aprovado",G25="Recusado",G25="Sem retorno",A25=""),"",Config!$B$5-A25)</f>
         <v/>
       </c>
       <c r="N25" s="29">
-        <f>IF(AND(OR(G25="Aprovado",G25="Recusado"),H25&lt;&gt;"",A25&lt;&gt;""),H25-A25,"")</f>
-        <v>1</v>
+        <f>IF(AND(OR(G25="Aprovado",G25="Recusado"),H25&lt;&gt;"",A25&lt;&gt;"",H25&gt;=A25),H25-A25,"")</f>
+        <v/>
       </c>
       <c r="O25" s="25" t="str">
         <f>IF(G25="","",IF(OR(G25="Aprovado",G25="Recusado",G25="Sem retorno"),G25,IF(AND(M25&lt;&gt;"",M25&gt;Config!$B$7),"Parado","Ativo")))</f>
-        <v>Aprovado</v>
+        <v>Sem retorno</v>
       </c>
       <c r="P25" s="39">
         <f>IF(A25="","",DATE(YEAR(A25),MONTH(A25),1))</f>
@@ -4408,7 +4408,7 @@
       </c>
       <c r="B26" s="32" t="inlineStr">
         <is>
-          <t>Eduardo Lima</t>
+          <t>Fernanda Freitas</t>
         </is>
       </c>
       <c r="C26" s="35" t="inlineStr">
@@ -4423,11 +4423,11 @@
       </c>
       <c r="E26" s="32" t="inlineStr">
         <is>
-          <t>MAPA</t>
+          <t>Teste ergométrico</t>
         </is>
       </c>
       <c r="F26" s="38" t="n">
-        <v>300</v>
+        <v>450</v>
       </c>
       <c r="G26" s="35" t="inlineStr">
         <is>
@@ -4435,12 +4435,12 @@
         </is>
       </c>
       <c r="H26" s="37" t="n">
-        <v>46273</v>
+        <v>46267</v>
       </c>
       <c r="I26" s="35" t="n"/>
       <c r="J26" s="32" t="inlineStr">
         <is>
-          <t>Agendado para 10/09</t>
+          <t>Agendado para 04/09</t>
         </is>
       </c>
       <c r="K26" s="30">
@@ -4449,15 +4449,15 @@
       </c>
       <c r="L26" s="26">
         <f>IF(OR(G26="",F26=""),"",F26*K26)</f>
-        <v>300</v>
+        <v>450</v>
       </c>
       <c r="M26" s="29">
         <f>IF(OR(G26="",G26="Aprovado",G26="Recusado",G26="Sem retorno",A26=""),"",Config!$B$5-A26)</f>
         <v/>
       </c>
       <c r="N26" s="29">
-        <f>IF(AND(OR(G26="Aprovado",G26="Recusado"),H26&lt;&gt;"",A26&lt;&gt;""),H26-A26,"")</f>
-        <v>18</v>
+        <f>IF(AND(OR(G26="Aprovado",G26="Recusado"),H26&lt;&gt;"",A26&lt;&gt;"",H26&gt;=A26),H26-A26,"")</f>
+        <v>12</v>
       </c>
       <c r="O26" s="25" t="str">
         <f>IF(G26="","",IF(OR(G26="Aprovado",G26="Recusado",G26="Sem retorno"),G26,IF(AND(M26&lt;&gt;"",M26&gt;Config!$B$7),"Parado","Ativo")))</f>
@@ -4474,11 +4474,11 @@
     </row>
     <row r="27">
       <c r="A27" s="37" t="n">
-        <v>46259</v>
+        <v>46258</v>
       </c>
       <c r="B27" s="32" t="inlineStr">
         <is>
-          <t>Rafael Dias</t>
+          <t>Rodrigo Moreira</t>
         </is>
       </c>
       <c r="C27" s="35" t="inlineStr">
@@ -4493,11 +4493,11 @@
       </c>
       <c r="E27" s="32" t="inlineStr">
         <is>
-          <t>MAPA</t>
+          <t>Teste ergométrico</t>
         </is>
       </c>
       <c r="F27" s="38" t="n">
-        <v>300</v>
+        <v>450</v>
       </c>
       <c r="G27" s="35" t="inlineStr">
         <is>
@@ -4505,12 +4505,12 @@
         </is>
       </c>
       <c r="H27" s="37" t="n">
-        <v>46269</v>
+        <v>46275</v>
       </c>
       <c r="I27" s="35" t="n"/>
       <c r="J27" s="32" t="inlineStr">
         <is>
-          <t>Agendado para 04/09</t>
+          <t>Agendado para 02/10</t>
         </is>
       </c>
       <c r="K27" s="30">
@@ -4519,15 +4519,15 @@
       </c>
       <c r="L27" s="26">
         <f>IF(OR(G27="",F27=""),"",F27*K27)</f>
-        <v>300</v>
+        <v>450</v>
       </c>
       <c r="M27" s="29">
         <f>IF(OR(G27="",G27="Aprovado",G27="Recusado",G27="Sem retorno",A27=""),"",Config!$B$5-A27)</f>
         <v/>
       </c>
       <c r="N27" s="29">
-        <f>IF(AND(OR(G27="Aprovado",G27="Recusado"),H27&lt;&gt;"",A27&lt;&gt;""),H27-A27,"")</f>
-        <v>10</v>
+        <f>IF(AND(OR(G27="Aprovado",G27="Recusado"),H27&lt;&gt;"",A27&lt;&gt;"",H27&gt;=A27),H27-A27,"")</f>
+        <v>17</v>
       </c>
       <c r="O27" s="25" t="str">
         <f>IF(G27="","",IF(OR(G27="Aprovado",G27="Recusado",G27="Sem retorno"),G27,IF(AND(M27&lt;&gt;"",M27&gt;Config!$B$7),"Parado","Ativo")))</f>
@@ -4576,8 +4576,8 @@
         </is>
       </c>
       <c r="H28" s="37">
-        <f>TODAY()-13</f>
-        <v>46266.0</v>
+        <f>TODAY()-17</f>
+        <v>46262.0</v>
       </c>
       <c r="I28" s="35" t="inlineStr">
         <is>
@@ -4598,8 +4598,8 @@
         <v/>
       </c>
       <c r="N28" s="29">
-        <f>IF(AND(OR(G28="Aprovado",G28="Recusado"),H28&lt;&gt;"",A28&lt;&gt;""),H28-A28,"")</f>
-        <v>7</v>
+        <f>IF(AND(OR(G28="Aprovado",G28="Recusado"),H28&lt;&gt;"",A28&lt;&gt;"",H28&gt;=A28),H28-A28,"")</f>
+        <v>3</v>
       </c>
       <c r="O28" s="25" t="str">
         <f>IF(G28="","",IF(OR(G28="Aprovado",G28="Recusado",G28="Sem retorno"),G28,IF(AND(M28&lt;&gt;"",M28&gt;Config!$B$7),"Parado","Ativo")))</f>
@@ -4615,13 +4615,12 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="37">
-        <f>TODAY()-16</f>
-        <v>46263.0</v>
+      <c r="A29" s="37" t="n">
+        <v>46262</v>
       </c>
       <c r="B29" s="32" t="inlineStr">
         <is>
-          <t>Patrícia Dias</t>
+          <t>Leandro Oliveira</t>
         </is>
       </c>
       <c r="C29" s="35" t="inlineStr">
@@ -4636,46 +4635,45 @@
       </c>
       <c r="E29" s="32" t="inlineStr">
         <is>
-          <t>MAPA</t>
+          <t>Teste ergométrico</t>
         </is>
       </c>
       <c r="F29" s="38" t="n">
-        <v>300</v>
+        <v>450</v>
       </c>
       <c r="G29" s="35" t="inlineStr">
         <is>
-          <t>Sem retorno</t>
-        </is>
-      </c>
-      <c r="H29" s="37">
-        <f>TODAY()-12</f>
-        <v>46267.0</v>
-      </c>
-      <c r="I29" s="35" t="inlineStr">
-        <is>
-          <t>Vai pensar / sem retorno</t>
-        </is>
-      </c>
-      <c r="J29" s="32" t="n"/>
+          <t>Aprovado</t>
+        </is>
+      </c>
+      <c r="H29" s="37" t="n">
+        <v>46276</v>
+      </c>
+      <c r="I29" s="35" t="n"/>
+      <c r="J29" s="32" t="inlineStr">
+        <is>
+          <t>Agendado para 22/09</t>
+        </is>
+      </c>
       <c r="K29" s="30">
         <f>IF(G29="","",IFERROR(INDEX(Config!$B$10:$B$14,MATCH(G29,Config!$A$10:$A$14,0)),0))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L29" s="26">
         <f>IF(OR(G29="",F29=""),"",F29*K29)</f>
-        <v>0</v>
+        <v>450</v>
       </c>
       <c r="M29" s="29">
         <f>IF(OR(G29="",G29="Aprovado",G29="Recusado",G29="Sem retorno",A29=""),"",Config!$B$5-A29)</f>
         <v/>
       </c>
       <c r="N29" s="29">
-        <f>IF(AND(OR(G29="Aprovado",G29="Recusado"),H29&lt;&gt;"",A29&lt;&gt;""),H29-A29,"")</f>
-        <v/>
+        <f>IF(AND(OR(G29="Aprovado",G29="Recusado"),H29&lt;&gt;"",A29&lt;&gt;"",H29&gt;=A29),H29-A29,"")</f>
+        <v>14</v>
       </c>
       <c r="O29" s="25" t="str">
         <f>IF(G29="","",IF(OR(G29="Aprovado",G29="Recusado",G29="Sem retorno"),G29,IF(AND(M29&lt;&gt;"",M29&gt;Config!$B$7),"Parado","Ativo")))</f>
-        <v>Sem retorno</v>
+        <v>Aprovado</v>
       </c>
       <c r="P29" s="39">
         <f>IF(A29="","",DATE(YEAR(A29),MONTH(A29),1))</f>
@@ -4687,13 +4685,12 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="37">
-        <f>TODAY()-12</f>
-        <v>46267.0</v>
+      <c r="A30" s="37" t="n">
+        <v>46262</v>
       </c>
       <c r="B30" s="32" t="inlineStr">
         <is>
-          <t>Mariana Reis</t>
+          <t>Gisele Ribeiro</t>
         </is>
       </c>
       <c r="C30" s="35" t="inlineStr">
@@ -4708,122 +4705,134 @@
       </c>
       <c r="E30" s="32" t="inlineStr">
         <is>
-          <t>MAPA + Holter</t>
+          <t>Teste ergométrico</t>
         </is>
       </c>
       <c r="F30" s="38" t="n">
-        <v>650</v>
+        <v>450</v>
       </c>
       <c r="G30" s="35" t="inlineStr">
         <is>
-          <t>Em análise</t>
-        </is>
-      </c>
-      <c r="H30" s="37" t="n"/>
+          <t>Aprovado</t>
+        </is>
+      </c>
+      <c r="H30" s="37" t="n">
+        <v>46275</v>
+      </c>
       <c r="I30" s="35" t="n"/>
-      <c r="J30" s="32" t="n"/>
+      <c r="J30" s="32" t="inlineStr">
+        <is>
+          <t>Agendado para 05/10</t>
+        </is>
+      </c>
       <c r="K30" s="30">
         <f>IF(G30="","",IFERROR(INDEX(Config!$B$10:$B$14,MATCH(G30,Config!$A$10:$A$14,0)),0))</f>
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="L30" s="26">
         <f>IF(OR(G30="",F30=""),"",F30*K30)</f>
-        <v>325</v>
+        <v>450</v>
       </c>
       <c r="M30" s="29">
         <f>IF(OR(G30="",G30="Aprovado",G30="Recusado",G30="Sem retorno",A30=""),"",Config!$B$5-A30)</f>
-        <v>12</v>
+        <v/>
       </c>
       <c r="N30" s="29">
-        <f>IF(AND(OR(G30="Aprovado",G30="Recusado"),H30&lt;&gt;"",A30&lt;&gt;""),H30-A30,"")</f>
-        <v/>
+        <f>IF(AND(OR(G30="Aprovado",G30="Recusado"),H30&lt;&gt;"",A30&lt;&gt;"",H30&gt;=A30),H30-A30,"")</f>
+        <v>13</v>
       </c>
       <c r="O30" s="25" t="str">
         <f>IF(G30="","",IF(OR(G30="Aprovado",G30="Recusado",G30="Sem retorno"),G30,IF(AND(M30&lt;&gt;"",M30&gt;Config!$B$7),"Parado","Ativo")))</f>
-        <v>Parado</v>
+        <v>Aprovado</v>
       </c>
       <c r="P30" s="39">
         <f>IF(A30="","",DATE(YEAR(A30),MONTH(A30),1))</f>
-        <v>46266.0</v>
+        <v>46235.0</v>
       </c>
       <c r="Q30" s="40">
         <f>IF(OR(G30="",O30="Aprovado",O30="Recusado",O30="Sem retorno"),0,IF(O30="Parado",2000,1000)+MIN(N(M30),500)+N(F30)/1000000-ROW()/100000)</f>
-        <v>2012.00035</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="37">
+        <f>TODAY()-16</f>
+        <v>46263.0</v>
+      </c>
+      <c r="B31" s="32" t="inlineStr">
+        <is>
+          <t>Patrícia Dias</t>
+        </is>
+      </c>
+      <c r="C31" s="35" t="inlineStr">
+        <is>
+          <t>Dr. Paulo Andrade</t>
+        </is>
+      </c>
+      <c r="D31" s="35" t="inlineStr">
+        <is>
+          <t>Exame cardiológico</t>
+        </is>
+      </c>
+      <c r="E31" s="32" t="inlineStr">
+        <is>
+          <t>MAPA</t>
+        </is>
+      </c>
+      <c r="F31" s="38" t="n">
+        <v>300</v>
+      </c>
+      <c r="G31" s="35" t="inlineStr">
+        <is>
+          <t>Sem retorno</t>
+        </is>
+      </c>
+      <c r="H31" s="37">
         <f>TODAY()-9</f>
         <v>46270.0</v>
       </c>
-      <c r="B31" s="32" t="inlineStr">
-        <is>
-          <t>Beatriz Monteiro</t>
-        </is>
-      </c>
-      <c r="C31" s="35" t="inlineStr">
-        <is>
-          <t>Dra. Renata Sousa</t>
-        </is>
-      </c>
-      <c r="D31" s="35" t="inlineStr">
-        <is>
-          <t>Avaliação endócrina</t>
-        </is>
-      </c>
-      <c r="E31" s="32" t="inlineStr">
-        <is>
-          <t>Avaliação endócrina + retorno</t>
-        </is>
-      </c>
-      <c r="F31" s="38" t="n">
-        <v>400</v>
-      </c>
-      <c r="G31" s="35" t="inlineStr">
-        <is>
-          <t>Em análise</t>
-        </is>
-      </c>
-      <c r="H31" s="37" t="n"/>
-      <c r="I31" s="35" t="n"/>
+      <c r="I31" s="35" t="inlineStr">
+        <is>
+          <t>Vai pensar / sem retorno</t>
+        </is>
+      </c>
       <c r="J31" s="32" t="n"/>
       <c r="K31" s="30">
         <f>IF(G31="","",IFERROR(INDEX(Config!$B$10:$B$14,MATCH(G31,Config!$A$10:$A$14,0)),0))</f>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="L31" s="26">
         <f>IF(OR(G31="",F31=""),"",F31*K31)</f>
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="M31" s="29">
         <f>IF(OR(G31="",G31="Aprovado",G31="Recusado",G31="Sem retorno",A31=""),"",Config!$B$5-A31)</f>
-        <v>9</v>
+        <v/>
       </c>
       <c r="N31" s="29">
-        <f>IF(AND(OR(G31="Aprovado",G31="Recusado"),H31&lt;&gt;"",A31&lt;&gt;""),H31-A31,"")</f>
+        <f>IF(AND(OR(G31="Aprovado",G31="Recusado"),H31&lt;&gt;"",A31&lt;&gt;"",H31&gt;=A31),H31-A31,"")</f>
         <v/>
       </c>
       <c r="O31" s="25" t="str">
         <f>IF(G31="","",IF(OR(G31="Aprovado",G31="Recusado",G31="Sem retorno"),G31,IF(AND(M31&lt;&gt;"",M31&gt;Config!$B$7),"Parado","Ativo")))</f>
-        <v>Parado</v>
+        <v>Sem retorno</v>
       </c>
       <c r="P31" s="39">
         <f>IF(A31="","",DATE(YEAR(A31),MONTH(A31),1))</f>
-        <v>46266.0</v>
+        <v>46235.0</v>
       </c>
       <c r="Q31" s="40">
         <f>IF(OR(G31="",O31="Aprovado",O31="Recusado",O31="Sem retorno"),0,IF(O31="Parado",2000,1000)+MIN(N(M31),500)+N(F31)/1000000-ROW()/100000)</f>
-        <v>2009.00009</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="37">
-        <f>TODAY()-6</f>
-        <v>46273.0</v>
+      <c r="A32" s="37" t="n">
+        <v>46265</v>
       </c>
       <c r="B32" s="32" t="inlineStr">
         <is>
-          <t>Rafael Dias</t>
+          <t>Lucas Lopes</t>
         </is>
       </c>
       <c r="C32" s="35" t="inlineStr">
@@ -4838,57 +4847,62 @@
       </c>
       <c r="E32" s="32" t="inlineStr">
         <is>
-          <t>Holter</t>
+          <t>MAPA</t>
         </is>
       </c>
       <c r="F32" s="38" t="n">
-        <v>350</v>
+        <v>300</v>
       </c>
       <c r="G32" s="35" t="inlineStr">
         <is>
-          <t>Em análise</t>
-        </is>
-      </c>
-      <c r="H32" s="37" t="n"/>
+          <t>Aprovado</t>
+        </is>
+      </c>
+      <c r="H32" s="37" t="n">
+        <v>46275</v>
+      </c>
       <c r="I32" s="35" t="n"/>
-      <c r="J32" s="32" t="n"/>
+      <c r="J32" s="32" t="inlineStr">
+        <is>
+          <t>Agendado para 01/10</t>
+        </is>
+      </c>
       <c r="K32" s="30">
         <f>IF(G32="","",IFERROR(INDEX(Config!$B$10:$B$14,MATCH(G32,Config!$A$10:$A$14,0)),0))</f>
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="L32" s="26">
         <f>IF(OR(G32="",F32=""),"",F32*K32)</f>
-        <v>175</v>
+        <v>300</v>
       </c>
       <c r="M32" s="29">
         <f>IF(OR(G32="",G32="Aprovado",G32="Recusado",G32="Sem retorno",A32=""),"",Config!$B$5-A32)</f>
-        <v>6</v>
+        <v/>
       </c>
       <c r="N32" s="29">
-        <f>IF(AND(OR(G32="Aprovado",G32="Recusado"),H32&lt;&gt;"",A32&lt;&gt;""),H32-A32,"")</f>
-        <v/>
+        <f>IF(AND(OR(G32="Aprovado",G32="Recusado"),H32&lt;&gt;"",A32&lt;&gt;"",H32&gt;=A32),H32-A32,"")</f>
+        <v>10</v>
       </c>
       <c r="O32" s="25" t="str">
         <f>IF(G32="","",IF(OR(G32="Aprovado",G32="Recusado",G32="Sem retorno"),G32,IF(AND(M32&lt;&gt;"",M32&gt;Config!$B$7),"Parado","Ativo")))</f>
-        <v>Ativo</v>
+        <v>Aprovado</v>
       </c>
       <c r="P32" s="39">
         <f>IF(A32="","",DATE(YEAR(A32),MONTH(A32),1))</f>
-        <v>46266.0</v>
+        <v>46235.0</v>
       </c>
       <c r="Q32" s="40">
         <f>IF(OR(G32="",O32="Aprovado",O32="Recusado",O32="Sem retorno"),0,IF(O32="Parado",2000,1000)+MIN(N(M32),500)+N(F32)/1000000-ROW()/100000)</f>
-        <v>1006.00003</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="37">
-        <f>TODAY()-3</f>
-        <v>46276.0</v>
+      <c r="A33" s="37" t="n">
+        <v>46266</v>
       </c>
       <c r="B33" s="32" t="inlineStr">
         <is>
-          <t>Roberta Lima</t>
+          <t>Paulo Reis</t>
         </is>
       </c>
       <c r="C33" s="35" t="inlineStr">
@@ -4898,44 +4912,50 @@
       </c>
       <c r="D33" s="35" t="inlineStr">
         <is>
-          <t>Check-up cardiológico</t>
+          <t>Exame cardiológico</t>
         </is>
       </c>
       <c r="E33" s="32" t="inlineStr">
         <is>
-          <t>Consulta + ECG + teste ergométrico</t>
+          <t>Holter</t>
         </is>
       </c>
       <c r="F33" s="38" t="n">
-        <v>960</v>
+        <v>350</v>
       </c>
       <c r="G33" s="35" t="inlineStr">
         <is>
-          <t>Apresentado</t>
-        </is>
-      </c>
-      <c r="H33" s="37" t="n"/>
+          <t>Aprovado</t>
+        </is>
+      </c>
+      <c r="H33" s="37" t="n">
+        <v>46274</v>
+      </c>
       <c r="I33" s="35" t="n"/>
-      <c r="J33" s="32" t="n"/>
+      <c r="J33" s="32" t="inlineStr">
+        <is>
+          <t>Agendado para 17/09</t>
+        </is>
+      </c>
       <c r="K33" s="30">
         <f>IF(G33="","",IFERROR(INDEX(Config!$B$10:$B$14,MATCH(G33,Config!$A$10:$A$14,0)),0))</f>
-        <v>0.3</v>
+        <v>1</v>
       </c>
       <c r="L33" s="26">
         <f>IF(OR(G33="",F33=""),"",F33*K33)</f>
-        <v>288</v>
+        <v>350</v>
       </c>
       <c r="M33" s="29">
         <f>IF(OR(G33="",G33="Aprovado",G33="Recusado",G33="Sem retorno",A33=""),"",Config!$B$5-A33)</f>
-        <v>3</v>
+        <v/>
       </c>
       <c r="N33" s="29">
-        <f>IF(AND(OR(G33="Aprovado",G33="Recusado"),H33&lt;&gt;"",A33&lt;&gt;""),H33-A33,"")</f>
-        <v/>
+        <f>IF(AND(OR(G33="Aprovado",G33="Recusado"),H33&lt;&gt;"",A33&lt;&gt;"",H33&gt;=A33),H33-A33,"")</f>
+        <v>8</v>
       </c>
       <c r="O33" s="25" t="str">
         <f>IF(G33="","",IF(OR(G33="Aprovado",G33="Recusado",G33="Sem retorno"),G33,IF(AND(M33&lt;&gt;"",M33&gt;Config!$B$7),"Parado","Ativo")))</f>
-        <v>Ativo</v>
+        <v>Aprovado</v>
       </c>
       <c r="P33" s="39">
         <f>IF(A33="","",DATE(YEAR(A33),MONTH(A33),1))</f>
@@ -4943,17 +4963,17 @@
       </c>
       <c r="Q33" s="40">
         <f>IF(OR(G33="",O33="Aprovado",O33="Recusado",O33="Sem retorno"),0,IF(O33="Parado",2000,1000)+MIN(N(M33),500)+N(F33)/1000000-ROW()/100000)</f>
-        <v>1003.00063</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="37">
-        <f>TODAY()-1</f>
-        <v>46278.0</v>
+        <f>TODAY()-12</f>
+        <v>46267.0</v>
       </c>
       <c r="B34" s="32" t="inlineStr">
         <is>
-          <t>Wagner Costa</t>
+          <t>Mariana Reis</t>
         </is>
       </c>
       <c r="C34" s="35" t="inlineStr">
@@ -4968,15 +4988,15 @@
       </c>
       <c r="E34" s="32" t="inlineStr">
         <is>
-          <t>Teste ergométrico</t>
+          <t>MAPA + Holter</t>
         </is>
       </c>
       <c r="F34" s="38" t="n">
-        <v>450</v>
+        <v>650</v>
       </c>
       <c r="G34" s="35" t="inlineStr">
         <is>
-          <t>Apresentado</t>
+          <t>Em análise</t>
         </is>
       </c>
       <c r="H34" s="37" t="n"/>
@@ -4984,23 +5004,23 @@
       <c r="J34" s="32" t="n"/>
       <c r="K34" s="30">
         <f>IF(G34="","",IFERROR(INDEX(Config!$B$10:$B$14,MATCH(G34,Config!$A$10:$A$14,0)),0))</f>
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="L34" s="26">
         <f>IF(OR(G34="",F34=""),"",F34*K34)</f>
-        <v>135</v>
+        <v>325</v>
       </c>
       <c r="M34" s="29">
         <f>IF(OR(G34="",G34="Aprovado",G34="Recusado",G34="Sem retorno",A34=""),"",Config!$B$5-A34)</f>
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="N34" s="29">
-        <f>IF(AND(OR(G34="Aprovado",G34="Recusado"),H34&lt;&gt;"",A34&lt;&gt;""),H34-A34,"")</f>
+        <f>IF(AND(OR(G34="Aprovado",G34="Recusado"),H34&lt;&gt;"",A34&lt;&gt;"",H34&gt;=A34),H34-A34,"")</f>
         <v/>
       </c>
       <c r="O34" s="25" t="str">
         <f>IF(G34="","",IF(OR(G34="Aprovado",G34="Recusado",G34="Sem retorno"),G34,IF(AND(M34&lt;&gt;"",M34&gt;Config!$B$7),"Parado","Ativo")))</f>
-        <v>Ativo</v>
+        <v>Parado</v>
       </c>
       <c r="P34" s="39">
         <f>IF(A34="","",DATE(YEAR(A34),MONTH(A34),1))</f>
@@ -5008,17 +5028,16 @@
       </c>
       <c r="Q34" s="40">
         <f>IF(OR(G34="",O34="Aprovado",O34="Recusado",O34="Sem retorno"),0,IF(O34="Parado",2000,1000)+MIN(N(M34),500)+N(F34)/1000000-ROW()/100000)</f>
-        <v>1001.00011</v>
+        <v>2012.00031</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="37">
-        <f>TODAY()</f>
-        <v>46279.0</v>
+      <c r="A35" s="37" t="n">
+        <v>46269</v>
       </c>
       <c r="B35" s="32" t="inlineStr">
         <is>
-          <t>Fábio Correia</t>
+          <t>Wagner Lima</t>
         </is>
       </c>
       <c r="C35" s="35" t="inlineStr">
@@ -5033,39 +5052,45 @@
       </c>
       <c r="E35" s="32" t="inlineStr">
         <is>
-          <t>MAPA + Holter</t>
+          <t>Holter</t>
         </is>
       </c>
       <c r="F35" s="38" t="n">
-        <v>650</v>
+        <v>350</v>
       </c>
       <c r="G35" s="35" t="inlineStr">
         <is>
-          <t>Apresentado</t>
-        </is>
-      </c>
-      <c r="H35" s="37" t="n"/>
+          <t>Aprovado</t>
+        </is>
+      </c>
+      <c r="H35" s="37" t="n">
+        <v>46275</v>
+      </c>
       <c r="I35" s="35" t="n"/>
-      <c r="J35" s="32" t="n"/>
+      <c r="J35" s="32" t="inlineStr">
+        <is>
+          <t>Agendado para 22/09</t>
+        </is>
+      </c>
       <c r="K35" s="30">
         <f>IF(G35="","",IFERROR(INDEX(Config!$B$10:$B$14,MATCH(G35,Config!$A$10:$A$14,0)),0))</f>
-        <v>0.3</v>
+        <v>1</v>
       </c>
       <c r="L35" s="26">
         <f>IF(OR(G35="",F35=""),"",F35*K35)</f>
-        <v>195</v>
+        <v>350</v>
       </c>
       <c r="M35" s="29">
         <f>IF(OR(G35="",G35="Aprovado",G35="Recusado",G35="Sem retorno",A35=""),"",Config!$B$5-A35)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="N35" s="29">
-        <f>IF(AND(OR(G35="Aprovado",G35="Recusado"),H35&lt;&gt;"",A35&lt;&gt;""),H35-A35,"")</f>
-        <v/>
+        <f>IF(AND(OR(G35="Aprovado",G35="Recusado"),H35&lt;&gt;"",A35&lt;&gt;"",H35&gt;=A35),H35-A35,"")</f>
+        <v>6</v>
       </c>
       <c r="O35" s="25" t="str">
         <f>IF(G35="","",IF(OR(G35="Aprovado",G35="Recusado",G35="Sem retorno"),G35,IF(AND(M35&lt;&gt;"",M35&gt;Config!$B$7),"Parado","Ativo")))</f>
-        <v>Ativo</v>
+        <v>Aprovado</v>
       </c>
       <c r="P35" s="39">
         <f>IF(A35="","",DATE(YEAR(A35),MONTH(A35),1))</f>
@@ -5073,69 +5098,64 @@
       </c>
       <c r="Q35" s="40">
         <f>IF(OR(G35="",O35="Aprovado",O35="Recusado",O35="Sem retorno"),0,IF(O35="Parado",2000,1000)+MIN(N(M35),500)+N(F35)/1000000-ROW()/100000)</f>
-        <v>1000.0003</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="37" t="n">
-        <v>46280</v>
+      <c r="A36" s="37">
+        <f>TODAY()-9</f>
+        <v>46270.0</v>
       </c>
       <c r="B36" s="32" t="inlineStr">
         <is>
-          <t>Ana Costa</t>
+          <t>Beatriz Monteiro</t>
         </is>
       </c>
       <c r="C36" s="35" t="inlineStr">
         <is>
-          <t>Dr. Paulo Andrade</t>
+          <t>Dra. Renata Sousa</t>
         </is>
       </c>
       <c r="D36" s="35" t="inlineStr">
         <is>
-          <t>Exame cardiológico</t>
+          <t>Avaliação endócrina</t>
         </is>
       </c>
       <c r="E36" s="32" t="inlineStr">
         <is>
-          <t>Holter</t>
+          <t>Avaliação endócrina + retorno</t>
         </is>
       </c>
       <c r="F36" s="38" t="n">
-        <v>350</v>
+        <v>400</v>
       </c>
       <c r="G36" s="35" t="inlineStr">
         <is>
-          <t>Aprovado</t>
-        </is>
-      </c>
-      <c r="H36" s="37" t="n">
-        <v>46276</v>
-      </c>
+          <t>Em análise</t>
+        </is>
+      </c>
+      <c r="H36" s="37" t="n"/>
       <c r="I36" s="35" t="n"/>
-      <c r="J36" s="32" t="inlineStr">
-        <is>
-          <t>Agendado para 21/09</t>
-        </is>
-      </c>
+      <c r="J36" s="32" t="n"/>
       <c r="K36" s="30">
         <f>IF(G36="","",IFERROR(INDEX(Config!$B$10:$B$14,MATCH(G36,Config!$A$10:$A$14,0)),0))</f>
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="L36" s="26">
         <f>IF(OR(G36="",F36=""),"",F36*K36)</f>
-        <v>350</v>
+        <v>200</v>
       </c>
       <c r="M36" s="29">
         <f>IF(OR(G36="",G36="Aprovado",G36="Recusado",G36="Sem retorno",A36=""),"",Config!$B$5-A36)</f>
-        <v/>
+        <v>9</v>
       </c>
       <c r="N36" s="29">
-        <f>IF(AND(OR(G36="Aprovado",G36="Recusado"),H36&lt;&gt;"",A36&lt;&gt;""),H36-A36,"")</f>
-        <v>-4</v>
+        <f>IF(AND(OR(G36="Aprovado",G36="Recusado"),H36&lt;&gt;"",A36&lt;&gt;"",H36&gt;=A36),H36-A36,"")</f>
+        <v/>
       </c>
       <c r="O36" s="25" t="str">
         <f>IF(G36="","",IF(OR(G36="Aprovado",G36="Recusado",G36="Sem retorno"),G36,IF(AND(M36&lt;&gt;"",M36&gt;Config!$B$7),"Parado","Ativo")))</f>
-        <v>Aprovado</v>
+        <v>Parado</v>
       </c>
       <c r="P36" s="39">
         <f>IF(A36="","",DATE(YEAR(A36),MONTH(A36),1))</f>
@@ -5143,16 +5163,17 @@
       </c>
       <c r="Q36" s="40">
         <f>IF(OR(G36="",O36="Aprovado",O36="Recusado",O36="Sem retorno"),0,IF(O36="Parado",2000,1000)+MIN(N(M36),500)+N(F36)/1000000-ROW()/100000)</f>
-        <v>0</v>
+        <v>2009.00004</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="37" t="n">
-        <v>46283</v>
+      <c r="A37" s="37">
+        <f>TODAY()-6</f>
+        <v>46273.0</v>
       </c>
       <c r="B37" s="32" t="inlineStr">
         <is>
-          <t>Viviane Ribeiro</t>
+          <t>Rafael Dias</t>
         </is>
       </c>
       <c r="C37" s="35" t="inlineStr">
@@ -5167,45 +5188,39 @@
       </c>
       <c r="E37" s="32" t="inlineStr">
         <is>
-          <t>MAPA</t>
+          <t>Holter</t>
         </is>
       </c>
       <c r="F37" s="38" t="n">
-        <v>300</v>
+        <v>350</v>
       </c>
       <c r="G37" s="35" t="inlineStr">
         <is>
-          <t>Aprovado</t>
-        </is>
-      </c>
-      <c r="H37" s="37" t="n">
-        <v>46276</v>
-      </c>
+          <t>Em análise</t>
+        </is>
+      </c>
+      <c r="H37" s="37" t="n"/>
       <c r="I37" s="35" t="n"/>
-      <c r="J37" s="32" t="inlineStr">
-        <is>
-          <t>Agendado para 05/10</t>
-        </is>
-      </c>
+      <c r="J37" s="32" t="n"/>
       <c r="K37" s="30">
         <f>IF(G37="","",IFERROR(INDEX(Config!$B$10:$B$14,MATCH(G37,Config!$A$10:$A$14,0)),0))</f>
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="L37" s="26">
         <f>IF(OR(G37="",F37=""),"",F37*K37)</f>
-        <v>300</v>
+        <v>175</v>
       </c>
       <c r="M37" s="29">
         <f>IF(OR(G37="",G37="Aprovado",G37="Recusado",G37="Sem retorno",A37=""),"",Config!$B$5-A37)</f>
-        <v/>
+        <v>6</v>
       </c>
       <c r="N37" s="29">
-        <f>IF(AND(OR(G37="Aprovado",G37="Recusado"),H37&lt;&gt;"",A37&lt;&gt;""),H37-A37,"")</f>
-        <v>-7</v>
+        <f>IF(AND(OR(G37="Aprovado",G37="Recusado"),H37&lt;&gt;"",A37&lt;&gt;"",H37&gt;=A37),H37-A37,"")</f>
+        <v/>
       </c>
       <c r="O37" s="25" t="str">
         <f>IF(G37="","",IF(OR(G37="Aprovado",G37="Recusado",G37="Sem retorno"),G37,IF(AND(M37&lt;&gt;"",M37&gt;Config!$B$7),"Parado","Ativo")))</f>
-        <v>Aprovado</v>
+        <v>Ativo</v>
       </c>
       <c r="P37" s="39">
         <f>IF(A37="","",DATE(YEAR(A37),MONTH(A37),1))</f>
@@ -5213,16 +5228,17 @@
       </c>
       <c r="Q37" s="40">
         <f>IF(OR(G37="",O37="Aprovado",O37="Recusado",O37="Sem retorno"),0,IF(O37="Parado",2000,1000)+MIN(N(M37),500)+N(F37)/1000000-ROW()/100000)</f>
-        <v>0</v>
+        <v>1005.99998</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="37" t="n">
-        <v>46286</v>
+      <c r="A38" s="37">
+        <f>TODAY()-3</f>
+        <v>46276.0</v>
       </c>
       <c r="B38" s="32" t="inlineStr">
         <is>
-          <t>Wagner Costa</t>
+          <t>Roberta Lima</t>
         </is>
       </c>
       <c r="C38" s="35" t="inlineStr">
@@ -5232,50 +5248,44 @@
       </c>
       <c r="D38" s="35" t="inlineStr">
         <is>
-          <t>Exame cardiológico</t>
+          <t>Check-up cardiológico</t>
         </is>
       </c>
       <c r="E38" s="32" t="inlineStr">
         <is>
-          <t>MAPA</t>
+          <t>Consulta + ECG + teste ergométrico</t>
         </is>
       </c>
       <c r="F38" s="38" t="n">
-        <v>300</v>
+        <v>960</v>
       </c>
       <c r="G38" s="35" t="inlineStr">
         <is>
-          <t>Aprovado</t>
-        </is>
-      </c>
-      <c r="H38" s="37" t="n">
-        <v>46276</v>
-      </c>
+          <t>Apresentado</t>
+        </is>
+      </c>
+      <c r="H38" s="37" t="n"/>
       <c r="I38" s="35" t="n"/>
-      <c r="J38" s="32" t="inlineStr">
-        <is>
-          <t>Agendado para 01/10</t>
-        </is>
-      </c>
+      <c r="J38" s="32" t="n"/>
       <c r="K38" s="30">
         <f>IF(G38="","",IFERROR(INDEX(Config!$B$10:$B$14,MATCH(G38,Config!$A$10:$A$14,0)),0))</f>
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="L38" s="26">
         <f>IF(OR(G38="",F38=""),"",F38*K38)</f>
-        <v>300</v>
+        <v>288</v>
       </c>
       <c r="M38" s="29">
         <f>IF(OR(G38="",G38="Aprovado",G38="Recusado",G38="Sem retorno",A38=""),"",Config!$B$5-A38)</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="N38" s="29">
-        <f>IF(AND(OR(G38="Aprovado",G38="Recusado"),H38&lt;&gt;"",A38&lt;&gt;""),H38-A38,"")</f>
-        <v>-10</v>
+        <f>IF(AND(OR(G38="Aprovado",G38="Recusado"),H38&lt;&gt;"",A38&lt;&gt;"",H38&gt;=A38),H38-A38,"")</f>
+        <v/>
       </c>
       <c r="O38" s="25" t="str">
         <f>IF(G38="","",IF(OR(G38="Aprovado",G38="Recusado",G38="Sem retorno"),G38,IF(AND(M38&lt;&gt;"",M38&gt;Config!$B$7),"Parado","Ativo")))</f>
-        <v>Aprovado</v>
+        <v>Ativo</v>
       </c>
       <c r="P38" s="39">
         <f>IF(A38="","",DATE(YEAR(A38),MONTH(A38),1))</f>
@@ -5283,16 +5293,17 @@
       </c>
       <c r="Q38" s="40">
         <f>IF(OR(G38="",O38="Aprovado",O38="Recusado",O38="Sem retorno"),0,IF(O38="Parado",2000,1000)+MIN(N(M38),500)+N(F38)/1000000-ROW()/100000)</f>
-        <v>0</v>
+        <v>1003.00058</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="37" t="n">
-        <v>46295</v>
+      <c r="A39" s="37">
+        <f>TODAY()-1</f>
+        <v>46278.0</v>
       </c>
       <c r="B39" s="32" t="inlineStr">
         <is>
-          <t>Gisele Ribeiro</t>
+          <t>Wagner Costa</t>
         </is>
       </c>
       <c r="C39" s="35" t="inlineStr">
@@ -5315,37 +5326,31 @@
       </c>
       <c r="G39" s="35" t="inlineStr">
         <is>
-          <t>Aprovado</t>
-        </is>
-      </c>
-      <c r="H39" s="37" t="n">
-        <v>46276</v>
-      </c>
+          <t>Apresentado</t>
+        </is>
+      </c>
+      <c r="H39" s="37" t="n"/>
       <c r="I39" s="35" t="n"/>
-      <c r="J39" s="32" t="inlineStr">
-        <is>
-          <t>Agendado para 05/10</t>
-        </is>
-      </c>
+      <c r="J39" s="32" t="n"/>
       <c r="K39" s="30">
         <f>IF(G39="","",IFERROR(INDEX(Config!$B$10:$B$14,MATCH(G39,Config!$A$10:$A$14,0)),0))</f>
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="L39" s="26">
         <f>IF(OR(G39="",F39=""),"",F39*K39)</f>
-        <v>450</v>
+        <v>135</v>
       </c>
       <c r="M39" s="29">
         <f>IF(OR(G39="",G39="Aprovado",G39="Recusado",G39="Sem retorno",A39=""),"",Config!$B$5-A39)</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="N39" s="29">
-        <f>IF(AND(OR(G39="Aprovado",G39="Recusado"),H39&lt;&gt;"",A39&lt;&gt;""),H39-A39,"")</f>
-        <v>-19</v>
+        <f>IF(AND(OR(G39="Aprovado",G39="Recusado"),H39&lt;&gt;"",A39&lt;&gt;"",H39&gt;=A39),H39-A39,"")</f>
+        <v/>
       </c>
       <c r="O39" s="25" t="str">
         <f>IF(G39="","",IF(OR(G39="Aprovado",G39="Recusado",G39="Sem retorno"),G39,IF(AND(M39&lt;&gt;"",M39&gt;Config!$B$7),"Parado","Ativo")))</f>
-        <v>Aprovado</v>
+        <v>Ativo</v>
       </c>
       <c r="P39" s="39">
         <f>IF(A39="","",DATE(YEAR(A39),MONTH(A39),1))</f>
@@ -5353,47 +5358,72 @@
       </c>
       <c r="Q39" s="40">
         <f>IF(OR(G39="",O39="Aprovado",O39="Recusado",O39="Sem retorno"),0,IF(O39="Parado",2000,1000)+MIN(N(M39),500)+N(F39)/1000000-ROW()/100000)</f>
-        <v>0</v>
+        <v>1001.00006</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="37" t="n"/>
-      <c r="B40" s="32" t="n"/>
-      <c r="C40" s="35" t="n"/>
-      <c r="D40" s="35" t="n"/>
-      <c r="E40" s="32" t="n"/>
-      <c r="F40" s="38" t="n"/>
-      <c r="G40" s="35" t="n"/>
+      <c r="A40" s="37">
+        <f>TODAY()</f>
+        <v>46279.0</v>
+      </c>
+      <c r="B40" s="32" t="inlineStr">
+        <is>
+          <t>Fábio Correia</t>
+        </is>
+      </c>
+      <c r="C40" s="35" t="inlineStr">
+        <is>
+          <t>Dr. Paulo Andrade</t>
+        </is>
+      </c>
+      <c r="D40" s="35" t="inlineStr">
+        <is>
+          <t>Exame cardiológico</t>
+        </is>
+      </c>
+      <c r="E40" s="32" t="inlineStr">
+        <is>
+          <t>MAPA + Holter</t>
+        </is>
+      </c>
+      <c r="F40" s="38" t="n">
+        <v>650</v>
+      </c>
+      <c r="G40" s="35" t="inlineStr">
+        <is>
+          <t>Apresentado</t>
+        </is>
+      </c>
       <c r="H40" s="37" t="n"/>
       <c r="I40" s="35" t="n"/>
       <c r="J40" s="32" t="n"/>
       <c r="K40" s="30">
         <f>IF(G40="","",IFERROR(INDEX(Config!$B$10:$B$14,MATCH(G40,Config!$A$10:$A$14,0)),0))</f>
-        <v/>
+        <v>0.3</v>
       </c>
       <c r="L40" s="26">
         <f>IF(OR(G40="",F40=""),"",F40*K40)</f>
-        <v/>
+        <v>195</v>
       </c>
       <c r="M40" s="29">
         <f>IF(OR(G40="",G40="Aprovado",G40="Recusado",G40="Sem retorno",A40=""),"",Config!$B$5-A40)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N40" s="29">
-        <f>IF(AND(OR(G40="Aprovado",G40="Recusado"),H40&lt;&gt;"",A40&lt;&gt;""),H40-A40,"")</f>
-        <v/>
-      </c>
-      <c r="O40" s="25">
+        <f>IF(AND(OR(G40="Aprovado",G40="Recusado"),H40&lt;&gt;"",A40&lt;&gt;"",H40&gt;=A40),H40-A40,"")</f>
+        <v/>
+      </c>
+      <c r="O40" s="25" t="str">
         <f>IF(G40="","",IF(OR(G40="Aprovado",G40="Recusado",G40="Sem retorno"),G40,IF(AND(M40&lt;&gt;"",M40&gt;Config!$B$7),"Parado","Ativo")))</f>
-        <v/>
+        <v>Ativo</v>
       </c>
       <c r="P40" s="39">
         <f>IF(A40="","",DATE(YEAR(A40),MONTH(A40),1))</f>
-        <v/>
+        <v>46266.0</v>
       </c>
       <c r="Q40" s="40">
         <f>IF(OR(G40="",O40="Aprovado",O40="Recusado",O40="Sem retorno"),0,IF(O40="Parado",2000,1000)+MIN(N(M40),500)+N(F40)/1000000-ROW()/100000)</f>
-        <v>0</v>
+        <v>1000.00025</v>
       </c>
     </row>
     <row r="41">
@@ -5420,7 +5450,7 @@
         <v/>
       </c>
       <c r="N41" s="29">
-        <f>IF(AND(OR(G41="Aprovado",G41="Recusado"),H41&lt;&gt;"",A41&lt;&gt;""),H41-A41,"")</f>
+        <f>IF(AND(OR(G41="Aprovado",G41="Recusado"),H41&lt;&gt;"",A41&lt;&gt;"",H41&gt;=A41),H41-A41,"")</f>
         <v/>
       </c>
       <c r="O41" s="25">
@@ -5460,7 +5490,7 @@
         <v/>
       </c>
       <c r="N42" s="29">
-        <f>IF(AND(OR(G42="Aprovado",G42="Recusado"),H42&lt;&gt;"",A42&lt;&gt;""),H42-A42,"")</f>
+        <f>IF(AND(OR(G42="Aprovado",G42="Recusado"),H42&lt;&gt;"",A42&lt;&gt;"",H42&gt;=A42),H42-A42,"")</f>
         <v/>
       </c>
       <c r="O42" s="25">
@@ -5500,7 +5530,7 @@
         <v/>
       </c>
       <c r="N43" s="29">
-        <f>IF(AND(OR(G43="Aprovado",G43="Recusado"),H43&lt;&gt;"",A43&lt;&gt;""),H43-A43,"")</f>
+        <f>IF(AND(OR(G43="Aprovado",G43="Recusado"),H43&lt;&gt;"",A43&lt;&gt;"",H43&gt;=A43),H43-A43,"")</f>
         <v/>
       </c>
       <c r="O43" s="25">
@@ -5540,7 +5570,7 @@
         <v/>
       </c>
       <c r="N44" s="29">
-        <f>IF(AND(OR(G44="Aprovado",G44="Recusado"),H44&lt;&gt;"",A44&lt;&gt;""),H44-A44,"")</f>
+        <f>IF(AND(OR(G44="Aprovado",G44="Recusado"),H44&lt;&gt;"",A44&lt;&gt;"",H44&gt;=A44),H44-A44,"")</f>
         <v/>
       </c>
       <c r="O44" s="25">
@@ -5580,7 +5610,7 @@
         <v/>
       </c>
       <c r="N45" s="29">
-        <f>IF(AND(OR(G45="Aprovado",G45="Recusado"),H45&lt;&gt;"",A45&lt;&gt;""),H45-A45,"")</f>
+        <f>IF(AND(OR(G45="Aprovado",G45="Recusado"),H45&lt;&gt;"",A45&lt;&gt;"",H45&gt;=A45),H45-A45,"")</f>
         <v/>
       </c>
       <c r="O45" s="25">
@@ -5620,7 +5650,7 @@
         <v/>
       </c>
       <c r="N46" s="29">
-        <f>IF(AND(OR(G46="Aprovado",G46="Recusado"),H46&lt;&gt;"",A46&lt;&gt;""),H46-A46,"")</f>
+        <f>IF(AND(OR(G46="Aprovado",G46="Recusado"),H46&lt;&gt;"",A46&lt;&gt;"",H46&gt;=A46),H46-A46,"")</f>
         <v/>
       </c>
       <c r="O46" s="25">
@@ -5660,7 +5690,7 @@
         <v/>
       </c>
       <c r="N47" s="29">
-        <f>IF(AND(OR(G47="Aprovado",G47="Recusado"),H47&lt;&gt;"",A47&lt;&gt;""),H47-A47,"")</f>
+        <f>IF(AND(OR(G47="Aprovado",G47="Recusado"),H47&lt;&gt;"",A47&lt;&gt;"",H47&gt;=A47),H47-A47,"")</f>
         <v/>
       </c>
       <c r="O47" s="25">
@@ -5700,7 +5730,7 @@
         <v/>
       </c>
       <c r="N48" s="29">
-        <f>IF(AND(OR(G48="Aprovado",G48="Recusado"),H48&lt;&gt;"",A48&lt;&gt;""),H48-A48,"")</f>
+        <f>IF(AND(OR(G48="Aprovado",G48="Recusado"),H48&lt;&gt;"",A48&lt;&gt;"",H48&gt;=A48),H48-A48,"")</f>
         <v/>
       </c>
       <c r="O48" s="25">
@@ -5740,7 +5770,7 @@
         <v/>
       </c>
       <c r="N49" s="29">
-        <f>IF(AND(OR(G49="Aprovado",G49="Recusado"),H49&lt;&gt;"",A49&lt;&gt;""),H49-A49,"")</f>
+        <f>IF(AND(OR(G49="Aprovado",G49="Recusado"),H49&lt;&gt;"",A49&lt;&gt;"",H49&gt;=A49),H49-A49,"")</f>
         <v/>
       </c>
       <c r="O49" s="25">
@@ -5780,7 +5810,7 @@
         <v/>
       </c>
       <c r="N50" s="29">
-        <f>IF(AND(OR(G50="Aprovado",G50="Recusado"),H50&lt;&gt;"",A50&lt;&gt;""),H50-A50,"")</f>
+        <f>IF(AND(OR(G50="Aprovado",G50="Recusado"),H50&lt;&gt;"",A50&lt;&gt;"",H50&gt;=A50),H50-A50,"")</f>
         <v/>
       </c>
       <c r="O50" s="25">
@@ -5820,7 +5850,7 @@
         <v/>
       </c>
       <c r="N51" s="29">
-        <f>IF(AND(OR(G51="Aprovado",G51="Recusado"),H51&lt;&gt;"",A51&lt;&gt;""),H51-A51,"")</f>
+        <f>IF(AND(OR(G51="Aprovado",G51="Recusado"),H51&lt;&gt;"",A51&lt;&gt;"",H51&gt;=A51),H51-A51,"")</f>
         <v/>
       </c>
       <c r="O51" s="25">
@@ -5860,7 +5890,7 @@
         <v/>
       </c>
       <c r="N52" s="29">
-        <f>IF(AND(OR(G52="Aprovado",G52="Recusado"),H52&lt;&gt;"",A52&lt;&gt;""),H52-A52,"")</f>
+        <f>IF(AND(OR(G52="Aprovado",G52="Recusado"),H52&lt;&gt;"",A52&lt;&gt;"",H52&gt;=A52),H52-A52,"")</f>
         <v/>
       </c>
       <c r="O52" s="25">
@@ -5900,7 +5930,7 @@
         <v/>
       </c>
       <c r="N53" s="29">
-        <f>IF(AND(OR(G53="Aprovado",G53="Recusado"),H53&lt;&gt;"",A53&lt;&gt;""),H53-A53,"")</f>
+        <f>IF(AND(OR(G53="Aprovado",G53="Recusado"),H53&lt;&gt;"",A53&lt;&gt;"",H53&gt;=A53),H53-A53,"")</f>
         <v/>
       </c>
       <c r="O53" s="25">
@@ -5940,7 +5970,7 @@
         <v/>
       </c>
       <c r="N54" s="29">
-        <f>IF(AND(OR(G54="Aprovado",G54="Recusado"),H54&lt;&gt;"",A54&lt;&gt;""),H54-A54,"")</f>
+        <f>IF(AND(OR(G54="Aprovado",G54="Recusado"),H54&lt;&gt;"",A54&lt;&gt;"",H54&gt;=A54),H54-A54,"")</f>
         <v/>
       </c>
       <c r="O54" s="25">
@@ -5980,7 +6010,7 @@
         <v/>
       </c>
       <c r="N55" s="29">
-        <f>IF(AND(OR(G55="Aprovado",G55="Recusado"),H55&lt;&gt;"",A55&lt;&gt;""),H55-A55,"")</f>
+        <f>IF(AND(OR(G55="Aprovado",G55="Recusado"),H55&lt;&gt;"",A55&lt;&gt;"",H55&gt;=A55),H55-A55,"")</f>
         <v/>
       </c>
       <c r="O55" s="25">
@@ -6020,7 +6050,7 @@
         <v/>
       </c>
       <c r="N56" s="29">
-        <f>IF(AND(OR(G56="Aprovado",G56="Recusado"),H56&lt;&gt;"",A56&lt;&gt;""),H56-A56,"")</f>
+        <f>IF(AND(OR(G56="Aprovado",G56="Recusado"),H56&lt;&gt;"",A56&lt;&gt;"",H56&gt;=A56),H56-A56,"")</f>
         <v/>
       </c>
       <c r="O56" s="25">
@@ -6060,7 +6090,7 @@
         <v/>
       </c>
       <c r="N57" s="29">
-        <f>IF(AND(OR(G57="Aprovado",G57="Recusado"),H57&lt;&gt;"",A57&lt;&gt;""),H57-A57,"")</f>
+        <f>IF(AND(OR(G57="Aprovado",G57="Recusado"),H57&lt;&gt;"",A57&lt;&gt;"",H57&gt;=A57),H57-A57,"")</f>
         <v/>
       </c>
       <c r="O57" s="25">
@@ -6100,7 +6130,7 @@
         <v/>
       </c>
       <c r="N58" s="29">
-        <f>IF(AND(OR(G58="Aprovado",G58="Recusado"),H58&lt;&gt;"",A58&lt;&gt;""),H58-A58,"")</f>
+        <f>IF(AND(OR(G58="Aprovado",G58="Recusado"),H58&lt;&gt;"",A58&lt;&gt;"",H58&gt;=A58),H58-A58,"")</f>
         <v/>
       </c>
       <c r="O58" s="25">
@@ -6140,7 +6170,7 @@
         <v/>
       </c>
       <c r="N59" s="29">
-        <f>IF(AND(OR(G59="Aprovado",G59="Recusado"),H59&lt;&gt;"",A59&lt;&gt;""),H59-A59,"")</f>
+        <f>IF(AND(OR(G59="Aprovado",G59="Recusado"),H59&lt;&gt;"",A59&lt;&gt;"",H59&gt;=A59),H59-A59,"")</f>
         <v/>
       </c>
       <c r="O59" s="25">
@@ -6180,7 +6210,7 @@
         <v/>
       </c>
       <c r="N60" s="29">
-        <f>IF(AND(OR(G60="Aprovado",G60="Recusado"),H60&lt;&gt;"",A60&lt;&gt;""),H60-A60,"")</f>
+        <f>IF(AND(OR(G60="Aprovado",G60="Recusado"),H60&lt;&gt;"",A60&lt;&gt;"",H60&gt;=A60),H60-A60,"")</f>
         <v/>
       </c>
       <c r="O60" s="25">
@@ -6220,7 +6250,7 @@
         <v/>
       </c>
       <c r="N61" s="29">
-        <f>IF(AND(OR(G61="Aprovado",G61="Recusado"),H61&lt;&gt;"",A61&lt;&gt;""),H61-A61,"")</f>
+        <f>IF(AND(OR(G61="Aprovado",G61="Recusado"),H61&lt;&gt;"",A61&lt;&gt;"",H61&gt;=A61),H61-A61,"")</f>
         <v/>
       </c>
       <c r="O61" s="25">
@@ -6260,7 +6290,7 @@
         <v/>
       </c>
       <c r="N62" s="29">
-        <f>IF(AND(OR(G62="Aprovado",G62="Recusado"),H62&lt;&gt;"",A62&lt;&gt;""),H62-A62,"")</f>
+        <f>IF(AND(OR(G62="Aprovado",G62="Recusado"),H62&lt;&gt;"",A62&lt;&gt;"",H62&gt;=A62),H62-A62,"")</f>
         <v/>
       </c>
       <c r="O62" s="25">
@@ -6300,7 +6330,7 @@
         <v/>
       </c>
       <c r="N63" s="29">
-        <f>IF(AND(OR(G63="Aprovado",G63="Recusado"),H63&lt;&gt;"",A63&lt;&gt;""),H63-A63,"")</f>
+        <f>IF(AND(OR(G63="Aprovado",G63="Recusado"),H63&lt;&gt;"",A63&lt;&gt;"",H63&gt;=A63),H63-A63,"")</f>
         <v/>
       </c>
       <c r="O63" s="25">
@@ -6340,7 +6370,7 @@
         <v/>
       </c>
       <c r="N64" s="29">
-        <f>IF(AND(OR(G64="Aprovado",G64="Recusado"),H64&lt;&gt;"",A64&lt;&gt;""),H64-A64,"")</f>
+        <f>IF(AND(OR(G64="Aprovado",G64="Recusado"),H64&lt;&gt;"",A64&lt;&gt;"",H64&gt;=A64),H64-A64,"")</f>
         <v/>
       </c>
       <c r="O64" s="25">
@@ -6380,7 +6410,7 @@
         <v/>
       </c>
       <c r="N65" s="29">
-        <f>IF(AND(OR(G65="Aprovado",G65="Recusado"),H65&lt;&gt;"",A65&lt;&gt;""),H65-A65,"")</f>
+        <f>IF(AND(OR(G65="Aprovado",G65="Recusado"),H65&lt;&gt;"",A65&lt;&gt;"",H65&gt;=A65),H65-A65,"")</f>
         <v/>
       </c>
       <c r="O65" s="25">
@@ -6420,7 +6450,7 @@
         <v/>
       </c>
       <c r="N66" s="29">
-        <f>IF(AND(OR(G66="Aprovado",G66="Recusado"),H66&lt;&gt;"",A66&lt;&gt;""),H66-A66,"")</f>
+        <f>IF(AND(OR(G66="Aprovado",G66="Recusado"),H66&lt;&gt;"",A66&lt;&gt;"",H66&gt;=A66),H66-A66,"")</f>
         <v/>
       </c>
       <c r="O66" s="25">
@@ -6460,7 +6490,7 @@
         <v/>
       </c>
       <c r="N67" s="29">
-        <f>IF(AND(OR(G67="Aprovado",G67="Recusado"),H67&lt;&gt;"",A67&lt;&gt;""),H67-A67,"")</f>
+        <f>IF(AND(OR(G67="Aprovado",G67="Recusado"),H67&lt;&gt;"",A67&lt;&gt;"",H67&gt;=A67),H67-A67,"")</f>
         <v/>
       </c>
       <c r="O67" s="25">
@@ -6500,7 +6530,7 @@
         <v/>
       </c>
       <c r="N68" s="29">
-        <f>IF(AND(OR(G68="Aprovado",G68="Recusado"),H68&lt;&gt;"",A68&lt;&gt;""),H68-A68,"")</f>
+        <f>IF(AND(OR(G68="Aprovado",G68="Recusado"),H68&lt;&gt;"",A68&lt;&gt;"",H68&gt;=A68),H68-A68,"")</f>
         <v/>
       </c>
       <c r="O68" s="25">
@@ -6540,7 +6570,7 @@
         <v/>
       </c>
       <c r="N69" s="29">
-        <f>IF(AND(OR(G69="Aprovado",G69="Recusado"),H69&lt;&gt;"",A69&lt;&gt;""),H69-A69,"")</f>
+        <f>IF(AND(OR(G69="Aprovado",G69="Recusado"),H69&lt;&gt;"",A69&lt;&gt;"",H69&gt;=A69),H69-A69,"")</f>
         <v/>
       </c>
       <c r="O69" s="25">
@@ -6580,7 +6610,7 @@
         <v/>
       </c>
       <c r="N70" s="29">
-        <f>IF(AND(OR(G70="Aprovado",G70="Recusado"),H70&lt;&gt;"",A70&lt;&gt;""),H70-A70,"")</f>
+        <f>IF(AND(OR(G70="Aprovado",G70="Recusado"),H70&lt;&gt;"",A70&lt;&gt;"",H70&gt;=A70),H70-A70,"")</f>
         <v/>
       </c>
       <c r="O70" s="25">
@@ -6620,7 +6650,7 @@
         <v/>
       </c>
       <c r="N71" s="29">
-        <f>IF(AND(OR(G71="Aprovado",G71="Recusado"),H71&lt;&gt;"",A71&lt;&gt;""),H71-A71,"")</f>
+        <f>IF(AND(OR(G71="Aprovado",G71="Recusado"),H71&lt;&gt;"",A71&lt;&gt;"",H71&gt;=A71),H71-A71,"")</f>
         <v/>
       </c>
       <c r="O71" s="25">
@@ -6660,7 +6690,7 @@
         <v/>
       </c>
       <c r="N72" s="29">
-        <f>IF(AND(OR(G72="Aprovado",G72="Recusado"),H72&lt;&gt;"",A72&lt;&gt;""),H72-A72,"")</f>
+        <f>IF(AND(OR(G72="Aprovado",G72="Recusado"),H72&lt;&gt;"",A72&lt;&gt;"",H72&gt;=A72),H72-A72,"")</f>
         <v/>
       </c>
       <c r="O72" s="25">
@@ -6700,7 +6730,7 @@
         <v/>
       </c>
       <c r="N73" s="29">
-        <f>IF(AND(OR(G73="Aprovado",G73="Recusado"),H73&lt;&gt;"",A73&lt;&gt;""),H73-A73,"")</f>
+        <f>IF(AND(OR(G73="Aprovado",G73="Recusado"),H73&lt;&gt;"",A73&lt;&gt;"",H73&gt;=A73),H73-A73,"")</f>
         <v/>
       </c>
       <c r="O73" s="25">
@@ -6740,7 +6770,7 @@
         <v/>
       </c>
       <c r="N74" s="29">
-        <f>IF(AND(OR(G74="Aprovado",G74="Recusado"),H74&lt;&gt;"",A74&lt;&gt;""),H74-A74,"")</f>
+        <f>IF(AND(OR(G74="Aprovado",G74="Recusado"),H74&lt;&gt;"",A74&lt;&gt;"",H74&gt;=A74),H74-A74,"")</f>
         <v/>
       </c>
       <c r="O74" s="25">
@@ -6780,7 +6810,7 @@
         <v/>
       </c>
       <c r="N75" s="29">
-        <f>IF(AND(OR(G75="Aprovado",G75="Recusado"),H75&lt;&gt;"",A75&lt;&gt;""),H75-A75,"")</f>
+        <f>IF(AND(OR(G75="Aprovado",G75="Recusado"),H75&lt;&gt;"",A75&lt;&gt;"",H75&gt;=A75),H75-A75,"")</f>
         <v/>
       </c>
       <c r="O75" s="25">
@@ -6820,7 +6850,7 @@
         <v/>
       </c>
       <c r="N76" s="29">
-        <f>IF(AND(OR(G76="Aprovado",G76="Recusado"),H76&lt;&gt;"",A76&lt;&gt;""),H76-A76,"")</f>
+        <f>IF(AND(OR(G76="Aprovado",G76="Recusado"),H76&lt;&gt;"",A76&lt;&gt;"",H76&gt;=A76),H76-A76,"")</f>
         <v/>
       </c>
       <c r="O76" s="25">
@@ -6860,7 +6890,7 @@
         <v/>
       </c>
       <c r="N77" s="29">
-        <f>IF(AND(OR(G77="Aprovado",G77="Recusado"),H77&lt;&gt;"",A77&lt;&gt;""),H77-A77,"")</f>
+        <f>IF(AND(OR(G77="Aprovado",G77="Recusado"),H77&lt;&gt;"",A77&lt;&gt;"",H77&gt;=A77),H77-A77,"")</f>
         <v/>
       </c>
       <c r="O77" s="25">
@@ -6900,7 +6930,7 @@
         <v/>
       </c>
       <c r="N78" s="29">
-        <f>IF(AND(OR(G78="Aprovado",G78="Recusado"),H78&lt;&gt;"",A78&lt;&gt;""),H78-A78,"")</f>
+        <f>IF(AND(OR(G78="Aprovado",G78="Recusado"),H78&lt;&gt;"",A78&lt;&gt;"",H78&gt;=A78),H78-A78,"")</f>
         <v/>
       </c>
       <c r="O78" s="25">
@@ -6940,7 +6970,7 @@
         <v/>
       </c>
       <c r="N79" s="29">
-        <f>IF(AND(OR(G79="Aprovado",G79="Recusado"),H79&lt;&gt;"",A79&lt;&gt;""),H79-A79,"")</f>
+        <f>IF(AND(OR(G79="Aprovado",G79="Recusado"),H79&lt;&gt;"",A79&lt;&gt;"",H79&gt;=A79),H79-A79,"")</f>
         <v/>
       </c>
       <c r="O79" s="25">
@@ -6980,7 +7010,7 @@
         <v/>
       </c>
       <c r="N80" s="29">
-        <f>IF(AND(OR(G80="Aprovado",G80="Recusado"),H80&lt;&gt;"",A80&lt;&gt;""),H80-A80,"")</f>
+        <f>IF(AND(OR(G80="Aprovado",G80="Recusado"),H80&lt;&gt;"",A80&lt;&gt;"",H80&gt;=A80),H80-A80,"")</f>
         <v/>
       </c>
       <c r="O80" s="25">
@@ -7020,7 +7050,7 @@
         <v/>
       </c>
       <c r="N81" s="29">
-        <f>IF(AND(OR(G81="Aprovado",G81="Recusado"),H81&lt;&gt;"",A81&lt;&gt;""),H81-A81,"")</f>
+        <f>IF(AND(OR(G81="Aprovado",G81="Recusado"),H81&lt;&gt;"",A81&lt;&gt;"",H81&gt;=A81),H81-A81,"")</f>
         <v/>
       </c>
       <c r="O81" s="25">
@@ -7060,7 +7090,7 @@
         <v/>
       </c>
       <c r="N82" s="29">
-        <f>IF(AND(OR(G82="Aprovado",G82="Recusado"),H82&lt;&gt;"",A82&lt;&gt;""),H82-A82,"")</f>
+        <f>IF(AND(OR(G82="Aprovado",G82="Recusado"),H82&lt;&gt;"",A82&lt;&gt;"",H82&gt;=A82),H82-A82,"")</f>
         <v/>
       </c>
       <c r="O82" s="25">
@@ -7100,7 +7130,7 @@
         <v/>
       </c>
       <c r="N83" s="29">
-        <f>IF(AND(OR(G83="Aprovado",G83="Recusado"),H83&lt;&gt;"",A83&lt;&gt;""),H83-A83,"")</f>
+        <f>IF(AND(OR(G83="Aprovado",G83="Recusado"),H83&lt;&gt;"",A83&lt;&gt;"",H83&gt;=A83),H83-A83,"")</f>
         <v/>
       </c>
       <c r="O83" s="25">
@@ -7140,7 +7170,7 @@
         <v/>
       </c>
       <c r="N84" s="29">
-        <f>IF(AND(OR(G84="Aprovado",G84="Recusado"),H84&lt;&gt;"",A84&lt;&gt;""),H84-A84,"")</f>
+        <f>IF(AND(OR(G84="Aprovado",G84="Recusado"),H84&lt;&gt;"",A84&lt;&gt;"",H84&gt;=A84),H84-A84,"")</f>
         <v/>
       </c>
       <c r="O84" s="25">
@@ -7180,7 +7210,7 @@
         <v/>
       </c>
       <c r="N85" s="29">
-        <f>IF(AND(OR(G85="Aprovado",G85="Recusado"),H85&lt;&gt;"",A85&lt;&gt;""),H85-A85,"")</f>
+        <f>IF(AND(OR(G85="Aprovado",G85="Recusado"),H85&lt;&gt;"",A85&lt;&gt;"",H85&gt;=A85),H85-A85,"")</f>
         <v/>
       </c>
       <c r="O85" s="25">
@@ -7220,7 +7250,7 @@
         <v/>
       </c>
       <c r="N86" s="29">
-        <f>IF(AND(OR(G86="Aprovado",G86="Recusado"),H86&lt;&gt;"",A86&lt;&gt;""),H86-A86,"")</f>
+        <f>IF(AND(OR(G86="Aprovado",G86="Recusado"),H86&lt;&gt;"",A86&lt;&gt;"",H86&gt;=A86),H86-A86,"")</f>
         <v/>
       </c>
       <c r="O86" s="25">
@@ -7260,7 +7290,7 @@
         <v/>
       </c>
       <c r="N87" s="29">
-        <f>IF(AND(OR(G87="Aprovado",G87="Recusado"),H87&lt;&gt;"",A87&lt;&gt;""),H87-A87,"")</f>
+        <f>IF(AND(OR(G87="Aprovado",G87="Recusado"),H87&lt;&gt;"",A87&lt;&gt;"",H87&gt;=A87),H87-A87,"")</f>
         <v/>
       </c>
       <c r="O87" s="25">
@@ -7300,7 +7330,7 @@
         <v/>
       </c>
       <c r="N88" s="29">
-        <f>IF(AND(OR(G88="Aprovado",G88="Recusado"),H88&lt;&gt;"",A88&lt;&gt;""),H88-A88,"")</f>
+        <f>IF(AND(OR(G88="Aprovado",G88="Recusado"),H88&lt;&gt;"",A88&lt;&gt;"",H88&gt;=A88),H88-A88,"")</f>
         <v/>
       </c>
       <c r="O88" s="25">
@@ -7340,7 +7370,7 @@
         <v/>
       </c>
       <c r="N89" s="29">
-        <f>IF(AND(OR(G89="Aprovado",G89="Recusado"),H89&lt;&gt;"",A89&lt;&gt;""),H89-A89,"")</f>
+        <f>IF(AND(OR(G89="Aprovado",G89="Recusado"),H89&lt;&gt;"",A89&lt;&gt;"",H89&gt;=A89),H89-A89,"")</f>
         <v/>
       </c>
       <c r="O89" s="25">
@@ -7380,7 +7410,7 @@
         <v/>
       </c>
       <c r="N90" s="29">
-        <f>IF(AND(OR(G90="Aprovado",G90="Recusado"),H90&lt;&gt;"",A90&lt;&gt;""),H90-A90,"")</f>
+        <f>IF(AND(OR(G90="Aprovado",G90="Recusado"),H90&lt;&gt;"",A90&lt;&gt;"",H90&gt;=A90),H90-A90,"")</f>
         <v/>
       </c>
       <c r="O90" s="25">
@@ -7420,7 +7450,7 @@
         <v/>
       </c>
       <c r="N91" s="29">
-        <f>IF(AND(OR(G91="Aprovado",G91="Recusado"),H91&lt;&gt;"",A91&lt;&gt;""),H91-A91,"")</f>
+        <f>IF(AND(OR(G91="Aprovado",G91="Recusado"),H91&lt;&gt;"",A91&lt;&gt;"",H91&gt;=A91),H91-A91,"")</f>
         <v/>
       </c>
       <c r="O91" s="25">
@@ -7460,7 +7490,7 @@
         <v/>
       </c>
       <c r="N92" s="29">
-        <f>IF(AND(OR(G92="Aprovado",G92="Recusado"),H92&lt;&gt;"",A92&lt;&gt;""),H92-A92,"")</f>
+        <f>IF(AND(OR(G92="Aprovado",G92="Recusado"),H92&lt;&gt;"",A92&lt;&gt;"",H92&gt;=A92),H92-A92,"")</f>
         <v/>
       </c>
       <c r="O92" s="25">
@@ -7500,7 +7530,7 @@
         <v/>
       </c>
       <c r="N93" s="29">
-        <f>IF(AND(OR(G93="Aprovado",G93="Recusado"),H93&lt;&gt;"",A93&lt;&gt;""),H93-A93,"")</f>
+        <f>IF(AND(OR(G93="Aprovado",G93="Recusado"),H93&lt;&gt;"",A93&lt;&gt;"",H93&gt;=A93),H93-A93,"")</f>
         <v/>
       </c>
       <c r="O93" s="25">
@@ -7540,7 +7570,7 @@
         <v/>
       </c>
       <c r="N94" s="29">
-        <f>IF(AND(OR(G94="Aprovado",G94="Recusado"),H94&lt;&gt;"",A94&lt;&gt;""),H94-A94,"")</f>
+        <f>IF(AND(OR(G94="Aprovado",G94="Recusado"),H94&lt;&gt;"",A94&lt;&gt;"",H94&gt;=A94),H94-A94,"")</f>
         <v/>
       </c>
       <c r="O94" s="25">
@@ -7580,7 +7610,7 @@
         <v/>
       </c>
       <c r="N95" s="29">
-        <f>IF(AND(OR(G95="Aprovado",G95="Recusado"),H95&lt;&gt;"",A95&lt;&gt;""),H95-A95,"")</f>
+        <f>IF(AND(OR(G95="Aprovado",G95="Recusado"),H95&lt;&gt;"",A95&lt;&gt;"",H95&gt;=A95),H95-A95,"")</f>
         <v/>
       </c>
       <c r="O95" s="25">
@@ -7620,7 +7650,7 @@
         <v/>
       </c>
       <c r="N96" s="29">
-        <f>IF(AND(OR(G96="Aprovado",G96="Recusado"),H96&lt;&gt;"",A96&lt;&gt;""),H96-A96,"")</f>
+        <f>IF(AND(OR(G96="Aprovado",G96="Recusado"),H96&lt;&gt;"",A96&lt;&gt;"",H96&gt;=A96),H96-A96,"")</f>
         <v/>
       </c>
       <c r="O96" s="25">
@@ -7660,7 +7690,7 @@
         <v/>
       </c>
       <c r="N97" s="29">
-        <f>IF(AND(OR(G97="Aprovado",G97="Recusado"),H97&lt;&gt;"",A97&lt;&gt;""),H97-A97,"")</f>
+        <f>IF(AND(OR(G97="Aprovado",G97="Recusado"),H97&lt;&gt;"",A97&lt;&gt;"",H97&gt;=A97),H97-A97,"")</f>
         <v/>
       </c>
       <c r="O97" s="25">
@@ -7700,7 +7730,7 @@
         <v/>
       </c>
       <c r="N98" s="29">
-        <f>IF(AND(OR(G98="Aprovado",G98="Recusado"),H98&lt;&gt;"",A98&lt;&gt;""),H98-A98,"")</f>
+        <f>IF(AND(OR(G98="Aprovado",G98="Recusado"),H98&lt;&gt;"",A98&lt;&gt;"",H98&gt;=A98),H98-A98,"")</f>
         <v/>
       </c>
       <c r="O98" s="25">
@@ -7740,7 +7770,7 @@
         <v/>
       </c>
       <c r="N99" s="29">
-        <f>IF(AND(OR(G99="Aprovado",G99="Recusado"),H99&lt;&gt;"",A99&lt;&gt;""),H99-A99,"")</f>
+        <f>IF(AND(OR(G99="Aprovado",G99="Recusado"),H99&lt;&gt;"",A99&lt;&gt;"",H99&gt;=A99),H99-A99,"")</f>
         <v/>
       </c>
       <c r="O99" s="25">
@@ -7780,7 +7810,7 @@
         <v/>
       </c>
       <c r="N100" s="29">
-        <f>IF(AND(OR(G100="Aprovado",G100="Recusado"),H100&lt;&gt;"",A100&lt;&gt;""),H100-A100,"")</f>
+        <f>IF(AND(OR(G100="Aprovado",G100="Recusado"),H100&lt;&gt;"",A100&lt;&gt;"",H100&gt;=A100),H100-A100,"")</f>
         <v/>
       </c>
       <c r="O100" s="25">
@@ -7820,7 +7850,7 @@
         <v/>
       </c>
       <c r="N101" s="29">
-        <f>IF(AND(OR(G101="Aprovado",G101="Recusado"),H101&lt;&gt;"",A101&lt;&gt;""),H101-A101,"")</f>
+        <f>IF(AND(OR(G101="Aprovado",G101="Recusado"),H101&lt;&gt;"",A101&lt;&gt;"",H101&gt;=A101),H101-A101,"")</f>
         <v/>
       </c>
       <c r="O101" s="25">
@@ -7860,7 +7890,7 @@
         <v/>
       </c>
       <c r="N102" s="29">
-        <f>IF(AND(OR(G102="Aprovado",G102="Recusado"),H102&lt;&gt;"",A102&lt;&gt;""),H102-A102,"")</f>
+        <f>IF(AND(OR(G102="Aprovado",G102="Recusado"),H102&lt;&gt;"",A102&lt;&gt;"",H102&gt;=A102),H102-A102,"")</f>
         <v/>
       </c>
       <c r="O102" s="25">
@@ -7900,7 +7930,7 @@
         <v/>
       </c>
       <c r="N103" s="29">
-        <f>IF(AND(OR(G103="Aprovado",G103="Recusado"),H103&lt;&gt;"",A103&lt;&gt;""),H103-A103,"")</f>
+        <f>IF(AND(OR(G103="Aprovado",G103="Recusado"),H103&lt;&gt;"",A103&lt;&gt;"",H103&gt;=A103),H103-A103,"")</f>
         <v/>
       </c>
       <c r="O103" s="25">
@@ -7940,7 +7970,7 @@
         <v/>
       </c>
       <c r="N104" s="29">
-        <f>IF(AND(OR(G104="Aprovado",G104="Recusado"),H104&lt;&gt;"",A104&lt;&gt;""),H104-A104,"")</f>
+        <f>IF(AND(OR(G104="Aprovado",G104="Recusado"),H104&lt;&gt;"",A104&lt;&gt;"",H104&gt;=A104),H104-A104,"")</f>
         <v/>
       </c>
       <c r="O104" s="25">
@@ -7980,7 +8010,7 @@
         <v/>
       </c>
       <c r="N105" s="29">
-        <f>IF(AND(OR(G105="Aprovado",G105="Recusado"),H105&lt;&gt;"",A105&lt;&gt;""),H105-A105,"")</f>
+        <f>IF(AND(OR(G105="Aprovado",G105="Recusado"),H105&lt;&gt;"",A105&lt;&gt;"",H105&gt;=A105),H105-A105,"")</f>
         <v/>
       </c>
       <c r="O105" s="25">
@@ -8020,7 +8050,7 @@
         <v/>
       </c>
       <c r="N106" s="29">
-        <f>IF(AND(OR(G106="Aprovado",G106="Recusado"),H106&lt;&gt;"",A106&lt;&gt;""),H106-A106,"")</f>
+        <f>IF(AND(OR(G106="Aprovado",G106="Recusado"),H106&lt;&gt;"",A106&lt;&gt;"",H106&gt;=A106),H106-A106,"")</f>
         <v/>
       </c>
       <c r="O106" s="25">
@@ -8060,7 +8090,7 @@
         <v/>
       </c>
       <c r="N107" s="29">
-        <f>IF(AND(OR(G107="Aprovado",G107="Recusado"),H107&lt;&gt;"",A107&lt;&gt;""),H107-A107,"")</f>
+        <f>IF(AND(OR(G107="Aprovado",G107="Recusado"),H107&lt;&gt;"",A107&lt;&gt;"",H107&gt;=A107),H107-A107,"")</f>
         <v/>
       </c>
       <c r="O107" s="25">
@@ -8100,7 +8130,7 @@
         <v/>
       </c>
       <c r="N108" s="29">
-        <f>IF(AND(OR(G108="Aprovado",G108="Recusado"),H108&lt;&gt;"",A108&lt;&gt;""),H108-A108,"")</f>
+        <f>IF(AND(OR(G108="Aprovado",G108="Recusado"),H108&lt;&gt;"",A108&lt;&gt;"",H108&gt;=A108),H108-A108,"")</f>
         <v/>
       </c>
       <c r="O108" s="25">
@@ -8140,7 +8170,7 @@
         <v/>
       </c>
       <c r="N109" s="29">
-        <f>IF(AND(OR(G109="Aprovado",G109="Recusado"),H109&lt;&gt;"",A109&lt;&gt;""),H109-A109,"")</f>
+        <f>IF(AND(OR(G109="Aprovado",G109="Recusado"),H109&lt;&gt;"",A109&lt;&gt;"",H109&gt;=A109),H109-A109,"")</f>
         <v/>
       </c>
       <c r="O109" s="25">
@@ -8180,7 +8210,7 @@
         <v/>
       </c>
       <c r="N110" s="29">
-        <f>IF(AND(OR(G110="Aprovado",G110="Recusado"),H110&lt;&gt;"",A110&lt;&gt;""),H110-A110,"")</f>
+        <f>IF(AND(OR(G110="Aprovado",G110="Recusado"),H110&lt;&gt;"",A110&lt;&gt;"",H110&gt;=A110),H110-A110,"")</f>
         <v/>
       </c>
       <c r="O110" s="25">
@@ -8220,7 +8250,7 @@
         <v/>
       </c>
       <c r="N111" s="29">
-        <f>IF(AND(OR(G111="Aprovado",G111="Recusado"),H111&lt;&gt;"",A111&lt;&gt;""),H111-A111,"")</f>
+        <f>IF(AND(OR(G111="Aprovado",G111="Recusado"),H111&lt;&gt;"",A111&lt;&gt;"",H111&gt;=A111),H111-A111,"")</f>
         <v/>
       </c>
       <c r="O111" s="25">
@@ -8260,7 +8290,7 @@
         <v/>
       </c>
       <c r="N112" s="29">
-        <f>IF(AND(OR(G112="Aprovado",G112="Recusado"),H112&lt;&gt;"",A112&lt;&gt;""),H112-A112,"")</f>
+        <f>IF(AND(OR(G112="Aprovado",G112="Recusado"),H112&lt;&gt;"",A112&lt;&gt;"",H112&gt;=A112),H112-A112,"")</f>
         <v/>
       </c>
       <c r="O112" s="25">
@@ -8300,7 +8330,7 @@
         <v/>
       </c>
       <c r="N113" s="29">
-        <f>IF(AND(OR(G113="Aprovado",G113="Recusado"),H113&lt;&gt;"",A113&lt;&gt;""),H113-A113,"")</f>
+        <f>IF(AND(OR(G113="Aprovado",G113="Recusado"),H113&lt;&gt;"",A113&lt;&gt;"",H113&gt;=A113),H113-A113,"")</f>
         <v/>
       </c>
       <c r="O113" s="25">
@@ -8340,7 +8370,7 @@
         <v/>
       </c>
       <c r="N114" s="29">
-        <f>IF(AND(OR(G114="Aprovado",G114="Recusado"),H114&lt;&gt;"",A114&lt;&gt;""),H114-A114,"")</f>
+        <f>IF(AND(OR(G114="Aprovado",G114="Recusado"),H114&lt;&gt;"",A114&lt;&gt;"",H114&gt;=A114),H114-A114,"")</f>
         <v/>
       </c>
       <c r="O114" s="25">
@@ -8380,7 +8410,7 @@
         <v/>
       </c>
       <c r="N115" s="29">
-        <f>IF(AND(OR(G115="Aprovado",G115="Recusado"),H115&lt;&gt;"",A115&lt;&gt;""),H115-A115,"")</f>
+        <f>IF(AND(OR(G115="Aprovado",G115="Recusado"),H115&lt;&gt;"",A115&lt;&gt;"",H115&gt;=A115),H115-A115,"")</f>
         <v/>
       </c>
       <c r="O115" s="25">
@@ -8420,7 +8450,7 @@
         <v/>
       </c>
       <c r="N116" s="29">
-        <f>IF(AND(OR(G116="Aprovado",G116="Recusado"),H116&lt;&gt;"",A116&lt;&gt;""),H116-A116,"")</f>
+        <f>IF(AND(OR(G116="Aprovado",G116="Recusado"),H116&lt;&gt;"",A116&lt;&gt;"",H116&gt;=A116),H116-A116,"")</f>
         <v/>
       </c>
       <c r="O116" s="25">
@@ -8460,7 +8490,7 @@
         <v/>
       </c>
       <c r="N117" s="29">
-        <f>IF(AND(OR(G117="Aprovado",G117="Recusado"),H117&lt;&gt;"",A117&lt;&gt;""),H117-A117,"")</f>
+        <f>IF(AND(OR(G117="Aprovado",G117="Recusado"),H117&lt;&gt;"",A117&lt;&gt;"",H117&gt;=A117),H117-A117,"")</f>
         <v/>
       </c>
       <c r="O117" s="25">
@@ -8500,7 +8530,7 @@
         <v/>
       </c>
       <c r="N118" s="29">
-        <f>IF(AND(OR(G118="Aprovado",G118="Recusado"),H118&lt;&gt;"",A118&lt;&gt;""),H118-A118,"")</f>
+        <f>IF(AND(OR(G118="Aprovado",G118="Recusado"),H118&lt;&gt;"",A118&lt;&gt;"",H118&gt;=A118),H118-A118,"")</f>
         <v/>
       </c>
       <c r="O118" s="25">
@@ -8540,7 +8570,7 @@
         <v/>
       </c>
       <c r="N119" s="29">
-        <f>IF(AND(OR(G119="Aprovado",G119="Recusado"),H119&lt;&gt;"",A119&lt;&gt;""),H119-A119,"")</f>
+        <f>IF(AND(OR(G119="Aprovado",G119="Recusado"),H119&lt;&gt;"",A119&lt;&gt;"",H119&gt;=A119),H119-A119,"")</f>
         <v/>
       </c>
       <c r="O119" s="25">
@@ -8580,7 +8610,7 @@
         <v/>
       </c>
       <c r="N120" s="29">
-        <f>IF(AND(OR(G120="Aprovado",G120="Recusado"),H120&lt;&gt;"",A120&lt;&gt;""),H120-A120,"")</f>
+        <f>IF(AND(OR(G120="Aprovado",G120="Recusado"),H120&lt;&gt;"",A120&lt;&gt;"",H120&gt;=A120),H120-A120,"")</f>
         <v/>
       </c>
       <c r="O120" s="25">
@@ -8620,7 +8650,7 @@
         <v/>
       </c>
       <c r="N121" s="29">
-        <f>IF(AND(OR(G121="Aprovado",G121="Recusado"),H121&lt;&gt;"",A121&lt;&gt;""),H121-A121,"")</f>
+        <f>IF(AND(OR(G121="Aprovado",G121="Recusado"),H121&lt;&gt;"",A121&lt;&gt;"",H121&gt;=A121),H121-A121,"")</f>
         <v/>
       </c>
       <c r="O121" s="25">
@@ -8660,7 +8690,7 @@
         <v/>
       </c>
       <c r="N122" s="29">
-        <f>IF(AND(OR(G122="Aprovado",G122="Recusado"),H122&lt;&gt;"",A122&lt;&gt;""),H122-A122,"")</f>
+        <f>IF(AND(OR(G122="Aprovado",G122="Recusado"),H122&lt;&gt;"",A122&lt;&gt;"",H122&gt;=A122),H122-A122,"")</f>
         <v/>
       </c>
       <c r="O122" s="25">
@@ -8700,7 +8730,7 @@
         <v/>
       </c>
       <c r="N123" s="29">
-        <f>IF(AND(OR(G123="Aprovado",G123="Recusado"),H123&lt;&gt;"",A123&lt;&gt;""),H123-A123,"")</f>
+        <f>IF(AND(OR(G123="Aprovado",G123="Recusado"),H123&lt;&gt;"",A123&lt;&gt;"",H123&gt;=A123),H123-A123,"")</f>
         <v/>
       </c>
       <c r="O123" s="25">
@@ -8740,7 +8770,7 @@
         <v/>
       </c>
       <c r="N124" s="29">
-        <f>IF(AND(OR(G124="Aprovado",G124="Recusado"),H124&lt;&gt;"",A124&lt;&gt;""),H124-A124,"")</f>
+        <f>IF(AND(OR(G124="Aprovado",G124="Recusado"),H124&lt;&gt;"",A124&lt;&gt;"",H124&gt;=A124),H124-A124,"")</f>
         <v/>
       </c>
       <c r="O124" s="25">
@@ -8780,7 +8810,7 @@
         <v/>
       </c>
       <c r="N125" s="29">
-        <f>IF(AND(OR(G125="Aprovado",G125="Recusado"),H125&lt;&gt;"",A125&lt;&gt;""),H125-A125,"")</f>
+        <f>IF(AND(OR(G125="Aprovado",G125="Recusado"),H125&lt;&gt;"",A125&lt;&gt;"",H125&gt;=A125),H125-A125,"")</f>
         <v/>
       </c>
       <c r="O125" s="25">
@@ -8820,7 +8850,7 @@
         <v/>
       </c>
       <c r="N126" s="29">
-        <f>IF(AND(OR(G126="Aprovado",G126="Recusado"),H126&lt;&gt;"",A126&lt;&gt;""),H126-A126,"")</f>
+        <f>IF(AND(OR(G126="Aprovado",G126="Recusado"),H126&lt;&gt;"",A126&lt;&gt;"",H126&gt;=A126),H126-A126,"")</f>
         <v/>
       </c>
       <c r="O126" s="25">
@@ -8860,7 +8890,7 @@
         <v/>
       </c>
       <c r="N127" s="29">
-        <f>IF(AND(OR(G127="Aprovado",G127="Recusado"),H127&lt;&gt;"",A127&lt;&gt;""),H127-A127,"")</f>
+        <f>IF(AND(OR(G127="Aprovado",G127="Recusado"),H127&lt;&gt;"",A127&lt;&gt;"",H127&gt;=A127),H127-A127,"")</f>
         <v/>
       </c>
       <c r="O127" s="25">
@@ -8900,7 +8930,7 @@
         <v/>
       </c>
       <c r="N128" s="29">
-        <f>IF(AND(OR(G128="Aprovado",G128="Recusado"),H128&lt;&gt;"",A128&lt;&gt;""),H128-A128,"")</f>
+        <f>IF(AND(OR(G128="Aprovado",G128="Recusado"),H128&lt;&gt;"",A128&lt;&gt;"",H128&gt;=A128),H128-A128,"")</f>
         <v/>
       </c>
       <c r="O128" s="25">
@@ -8940,7 +8970,7 @@
         <v/>
       </c>
       <c r="N129" s="29">
-        <f>IF(AND(OR(G129="Aprovado",G129="Recusado"),H129&lt;&gt;"",A129&lt;&gt;""),H129-A129,"")</f>
+        <f>IF(AND(OR(G129="Aprovado",G129="Recusado"),H129&lt;&gt;"",A129&lt;&gt;"",H129&gt;=A129),H129-A129,"")</f>
         <v/>
       </c>
       <c r="O129" s="25">
@@ -8980,7 +9010,7 @@
         <v/>
       </c>
       <c r="N130" s="29">
-        <f>IF(AND(OR(G130="Aprovado",G130="Recusado"),H130&lt;&gt;"",A130&lt;&gt;""),H130-A130,"")</f>
+        <f>IF(AND(OR(G130="Aprovado",G130="Recusado"),H130&lt;&gt;"",A130&lt;&gt;"",H130&gt;=A130),H130-A130,"")</f>
         <v/>
       </c>
       <c r="O130" s="25">
@@ -9020,7 +9050,7 @@
         <v/>
       </c>
       <c r="N131" s="29">
-        <f>IF(AND(OR(G131="Aprovado",G131="Recusado"),H131&lt;&gt;"",A131&lt;&gt;""),H131-A131,"")</f>
+        <f>IF(AND(OR(G131="Aprovado",G131="Recusado"),H131&lt;&gt;"",A131&lt;&gt;"",H131&gt;=A131),H131-A131,"")</f>
         <v/>
       </c>
       <c r="O131" s="25">
@@ -9060,7 +9090,7 @@
         <v/>
       </c>
       <c r="N132" s="29">
-        <f>IF(AND(OR(G132="Aprovado",G132="Recusado"),H132&lt;&gt;"",A132&lt;&gt;""),H132-A132,"")</f>
+        <f>IF(AND(OR(G132="Aprovado",G132="Recusado"),H132&lt;&gt;"",A132&lt;&gt;"",H132&gt;=A132),H132-A132,"")</f>
         <v/>
       </c>
       <c r="O132" s="25">
@@ -9100,7 +9130,7 @@
         <v/>
       </c>
       <c r="N133" s="29">
-        <f>IF(AND(OR(G133="Aprovado",G133="Recusado"),H133&lt;&gt;"",A133&lt;&gt;""),H133-A133,"")</f>
+        <f>IF(AND(OR(G133="Aprovado",G133="Recusado"),H133&lt;&gt;"",A133&lt;&gt;"",H133&gt;=A133),H133-A133,"")</f>
         <v/>
       </c>
       <c r="O133" s="25">
@@ -9140,7 +9170,7 @@
         <v/>
       </c>
       <c r="N134" s="29">
-        <f>IF(AND(OR(G134="Aprovado",G134="Recusado"),H134&lt;&gt;"",A134&lt;&gt;""),H134-A134,"")</f>
+        <f>IF(AND(OR(G134="Aprovado",G134="Recusado"),H134&lt;&gt;"",A134&lt;&gt;"",H134&gt;=A134),H134-A134,"")</f>
         <v/>
       </c>
       <c r="O134" s="25">
@@ -9180,7 +9210,7 @@
         <v/>
       </c>
       <c r="N135" s="29">
-        <f>IF(AND(OR(G135="Aprovado",G135="Recusado"),H135&lt;&gt;"",A135&lt;&gt;""),H135-A135,"")</f>
+        <f>IF(AND(OR(G135="Aprovado",G135="Recusado"),H135&lt;&gt;"",A135&lt;&gt;"",H135&gt;=A135),H135-A135,"")</f>
         <v/>
       </c>
       <c r="O135" s="25">
@@ -9220,7 +9250,7 @@
         <v/>
       </c>
       <c r="N136" s="29">
-        <f>IF(AND(OR(G136="Aprovado",G136="Recusado"),H136&lt;&gt;"",A136&lt;&gt;""),H136-A136,"")</f>
+        <f>IF(AND(OR(G136="Aprovado",G136="Recusado"),H136&lt;&gt;"",A136&lt;&gt;"",H136&gt;=A136),H136-A136,"")</f>
         <v/>
       </c>
       <c r="O136" s="25">
@@ -9260,7 +9290,7 @@
         <v/>
       </c>
       <c r="N137" s="29">
-        <f>IF(AND(OR(G137="Aprovado",G137="Recusado"),H137&lt;&gt;"",A137&lt;&gt;""),H137-A137,"")</f>
+        <f>IF(AND(OR(G137="Aprovado",G137="Recusado"),H137&lt;&gt;"",A137&lt;&gt;"",H137&gt;=A137),H137-A137,"")</f>
         <v/>
       </c>
       <c r="O137" s="25">
@@ -9300,7 +9330,7 @@
         <v/>
       </c>
       <c r="N138" s="29">
-        <f>IF(AND(OR(G138="Aprovado",G138="Recusado"),H138&lt;&gt;"",A138&lt;&gt;""),H138-A138,"")</f>
+        <f>IF(AND(OR(G138="Aprovado",G138="Recusado"),H138&lt;&gt;"",A138&lt;&gt;"",H138&gt;=A138),H138-A138,"")</f>
         <v/>
       </c>
       <c r="O138" s="25">
@@ -9340,7 +9370,7 @@
         <v/>
       </c>
       <c r="N139" s="29">
-        <f>IF(AND(OR(G139="Aprovado",G139="Recusado"),H139&lt;&gt;"",A139&lt;&gt;""),H139-A139,"")</f>
+        <f>IF(AND(OR(G139="Aprovado",G139="Recusado"),H139&lt;&gt;"",A139&lt;&gt;"",H139&gt;=A139),H139-A139,"")</f>
         <v/>
       </c>
       <c r="O139" s="25">
@@ -9380,7 +9410,7 @@
         <v/>
       </c>
       <c r="N140" s="29">
-        <f>IF(AND(OR(G140="Aprovado",G140="Recusado"),H140&lt;&gt;"",A140&lt;&gt;""),H140-A140,"")</f>
+        <f>IF(AND(OR(G140="Aprovado",G140="Recusado"),H140&lt;&gt;"",A140&lt;&gt;"",H140&gt;=A140),H140-A140,"")</f>
         <v/>
       </c>
       <c r="O140" s="25">
@@ -9420,7 +9450,7 @@
         <v/>
       </c>
       <c r="N141" s="29">
-        <f>IF(AND(OR(G141="Aprovado",G141="Recusado"),H141&lt;&gt;"",A141&lt;&gt;""),H141-A141,"")</f>
+        <f>IF(AND(OR(G141="Aprovado",G141="Recusado"),H141&lt;&gt;"",A141&lt;&gt;"",H141&gt;=A141),H141-A141,"")</f>
         <v/>
       </c>
       <c r="O141" s="25">
@@ -9460,7 +9490,7 @@
         <v/>
       </c>
       <c r="N142" s="29">
-        <f>IF(AND(OR(G142="Aprovado",G142="Recusado"),H142&lt;&gt;"",A142&lt;&gt;""),H142-A142,"")</f>
+        <f>IF(AND(OR(G142="Aprovado",G142="Recusado"),H142&lt;&gt;"",A142&lt;&gt;"",H142&gt;=A142),H142-A142,"")</f>
         <v/>
       </c>
       <c r="O142" s="25">
@@ -9500,7 +9530,7 @@
         <v/>
       </c>
       <c r="N143" s="29">
-        <f>IF(AND(OR(G143="Aprovado",G143="Recusado"),H143&lt;&gt;"",A143&lt;&gt;""),H143-A143,"")</f>
+        <f>IF(AND(OR(G143="Aprovado",G143="Recusado"),H143&lt;&gt;"",A143&lt;&gt;"",H143&gt;=A143),H143-A143,"")</f>
         <v/>
       </c>
       <c r="O143" s="25">
@@ -9540,7 +9570,7 @@
         <v/>
       </c>
       <c r="N144" s="29">
-        <f>IF(AND(OR(G144="Aprovado",G144="Recusado"),H144&lt;&gt;"",A144&lt;&gt;""),H144-A144,"")</f>
+        <f>IF(AND(OR(G144="Aprovado",G144="Recusado"),H144&lt;&gt;"",A144&lt;&gt;"",H144&gt;=A144),H144-A144,"")</f>
         <v/>
       </c>
       <c r="O144" s="25">
@@ -9580,7 +9610,7 @@
         <v/>
       </c>
       <c r="N145" s="29">
-        <f>IF(AND(OR(G145="Aprovado",G145="Recusado"),H145&lt;&gt;"",A145&lt;&gt;""),H145-A145,"")</f>
+        <f>IF(AND(OR(G145="Aprovado",G145="Recusado"),H145&lt;&gt;"",A145&lt;&gt;"",H145&gt;=A145),H145-A145,"")</f>
         <v/>
       </c>
       <c r="O145" s="25">
@@ -9620,7 +9650,7 @@
         <v/>
       </c>
       <c r="N146" s="29">
-        <f>IF(AND(OR(G146="Aprovado",G146="Recusado"),H146&lt;&gt;"",A146&lt;&gt;""),H146-A146,"")</f>
+        <f>IF(AND(OR(G146="Aprovado",G146="Recusado"),H146&lt;&gt;"",A146&lt;&gt;"",H146&gt;=A146),H146-A146,"")</f>
         <v/>
       </c>
       <c r="O146" s="25">
@@ -9660,7 +9690,7 @@
         <v/>
       </c>
       <c r="N147" s="29">
-        <f>IF(AND(OR(G147="Aprovado",G147="Recusado"),H147&lt;&gt;"",A147&lt;&gt;""),H147-A147,"")</f>
+        <f>IF(AND(OR(G147="Aprovado",G147="Recusado"),H147&lt;&gt;"",A147&lt;&gt;"",H147&gt;=A147),H147-A147,"")</f>
         <v/>
       </c>
       <c r="O147" s="25">
@@ -9700,7 +9730,7 @@
         <v/>
       </c>
       <c r="N148" s="29">
-        <f>IF(AND(OR(G148="Aprovado",G148="Recusado"),H148&lt;&gt;"",A148&lt;&gt;""),H148-A148,"")</f>
+        <f>IF(AND(OR(G148="Aprovado",G148="Recusado"),H148&lt;&gt;"",A148&lt;&gt;"",H148&gt;=A148),H148-A148,"")</f>
         <v/>
       </c>
       <c r="O148" s="25">
@@ -9740,7 +9770,7 @@
         <v/>
       </c>
       <c r="N149" s="29">
-        <f>IF(AND(OR(G149="Aprovado",G149="Recusado"),H149&lt;&gt;"",A149&lt;&gt;""),H149-A149,"")</f>
+        <f>IF(AND(OR(G149="Aprovado",G149="Recusado"),H149&lt;&gt;"",A149&lt;&gt;"",H149&gt;=A149),H149-A149,"")</f>
         <v/>
       </c>
       <c r="O149" s="25">
@@ -9780,7 +9810,7 @@
         <v/>
       </c>
       <c r="N150" s="29">
-        <f>IF(AND(OR(G150="Aprovado",G150="Recusado"),H150&lt;&gt;"",A150&lt;&gt;""),H150-A150,"")</f>
+        <f>IF(AND(OR(G150="Aprovado",G150="Recusado"),H150&lt;&gt;"",A150&lt;&gt;"",H150&gt;=A150),H150-A150,"")</f>
         <v/>
       </c>
       <c r="O150" s="25">
@@ -9820,7 +9850,7 @@
         <v/>
       </c>
       <c r="N151" s="29">
-        <f>IF(AND(OR(G151="Aprovado",G151="Recusado"),H151&lt;&gt;"",A151&lt;&gt;""),H151-A151,"")</f>
+        <f>IF(AND(OR(G151="Aprovado",G151="Recusado"),H151&lt;&gt;"",A151&lt;&gt;"",H151&gt;=A151),H151-A151,"")</f>
         <v/>
       </c>
       <c r="O151" s="25">
@@ -9860,7 +9890,7 @@
         <v/>
       </c>
       <c r="N152" s="29">
-        <f>IF(AND(OR(G152="Aprovado",G152="Recusado"),H152&lt;&gt;"",A152&lt;&gt;""),H152-A152,"")</f>
+        <f>IF(AND(OR(G152="Aprovado",G152="Recusado"),H152&lt;&gt;"",A152&lt;&gt;"",H152&gt;=A152),H152-A152,"")</f>
         <v/>
       </c>
       <c r="O152" s="25">
@@ -9900,7 +9930,7 @@
         <v/>
       </c>
       <c r="N153" s="29">
-        <f>IF(AND(OR(G153="Aprovado",G153="Recusado"),H153&lt;&gt;"",A153&lt;&gt;""),H153-A153,"")</f>
+        <f>IF(AND(OR(G153="Aprovado",G153="Recusado"),H153&lt;&gt;"",A153&lt;&gt;"",H153&gt;=A153),H153-A153,"")</f>
         <v/>
       </c>
       <c r="O153" s="25">
@@ -9940,7 +9970,7 @@
         <v/>
       </c>
       <c r="N154" s="29">
-        <f>IF(AND(OR(G154="Aprovado",G154="Recusado"),H154&lt;&gt;"",A154&lt;&gt;""),H154-A154,"")</f>
+        <f>IF(AND(OR(G154="Aprovado",G154="Recusado"),H154&lt;&gt;"",A154&lt;&gt;"",H154&gt;=A154),H154-A154,"")</f>
         <v/>
       </c>
       <c r="O154" s="25">
@@ -9980,7 +10010,7 @@
         <v/>
       </c>
       <c r="N155" s="29">
-        <f>IF(AND(OR(G155="Aprovado",G155="Recusado"),H155&lt;&gt;"",A155&lt;&gt;""),H155-A155,"")</f>
+        <f>IF(AND(OR(G155="Aprovado",G155="Recusado"),H155&lt;&gt;"",A155&lt;&gt;"",H155&gt;=A155),H155-A155,"")</f>
         <v/>
       </c>
       <c r="O155" s="25">
@@ -10020,7 +10050,7 @@
         <v/>
       </c>
       <c r="N156" s="29">
-        <f>IF(AND(OR(G156="Aprovado",G156="Recusado"),H156&lt;&gt;"",A156&lt;&gt;""),H156-A156,"")</f>
+        <f>IF(AND(OR(G156="Aprovado",G156="Recusado"),H156&lt;&gt;"",A156&lt;&gt;"",H156&gt;=A156),H156-A156,"")</f>
         <v/>
       </c>
       <c r="O156" s="25">
@@ -10060,7 +10090,7 @@
         <v/>
       </c>
       <c r="N157" s="29">
-        <f>IF(AND(OR(G157="Aprovado",G157="Recusado"),H157&lt;&gt;"",A157&lt;&gt;""),H157-A157,"")</f>
+        <f>IF(AND(OR(G157="Aprovado",G157="Recusado"),H157&lt;&gt;"",A157&lt;&gt;"",H157&gt;=A157),H157-A157,"")</f>
         <v/>
       </c>
       <c r="O157" s="25">
@@ -10100,7 +10130,7 @@
         <v/>
       </c>
       <c r="N158" s="29">
-        <f>IF(AND(OR(G158="Aprovado",G158="Recusado"),H158&lt;&gt;"",A158&lt;&gt;""),H158-A158,"")</f>
+        <f>IF(AND(OR(G158="Aprovado",G158="Recusado"),H158&lt;&gt;"",A158&lt;&gt;"",H158&gt;=A158),H158-A158,"")</f>
         <v/>
       </c>
       <c r="O158" s="25">
@@ -10140,7 +10170,7 @@
         <v/>
       </c>
       <c r="N159" s="29">
-        <f>IF(AND(OR(G159="Aprovado",G159="Recusado"),H159&lt;&gt;"",A159&lt;&gt;""),H159-A159,"")</f>
+        <f>IF(AND(OR(G159="Aprovado",G159="Recusado"),H159&lt;&gt;"",A159&lt;&gt;"",H159&gt;=A159),H159-A159,"")</f>
         <v/>
       </c>
       <c r="O159" s="25">
@@ -10180,7 +10210,7 @@
         <v/>
       </c>
       <c r="N160" s="29">
-        <f>IF(AND(OR(G160="Aprovado",G160="Recusado"),H160&lt;&gt;"",A160&lt;&gt;""),H160-A160,"")</f>
+        <f>IF(AND(OR(G160="Aprovado",G160="Recusado"),H160&lt;&gt;"",A160&lt;&gt;"",H160&gt;=A160),H160-A160,"")</f>
         <v/>
       </c>
       <c r="O160" s="25">
@@ -10220,7 +10250,7 @@
         <v/>
       </c>
       <c r="N161" s="29">
-        <f>IF(AND(OR(G161="Aprovado",G161="Recusado"),H161&lt;&gt;"",A161&lt;&gt;""),H161-A161,"")</f>
+        <f>IF(AND(OR(G161="Aprovado",G161="Recusado"),H161&lt;&gt;"",A161&lt;&gt;"",H161&gt;=A161),H161-A161,"")</f>
         <v/>
       </c>
       <c r="O161" s="25">
@@ -10260,7 +10290,7 @@
         <v/>
       </c>
       <c r="N162" s="29">
-        <f>IF(AND(OR(G162="Aprovado",G162="Recusado"),H162&lt;&gt;"",A162&lt;&gt;""),H162-A162,"")</f>
+        <f>IF(AND(OR(G162="Aprovado",G162="Recusado"),H162&lt;&gt;"",A162&lt;&gt;"",H162&gt;=A162),H162-A162,"")</f>
         <v/>
       </c>
       <c r="O162" s="25">
@@ -10300,7 +10330,7 @@
         <v/>
       </c>
       <c r="N163" s="29">
-        <f>IF(AND(OR(G163="Aprovado",G163="Recusado"),H163&lt;&gt;"",A163&lt;&gt;""),H163-A163,"")</f>
+        <f>IF(AND(OR(G163="Aprovado",G163="Recusado"),H163&lt;&gt;"",A163&lt;&gt;"",H163&gt;=A163),H163-A163,"")</f>
         <v/>
       </c>
       <c r="O163" s="25">
@@ -10340,7 +10370,7 @@
         <v/>
       </c>
       <c r="N164" s="29">
-        <f>IF(AND(OR(G164="Aprovado",G164="Recusado"),H164&lt;&gt;"",A164&lt;&gt;""),H164-A164,"")</f>
+        <f>IF(AND(OR(G164="Aprovado",G164="Recusado"),H164&lt;&gt;"",A164&lt;&gt;"",H164&gt;=A164),H164-A164,"")</f>
         <v/>
       </c>
       <c r="O164" s="25">
@@ -10380,7 +10410,7 @@
         <v/>
       </c>
       <c r="N165" s="29">
-        <f>IF(AND(OR(G165="Aprovado",G165="Recusado"),H165&lt;&gt;"",A165&lt;&gt;""),H165-A165,"")</f>
+        <f>IF(AND(OR(G165="Aprovado",G165="Recusado"),H165&lt;&gt;"",A165&lt;&gt;"",H165&gt;=A165),H165-A165,"")</f>
         <v/>
       </c>
       <c r="O165" s="25">
@@ -10420,7 +10450,7 @@
         <v/>
       </c>
       <c r="N166" s="29">
-        <f>IF(AND(OR(G166="Aprovado",G166="Recusado"),H166&lt;&gt;"",A166&lt;&gt;""),H166-A166,"")</f>
+        <f>IF(AND(OR(G166="Aprovado",G166="Recusado"),H166&lt;&gt;"",A166&lt;&gt;"",H166&gt;=A166),H166-A166,"")</f>
         <v/>
       </c>
       <c r="O166" s="25">
@@ -10460,7 +10490,7 @@
         <v/>
       </c>
       <c r="N167" s="29">
-        <f>IF(AND(OR(G167="Aprovado",G167="Recusado"),H167&lt;&gt;"",A167&lt;&gt;""),H167-A167,"")</f>
+        <f>IF(AND(OR(G167="Aprovado",G167="Recusado"),H167&lt;&gt;"",A167&lt;&gt;"",H167&gt;=A167),H167-A167,"")</f>
         <v/>
       </c>
       <c r="O167" s="25">
@@ -10500,7 +10530,7 @@
         <v/>
       </c>
       <c r="N168" s="29">
-        <f>IF(AND(OR(G168="Aprovado",G168="Recusado"),H168&lt;&gt;"",A168&lt;&gt;""),H168-A168,"")</f>
+        <f>IF(AND(OR(G168="Aprovado",G168="Recusado"),H168&lt;&gt;"",A168&lt;&gt;"",H168&gt;=A168),H168-A168,"")</f>
         <v/>
       </c>
       <c r="O168" s="25">
@@ -10540,7 +10570,7 @@
         <v/>
       </c>
       <c r="N169" s="29">
-        <f>IF(AND(OR(G169="Aprovado",G169="Recusado"),H169&lt;&gt;"",A169&lt;&gt;""),H169-A169,"")</f>
+        <f>IF(AND(OR(G169="Aprovado",G169="Recusado"),H169&lt;&gt;"",A169&lt;&gt;"",H169&gt;=A169),H169-A169,"")</f>
         <v/>
       </c>
       <c r="O169" s="25">
@@ -10580,7 +10610,7 @@
         <v/>
       </c>
       <c r="N170" s="29">
-        <f>IF(AND(OR(G170="Aprovado",G170="Recusado"),H170&lt;&gt;"",A170&lt;&gt;""),H170-A170,"")</f>
+        <f>IF(AND(OR(G170="Aprovado",G170="Recusado"),H170&lt;&gt;"",A170&lt;&gt;"",H170&gt;=A170),H170-A170,"")</f>
         <v/>
       </c>
       <c r="O170" s="25">
@@ -10620,7 +10650,7 @@
         <v/>
       </c>
       <c r="N171" s="29">
-        <f>IF(AND(OR(G171="Aprovado",G171="Recusado"),H171&lt;&gt;"",A171&lt;&gt;""),H171-A171,"")</f>
+        <f>IF(AND(OR(G171="Aprovado",G171="Recusado"),H171&lt;&gt;"",A171&lt;&gt;"",H171&gt;=A171),H171-A171,"")</f>
         <v/>
       </c>
       <c r="O171" s="25">
@@ -10660,7 +10690,7 @@
         <v/>
       </c>
       <c r="N172" s="29">
-        <f>IF(AND(OR(G172="Aprovado",G172="Recusado"),H172&lt;&gt;"",A172&lt;&gt;""),H172-A172,"")</f>
+        <f>IF(AND(OR(G172="Aprovado",G172="Recusado"),H172&lt;&gt;"",A172&lt;&gt;"",H172&gt;=A172),H172-A172,"")</f>
         <v/>
       </c>
       <c r="O172" s="25">
@@ -10700,7 +10730,7 @@
         <v/>
       </c>
       <c r="N173" s="29">
-        <f>IF(AND(OR(G173="Aprovado",G173="Recusado"),H173&lt;&gt;"",A173&lt;&gt;""),H173-A173,"")</f>
+        <f>IF(AND(OR(G173="Aprovado",G173="Recusado"),H173&lt;&gt;"",A173&lt;&gt;"",H173&gt;=A173),H173-A173,"")</f>
         <v/>
       </c>
       <c r="O173" s="25">
@@ -10740,7 +10770,7 @@
         <v/>
       </c>
       <c r="N174" s="29">
-        <f>IF(AND(OR(G174="Aprovado",G174="Recusado"),H174&lt;&gt;"",A174&lt;&gt;""),H174-A174,"")</f>
+        <f>IF(AND(OR(G174="Aprovado",G174="Recusado"),H174&lt;&gt;"",A174&lt;&gt;"",H174&gt;=A174),H174-A174,"")</f>
         <v/>
       </c>
       <c r="O174" s="25">
@@ -10780,7 +10810,7 @@
         <v/>
       </c>
       <c r="N175" s="29">
-        <f>IF(AND(OR(G175="Aprovado",G175="Recusado"),H175&lt;&gt;"",A175&lt;&gt;""),H175-A175,"")</f>
+        <f>IF(AND(OR(G175="Aprovado",G175="Recusado"),H175&lt;&gt;"",A175&lt;&gt;"",H175&gt;=A175),H175-A175,"")</f>
         <v/>
       </c>
       <c r="O175" s="25">
@@ -10820,7 +10850,7 @@
         <v/>
       </c>
       <c r="N176" s="29">
-        <f>IF(AND(OR(G176="Aprovado",G176="Recusado"),H176&lt;&gt;"",A176&lt;&gt;""),H176-A176,"")</f>
+        <f>IF(AND(OR(G176="Aprovado",G176="Recusado"),H176&lt;&gt;"",A176&lt;&gt;"",H176&gt;=A176),H176-A176,"")</f>
         <v/>
       </c>
       <c r="O176" s="25">
@@ -10860,7 +10890,7 @@
         <v/>
       </c>
       <c r="N177" s="29">
-        <f>IF(AND(OR(G177="Aprovado",G177="Recusado"),H177&lt;&gt;"",A177&lt;&gt;""),H177-A177,"")</f>
+        <f>IF(AND(OR(G177="Aprovado",G177="Recusado"),H177&lt;&gt;"",A177&lt;&gt;"",H177&gt;=A177),H177-A177,"")</f>
         <v/>
       </c>
       <c r="O177" s="25">
@@ -10900,7 +10930,7 @@
         <v/>
       </c>
       <c r="N178" s="29">
-        <f>IF(AND(OR(G178="Aprovado",G178="Recusado"),H178&lt;&gt;"",A178&lt;&gt;""),H178-A178,"")</f>
+        <f>IF(AND(OR(G178="Aprovado",G178="Recusado"),H178&lt;&gt;"",A178&lt;&gt;"",H178&gt;=A178),H178-A178,"")</f>
         <v/>
       </c>
       <c r="O178" s="25">
@@ -10940,7 +10970,7 @@
         <v/>
       </c>
       <c r="N179" s="29">
-        <f>IF(AND(OR(G179="Aprovado",G179="Recusado"),H179&lt;&gt;"",A179&lt;&gt;""),H179-A179,"")</f>
+        <f>IF(AND(OR(G179="Aprovado",G179="Recusado"),H179&lt;&gt;"",A179&lt;&gt;"",H179&gt;=A179),H179-A179,"")</f>
         <v/>
       </c>
       <c r="O179" s="25">
@@ -10980,7 +11010,7 @@
         <v/>
       </c>
       <c r="N180" s="29">
-        <f>IF(AND(OR(G180="Aprovado",G180="Recusado"),H180&lt;&gt;"",A180&lt;&gt;""),H180-A180,"")</f>
+        <f>IF(AND(OR(G180="Aprovado",G180="Recusado"),H180&lt;&gt;"",A180&lt;&gt;"",H180&gt;=A180),H180-A180,"")</f>
         <v/>
       </c>
       <c r="O180" s="25">
@@ -11020,7 +11050,7 @@
         <v/>
       </c>
       <c r="N181" s="29">
-        <f>IF(AND(OR(G181="Aprovado",G181="Recusado"),H181&lt;&gt;"",A181&lt;&gt;""),H181-A181,"")</f>
+        <f>IF(AND(OR(G181="Aprovado",G181="Recusado"),H181&lt;&gt;"",A181&lt;&gt;"",H181&gt;=A181),H181-A181,"")</f>
         <v/>
       </c>
       <c r="O181" s="25">
@@ -11060,7 +11090,7 @@
         <v/>
       </c>
       <c r="N182" s="29">
-        <f>IF(AND(OR(G182="Aprovado",G182="Recusado"),H182&lt;&gt;"",A182&lt;&gt;""),H182-A182,"")</f>
+        <f>IF(AND(OR(G182="Aprovado",G182="Recusado"),H182&lt;&gt;"",A182&lt;&gt;"",H182&gt;=A182),H182-A182,"")</f>
         <v/>
       </c>
       <c r="O182" s="25">
@@ -11100,7 +11130,7 @@
         <v/>
       </c>
       <c r="N183" s="29">
-        <f>IF(AND(OR(G183="Aprovado",G183="Recusado"),H183&lt;&gt;"",A183&lt;&gt;""),H183-A183,"")</f>
+        <f>IF(AND(OR(G183="Aprovado",G183="Recusado"),H183&lt;&gt;"",A183&lt;&gt;"",H183&gt;=A183),H183-A183,"")</f>
         <v/>
       </c>
       <c r="O183" s="25">
@@ -11140,7 +11170,7 @@
         <v/>
       </c>
       <c r="N184" s="29">
-        <f>IF(AND(OR(G184="Aprovado",G184="Recusado"),H184&lt;&gt;"",A184&lt;&gt;""),H184-A184,"")</f>
+        <f>IF(AND(OR(G184="Aprovado",G184="Recusado"),H184&lt;&gt;"",A184&lt;&gt;"",H184&gt;=A184),H184-A184,"")</f>
         <v/>
       </c>
       <c r="O184" s="25">
@@ -11180,7 +11210,7 @@
         <v/>
       </c>
       <c r="N185" s="29">
-        <f>IF(AND(OR(G185="Aprovado",G185="Recusado"),H185&lt;&gt;"",A185&lt;&gt;""),H185-A185,"")</f>
+        <f>IF(AND(OR(G185="Aprovado",G185="Recusado"),H185&lt;&gt;"",A185&lt;&gt;"",H185&gt;=A185),H185-A185,"")</f>
         <v/>
       </c>
       <c r="O185" s="25">
@@ -11220,7 +11250,7 @@
         <v/>
       </c>
       <c r="N186" s="29">
-        <f>IF(AND(OR(G186="Aprovado",G186="Recusado"),H186&lt;&gt;"",A186&lt;&gt;""),H186-A186,"")</f>
+        <f>IF(AND(OR(G186="Aprovado",G186="Recusado"),H186&lt;&gt;"",A186&lt;&gt;"",H186&gt;=A186),H186-A186,"")</f>
         <v/>
       </c>
       <c r="O186" s="25">
@@ -11260,7 +11290,7 @@
         <v/>
       </c>
       <c r="N187" s="29">
-        <f>IF(AND(OR(G187="Aprovado",G187="Recusado"),H187&lt;&gt;"",A187&lt;&gt;""),H187-A187,"")</f>
+        <f>IF(AND(OR(G187="Aprovado",G187="Recusado"),H187&lt;&gt;"",A187&lt;&gt;"",H187&gt;=A187),H187-A187,"")</f>
         <v/>
       </c>
       <c r="O187" s="25">
@@ -11300,7 +11330,7 @@
         <v/>
       </c>
       <c r="N188" s="29">
-        <f>IF(AND(OR(G188="Aprovado",G188="Recusado"),H188&lt;&gt;"",A188&lt;&gt;""),H188-A188,"")</f>
+        <f>IF(AND(OR(G188="Aprovado",G188="Recusado"),H188&lt;&gt;"",A188&lt;&gt;"",H188&gt;=A188),H188-A188,"")</f>
         <v/>
       </c>
       <c r="O188" s="25">
@@ -11340,7 +11370,7 @@
         <v/>
       </c>
       <c r="N189" s="29">
-        <f>IF(AND(OR(G189="Aprovado",G189="Recusado"),H189&lt;&gt;"",A189&lt;&gt;""),H189-A189,"")</f>
+        <f>IF(AND(OR(G189="Aprovado",G189="Recusado"),H189&lt;&gt;"",A189&lt;&gt;"",H189&gt;=A189),H189-A189,"")</f>
         <v/>
       </c>
       <c r="O189" s="25">
@@ -11380,7 +11410,7 @@
         <v/>
       </c>
       <c r="N190" s="29">
-        <f>IF(AND(OR(G190="Aprovado",G190="Recusado"),H190&lt;&gt;"",A190&lt;&gt;""),H190-A190,"")</f>
+        <f>IF(AND(OR(G190="Aprovado",G190="Recusado"),H190&lt;&gt;"",A190&lt;&gt;"",H190&gt;=A190),H190-A190,"")</f>
         <v/>
       </c>
       <c r="O190" s="25">
@@ -11420,7 +11450,7 @@
         <v/>
       </c>
       <c r="N191" s="29">
-        <f>IF(AND(OR(G191="Aprovado",G191="Recusado"),H191&lt;&gt;"",A191&lt;&gt;""),H191-A191,"")</f>
+        <f>IF(AND(OR(G191="Aprovado",G191="Recusado"),H191&lt;&gt;"",A191&lt;&gt;"",H191&gt;=A191),H191-A191,"")</f>
         <v/>
       </c>
       <c r="O191" s="25">
@@ -11460,7 +11490,7 @@
         <v/>
       </c>
       <c r="N192" s="29">
-        <f>IF(AND(OR(G192="Aprovado",G192="Recusado"),H192&lt;&gt;"",A192&lt;&gt;""),H192-A192,"")</f>
+        <f>IF(AND(OR(G192="Aprovado",G192="Recusado"),H192&lt;&gt;"",A192&lt;&gt;"",H192&gt;=A192),H192-A192,"")</f>
         <v/>
       </c>
       <c r="O192" s="25">
@@ -11500,7 +11530,7 @@
         <v/>
       </c>
       <c r="N193" s="29">
-        <f>IF(AND(OR(G193="Aprovado",G193="Recusado"),H193&lt;&gt;"",A193&lt;&gt;""),H193-A193,"")</f>
+        <f>IF(AND(OR(G193="Aprovado",G193="Recusado"),H193&lt;&gt;"",A193&lt;&gt;"",H193&gt;=A193),H193-A193,"")</f>
         <v/>
       </c>
       <c r="O193" s="25">
@@ -11540,7 +11570,7 @@
         <v/>
       </c>
       <c r="N194" s="29">
-        <f>IF(AND(OR(G194="Aprovado",G194="Recusado"),H194&lt;&gt;"",A194&lt;&gt;""),H194-A194,"")</f>
+        <f>IF(AND(OR(G194="Aprovado",G194="Recusado"),H194&lt;&gt;"",A194&lt;&gt;"",H194&gt;=A194),H194-A194,"")</f>
         <v/>
       </c>
       <c r="O194" s="25">
@@ -11580,7 +11610,7 @@
         <v/>
       </c>
       <c r="N195" s="29">
-        <f>IF(AND(OR(G195="Aprovado",G195="Recusado"),H195&lt;&gt;"",A195&lt;&gt;""),H195-A195,"")</f>
+        <f>IF(AND(OR(G195="Aprovado",G195="Recusado"),H195&lt;&gt;"",A195&lt;&gt;"",H195&gt;=A195),H195-A195,"")</f>
         <v/>
       </c>
       <c r="O195" s="25">
@@ -11620,7 +11650,7 @@
         <v/>
       </c>
       <c r="N196" s="29">
-        <f>IF(AND(OR(G196="Aprovado",G196="Recusado"),H196&lt;&gt;"",A196&lt;&gt;""),H196-A196,"")</f>
+        <f>IF(AND(OR(G196="Aprovado",G196="Recusado"),H196&lt;&gt;"",A196&lt;&gt;"",H196&gt;=A196),H196-A196,"")</f>
         <v/>
       </c>
       <c r="O196" s="25">
@@ -11660,7 +11690,7 @@
         <v/>
       </c>
       <c r="N197" s="29">
-        <f>IF(AND(OR(G197="Aprovado",G197="Recusado"),H197&lt;&gt;"",A197&lt;&gt;""),H197-A197,"")</f>
+        <f>IF(AND(OR(G197="Aprovado",G197="Recusado"),H197&lt;&gt;"",A197&lt;&gt;"",H197&gt;=A197),H197-A197,"")</f>
         <v/>
       </c>
       <c r="O197" s="25">
@@ -11700,7 +11730,7 @@
         <v/>
       </c>
       <c r="N198" s="29">
-        <f>IF(AND(OR(G198="Aprovado",G198="Recusado"),H198&lt;&gt;"",A198&lt;&gt;""),H198-A198,"")</f>
+        <f>IF(AND(OR(G198="Aprovado",G198="Recusado"),H198&lt;&gt;"",A198&lt;&gt;"",H198&gt;=A198),H198-A198,"")</f>
         <v/>
       </c>
       <c r="O198" s="25">
@@ -11740,7 +11770,7 @@
         <v/>
       </c>
       <c r="N199" s="29">
-        <f>IF(AND(OR(G199="Aprovado",G199="Recusado"),H199&lt;&gt;"",A199&lt;&gt;""),H199-A199,"")</f>
+        <f>IF(AND(OR(G199="Aprovado",G199="Recusado"),H199&lt;&gt;"",A199&lt;&gt;"",H199&gt;=A199),H199-A199,"")</f>
         <v/>
       </c>
       <c r="O199" s="25">
@@ -11780,7 +11810,7 @@
         <v/>
       </c>
       <c r="N200" s="29">
-        <f>IF(AND(OR(G200="Aprovado",G200="Recusado"),H200&lt;&gt;"",A200&lt;&gt;""),H200-A200,"")</f>
+        <f>IF(AND(OR(G200="Aprovado",G200="Recusado"),H200&lt;&gt;"",A200&lt;&gt;"",H200&gt;=A200),H200-A200,"")</f>
         <v/>
       </c>
       <c r="O200" s="25">
@@ -11820,7 +11850,7 @@
         <v/>
       </c>
       <c r="N201" s="29">
-        <f>IF(AND(OR(G201="Aprovado",G201="Recusado"),H201&lt;&gt;"",A201&lt;&gt;""),H201-A201,"")</f>
+        <f>IF(AND(OR(G201="Aprovado",G201="Recusado"),H201&lt;&gt;"",A201&lt;&gt;"",H201&gt;=A201),H201-A201,"")</f>
         <v/>
       </c>
       <c r="O201" s="25">
@@ -11860,7 +11890,7 @@
         <v/>
       </c>
       <c r="N202" s="29">
-        <f>IF(AND(OR(G202="Aprovado",G202="Recusado"),H202&lt;&gt;"",A202&lt;&gt;""),H202-A202,"")</f>
+        <f>IF(AND(OR(G202="Aprovado",G202="Recusado"),H202&lt;&gt;"",A202&lt;&gt;"",H202&gt;=A202),H202-A202,"")</f>
         <v/>
       </c>
       <c r="O202" s="25">
@@ -11900,7 +11930,7 @@
         <v/>
       </c>
       <c r="N203" s="29">
-        <f>IF(AND(OR(G203="Aprovado",G203="Recusado"),H203&lt;&gt;"",A203&lt;&gt;""),H203-A203,"")</f>
+        <f>IF(AND(OR(G203="Aprovado",G203="Recusado"),H203&lt;&gt;"",A203&lt;&gt;"",H203&gt;=A203),H203-A203,"")</f>
         <v/>
       </c>
       <c r="O203" s="25">
@@ -11940,7 +11970,7 @@
         <v/>
       </c>
       <c r="N204" s="29">
-        <f>IF(AND(OR(G204="Aprovado",G204="Recusado"),H204&lt;&gt;"",A204&lt;&gt;""),H204-A204,"")</f>
+        <f>IF(AND(OR(G204="Aprovado",G204="Recusado"),H204&lt;&gt;"",A204&lt;&gt;"",H204&gt;=A204),H204-A204,"")</f>
         <v/>
       </c>
       <c r="O204" s="25">
@@ -11980,7 +12010,7 @@
         <v/>
       </c>
       <c r="N205" s="29">
-        <f>IF(AND(OR(G205="Aprovado",G205="Recusado"),H205&lt;&gt;"",A205&lt;&gt;""),H205-A205,"")</f>
+        <f>IF(AND(OR(G205="Aprovado",G205="Recusado"),H205&lt;&gt;"",A205&lt;&gt;"",H205&gt;=A205),H205-A205,"")</f>
         <v/>
       </c>
       <c r="O205" s="25">
@@ -12020,7 +12050,7 @@
         <v/>
       </c>
       <c r="N206" s="29">
-        <f>IF(AND(OR(G206="Aprovado",G206="Recusado"),H206&lt;&gt;"",A206&lt;&gt;""),H206-A206,"")</f>
+        <f>IF(AND(OR(G206="Aprovado",G206="Recusado"),H206&lt;&gt;"",A206&lt;&gt;"",H206&gt;=A206),H206-A206,"")</f>
         <v/>
       </c>
       <c r="O206" s="25">
@@ -12060,7 +12090,7 @@
         <v/>
       </c>
       <c r="N207" s="29">
-        <f>IF(AND(OR(G207="Aprovado",G207="Recusado"),H207&lt;&gt;"",A207&lt;&gt;""),H207-A207,"")</f>
+        <f>IF(AND(OR(G207="Aprovado",G207="Recusado"),H207&lt;&gt;"",A207&lt;&gt;"",H207&gt;=A207),H207-A207,"")</f>
         <v/>
       </c>
       <c r="O207" s="25">
@@ -12100,7 +12130,7 @@
         <v/>
       </c>
       <c r="N208" s="29">
-        <f>IF(AND(OR(G208="Aprovado",G208="Recusado"),H208&lt;&gt;"",A208&lt;&gt;""),H208-A208,"")</f>
+        <f>IF(AND(OR(G208="Aprovado",G208="Recusado"),H208&lt;&gt;"",A208&lt;&gt;"",H208&gt;=A208),H208-A208,"")</f>
         <v/>
       </c>
       <c r="O208" s="25">
@@ -12140,7 +12170,7 @@
         <v/>
       </c>
       <c r="N209" s="29">
-        <f>IF(AND(OR(G209="Aprovado",G209="Recusado"),H209&lt;&gt;"",A209&lt;&gt;""),H209-A209,"")</f>
+        <f>IF(AND(OR(G209="Aprovado",G209="Recusado"),H209&lt;&gt;"",A209&lt;&gt;"",H209&gt;=A209),H209-A209,"")</f>
         <v/>
       </c>
       <c r="O209" s="25">
@@ -12180,7 +12210,7 @@
         <v/>
       </c>
       <c r="N210" s="29">
-        <f>IF(AND(OR(G210="Aprovado",G210="Recusado"),H210&lt;&gt;"",A210&lt;&gt;""),H210-A210,"")</f>
+        <f>IF(AND(OR(G210="Aprovado",G210="Recusado"),H210&lt;&gt;"",A210&lt;&gt;"",H210&gt;=A210),H210-A210,"")</f>
         <v/>
       </c>
       <c r="O210" s="25">
@@ -12220,7 +12250,7 @@
         <v/>
       </c>
       <c r="N211" s="29">
-        <f>IF(AND(OR(G211="Aprovado",G211="Recusado"),H211&lt;&gt;"",A211&lt;&gt;""),H211-A211,"")</f>
+        <f>IF(AND(OR(G211="Aprovado",G211="Recusado"),H211&lt;&gt;"",A211&lt;&gt;"",H211&gt;=A211),H211-A211,"")</f>
         <v/>
       </c>
       <c r="O211" s="25">
@@ -12260,7 +12290,7 @@
         <v/>
       </c>
       <c r="N212" s="29">
-        <f>IF(AND(OR(G212="Aprovado",G212="Recusado"),H212&lt;&gt;"",A212&lt;&gt;""),H212-A212,"")</f>
+        <f>IF(AND(OR(G212="Aprovado",G212="Recusado"),H212&lt;&gt;"",A212&lt;&gt;"",H212&gt;=A212),H212-A212,"")</f>
         <v/>
       </c>
       <c r="O212" s="25">
@@ -12300,7 +12330,7 @@
         <v/>
       </c>
       <c r="N213" s="29">
-        <f>IF(AND(OR(G213="Aprovado",G213="Recusado"),H213&lt;&gt;"",A213&lt;&gt;""),H213-A213,"")</f>
+        <f>IF(AND(OR(G213="Aprovado",G213="Recusado"),H213&lt;&gt;"",A213&lt;&gt;"",H213&gt;=A213),H213-A213,"")</f>
         <v/>
       </c>
       <c r="O213" s="25">
@@ -12340,7 +12370,7 @@
         <v/>
       </c>
       <c r="N214" s="29">
-        <f>IF(AND(OR(G214="Aprovado",G214="Recusado"),H214&lt;&gt;"",A214&lt;&gt;""),H214-A214,"")</f>
+        <f>IF(AND(OR(G214="Aprovado",G214="Recusado"),H214&lt;&gt;"",A214&lt;&gt;"",H214&gt;=A214),H214-A214,"")</f>
         <v/>
       </c>
       <c r="O214" s="25">
@@ -12380,7 +12410,7 @@
         <v/>
       </c>
       <c r="N215" s="29">
-        <f>IF(AND(OR(G215="Aprovado",G215="Recusado"),H215&lt;&gt;"",A215&lt;&gt;""),H215-A215,"")</f>
+        <f>IF(AND(OR(G215="Aprovado",G215="Recusado"),H215&lt;&gt;"",A215&lt;&gt;"",H215&gt;=A215),H215-A215,"")</f>
         <v/>
       </c>
       <c r="O215" s="25">
@@ -12420,7 +12450,7 @@
         <v/>
       </c>
       <c r="N216" s="29">
-        <f>IF(AND(OR(G216="Aprovado",G216="Recusado"),H216&lt;&gt;"",A216&lt;&gt;""),H216-A216,"")</f>
+        <f>IF(AND(OR(G216="Aprovado",G216="Recusado"),H216&lt;&gt;"",A216&lt;&gt;"",H216&gt;=A216),H216-A216,"")</f>
         <v/>
       </c>
       <c r="O216" s="25">
@@ -12460,7 +12490,7 @@
         <v/>
       </c>
       <c r="N217" s="29">
-        <f>IF(AND(OR(G217="Aprovado",G217="Recusado"),H217&lt;&gt;"",A217&lt;&gt;""),H217-A217,"")</f>
+        <f>IF(AND(OR(G217="Aprovado",G217="Recusado"),H217&lt;&gt;"",A217&lt;&gt;"",H217&gt;=A217),H217-A217,"")</f>
         <v/>
       </c>
       <c r="O217" s="25">
@@ -12500,7 +12530,7 @@
         <v/>
       </c>
       <c r="N218" s="29">
-        <f>IF(AND(OR(G218="Aprovado",G218="Recusado"),H218&lt;&gt;"",A218&lt;&gt;""),H218-A218,"")</f>
+        <f>IF(AND(OR(G218="Aprovado",G218="Recusado"),H218&lt;&gt;"",A218&lt;&gt;"",H218&gt;=A218),H218-A218,"")</f>
         <v/>
       </c>
       <c r="O218" s="25">
@@ -12540,7 +12570,7 @@
         <v/>
       </c>
       <c r="N219" s="29">
-        <f>IF(AND(OR(G219="Aprovado",G219="Recusado"),H219&lt;&gt;"",A219&lt;&gt;""),H219-A219,"")</f>
+        <f>IF(AND(OR(G219="Aprovado",G219="Recusado"),H219&lt;&gt;"",A219&lt;&gt;"",H219&gt;=A219),H219-A219,"")</f>
         <v/>
       </c>
       <c r="O219" s="25">
@@ -12580,7 +12610,7 @@
         <v/>
       </c>
       <c r="N220" s="29">
-        <f>IF(AND(OR(G220="Aprovado",G220="Recusado"),H220&lt;&gt;"",A220&lt;&gt;""),H220-A220,"")</f>
+        <f>IF(AND(OR(G220="Aprovado",G220="Recusado"),H220&lt;&gt;"",A220&lt;&gt;"",H220&gt;=A220),H220-A220,"")</f>
         <v/>
       </c>
       <c r="O220" s="25">
@@ -12620,7 +12650,7 @@
         <v/>
       </c>
       <c r="N221" s="29">
-        <f>IF(AND(OR(G221="Aprovado",G221="Recusado"),H221&lt;&gt;"",A221&lt;&gt;""),H221-A221,"")</f>
+        <f>IF(AND(OR(G221="Aprovado",G221="Recusado"),H221&lt;&gt;"",A221&lt;&gt;"",H221&gt;=A221),H221-A221,"")</f>
         <v/>
       </c>
       <c r="O221" s="25">
@@ -12660,7 +12690,7 @@
         <v/>
       </c>
       <c r="N222" s="29">
-        <f>IF(AND(OR(G222="Aprovado",G222="Recusado"),H222&lt;&gt;"",A222&lt;&gt;""),H222-A222,"")</f>
+        <f>IF(AND(OR(G222="Aprovado",G222="Recusado"),H222&lt;&gt;"",A222&lt;&gt;"",H222&gt;=A222),H222-A222,"")</f>
         <v/>
       </c>
       <c r="O222" s="25">
@@ -12700,7 +12730,7 @@
         <v/>
       </c>
       <c r="N223" s="29">
-        <f>IF(AND(OR(G223="Aprovado",G223="Recusado"),H223&lt;&gt;"",A223&lt;&gt;""),H223-A223,"")</f>
+        <f>IF(AND(OR(G223="Aprovado",G223="Recusado"),H223&lt;&gt;"",A223&lt;&gt;"",H223&gt;=A223),H223-A223,"")</f>
         <v/>
       </c>
       <c r="O223" s="25">
@@ -12740,7 +12770,7 @@
         <v/>
       </c>
       <c r="N224" s="29">
-        <f>IF(AND(OR(G224="Aprovado",G224="Recusado"),H224&lt;&gt;"",A224&lt;&gt;""),H224-A224,"")</f>
+        <f>IF(AND(OR(G224="Aprovado",G224="Recusado"),H224&lt;&gt;"",A224&lt;&gt;"",H224&gt;=A224),H224-A224,"")</f>
         <v/>
       </c>
       <c r="O224" s="25">
@@ -12780,7 +12810,7 @@
         <v/>
       </c>
       <c r="N225" s="29">
-        <f>IF(AND(OR(G225="Aprovado",G225="Recusado"),H225&lt;&gt;"",A225&lt;&gt;""),H225-A225,"")</f>
+        <f>IF(AND(OR(G225="Aprovado",G225="Recusado"),H225&lt;&gt;"",A225&lt;&gt;"",H225&gt;=A225),H225-A225,"")</f>
         <v/>
       </c>
       <c r="O225" s="25">
@@ -12820,7 +12850,7 @@
         <v/>
       </c>
       <c r="N226" s="29">
-        <f>IF(AND(OR(G226="Aprovado",G226="Recusado"),H226&lt;&gt;"",A226&lt;&gt;""),H226-A226,"")</f>
+        <f>IF(AND(OR(G226="Aprovado",G226="Recusado"),H226&lt;&gt;"",A226&lt;&gt;"",H226&gt;=A226),H226-A226,"")</f>
         <v/>
       </c>
       <c r="O226" s="25">
@@ -12860,7 +12890,7 @@
         <v/>
       </c>
       <c r="N227" s="29">
-        <f>IF(AND(OR(G227="Aprovado",G227="Recusado"),H227&lt;&gt;"",A227&lt;&gt;""),H227-A227,"")</f>
+        <f>IF(AND(OR(G227="Aprovado",G227="Recusado"),H227&lt;&gt;"",A227&lt;&gt;"",H227&gt;=A227),H227-A227,"")</f>
         <v/>
       </c>
       <c r="O227" s="25">
@@ -12900,7 +12930,7 @@
         <v/>
       </c>
       <c r="N228" s="29">
-        <f>IF(AND(OR(G228="Aprovado",G228="Recusado"),H228&lt;&gt;"",A228&lt;&gt;""),H228-A228,"")</f>
+        <f>IF(AND(OR(G228="Aprovado",G228="Recusado"),H228&lt;&gt;"",A228&lt;&gt;"",H228&gt;=A228),H228-A228,"")</f>
         <v/>
       </c>
       <c r="O228" s="25">
@@ -12940,7 +12970,7 @@
         <v/>
       </c>
       <c r="N229" s="29">
-        <f>IF(AND(OR(G229="Aprovado",G229="Recusado"),H229&lt;&gt;"",A229&lt;&gt;""),H229-A229,"")</f>
+        <f>IF(AND(OR(G229="Aprovado",G229="Recusado"),H229&lt;&gt;"",A229&lt;&gt;"",H229&gt;=A229),H229-A229,"")</f>
         <v/>
       </c>
       <c r="O229" s="25">
@@ -12980,7 +13010,7 @@
         <v/>
       </c>
       <c r="N230" s="29">
-        <f>IF(AND(OR(G230="Aprovado",G230="Recusado"),H230&lt;&gt;"",A230&lt;&gt;""),H230-A230,"")</f>
+        <f>IF(AND(OR(G230="Aprovado",G230="Recusado"),H230&lt;&gt;"",A230&lt;&gt;"",H230&gt;=A230),H230-A230,"")</f>
         <v/>
       </c>
       <c r="O230" s="25">
@@ -13020,7 +13050,7 @@
         <v/>
       </c>
       <c r="N231" s="29">
-        <f>IF(AND(OR(G231="Aprovado",G231="Recusado"),H231&lt;&gt;"",A231&lt;&gt;""),H231-A231,"")</f>
+        <f>IF(AND(OR(G231="Aprovado",G231="Recusado"),H231&lt;&gt;"",A231&lt;&gt;"",H231&gt;=A231),H231-A231,"")</f>
         <v/>
       </c>
       <c r="O231" s="25">
@@ -13060,7 +13090,7 @@
         <v/>
       </c>
       <c r="N232" s="29">
-        <f>IF(AND(OR(G232="Aprovado",G232="Recusado"),H232&lt;&gt;"",A232&lt;&gt;""),H232-A232,"")</f>
+        <f>IF(AND(OR(G232="Aprovado",G232="Recusado"),H232&lt;&gt;"",A232&lt;&gt;"",H232&gt;=A232),H232-A232,"")</f>
         <v/>
       </c>
       <c r="O232" s="25">
@@ -13100,7 +13130,7 @@
         <v/>
       </c>
       <c r="N233" s="29">
-        <f>IF(AND(OR(G233="Aprovado",G233="Recusado"),H233&lt;&gt;"",A233&lt;&gt;""),H233-A233,"")</f>
+        <f>IF(AND(OR(G233="Aprovado",G233="Recusado"),H233&lt;&gt;"",A233&lt;&gt;"",H233&gt;=A233),H233-A233,"")</f>
         <v/>
       </c>
       <c r="O233" s="25">
@@ -13140,7 +13170,7 @@
         <v/>
       </c>
       <c r="N234" s="29">
-        <f>IF(AND(OR(G234="Aprovado",G234="Recusado"),H234&lt;&gt;"",A234&lt;&gt;""),H234-A234,"")</f>
+        <f>IF(AND(OR(G234="Aprovado",G234="Recusado"),H234&lt;&gt;"",A234&lt;&gt;"",H234&gt;=A234),H234-A234,"")</f>
         <v/>
       </c>
       <c r="O234" s="25">
@@ -13180,7 +13210,7 @@
         <v/>
       </c>
       <c r="N235" s="29">
-        <f>IF(AND(OR(G235="Aprovado",G235="Recusado"),H235&lt;&gt;"",A235&lt;&gt;""),H235-A235,"")</f>
+        <f>IF(AND(OR(G235="Aprovado",G235="Recusado"),H235&lt;&gt;"",A235&lt;&gt;"",H235&gt;=A235),H235-A235,"")</f>
         <v/>
       </c>
       <c r="O235" s="25">
@@ -13220,7 +13250,7 @@
         <v/>
       </c>
       <c r="N236" s="29">
-        <f>IF(AND(OR(G236="Aprovado",G236="Recusado"),H236&lt;&gt;"",A236&lt;&gt;""),H236-A236,"")</f>
+        <f>IF(AND(OR(G236="Aprovado",G236="Recusado"),H236&lt;&gt;"",A236&lt;&gt;"",H236&gt;=A236),H236-A236,"")</f>
         <v/>
       </c>
       <c r="O236" s="25">
@@ -13260,7 +13290,7 @@
         <v/>
       </c>
       <c r="N237" s="29">
-        <f>IF(AND(OR(G237="Aprovado",G237="Recusado"),H237&lt;&gt;"",A237&lt;&gt;""),H237-A237,"")</f>
+        <f>IF(AND(OR(G237="Aprovado",G237="Recusado"),H237&lt;&gt;"",A237&lt;&gt;"",H237&gt;=A237),H237-A237,"")</f>
         <v/>
       </c>
       <c r="O237" s="25">
@@ -13300,7 +13330,7 @@
         <v/>
       </c>
       <c r="N238" s="29">
-        <f>IF(AND(OR(G238="Aprovado",G238="Recusado"),H238&lt;&gt;"",A238&lt;&gt;""),H238-A238,"")</f>
+        <f>IF(AND(OR(G238="Aprovado",G238="Recusado"),H238&lt;&gt;"",A238&lt;&gt;"",H238&gt;=A238),H238-A238,"")</f>
         <v/>
       </c>
       <c r="O238" s="25">
@@ -13340,7 +13370,7 @@
         <v/>
       </c>
       <c r="N239" s="29">
-        <f>IF(AND(OR(G239="Aprovado",G239="Recusado"),H239&lt;&gt;"",A239&lt;&gt;""),H239-A239,"")</f>
+        <f>IF(AND(OR(G239="Aprovado",G239="Recusado"),H239&lt;&gt;"",A239&lt;&gt;"",H239&gt;=A239),H239-A239,"")</f>
         <v/>
       </c>
       <c r="O239" s="25">
@@ -13380,7 +13410,7 @@
         <v/>
       </c>
       <c r="N240" s="29">
-        <f>IF(AND(OR(G240="Aprovado",G240="Recusado"),H240&lt;&gt;"",A240&lt;&gt;""),H240-A240,"")</f>
+        <f>IF(AND(OR(G240="Aprovado",G240="Recusado"),H240&lt;&gt;"",A240&lt;&gt;"",H240&gt;=A240),H240-A240,"")</f>
         <v/>
       </c>
       <c r="O240" s="25">
@@ -13420,7 +13450,7 @@
         <v/>
       </c>
       <c r="N241" s="29">
-        <f>IF(AND(OR(G241="Aprovado",G241="Recusado"),H241&lt;&gt;"",A241&lt;&gt;""),H241-A241,"")</f>
+        <f>IF(AND(OR(G241="Aprovado",G241="Recusado"),H241&lt;&gt;"",A241&lt;&gt;"",H241&gt;=A241),H241-A241,"")</f>
         <v/>
       </c>
       <c r="O241" s="25">
@@ -13460,7 +13490,7 @@
         <v/>
       </c>
       <c r="N242" s="29">
-        <f>IF(AND(OR(G242="Aprovado",G242="Recusado"),H242&lt;&gt;"",A242&lt;&gt;""),H242-A242,"")</f>
+        <f>IF(AND(OR(G242="Aprovado",G242="Recusado"),H242&lt;&gt;"",A242&lt;&gt;"",H242&gt;=A242),H242-A242,"")</f>
         <v/>
       </c>
       <c r="O242" s="25">
@@ -13500,7 +13530,7 @@
         <v/>
       </c>
       <c r="N243" s="29">
-        <f>IF(AND(OR(G243="Aprovado",G243="Recusado"),H243&lt;&gt;"",A243&lt;&gt;""),H243-A243,"")</f>
+        <f>IF(AND(OR(G243="Aprovado",G243="Recusado"),H243&lt;&gt;"",A243&lt;&gt;"",H243&gt;=A243),H243-A243,"")</f>
         <v/>
       </c>
       <c r="O243" s="25">
@@ -13540,7 +13570,7 @@
         <v/>
       </c>
       <c r="N244" s="29">
-        <f>IF(AND(OR(G244="Aprovado",G244="Recusado"),H244&lt;&gt;"",A244&lt;&gt;""),H244-A244,"")</f>
+        <f>IF(AND(OR(G244="Aprovado",G244="Recusado"),H244&lt;&gt;"",A244&lt;&gt;"",H244&gt;=A244),H244-A244,"")</f>
         <v/>
       </c>
       <c r="O244" s="25">
@@ -13580,7 +13610,7 @@
         <v/>
       </c>
       <c r="N245" s="29">
-        <f>IF(AND(OR(G245="Aprovado",G245="Recusado"),H245&lt;&gt;"",A245&lt;&gt;""),H245-A245,"")</f>
+        <f>IF(AND(OR(G245="Aprovado",G245="Recusado"),H245&lt;&gt;"",A245&lt;&gt;"",H245&gt;=A245),H245-A245,"")</f>
         <v/>
       </c>
       <c r="O245" s="25">
@@ -13620,7 +13650,7 @@
         <v/>
       </c>
       <c r="N246" s="29">
-        <f>IF(AND(OR(G246="Aprovado",G246="Recusado"),H246&lt;&gt;"",A246&lt;&gt;""),H246-A246,"")</f>
+        <f>IF(AND(OR(G246="Aprovado",G246="Recusado"),H246&lt;&gt;"",A246&lt;&gt;"",H246&gt;=A246),H246-A246,"")</f>
         <v/>
       </c>
       <c r="O246" s="25">
@@ -13660,7 +13690,7 @@
         <v/>
       </c>
       <c r="N247" s="29">
-        <f>IF(AND(OR(G247="Aprovado",G247="Recusado"),H247&lt;&gt;"",A247&lt;&gt;""),H247-A247,"")</f>
+        <f>IF(AND(OR(G247="Aprovado",G247="Recusado"),H247&lt;&gt;"",A247&lt;&gt;"",H247&gt;=A247),H247-A247,"")</f>
         <v/>
       </c>
       <c r="O247" s="25">
@@ -13700,7 +13730,7 @@
         <v/>
       </c>
       <c r="N248" s="29">
-        <f>IF(AND(OR(G248="Aprovado",G248="Recusado"),H248&lt;&gt;"",A248&lt;&gt;""),H248-A248,"")</f>
+        <f>IF(AND(OR(G248="Aprovado",G248="Recusado"),H248&lt;&gt;"",A248&lt;&gt;"",H248&gt;=A248),H248-A248,"")</f>
         <v/>
       </c>
       <c r="O248" s="25">
@@ -13740,7 +13770,7 @@
         <v/>
       </c>
       <c r="N249" s="29">
-        <f>IF(AND(OR(G249="Aprovado",G249="Recusado"),H249&lt;&gt;"",A249&lt;&gt;""),H249-A249,"")</f>
+        <f>IF(AND(OR(G249="Aprovado",G249="Recusado"),H249&lt;&gt;"",A249&lt;&gt;"",H249&gt;=A249),H249-A249,"")</f>
         <v/>
       </c>
       <c r="O249" s="25">
@@ -13780,7 +13810,7 @@
         <v/>
       </c>
       <c r="N250" s="29">
-        <f>IF(AND(OR(G250="Aprovado",G250="Recusado"),H250&lt;&gt;"",A250&lt;&gt;""),H250-A250,"")</f>
+        <f>IF(AND(OR(G250="Aprovado",G250="Recusado"),H250&lt;&gt;"",A250&lt;&gt;"",H250&gt;=A250),H250-A250,"")</f>
         <v/>
       </c>
       <c r="O250" s="25">
@@ -13820,7 +13850,7 @@
         <v/>
       </c>
       <c r="N251" s="29">
-        <f>IF(AND(OR(G251="Aprovado",G251="Recusado"),H251&lt;&gt;"",A251&lt;&gt;""),H251-A251,"")</f>
+        <f>IF(AND(OR(G251="Aprovado",G251="Recusado"),H251&lt;&gt;"",A251&lt;&gt;"",H251&gt;=A251),H251-A251,"")</f>
         <v/>
       </c>
       <c r="O251" s="25">
@@ -13860,7 +13890,7 @@
         <v/>
       </c>
       <c r="N252" s="29">
-        <f>IF(AND(OR(G252="Aprovado",G252="Recusado"),H252&lt;&gt;"",A252&lt;&gt;""),H252-A252,"")</f>
+        <f>IF(AND(OR(G252="Aprovado",G252="Recusado"),H252&lt;&gt;"",A252&lt;&gt;"",H252&gt;=A252),H252-A252,"")</f>
         <v/>
       </c>
       <c r="O252" s="25">
@@ -13900,7 +13930,7 @@
         <v/>
       </c>
       <c r="N253" s="29">
-        <f>IF(AND(OR(G253="Aprovado",G253="Recusado"),H253&lt;&gt;"",A253&lt;&gt;""),H253-A253,"")</f>
+        <f>IF(AND(OR(G253="Aprovado",G253="Recusado"),H253&lt;&gt;"",A253&lt;&gt;"",H253&gt;=A253),H253-A253,"")</f>
         <v/>
       </c>
       <c r="O253" s="25">
@@ -13940,7 +13970,7 @@
         <v/>
       </c>
       <c r="N254" s="29">
-        <f>IF(AND(OR(G254="Aprovado",G254="Recusado"),H254&lt;&gt;"",A254&lt;&gt;""),H254-A254,"")</f>
+        <f>IF(AND(OR(G254="Aprovado",G254="Recusado"),H254&lt;&gt;"",A254&lt;&gt;"",H254&gt;=A254),H254-A254,"")</f>
         <v/>
       </c>
       <c r="O254" s="25">
@@ -13980,7 +14010,7 @@
         <v/>
       </c>
       <c r="N255" s="29">
-        <f>IF(AND(OR(G255="Aprovado",G255="Recusado"),H255&lt;&gt;"",A255&lt;&gt;""),H255-A255,"")</f>
+        <f>IF(AND(OR(G255="Aprovado",G255="Recusado"),H255&lt;&gt;"",A255&lt;&gt;"",H255&gt;=A255),H255-A255,"")</f>
         <v/>
       </c>
       <c r="O255" s="25">
@@ -14020,7 +14050,7 @@
         <v/>
       </c>
       <c r="N256" s="29">
-        <f>IF(AND(OR(G256="Aprovado",G256="Recusado"),H256&lt;&gt;"",A256&lt;&gt;""),H256-A256,"")</f>
+        <f>IF(AND(OR(G256="Aprovado",G256="Recusado"),H256&lt;&gt;"",A256&lt;&gt;"",H256&gt;=A256),H256-A256,"")</f>
         <v/>
       </c>
       <c r="O256" s="25">
@@ -14060,7 +14090,7 @@
         <v/>
       </c>
       <c r="N257" s="29">
-        <f>IF(AND(OR(G257="Aprovado",G257="Recusado"),H257&lt;&gt;"",A257&lt;&gt;""),H257-A257,"")</f>
+        <f>IF(AND(OR(G257="Aprovado",G257="Recusado"),H257&lt;&gt;"",A257&lt;&gt;"",H257&gt;=A257),H257-A257,"")</f>
         <v/>
       </c>
       <c r="O257" s="25">
@@ -14100,7 +14130,7 @@
         <v/>
       </c>
       <c r="N258" s="29">
-        <f>IF(AND(OR(G258="Aprovado",G258="Recusado"),H258&lt;&gt;"",A258&lt;&gt;""),H258-A258,"")</f>
+        <f>IF(AND(OR(G258="Aprovado",G258="Recusado"),H258&lt;&gt;"",A258&lt;&gt;"",H258&gt;=A258),H258-A258,"")</f>
         <v/>
       </c>
       <c r="O258" s="25">
@@ -14140,7 +14170,7 @@
         <v/>
       </c>
       <c r="N259" s="29">
-        <f>IF(AND(OR(G259="Aprovado",G259="Recusado"),H259&lt;&gt;"",A259&lt;&gt;""),H259-A259,"")</f>
+        <f>IF(AND(OR(G259="Aprovado",G259="Recusado"),H259&lt;&gt;"",A259&lt;&gt;"",H259&gt;=A259),H259-A259,"")</f>
         <v/>
       </c>
       <c r="O259" s="25">
@@ -14180,7 +14210,7 @@
         <v/>
       </c>
       <c r="N260" s="29">
-        <f>IF(AND(OR(G260="Aprovado",G260="Recusado"),H260&lt;&gt;"",A260&lt;&gt;""),H260-A260,"")</f>
+        <f>IF(AND(OR(G260="Aprovado",G260="Recusado"),H260&lt;&gt;"",A260&lt;&gt;"",H260&gt;=A260),H260-A260,"")</f>
         <v/>
       </c>
       <c r="O260" s="25">
@@ -14220,7 +14250,7 @@
         <v/>
       </c>
       <c r="N261" s="29">
-        <f>IF(AND(OR(G261="Aprovado",G261="Recusado"),H261&lt;&gt;"",A261&lt;&gt;""),H261-A261,"")</f>
+        <f>IF(AND(OR(G261="Aprovado",G261="Recusado"),H261&lt;&gt;"",A261&lt;&gt;"",H261&gt;=A261),H261-A261,"")</f>
         <v/>
       </c>
       <c r="O261" s="25">
@@ -14260,7 +14290,7 @@
         <v/>
       </c>
       <c r="N262" s="29">
-        <f>IF(AND(OR(G262="Aprovado",G262="Recusado"),H262&lt;&gt;"",A262&lt;&gt;""),H262-A262,"")</f>
+        <f>IF(AND(OR(G262="Aprovado",G262="Recusado"),H262&lt;&gt;"",A262&lt;&gt;"",H262&gt;=A262),H262-A262,"")</f>
         <v/>
       </c>
       <c r="O262" s="25">
@@ -14300,7 +14330,7 @@
         <v/>
       </c>
       <c r="N263" s="29">
-        <f>IF(AND(OR(G263="Aprovado",G263="Recusado"),H263&lt;&gt;"",A263&lt;&gt;""),H263-A263,"")</f>
+        <f>IF(AND(OR(G263="Aprovado",G263="Recusado"),H263&lt;&gt;"",A263&lt;&gt;"",H263&gt;=A263),H263-A263,"")</f>
         <v/>
       </c>
       <c r="O263" s="25">
@@ -14340,7 +14370,7 @@
         <v/>
       </c>
       <c r="N264" s="29">
-        <f>IF(AND(OR(G264="Aprovado",G264="Recusado"),H264&lt;&gt;"",A264&lt;&gt;""),H264-A264,"")</f>
+        <f>IF(AND(OR(G264="Aprovado",G264="Recusado"),H264&lt;&gt;"",A264&lt;&gt;"",H264&gt;=A264),H264-A264,"")</f>
         <v/>
       </c>
       <c r="O264" s="25">
@@ -14380,7 +14410,7 @@
         <v/>
       </c>
       <c r="N265" s="29">
-        <f>IF(AND(OR(G265="Aprovado",G265="Recusado"),H265&lt;&gt;"",A265&lt;&gt;""),H265-A265,"")</f>
+        <f>IF(AND(OR(G265="Aprovado",G265="Recusado"),H265&lt;&gt;"",A265&lt;&gt;"",H265&gt;=A265),H265-A265,"")</f>
         <v/>
       </c>
       <c r="O265" s="25">
@@ -14420,7 +14450,7 @@
         <v/>
       </c>
       <c r="N266" s="29">
-        <f>IF(AND(OR(G266="Aprovado",G266="Recusado"),H266&lt;&gt;"",A266&lt;&gt;""),H266-A266,"")</f>
+        <f>IF(AND(OR(G266="Aprovado",G266="Recusado"),H266&lt;&gt;"",A266&lt;&gt;"",H266&gt;=A266),H266-A266,"")</f>
         <v/>
       </c>
       <c r="O266" s="25">
@@ -14460,7 +14490,7 @@
         <v/>
       </c>
       <c r="N267" s="29">
-        <f>IF(AND(OR(G267="Aprovado",G267="Recusado"),H267&lt;&gt;"",A267&lt;&gt;""),H267-A267,"")</f>
+        <f>IF(AND(OR(G267="Aprovado",G267="Recusado"),H267&lt;&gt;"",A267&lt;&gt;"",H267&gt;=A267),H267-A267,"")</f>
         <v/>
       </c>
       <c r="O267" s="25">
@@ -14500,7 +14530,7 @@
         <v/>
       </c>
       <c r="N268" s="29">
-        <f>IF(AND(OR(G268="Aprovado",G268="Recusado"),H268&lt;&gt;"",A268&lt;&gt;""),H268-A268,"")</f>
+        <f>IF(AND(OR(G268="Aprovado",G268="Recusado"),H268&lt;&gt;"",A268&lt;&gt;"",H268&gt;=A268),H268-A268,"")</f>
         <v/>
       </c>
       <c r="O268" s="25">
@@ -14540,7 +14570,7 @@
         <v/>
       </c>
       <c r="N269" s="29">
-        <f>IF(AND(OR(G269="Aprovado",G269="Recusado"),H269&lt;&gt;"",A269&lt;&gt;""),H269-A269,"")</f>
+        <f>IF(AND(OR(G269="Aprovado",G269="Recusado"),H269&lt;&gt;"",A269&lt;&gt;"",H269&gt;=A269),H269-A269,"")</f>
         <v/>
       </c>
       <c r="O269" s="25">
@@ -14580,7 +14610,7 @@
         <v/>
       </c>
       <c r="N270" s="29">
-        <f>IF(AND(OR(G270="Aprovado",G270="Recusado"),H270&lt;&gt;"",A270&lt;&gt;""),H270-A270,"")</f>
+        <f>IF(AND(OR(G270="Aprovado",G270="Recusado"),H270&lt;&gt;"",A270&lt;&gt;"",H270&gt;=A270),H270-A270,"")</f>
         <v/>
       </c>
       <c r="O270" s="25">
@@ -14620,7 +14650,7 @@
         <v/>
       </c>
       <c r="N271" s="29">
-        <f>IF(AND(OR(G271="Aprovado",G271="Recusado"),H271&lt;&gt;"",A271&lt;&gt;""),H271-A271,"")</f>
+        <f>IF(AND(OR(G271="Aprovado",G271="Recusado"),H271&lt;&gt;"",A271&lt;&gt;"",H271&gt;=A271),H271-A271,"")</f>
         <v/>
       </c>
       <c r="O271" s="25">
@@ -14660,7 +14690,7 @@
         <v/>
       </c>
       <c r="N272" s="29">
-        <f>IF(AND(OR(G272="Aprovado",G272="Recusado"),H272&lt;&gt;"",A272&lt;&gt;""),H272-A272,"")</f>
+        <f>IF(AND(OR(G272="Aprovado",G272="Recusado"),H272&lt;&gt;"",A272&lt;&gt;"",H272&gt;=A272),H272-A272,"")</f>
         <v/>
       </c>
       <c r="O272" s="25">
@@ -14700,7 +14730,7 @@
         <v/>
       </c>
       <c r="N273" s="29">
-        <f>IF(AND(OR(G273="Aprovado",G273="Recusado"),H273&lt;&gt;"",A273&lt;&gt;""),H273-A273,"")</f>
+        <f>IF(AND(OR(G273="Aprovado",G273="Recusado"),H273&lt;&gt;"",A273&lt;&gt;"",H273&gt;=A273),H273-A273,"")</f>
         <v/>
       </c>
       <c r="O273" s="25">
@@ -14740,7 +14770,7 @@
         <v/>
       </c>
       <c r="N274" s="29">
-        <f>IF(AND(OR(G274="Aprovado",G274="Recusado"),H274&lt;&gt;"",A274&lt;&gt;""),H274-A274,"")</f>
+        <f>IF(AND(OR(G274="Aprovado",G274="Recusado"),H274&lt;&gt;"",A274&lt;&gt;"",H274&gt;=A274),H274-A274,"")</f>
         <v/>
       </c>
       <c r="O274" s="25">
@@ -14780,7 +14810,7 @@
         <v/>
       </c>
       <c r="N275" s="29">
-        <f>IF(AND(OR(G275="Aprovado",G275="Recusado"),H275&lt;&gt;"",A275&lt;&gt;""),H275-A275,"")</f>
+        <f>IF(AND(OR(G275="Aprovado",G275="Recusado"),H275&lt;&gt;"",A275&lt;&gt;"",H275&gt;=A275),H275-A275,"")</f>
         <v/>
       </c>
       <c r="O275" s="25">
@@ -14820,7 +14850,7 @@
         <v/>
       </c>
       <c r="N276" s="29">
-        <f>IF(AND(OR(G276="Aprovado",G276="Recusado"),H276&lt;&gt;"",A276&lt;&gt;""),H276-A276,"")</f>
+        <f>IF(AND(OR(G276="Aprovado",G276="Recusado"),H276&lt;&gt;"",A276&lt;&gt;"",H276&gt;=A276),H276-A276,"")</f>
         <v/>
       </c>
       <c r="O276" s="25">
@@ -14860,7 +14890,7 @@
         <v/>
       </c>
       <c r="N277" s="29">
-        <f>IF(AND(OR(G277="Aprovado",G277="Recusado"),H277&lt;&gt;"",A277&lt;&gt;""),H277-A277,"")</f>
+        <f>IF(AND(OR(G277="Aprovado",G277="Recusado"),H277&lt;&gt;"",A277&lt;&gt;"",H277&gt;=A277),H277-A277,"")</f>
         <v/>
       </c>
       <c r="O277" s="25">
@@ -14900,7 +14930,7 @@
         <v/>
       </c>
       <c r="N278" s="29">
-        <f>IF(AND(OR(G278="Aprovado",G278="Recusado"),H278&lt;&gt;"",A278&lt;&gt;""),H278-A278,"")</f>
+        <f>IF(AND(OR(G278="Aprovado",G278="Recusado"),H278&lt;&gt;"",A278&lt;&gt;"",H278&gt;=A278),H278-A278,"")</f>
         <v/>
       </c>
       <c r="O278" s="25">
@@ -14940,7 +14970,7 @@
         <v/>
       </c>
       <c r="N279" s="29">
-        <f>IF(AND(OR(G279="Aprovado",G279="Recusado"),H279&lt;&gt;"",A279&lt;&gt;""),H279-A279,"")</f>
+        <f>IF(AND(OR(G279="Aprovado",G279="Recusado"),H279&lt;&gt;"",A279&lt;&gt;"",H279&gt;=A279),H279-A279,"")</f>
         <v/>
       </c>
       <c r="O279" s="25">
@@ -14980,7 +15010,7 @@
         <v/>
       </c>
       <c r="N280" s="29">
-        <f>IF(AND(OR(G280="Aprovado",G280="Recusado"),H280&lt;&gt;"",A280&lt;&gt;""),H280-A280,"")</f>
+        <f>IF(AND(OR(G280="Aprovado",G280="Recusado"),H280&lt;&gt;"",A280&lt;&gt;"",H280&gt;=A280),H280-A280,"")</f>
         <v/>
       </c>
       <c r="O280" s="25">
@@ -15020,7 +15050,7 @@
         <v/>
       </c>
       <c r="N281" s="29">
-        <f>IF(AND(OR(G281="Aprovado",G281="Recusado"),H281&lt;&gt;"",A281&lt;&gt;""),H281-A281,"")</f>
+        <f>IF(AND(OR(G281="Aprovado",G281="Recusado"),H281&lt;&gt;"",A281&lt;&gt;"",H281&gt;=A281),H281-A281,"")</f>
         <v/>
       </c>
       <c r="O281" s="25">
@@ -15060,7 +15090,7 @@
         <v/>
       </c>
       <c r="N282" s="29">
-        <f>IF(AND(OR(G282="Aprovado",G282="Recusado"),H282&lt;&gt;"",A282&lt;&gt;""),H282-A282,"")</f>
+        <f>IF(AND(OR(G282="Aprovado",G282="Recusado"),H282&lt;&gt;"",A282&lt;&gt;"",H282&gt;=A282),H282-A282,"")</f>
         <v/>
       </c>
       <c r="O282" s="25">
@@ -15100,7 +15130,7 @@
         <v/>
       </c>
       <c r="N283" s="29">
-        <f>IF(AND(OR(G283="Aprovado",G283="Recusado"),H283&lt;&gt;"",A283&lt;&gt;""),H283-A283,"")</f>
+        <f>IF(AND(OR(G283="Aprovado",G283="Recusado"),H283&lt;&gt;"",A283&lt;&gt;"",H283&gt;=A283),H283-A283,"")</f>
         <v/>
       </c>
       <c r="O283" s="25">
@@ -15140,7 +15170,7 @@
         <v/>
       </c>
       <c r="N284" s="29">
-        <f>IF(AND(OR(G284="Aprovado",G284="Recusado"),H284&lt;&gt;"",A284&lt;&gt;""),H284-A284,"")</f>
+        <f>IF(AND(OR(G284="Aprovado",G284="Recusado"),H284&lt;&gt;"",A284&lt;&gt;"",H284&gt;=A284),H284-A284,"")</f>
         <v/>
       </c>
       <c r="O284" s="25">
@@ -15180,7 +15210,7 @@
         <v/>
       </c>
       <c r="N285" s="29">
-        <f>IF(AND(OR(G285="Aprovado",G285="Recusado"),H285&lt;&gt;"",A285&lt;&gt;""),H285-A285,"")</f>
+        <f>IF(AND(OR(G285="Aprovado",G285="Recusado"),H285&lt;&gt;"",A285&lt;&gt;"",H285&gt;=A285),H285-A285,"")</f>
         <v/>
       </c>
       <c r="O285" s="25">
@@ -15220,7 +15250,7 @@
         <v/>
       </c>
       <c r="N286" s="29">
-        <f>IF(AND(OR(G286="Aprovado",G286="Recusado"),H286&lt;&gt;"",A286&lt;&gt;""),H286-A286,"")</f>
+        <f>IF(AND(OR(G286="Aprovado",G286="Recusado"),H286&lt;&gt;"",A286&lt;&gt;"",H286&gt;=A286),H286-A286,"")</f>
         <v/>
       </c>
       <c r="O286" s="25">
@@ -15260,7 +15290,7 @@
         <v/>
       </c>
       <c r="N287" s="29">
-        <f>IF(AND(OR(G287="Aprovado",G287="Recusado"),H287&lt;&gt;"",A287&lt;&gt;""),H287-A287,"")</f>
+        <f>IF(AND(OR(G287="Aprovado",G287="Recusado"),H287&lt;&gt;"",A287&lt;&gt;"",H287&gt;=A287),H287-A287,"")</f>
         <v/>
       </c>
       <c r="O287" s="25">
@@ -15300,7 +15330,7 @@
         <v/>
       </c>
       <c r="N288" s="29">
-        <f>IF(AND(OR(G288="Aprovado",G288="Recusado"),H288&lt;&gt;"",A288&lt;&gt;""),H288-A288,"")</f>
+        <f>IF(AND(OR(G288="Aprovado",G288="Recusado"),H288&lt;&gt;"",A288&lt;&gt;"",H288&gt;=A288),H288-A288,"")</f>
         <v/>
       </c>
       <c r="O288" s="25">
@@ -15340,7 +15370,7 @@
         <v/>
       </c>
       <c r="N289" s="29">
-        <f>IF(AND(OR(G289="Aprovado",G289="Recusado"),H289&lt;&gt;"",A289&lt;&gt;""),H289-A289,"")</f>
+        <f>IF(AND(OR(G289="Aprovado",G289="Recusado"),H289&lt;&gt;"",A289&lt;&gt;"",H289&gt;=A289),H289-A289,"")</f>
         <v/>
       </c>
       <c r="O289" s="25">
@@ -15380,7 +15410,7 @@
         <v/>
       </c>
       <c r="N290" s="29">
-        <f>IF(AND(OR(G290="Aprovado",G290="Recusado"),H290&lt;&gt;"",A290&lt;&gt;""),H290-A290,"")</f>
+        <f>IF(AND(OR(G290="Aprovado",G290="Recusado"),H290&lt;&gt;"",A290&lt;&gt;"",H290&gt;=A290),H290-A290,"")</f>
         <v/>
       </c>
       <c r="O290" s="25">
@@ -15420,7 +15450,7 @@
         <v/>
       </c>
       <c r="N291" s="29">
-        <f>IF(AND(OR(G291="Aprovado",G291="Recusado"),H291&lt;&gt;"",A291&lt;&gt;""),H291-A291,"")</f>
+        <f>IF(AND(OR(G291="Aprovado",G291="Recusado"),H291&lt;&gt;"",A291&lt;&gt;"",H291&gt;=A291),H291-A291,"")</f>
         <v/>
       </c>
       <c r="O291" s="25">
@@ -15460,7 +15490,7 @@
         <v/>
       </c>
       <c r="N292" s="29">
-        <f>IF(AND(OR(G292="Aprovado",G292="Recusado"),H292&lt;&gt;"",A292&lt;&gt;""),H292-A292,"")</f>
+        <f>IF(AND(OR(G292="Aprovado",G292="Recusado"),H292&lt;&gt;"",A292&lt;&gt;"",H292&gt;=A292),H292-A292,"")</f>
         <v/>
       </c>
       <c r="O292" s="25">
@@ -15500,7 +15530,7 @@
         <v/>
       </c>
       <c r="N293" s="29">
-        <f>IF(AND(OR(G293="Aprovado",G293="Recusado"),H293&lt;&gt;"",A293&lt;&gt;""),H293-A293,"")</f>
+        <f>IF(AND(OR(G293="Aprovado",G293="Recusado"),H293&lt;&gt;"",A293&lt;&gt;"",H293&gt;=A293),H293-A293,"")</f>
         <v/>
       </c>
       <c r="O293" s="25">
@@ -15540,7 +15570,7 @@
         <v/>
       </c>
       <c r="N294" s="29">
-        <f>IF(AND(OR(G294="Aprovado",G294="Recusado"),H294&lt;&gt;"",A294&lt;&gt;""),H294-A294,"")</f>
+        <f>IF(AND(OR(G294="Aprovado",G294="Recusado"),H294&lt;&gt;"",A294&lt;&gt;"",H294&gt;=A294),H294-A294,"")</f>
         <v/>
       </c>
       <c r="O294" s="25">
@@ -15580,7 +15610,7 @@
         <v/>
       </c>
       <c r="N295" s="29">
-        <f>IF(AND(OR(G295="Aprovado",G295="Recusado"),H295&lt;&gt;"",A295&lt;&gt;""),H295-A295,"")</f>
+        <f>IF(AND(OR(G295="Aprovado",G295="Recusado"),H295&lt;&gt;"",A295&lt;&gt;"",H295&gt;=A295),H295-A295,"")</f>
         <v/>
       </c>
       <c r="O295" s="25">
@@ -15620,7 +15650,7 @@
         <v/>
       </c>
       <c r="N296" s="29">
-        <f>IF(AND(OR(G296="Aprovado",G296="Recusado"),H296&lt;&gt;"",A296&lt;&gt;""),H296-A296,"")</f>
+        <f>IF(AND(OR(G296="Aprovado",G296="Recusado"),H296&lt;&gt;"",A296&lt;&gt;"",H296&gt;=A296),H296-A296,"")</f>
         <v/>
       </c>
       <c r="O296" s="25">
@@ -15660,7 +15690,7 @@
         <v/>
       </c>
       <c r="N297" s="29">
-        <f>IF(AND(OR(G297="Aprovado",G297="Recusado"),H297&lt;&gt;"",A297&lt;&gt;""),H297-A297,"")</f>
+        <f>IF(AND(OR(G297="Aprovado",G297="Recusado"),H297&lt;&gt;"",A297&lt;&gt;"",H297&gt;=A297),H297-A297,"")</f>
         <v/>
       </c>
       <c r="O297" s="25">
@@ -15700,7 +15730,7 @@
         <v/>
       </c>
       <c r="N298" s="29">
-        <f>IF(AND(OR(G298="Aprovado",G298="Recusado"),H298&lt;&gt;"",A298&lt;&gt;""),H298-A298,"")</f>
+        <f>IF(AND(OR(G298="Aprovado",G298="Recusado"),H298&lt;&gt;"",A298&lt;&gt;"",H298&gt;=A298),H298-A298,"")</f>
         <v/>
       </c>
       <c r="O298" s="25">
@@ -15740,7 +15770,7 @@
         <v/>
       </c>
       <c r="N299" s="29">
-        <f>IF(AND(OR(G299="Aprovado",G299="Recusado"),H299&lt;&gt;"",A299&lt;&gt;""),H299-A299,"")</f>
+        <f>IF(AND(OR(G299="Aprovado",G299="Recusado"),H299&lt;&gt;"",A299&lt;&gt;"",H299&gt;=A299),H299-A299,"")</f>
         <v/>
       </c>
       <c r="O299" s="25">
@@ -15780,7 +15810,7 @@
         <v/>
       </c>
       <c r="N300" s="29">
-        <f>IF(AND(OR(G300="Aprovado",G300="Recusado"),H300&lt;&gt;"",A300&lt;&gt;""),H300-A300,"")</f>
+        <f>IF(AND(OR(G300="Aprovado",G300="Recusado"),H300&lt;&gt;"",A300&lt;&gt;"",H300&gt;=A300),H300-A300,"")</f>
         <v/>
       </c>
       <c r="O300" s="25">
@@ -15820,7 +15850,7 @@
         <v/>
       </c>
       <c r="N301" s="29">
-        <f>IF(AND(OR(G301="Aprovado",G301="Recusado"),H301&lt;&gt;"",A301&lt;&gt;""),H301-A301,"")</f>
+        <f>IF(AND(OR(G301="Aprovado",G301="Recusado"),H301&lt;&gt;"",A301&lt;&gt;"",H301&gt;=A301),H301-A301,"")</f>
         <v/>
       </c>
       <c r="O301" s="25">
@@ -15860,7 +15890,7 @@
         <v/>
       </c>
       <c r="N302" s="29">
-        <f>IF(AND(OR(G302="Aprovado",G302="Recusado"),H302&lt;&gt;"",A302&lt;&gt;""),H302-A302,"")</f>
+        <f>IF(AND(OR(G302="Aprovado",G302="Recusado"),H302&lt;&gt;"",A302&lt;&gt;"",H302&gt;=A302),H302-A302,"")</f>
         <v/>
       </c>
       <c r="O302" s="25">
@@ -15900,7 +15930,7 @@
         <v/>
       </c>
       <c r="N303" s="29">
-        <f>IF(AND(OR(G303="Aprovado",G303="Recusado"),H303&lt;&gt;"",A303&lt;&gt;""),H303-A303,"")</f>
+        <f>IF(AND(OR(G303="Aprovado",G303="Recusado"),H303&lt;&gt;"",A303&lt;&gt;"",H303&gt;=A303),H303-A303,"")</f>
         <v/>
       </c>
       <c r="O303" s="25">
@@ -15940,7 +15970,7 @@
         <v/>
       </c>
       <c r="N304" s="29">
-        <f>IF(AND(OR(G304="Aprovado",G304="Recusado"),H304&lt;&gt;"",A304&lt;&gt;""),H304-A304,"")</f>
+        <f>IF(AND(OR(G304="Aprovado",G304="Recusado"),H304&lt;&gt;"",A304&lt;&gt;"",H304&gt;=A304),H304-A304,"")</f>
         <v/>
       </c>
       <c r="O304" s="25">
@@ -15960,6 +15990,20 @@
       <c r="A306" s="19" t="inlineStr">
         <is>
           <t>Amarelo: parado há mais dias que o limite da Config. Verde: aprovado. Cinza: recusado ou sem retorno. Motivo em vermelho: recusado sem motivo (preencha, é o que ensina). Datas de orçamentos ainda abertos no exemplo são relativas a hoje.</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" s="19" t="inlineStr">
+        <is>
+          <t>A data da decisão nunca é anterior à da apresentação: um orçamento aprovado hoje para um exame marcado para a semana que vem tem apresentação e decisão no passado e o agendamento no futuro (a observação guarda a data marcada). Se "Dias até decidir" ficar vazio numa linha decidida, é sinal de que as duas datas estão trocadas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" s="19" t="inlineStr">
+        <is>
+          <t>Orçamento aprovado a prazo: só para quem não tem parcela vencida em aberto na planilha 14. Com parcela em atraso, o combinado é à vista — a mesma regra da régua de cobrança.</t>
         </is>
       </c>
     </row>

--- a/projetos/gestao-ia-planilhas/produto/kit-medicos/15-orcamentos.xlsx
+++ b/projetos/gestao-ia-planilhas/produto/kit-medicos/15-orcamentos.xlsx
@@ -21,10 +21,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
-    <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
-    <numFmt numFmtId="165" formatCode="&quot;R$&quot; #,##0;[Red]-&quot;R$&quot; #,##0"/>
-    <numFmt numFmtId="166" formatCode="mm/yyyy"/>
+  <numFmts count="4">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="165" formatCode="dd/mm/yyyy"/>
+    <numFmt numFmtId="166" formatCode="&quot;R$&quot; #,##0;[Red]-&quot;R$&quot; #,##0"/>
+    <numFmt numFmtId="167" formatCode="mm/yyyy"/>
   </numFmts>
   <fonts count="17">
     <font>
@@ -252,13 +253,13 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="1" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="1" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="1" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="1" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="10" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="10" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="9" fontId="10" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -283,7 +284,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -298,10 +299,10 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="4" fillId="2" borderId="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="2" borderId="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="4" fillId="2" borderId="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <protection locked="0" hidden="0"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -312,15 +313,15 @@
       <alignment horizontal="center"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
     <xf numFmtId="165" fontId="4" fillId="2" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="4" fillId="2" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -830,7 +831,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B18"/>
+  <dimension ref="A1:B19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1015,17 +1016,29 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Clínica Vida Plena é uma clínica fictícia. Pacientes, convênios, nomes, contatos e valores são inventados; não há nenhum dado clínico. Apague o exemplo antes de começar. Agenda futura e vencimentos em aberto do exemplo são relativos a hoje.</t>
+          <t>Clínica Vida Plena é uma clínica fictícia. Pacientes, convênios, nomes, contatos e valores são inventados; não há nenhum dado clínico. Apague o exemplo antes de começar.</t>
         </is>
       </c>
     </row>
     <row r="18" ht="46" customHeight="1">
       <c r="A18" s="3" t="inlineStr">
         <is>
+          <t>Data de referência</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>O exemplo está congelado em 14/09/2026, para todos os arquivos do kit mostrarem a mesma foto e os números fecharem entre eles. Ao começar a usar com os seus dados, troque a data de referência em Config por =HOJE(): daí em diante ela acompanha o dia.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="46" customHeight="1">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
           <t>Suporte</t>
         </is>
       </c>
-      <c r="B18" s="4" t="inlineStr">
+      <c r="B19" s="4" t="inlineStr">
         <is>
           <t>suporte@seusociogestor.com.br · resposta em até 5 dias úteis · reembolso em até 7 dias pelo mesmo canal.</t>
         </is>
@@ -2520,9 +2533,8 @@
           <t>Data de referência (hoje)</t>
         </is>
       </c>
-      <c r="B5" s="33">
-        <f>TODAY()</f>
-        <v>46279.0</v>
+      <c r="B5" s="33" t="n">
+        <v>46279</v>
       </c>
     </row>
     <row r="6">
@@ -3061,9 +3073,8 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="37">
-        <f>TODAY()-70</f>
-        <v>46209.0</v>
+      <c r="A7" s="37" t="n">
+        <v>46209</v>
       </c>
       <c r="B7" s="32" t="inlineStr">
         <is>
@@ -3093,9 +3104,8 @@
           <t>Recusado</t>
         </is>
       </c>
-      <c r="H7" s="37">
-        <f>TODAY()-65</f>
-        <v>46214.0</v>
+      <c r="H7" s="37" t="n">
+        <v>46214</v>
       </c>
       <c r="I7" s="35" t="inlineStr">
         <is>
@@ -3483,9 +3493,8 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="37">
-        <f>TODAY()-55</f>
-        <v>46224.0</v>
+      <c r="A13" s="37" t="n">
+        <v>46224</v>
       </c>
       <c r="B13" s="32" t="inlineStr">
         <is>
@@ -3515,9 +3524,8 @@
           <t>Recusado</t>
         </is>
       </c>
-      <c r="H13" s="37">
-        <f>TODAY()-51</f>
-        <v>46228.0</v>
+      <c r="H13" s="37" t="n">
+        <v>46228</v>
       </c>
       <c r="I13" s="35" t="inlineStr">
         <is>
@@ -3625,9 +3633,8 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="37">
-        <f>TODAY()-45</f>
-        <v>46234.0</v>
+      <c r="A15" s="37" t="n">
+        <v>46234</v>
       </c>
       <c r="B15" s="32" t="inlineStr">
         <is>
@@ -3657,9 +3664,8 @@
           <t>Recusado</t>
         </is>
       </c>
-      <c r="H15" s="37">
-        <f>TODAY()-41</f>
-        <v>46238.0</v>
+      <c r="H15" s="37" t="n">
+        <v>46238</v>
       </c>
       <c r="I15" s="35" t="inlineStr">
         <is>
@@ -3767,9 +3773,8 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="37">
-        <f>TODAY()-40</f>
-        <v>46239.0</v>
+      <c r="A17" s="37" t="n">
+        <v>46239</v>
       </c>
       <c r="B17" s="32" t="inlineStr">
         <is>
@@ -3799,9 +3804,8 @@
           <t>Sem retorno</t>
         </is>
       </c>
-      <c r="H17" s="37">
-        <f>TODAY()-30</f>
-        <v>46249.0</v>
+      <c r="H17" s="37" t="n">
+        <v>46249</v>
       </c>
       <c r="I17" s="35" t="inlineStr">
         <is>
@@ -4049,9 +4053,8 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="37">
-        <f>TODAY()-32</f>
-        <v>46247.0</v>
+      <c r="A21" s="37" t="n">
+        <v>46247</v>
       </c>
       <c r="B21" s="32" t="inlineStr">
         <is>
@@ -4081,9 +4084,8 @@
           <t>Recusado</t>
         </is>
       </c>
-      <c r="H21" s="37">
-        <f>TODAY()-23</f>
-        <v>46256.0</v>
+      <c r="H21" s="37" t="n">
+        <v>46256</v>
       </c>
       <c r="I21" s="35" t="inlineStr">
         <is>
@@ -4331,9 +4333,8 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="37">
-        <f>TODAY()-26</f>
-        <v>46253.0</v>
+      <c r="A25" s="37" t="n">
+        <v>46253</v>
       </c>
       <c r="B25" s="32" t="inlineStr">
         <is>
@@ -4363,9 +4364,8 @@
           <t>Sem retorno</t>
         </is>
       </c>
-      <c r="H25" s="37">
-        <f>TODAY()-17</f>
-        <v>46262.0</v>
+      <c r="H25" s="37" t="n">
+        <v>46262</v>
       </c>
       <c r="I25" s="35" t="inlineStr">
         <is>
@@ -4543,9 +4543,8 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="37">
-        <f>TODAY()-20</f>
-        <v>46259.0</v>
+      <c r="A28" s="37" t="n">
+        <v>46259</v>
       </c>
       <c r="B28" s="32" t="inlineStr">
         <is>
@@ -4575,9 +4574,8 @@
           <t>Recusado</t>
         </is>
       </c>
-      <c r="H28" s="37">
-        <f>TODAY()-17</f>
-        <v>46262.0</v>
+      <c r="H28" s="37" t="n">
+        <v>46262</v>
       </c>
       <c r="I28" s="35" t="inlineStr">
         <is>
@@ -4755,9 +4753,8 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="37">
-        <f>TODAY()-16</f>
-        <v>46263.0</v>
+      <c r="A31" s="37" t="n">
+        <v>46263</v>
       </c>
       <c r="B31" s="32" t="inlineStr">
         <is>
@@ -4787,9 +4784,8 @@
           <t>Sem retorno</t>
         </is>
       </c>
-      <c r="H31" s="37">
-        <f>TODAY()-9</f>
-        <v>46270.0</v>
+      <c r="H31" s="37" t="n">
+        <v>46270</v>
       </c>
       <c r="I31" s="35" t="inlineStr">
         <is>
@@ -4967,9 +4963,8 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="37">
-        <f>TODAY()-12</f>
-        <v>46267.0</v>
+      <c r="A34" s="37" t="n">
+        <v>46267</v>
       </c>
       <c r="B34" s="32" t="inlineStr">
         <is>
@@ -5102,9 +5097,8 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="37">
-        <f>TODAY()-9</f>
-        <v>46270.0</v>
+      <c r="A36" s="37" t="n">
+        <v>46270</v>
       </c>
       <c r="B36" s="32" t="inlineStr">
         <is>
@@ -5167,9 +5161,8 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="37">
-        <f>TODAY()-6</f>
-        <v>46273.0</v>
+      <c r="A37" s="37" t="n">
+        <v>46273</v>
       </c>
       <c r="B37" s="32" t="inlineStr">
         <is>
@@ -5232,9 +5225,8 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="37">
-        <f>TODAY()-3</f>
-        <v>46276.0</v>
+      <c r="A38" s="37" t="n">
+        <v>46276</v>
       </c>
       <c r="B38" s="32" t="inlineStr">
         <is>
@@ -5297,9 +5289,8 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="37">
-        <f>TODAY()-1</f>
-        <v>46278.0</v>
+      <c r="A39" s="37" t="n">
+        <v>46278</v>
       </c>
       <c r="B39" s="32" t="inlineStr">
         <is>
@@ -5362,9 +5353,8 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="37">
-        <f>TODAY()</f>
-        <v>46279.0</v>
+      <c r="A40" s="37" t="n">
+        <v>46279</v>
       </c>
       <c r="B40" s="32" t="inlineStr">
         <is>

--- a/projetos/gestao-ia-planilhas/produto/kit-medicos/15-orcamentos.xlsx
+++ b/projetos/gestao-ia-planilhas/produto/kit-medicos/15-orcamentos.xlsx
@@ -1137,7 +1137,7 @@
       </c>
       <c r="D5" s="10" t="n"/>
       <c r="E5" s="15">
-        <f>SUMIFS(Orçamentos!$F$5:$F$304,Orçamentos!$G$5:$G$304,"Aprovado",Orçamentos!$H$5:$H$304,"&gt;="&amp;DATE(YEAR(Config!$B$5),3*INT((MONTH(Config!$B$5)-1)/3)+1,1))</f>
+        <f>SUMIFS(Orçamentos!$F$5:$F$304,Orçamentos!$G$5:$G$304,"Aprovado",Orçamentos!$H$5:$H$304,"&gt;="&amp;DATE(YEAR(Config!$B$5),3*INT((MONTH(Config!$B$5)-1)/3)+1,1),Orçamentos!$H$5:$H$304,"&lt;"&amp;DATE(YEAR(Config!$B$5)+(3*INT((MONTH(Config!$B$5)-1)/3)+4&gt;12),IF(3*INT((MONTH(Config!$B$5)-1)/3)+4&gt;12,1,3*INT((MONTH(Config!$B$5)-1)/3)+4),1))</f>
         <v>8960</v>
       </c>
       <c r="F5" s="12" t="n"/>
@@ -16027,22 +16027,22 @@
     <dataValidation sqref="D5:D304" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>=OFFSET(Config!$A$18,0,0,MAX(1,COUNTA(Config!$A$18:$A$27)),1)</formula1>
     </dataValidation>
-    <dataValidation sqref="E5:E304" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="E5:E304" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>=OFFSET(Config!$G$18,0,0,MAX(1,COUNTA(Config!$G$18:$G$27)),1)</formula1>
     </dataValidation>
     <dataValidation sqref="G5:G304" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>=Config!$A$10:$A$14</formula1>
     </dataValidation>
-    <dataValidation sqref="I5:I304" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="I5:I304" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>=OFFSET(Config!$C$18,0,0,MAX(1,COUNTA(Config!$C$18:$C$27)),1)</formula1>
     </dataValidation>
-    <dataValidation sqref="A5:A304" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="date" operator="greaterThan">
+    <dataValidation sqref="A5:A304" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="date" operator="greaterThan">
       <formula1>1</formula1>
     </dataValidation>
-    <dataValidation sqref="F5:F304" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="decimal" operator="greaterThanOrEqual">
+    <dataValidation sqref="F5:F304" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="decimal" operator="greaterThanOrEqual">
       <formula1>0</formula1>
     </dataValidation>
-    <dataValidation sqref="H5:H304" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="date" operator="greaterThan">
+    <dataValidation sqref="H5:H304" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="date" operator="greaterThan">
       <formula1>1</formula1>
     </dataValidation>
   </dataValidations>

--- a/projetos/gestao-ia-planilhas/produto/kit-medicos/15-orcamentos.xlsx
+++ b/projetos/gestao-ia-planilhas/produto/kit-medicos/15-orcamentos.xlsx
@@ -1004,7 +1004,7 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>Faça upload no Google Drive e abra com o Google Sheets. Fórmulas, listas, cores e gráficos funcionam.</t>
+          <t>Faça upload no Google Drive e abra com o Google Sheets. Fórmulas, listas, cores, semáforos e gráficos funcionam: as regras de cor que dependem do mês escolhido em Config usam INDIRECT, que é a forma que o Sheets aceita para regra condicional apontar para outra aba.</t>
         </is>
       </c>
     </row>
@@ -1028,7 +1028,7 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>O exemplo está congelado em 14/09/2026, para todos os arquivos do kit mostrarem a mesma foto e os números fecharem entre eles. Ao começar a usar com os seus dados, troque a data de referência em Config por =HOJE(): daí em diante ela acompanha o dia.</t>
+          <t>O exemplo está congelado em 14/09/2026, para todos os arquivos do kit mostrarem a mesma foto e os números fecharem entre eles. Ao começar a usar com os SEUS dados, troque em Config: a data de referência por =HOJE(), o ano, o mês do painel, o trimestre (onde houver) e a lista de feriados. Trocar só a data de referência deixa o resto apontando para 2026.</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
         <v>46174.0</v>
       </c>
       <c r="Q5" s="40">
-        <f>IF(OR(G5="",O5="Aprovado",O5="Recusado",O5="Sem retorno"),0,IF(O5="Parado",2000,1000)+MIN(N(M5),500)+N(F5)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G5="",O5="Aprovado",O5="Recusado",O5="Sem retorno"),0,IF(O5="Parado",2,1)*1E+13+MIN(N(M5),500)*1E+10+MIN(ROUND(N(F5),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
         <v>46174.0</v>
       </c>
       <c r="Q6" s="40">
-        <f>IF(OR(G6="",O6="Aprovado",O6="Recusado",O6="Sem retorno"),0,IF(O6="Parado",2000,1000)+MIN(N(M6),500)+N(F6)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G6="",O6="Aprovado",O6="Recusado",O6="Sem retorno"),0,IF(O6="Parado",2,1)*1E+13+MIN(N(M6),500)*1E+10+MIN(ROUND(N(F6),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
         <v>46204.0</v>
       </c>
       <c r="Q7" s="40">
-        <f>IF(OR(G7="",O7="Aprovado",O7="Recusado",O7="Sem retorno"),0,IF(O7="Parado",2000,1000)+MIN(N(M7),500)+N(F7)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G7="",O7="Aprovado",O7="Recusado",O7="Sem retorno"),0,IF(O7="Parado",2,1)*1E+13+MIN(N(M7),500)*1E+10+MIN(ROUND(N(F7),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
         <v>46204.0</v>
       </c>
       <c r="Q8" s="40">
-        <f>IF(OR(G8="",O8="Aprovado",O8="Recusado",O8="Sem retorno"),0,IF(O8="Parado",2000,1000)+MIN(N(M8),500)+N(F8)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G8="",O8="Aprovado",O8="Recusado",O8="Sem retorno"),0,IF(O8="Parado",2,1)*1E+13+MIN(N(M8),500)*1E+10+MIN(ROUND(N(F8),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
         <v>46204.0</v>
       </c>
       <c r="Q9" s="40">
-        <f>IF(OR(G9="",O9="Aprovado",O9="Recusado",O9="Sem retorno"),0,IF(O9="Parado",2000,1000)+MIN(N(M9),500)+N(F9)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G9="",O9="Aprovado",O9="Recusado",O9="Sem retorno"),0,IF(O9="Parado",2,1)*1E+13+MIN(N(M9),500)*1E+10+MIN(ROUND(N(F9),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
         <v>46204.0</v>
       </c>
       <c r="Q10" s="40">
-        <f>IF(OR(G10="",O10="Aprovado",O10="Recusado",O10="Sem retorno"),0,IF(O10="Parado",2000,1000)+MIN(N(M10),500)+N(F10)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G10="",O10="Aprovado",O10="Recusado",O10="Sem retorno"),0,IF(O10="Parado",2,1)*1E+13+MIN(N(M10),500)*1E+10+MIN(ROUND(N(F10),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
         <v>46204.0</v>
       </c>
       <c r="Q11" s="40">
-        <f>IF(OR(G11="",O11="Aprovado",O11="Recusado",O11="Sem retorno"),0,IF(O11="Parado",2000,1000)+MIN(N(M11),500)+N(F11)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G11="",O11="Aprovado",O11="Recusado",O11="Sem retorno"),0,IF(O11="Parado",2,1)*1E+13+MIN(N(M11),500)*1E+10+MIN(ROUND(N(F11),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
         <v>46204.0</v>
       </c>
       <c r="Q12" s="40">
-        <f>IF(OR(G12="",O12="Aprovado",O12="Recusado",O12="Sem retorno"),0,IF(O12="Parado",2000,1000)+MIN(N(M12),500)+N(F12)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G12="",O12="Aprovado",O12="Recusado",O12="Sem retorno"),0,IF(O12="Parado",2,1)*1E+13+MIN(N(M12),500)*1E+10+MIN(ROUND(N(F12),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
         <v>46204.0</v>
       </c>
       <c r="Q13" s="40">
-        <f>IF(OR(G13="",O13="Aprovado",O13="Recusado",O13="Sem retorno"),0,IF(O13="Parado",2000,1000)+MIN(N(M13),500)+N(F13)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G13="",O13="Aprovado",O13="Recusado",O13="Sem retorno"),0,IF(O13="Parado",2,1)*1E+13+MIN(N(M13),500)*1E+10+MIN(ROUND(N(F13),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -3628,7 +3628,7 @@
         <v>46204.0</v>
       </c>
       <c r="Q14" s="40">
-        <f>IF(OR(G14="",O14="Aprovado",O14="Recusado",O14="Sem retorno"),0,IF(O14="Parado",2000,1000)+MIN(N(M14),500)+N(F14)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G14="",O14="Aprovado",O14="Recusado",O14="Sem retorno"),0,IF(O14="Parado",2,1)*1E+13+MIN(N(M14),500)*1E+10+MIN(ROUND(N(F14),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -3698,7 +3698,7 @@
         <v>46204.0</v>
       </c>
       <c r="Q15" s="40">
-        <f>IF(OR(G15="",O15="Aprovado",O15="Recusado",O15="Sem retorno"),0,IF(O15="Parado",2000,1000)+MIN(N(M15),500)+N(F15)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G15="",O15="Aprovado",O15="Recusado",O15="Sem retorno"),0,IF(O15="Parado",2,1)*1E+13+MIN(N(M15),500)*1E+10+MIN(ROUND(N(F15),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
         <v>46235.0</v>
       </c>
       <c r="Q16" s="40">
-        <f>IF(OR(G16="",O16="Aprovado",O16="Recusado",O16="Sem retorno"),0,IF(O16="Parado",2000,1000)+MIN(N(M16),500)+N(F16)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G16="",O16="Aprovado",O16="Recusado",O16="Sem retorno"),0,IF(O16="Parado",2,1)*1E+13+MIN(N(M16),500)*1E+10+MIN(ROUND(N(F16),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -3838,7 +3838,7 @@
         <v>46235.0</v>
       </c>
       <c r="Q17" s="40">
-        <f>IF(OR(G17="",O17="Aprovado",O17="Recusado",O17="Sem retorno"),0,IF(O17="Parado",2000,1000)+MIN(N(M17),500)+N(F17)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G17="",O17="Aprovado",O17="Recusado",O17="Sem retorno"),0,IF(O17="Parado",2,1)*1E+13+MIN(N(M17),500)*1E+10+MIN(ROUND(N(F17),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -3908,7 +3908,7 @@
         <v>46235.0</v>
       </c>
       <c r="Q18" s="40">
-        <f>IF(OR(G18="",O18="Aprovado",O18="Recusado",O18="Sem retorno"),0,IF(O18="Parado",2000,1000)+MIN(N(M18),500)+N(F18)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G18="",O18="Aprovado",O18="Recusado",O18="Sem retorno"),0,IF(O18="Parado",2,1)*1E+13+MIN(N(M18),500)*1E+10+MIN(ROUND(N(F18),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
         <v>46235.0</v>
       </c>
       <c r="Q19" s="40">
-        <f>IF(OR(G19="",O19="Aprovado",O19="Recusado",O19="Sem retorno"),0,IF(O19="Parado",2000,1000)+MIN(N(M19),500)+N(F19)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G19="",O19="Aprovado",O19="Recusado",O19="Sem retorno"),0,IF(O19="Parado",2,1)*1E+13+MIN(N(M19),500)*1E+10+MIN(ROUND(N(F19),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -4048,7 +4048,7 @@
         <v>46235.0</v>
       </c>
       <c r="Q20" s="40">
-        <f>IF(OR(G20="",O20="Aprovado",O20="Recusado",O20="Sem retorno"),0,IF(O20="Parado",2000,1000)+MIN(N(M20),500)+N(F20)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G20="",O20="Aprovado",O20="Recusado",O20="Sem retorno"),0,IF(O20="Parado",2,1)*1E+13+MIN(N(M20),500)*1E+10+MIN(ROUND(N(F20),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -4118,7 +4118,7 @@
         <v>46235.0</v>
       </c>
       <c r="Q21" s="40">
-        <f>IF(OR(G21="",O21="Aprovado",O21="Recusado",O21="Sem retorno"),0,IF(O21="Parado",2000,1000)+MIN(N(M21),500)+N(F21)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G21="",O21="Aprovado",O21="Recusado",O21="Sem retorno"),0,IF(O21="Parado",2,1)*1E+13+MIN(N(M21),500)*1E+10+MIN(ROUND(N(F21),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
         <v>46235.0</v>
       </c>
       <c r="Q22" s="40">
-        <f>IF(OR(G22="",O22="Aprovado",O22="Recusado",O22="Sem retorno"),0,IF(O22="Parado",2000,1000)+MIN(N(M22),500)+N(F22)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G22="",O22="Aprovado",O22="Recusado",O22="Sem retorno"),0,IF(O22="Parado",2,1)*1E+13+MIN(N(M22),500)*1E+10+MIN(ROUND(N(F22),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -4258,7 +4258,7 @@
         <v>46235.0</v>
       </c>
       <c r="Q23" s="40">
-        <f>IF(OR(G23="",O23="Aprovado",O23="Recusado",O23="Sem retorno"),0,IF(O23="Parado",2000,1000)+MIN(N(M23),500)+N(F23)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G23="",O23="Aprovado",O23="Recusado",O23="Sem retorno"),0,IF(O23="Parado",2,1)*1E+13+MIN(N(M23),500)*1E+10+MIN(ROUND(N(F23),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -4328,7 +4328,7 @@
         <v>46235.0</v>
       </c>
       <c r="Q24" s="40">
-        <f>IF(OR(G24="",O24="Aprovado",O24="Recusado",O24="Sem retorno"),0,IF(O24="Parado",2000,1000)+MIN(N(M24),500)+N(F24)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G24="",O24="Aprovado",O24="Recusado",O24="Sem retorno"),0,IF(O24="Parado",2,1)*1E+13+MIN(N(M24),500)*1E+10+MIN(ROUND(N(F24),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
         <v>46235.0</v>
       </c>
       <c r="Q25" s="40">
-        <f>IF(OR(G25="",O25="Aprovado",O25="Recusado",O25="Sem retorno"),0,IF(O25="Parado",2000,1000)+MIN(N(M25),500)+N(F25)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G25="",O25="Aprovado",O25="Recusado",O25="Sem retorno"),0,IF(O25="Parado",2,1)*1E+13+MIN(N(M25),500)*1E+10+MIN(ROUND(N(F25),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -4468,7 +4468,7 @@
         <v>46235.0</v>
       </c>
       <c r="Q26" s="40">
-        <f>IF(OR(G26="",O26="Aprovado",O26="Recusado",O26="Sem retorno"),0,IF(O26="Parado",2000,1000)+MIN(N(M26),500)+N(F26)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G26="",O26="Aprovado",O26="Recusado",O26="Sem retorno"),0,IF(O26="Parado",2,1)*1E+13+MIN(N(M26),500)*1E+10+MIN(ROUND(N(F26),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -4538,7 +4538,7 @@
         <v>46235.0</v>
       </c>
       <c r="Q27" s="40">
-        <f>IF(OR(G27="",O27="Aprovado",O27="Recusado",O27="Sem retorno"),0,IF(O27="Parado",2000,1000)+MIN(N(M27),500)+N(F27)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G27="",O27="Aprovado",O27="Recusado",O27="Sem retorno"),0,IF(O27="Parado",2,1)*1E+13+MIN(N(M27),500)*1E+10+MIN(ROUND(N(F27),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -4608,7 +4608,7 @@
         <v>46235.0</v>
       </c>
       <c r="Q28" s="40">
-        <f>IF(OR(G28="",O28="Aprovado",O28="Recusado",O28="Sem retorno"),0,IF(O28="Parado",2000,1000)+MIN(N(M28),500)+N(F28)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G28="",O28="Aprovado",O28="Recusado",O28="Sem retorno"),0,IF(O28="Parado",2,1)*1E+13+MIN(N(M28),500)*1E+10+MIN(ROUND(N(F28),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -4678,7 +4678,7 @@
         <v>46235.0</v>
       </c>
       <c r="Q29" s="40">
-        <f>IF(OR(G29="",O29="Aprovado",O29="Recusado",O29="Sem retorno"),0,IF(O29="Parado",2000,1000)+MIN(N(M29),500)+N(F29)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G29="",O29="Aprovado",O29="Recusado",O29="Sem retorno"),0,IF(O29="Parado",2,1)*1E+13+MIN(N(M29),500)*1E+10+MIN(ROUND(N(F29),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -4748,7 +4748,7 @@
         <v>46235.0</v>
       </c>
       <c r="Q30" s="40">
-        <f>IF(OR(G30="",O30="Aprovado",O30="Recusado",O30="Sem retorno"),0,IF(O30="Parado",2000,1000)+MIN(N(M30),500)+N(F30)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G30="",O30="Aprovado",O30="Recusado",O30="Sem retorno"),0,IF(O30="Parado",2,1)*1E+13+MIN(N(M30),500)*1E+10+MIN(ROUND(N(F30),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -4818,7 +4818,7 @@
         <v>46235.0</v>
       </c>
       <c r="Q31" s="40">
-        <f>IF(OR(G31="",O31="Aprovado",O31="Recusado",O31="Sem retorno"),0,IF(O31="Parado",2000,1000)+MIN(N(M31),500)+N(F31)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G31="",O31="Aprovado",O31="Recusado",O31="Sem retorno"),0,IF(O31="Parado",2,1)*1E+13+MIN(N(M31),500)*1E+10+MIN(ROUND(N(F31),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -4888,7 +4888,7 @@
         <v>46235.0</v>
       </c>
       <c r="Q32" s="40">
-        <f>IF(OR(G32="",O32="Aprovado",O32="Recusado",O32="Sem retorno"),0,IF(O32="Parado",2000,1000)+MIN(N(M32),500)+N(F32)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G32="",O32="Aprovado",O32="Recusado",O32="Sem retorno"),0,IF(O32="Parado",2,1)*1E+13+MIN(N(M32),500)*1E+10+MIN(ROUND(N(F32),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -4958,7 +4958,7 @@
         <v>46266.0</v>
       </c>
       <c r="Q33" s="40">
-        <f>IF(OR(G33="",O33="Aprovado",O33="Recusado",O33="Sem retorno"),0,IF(O33="Parado",2000,1000)+MIN(N(M33),500)+N(F33)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G33="",O33="Aprovado",O33="Recusado",O33="Sem retorno"),0,IF(O33="Parado",2,1)*1E+13+MIN(N(M33),500)*1E+10+MIN(ROUND(N(F33),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -5022,8 +5022,8 @@
         <v>46266.0</v>
       </c>
       <c r="Q34" s="40">
-        <f>IF(OR(G34="",O34="Aprovado",O34="Recusado",O34="Sem retorno"),0,IF(O34="Parado",2000,1000)+MIN(N(M34),500)+N(F34)/1000000-ROW()/100000)</f>
-        <v>2012.00031</v>
+        <f>IF(OR(G34="",O34="Aprovado",O34="Recusado",O34="Sem retorno"),0,IF(O34="Parado",2,1)*1E+13+MIN(N(M34),500)*1E+10+MIN(ROUND(N(F34),0),999999)*1E+4+(304+1-ROW()))</f>
+        <v>20120006500271</v>
       </c>
     </row>
     <row r="35">
@@ -5092,7 +5092,7 @@
         <v>46266.0</v>
       </c>
       <c r="Q35" s="40">
-        <f>IF(OR(G35="",O35="Aprovado",O35="Recusado",O35="Sem retorno"),0,IF(O35="Parado",2000,1000)+MIN(N(M35),500)+N(F35)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G35="",O35="Aprovado",O35="Recusado",O35="Sem retorno"),0,IF(O35="Parado",2,1)*1E+13+MIN(N(M35),500)*1E+10+MIN(ROUND(N(F35),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -5156,8 +5156,8 @@
         <v>46266.0</v>
       </c>
       <c r="Q36" s="40">
-        <f>IF(OR(G36="",O36="Aprovado",O36="Recusado",O36="Sem retorno"),0,IF(O36="Parado",2000,1000)+MIN(N(M36),500)+N(F36)/1000000-ROW()/100000)</f>
-        <v>2009.00004</v>
+        <f>IF(OR(G36="",O36="Aprovado",O36="Recusado",O36="Sem retorno"),0,IF(O36="Parado",2,1)*1E+13+MIN(N(M36),500)*1E+10+MIN(ROUND(N(F36),0),999999)*1E+4+(304+1-ROW()))</f>
+        <v>20090004000269</v>
       </c>
     </row>
     <row r="37">
@@ -5220,8 +5220,8 @@
         <v>46266.0</v>
       </c>
       <c r="Q37" s="40">
-        <f>IF(OR(G37="",O37="Aprovado",O37="Recusado",O37="Sem retorno"),0,IF(O37="Parado",2000,1000)+MIN(N(M37),500)+N(F37)/1000000-ROW()/100000)</f>
-        <v>1005.99998</v>
+        <f>IF(OR(G37="",O37="Aprovado",O37="Recusado",O37="Sem retorno"),0,IF(O37="Parado",2,1)*1E+13+MIN(N(M37),500)*1E+10+MIN(ROUND(N(F37),0),999999)*1E+4+(304+1-ROW()))</f>
+        <v>10060003500268</v>
       </c>
     </row>
     <row r="38">
@@ -5284,8 +5284,8 @@
         <v>46266.0</v>
       </c>
       <c r="Q38" s="40">
-        <f>IF(OR(G38="",O38="Aprovado",O38="Recusado",O38="Sem retorno"),0,IF(O38="Parado",2000,1000)+MIN(N(M38),500)+N(F38)/1000000-ROW()/100000)</f>
-        <v>1003.00058</v>
+        <f>IF(OR(G38="",O38="Aprovado",O38="Recusado",O38="Sem retorno"),0,IF(O38="Parado",2,1)*1E+13+MIN(N(M38),500)*1E+10+MIN(ROUND(N(F38),0),999999)*1E+4+(304+1-ROW()))</f>
+        <v>10030009600267</v>
       </c>
     </row>
     <row r="39">
@@ -5348,8 +5348,8 @@
         <v>46266.0</v>
       </c>
       <c r="Q39" s="40">
-        <f>IF(OR(G39="",O39="Aprovado",O39="Recusado",O39="Sem retorno"),0,IF(O39="Parado",2000,1000)+MIN(N(M39),500)+N(F39)/1000000-ROW()/100000)</f>
-        <v>1001.00006</v>
+        <f>IF(OR(G39="",O39="Aprovado",O39="Recusado",O39="Sem retorno"),0,IF(O39="Parado",2,1)*1E+13+MIN(N(M39),500)*1E+10+MIN(ROUND(N(F39),0),999999)*1E+4+(304+1-ROW()))</f>
+        <v>10010004500266</v>
       </c>
     </row>
     <row r="40">
@@ -5412,8 +5412,8 @@
         <v>46266.0</v>
       </c>
       <c r="Q40" s="40">
-        <f>IF(OR(G40="",O40="Aprovado",O40="Recusado",O40="Sem retorno"),0,IF(O40="Parado",2000,1000)+MIN(N(M40),500)+N(F40)/1000000-ROW()/100000)</f>
-        <v>1000.00025</v>
+        <f>IF(OR(G40="",O40="Aprovado",O40="Recusado",O40="Sem retorno"),0,IF(O40="Parado",2,1)*1E+13+MIN(N(M40),500)*1E+10+MIN(ROUND(N(F40),0),999999)*1E+4+(304+1-ROW()))</f>
+        <v>10000006500265</v>
       </c>
     </row>
     <row r="41">
@@ -5452,7 +5452,7 @@
         <v/>
       </c>
       <c r="Q41" s="40">
-        <f>IF(OR(G41="",O41="Aprovado",O41="Recusado",O41="Sem retorno"),0,IF(O41="Parado",2000,1000)+MIN(N(M41),500)+N(F41)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G41="",O41="Aprovado",O41="Recusado",O41="Sem retorno"),0,IF(O41="Parado",2,1)*1E+13+MIN(N(M41),500)*1E+10+MIN(ROUND(N(F41),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -5492,7 +5492,7 @@
         <v/>
       </c>
       <c r="Q42" s="40">
-        <f>IF(OR(G42="",O42="Aprovado",O42="Recusado",O42="Sem retorno"),0,IF(O42="Parado",2000,1000)+MIN(N(M42),500)+N(F42)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G42="",O42="Aprovado",O42="Recusado",O42="Sem retorno"),0,IF(O42="Parado",2,1)*1E+13+MIN(N(M42),500)*1E+10+MIN(ROUND(N(F42),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -5532,7 +5532,7 @@
         <v/>
       </c>
       <c r="Q43" s="40">
-        <f>IF(OR(G43="",O43="Aprovado",O43="Recusado",O43="Sem retorno"),0,IF(O43="Parado",2000,1000)+MIN(N(M43),500)+N(F43)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G43="",O43="Aprovado",O43="Recusado",O43="Sem retorno"),0,IF(O43="Parado",2,1)*1E+13+MIN(N(M43),500)*1E+10+MIN(ROUND(N(F43),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -5572,7 +5572,7 @@
         <v/>
       </c>
       <c r="Q44" s="40">
-        <f>IF(OR(G44="",O44="Aprovado",O44="Recusado",O44="Sem retorno"),0,IF(O44="Parado",2000,1000)+MIN(N(M44),500)+N(F44)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G44="",O44="Aprovado",O44="Recusado",O44="Sem retorno"),0,IF(O44="Parado",2,1)*1E+13+MIN(N(M44),500)*1E+10+MIN(ROUND(N(F44),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -5612,7 +5612,7 @@
         <v/>
       </c>
       <c r="Q45" s="40">
-        <f>IF(OR(G45="",O45="Aprovado",O45="Recusado",O45="Sem retorno"),0,IF(O45="Parado",2000,1000)+MIN(N(M45),500)+N(F45)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G45="",O45="Aprovado",O45="Recusado",O45="Sem retorno"),0,IF(O45="Parado",2,1)*1E+13+MIN(N(M45),500)*1E+10+MIN(ROUND(N(F45),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -5652,7 +5652,7 @@
         <v/>
       </c>
       <c r="Q46" s="40">
-        <f>IF(OR(G46="",O46="Aprovado",O46="Recusado",O46="Sem retorno"),0,IF(O46="Parado",2000,1000)+MIN(N(M46),500)+N(F46)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G46="",O46="Aprovado",O46="Recusado",O46="Sem retorno"),0,IF(O46="Parado",2,1)*1E+13+MIN(N(M46),500)*1E+10+MIN(ROUND(N(F46),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -5692,7 +5692,7 @@
         <v/>
       </c>
       <c r="Q47" s="40">
-        <f>IF(OR(G47="",O47="Aprovado",O47="Recusado",O47="Sem retorno"),0,IF(O47="Parado",2000,1000)+MIN(N(M47),500)+N(F47)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G47="",O47="Aprovado",O47="Recusado",O47="Sem retorno"),0,IF(O47="Parado",2,1)*1E+13+MIN(N(M47),500)*1E+10+MIN(ROUND(N(F47),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -5732,7 +5732,7 @@
         <v/>
       </c>
       <c r="Q48" s="40">
-        <f>IF(OR(G48="",O48="Aprovado",O48="Recusado",O48="Sem retorno"),0,IF(O48="Parado",2000,1000)+MIN(N(M48),500)+N(F48)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G48="",O48="Aprovado",O48="Recusado",O48="Sem retorno"),0,IF(O48="Parado",2,1)*1E+13+MIN(N(M48),500)*1E+10+MIN(ROUND(N(F48),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -5772,7 +5772,7 @@
         <v/>
       </c>
       <c r="Q49" s="40">
-        <f>IF(OR(G49="",O49="Aprovado",O49="Recusado",O49="Sem retorno"),0,IF(O49="Parado",2000,1000)+MIN(N(M49),500)+N(F49)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G49="",O49="Aprovado",O49="Recusado",O49="Sem retorno"),0,IF(O49="Parado",2,1)*1E+13+MIN(N(M49),500)*1E+10+MIN(ROUND(N(F49),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -5812,7 +5812,7 @@
         <v/>
       </c>
       <c r="Q50" s="40">
-        <f>IF(OR(G50="",O50="Aprovado",O50="Recusado",O50="Sem retorno"),0,IF(O50="Parado",2000,1000)+MIN(N(M50),500)+N(F50)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G50="",O50="Aprovado",O50="Recusado",O50="Sem retorno"),0,IF(O50="Parado",2,1)*1E+13+MIN(N(M50),500)*1E+10+MIN(ROUND(N(F50),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -5852,7 +5852,7 @@
         <v/>
       </c>
       <c r="Q51" s="40">
-        <f>IF(OR(G51="",O51="Aprovado",O51="Recusado",O51="Sem retorno"),0,IF(O51="Parado",2000,1000)+MIN(N(M51),500)+N(F51)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G51="",O51="Aprovado",O51="Recusado",O51="Sem retorno"),0,IF(O51="Parado",2,1)*1E+13+MIN(N(M51),500)*1E+10+MIN(ROUND(N(F51),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -5892,7 +5892,7 @@
         <v/>
       </c>
       <c r="Q52" s="40">
-        <f>IF(OR(G52="",O52="Aprovado",O52="Recusado",O52="Sem retorno"),0,IF(O52="Parado",2000,1000)+MIN(N(M52),500)+N(F52)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G52="",O52="Aprovado",O52="Recusado",O52="Sem retorno"),0,IF(O52="Parado",2,1)*1E+13+MIN(N(M52),500)*1E+10+MIN(ROUND(N(F52),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -5932,7 +5932,7 @@
         <v/>
       </c>
       <c r="Q53" s="40">
-        <f>IF(OR(G53="",O53="Aprovado",O53="Recusado",O53="Sem retorno"),0,IF(O53="Parado",2000,1000)+MIN(N(M53),500)+N(F53)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G53="",O53="Aprovado",O53="Recusado",O53="Sem retorno"),0,IF(O53="Parado",2,1)*1E+13+MIN(N(M53),500)*1E+10+MIN(ROUND(N(F53),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -5972,7 +5972,7 @@
         <v/>
       </c>
       <c r="Q54" s="40">
-        <f>IF(OR(G54="",O54="Aprovado",O54="Recusado",O54="Sem retorno"),0,IF(O54="Parado",2000,1000)+MIN(N(M54),500)+N(F54)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G54="",O54="Aprovado",O54="Recusado",O54="Sem retorno"),0,IF(O54="Parado",2,1)*1E+13+MIN(N(M54),500)*1E+10+MIN(ROUND(N(F54),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -6012,7 +6012,7 @@
         <v/>
       </c>
       <c r="Q55" s="40">
-        <f>IF(OR(G55="",O55="Aprovado",O55="Recusado",O55="Sem retorno"),0,IF(O55="Parado",2000,1000)+MIN(N(M55),500)+N(F55)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G55="",O55="Aprovado",O55="Recusado",O55="Sem retorno"),0,IF(O55="Parado",2,1)*1E+13+MIN(N(M55),500)*1E+10+MIN(ROUND(N(F55),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -6052,7 +6052,7 @@
         <v/>
       </c>
       <c r="Q56" s="40">
-        <f>IF(OR(G56="",O56="Aprovado",O56="Recusado",O56="Sem retorno"),0,IF(O56="Parado",2000,1000)+MIN(N(M56),500)+N(F56)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G56="",O56="Aprovado",O56="Recusado",O56="Sem retorno"),0,IF(O56="Parado",2,1)*1E+13+MIN(N(M56),500)*1E+10+MIN(ROUND(N(F56),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -6092,7 +6092,7 @@
         <v/>
       </c>
       <c r="Q57" s="40">
-        <f>IF(OR(G57="",O57="Aprovado",O57="Recusado",O57="Sem retorno"),0,IF(O57="Parado",2000,1000)+MIN(N(M57),500)+N(F57)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G57="",O57="Aprovado",O57="Recusado",O57="Sem retorno"),0,IF(O57="Parado",2,1)*1E+13+MIN(N(M57),500)*1E+10+MIN(ROUND(N(F57),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -6132,7 +6132,7 @@
         <v/>
       </c>
       <c r="Q58" s="40">
-        <f>IF(OR(G58="",O58="Aprovado",O58="Recusado",O58="Sem retorno"),0,IF(O58="Parado",2000,1000)+MIN(N(M58),500)+N(F58)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G58="",O58="Aprovado",O58="Recusado",O58="Sem retorno"),0,IF(O58="Parado",2,1)*1E+13+MIN(N(M58),500)*1E+10+MIN(ROUND(N(F58),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -6172,7 +6172,7 @@
         <v/>
       </c>
       <c r="Q59" s="40">
-        <f>IF(OR(G59="",O59="Aprovado",O59="Recusado",O59="Sem retorno"),0,IF(O59="Parado",2000,1000)+MIN(N(M59),500)+N(F59)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G59="",O59="Aprovado",O59="Recusado",O59="Sem retorno"),0,IF(O59="Parado",2,1)*1E+13+MIN(N(M59),500)*1E+10+MIN(ROUND(N(F59),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -6212,7 +6212,7 @@
         <v/>
       </c>
       <c r="Q60" s="40">
-        <f>IF(OR(G60="",O60="Aprovado",O60="Recusado",O60="Sem retorno"),0,IF(O60="Parado",2000,1000)+MIN(N(M60),500)+N(F60)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G60="",O60="Aprovado",O60="Recusado",O60="Sem retorno"),0,IF(O60="Parado",2,1)*1E+13+MIN(N(M60),500)*1E+10+MIN(ROUND(N(F60),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -6252,7 +6252,7 @@
         <v/>
       </c>
       <c r="Q61" s="40">
-        <f>IF(OR(G61="",O61="Aprovado",O61="Recusado",O61="Sem retorno"),0,IF(O61="Parado",2000,1000)+MIN(N(M61),500)+N(F61)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G61="",O61="Aprovado",O61="Recusado",O61="Sem retorno"),0,IF(O61="Parado",2,1)*1E+13+MIN(N(M61),500)*1E+10+MIN(ROUND(N(F61),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -6292,7 +6292,7 @@
         <v/>
       </c>
       <c r="Q62" s="40">
-        <f>IF(OR(G62="",O62="Aprovado",O62="Recusado",O62="Sem retorno"),0,IF(O62="Parado",2000,1000)+MIN(N(M62),500)+N(F62)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G62="",O62="Aprovado",O62="Recusado",O62="Sem retorno"),0,IF(O62="Parado",2,1)*1E+13+MIN(N(M62),500)*1E+10+MIN(ROUND(N(F62),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -6332,7 +6332,7 @@
         <v/>
       </c>
       <c r="Q63" s="40">
-        <f>IF(OR(G63="",O63="Aprovado",O63="Recusado",O63="Sem retorno"),0,IF(O63="Parado",2000,1000)+MIN(N(M63),500)+N(F63)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G63="",O63="Aprovado",O63="Recusado",O63="Sem retorno"),0,IF(O63="Parado",2,1)*1E+13+MIN(N(M63),500)*1E+10+MIN(ROUND(N(F63),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -6372,7 +6372,7 @@
         <v/>
       </c>
       <c r="Q64" s="40">
-        <f>IF(OR(G64="",O64="Aprovado",O64="Recusado",O64="Sem retorno"),0,IF(O64="Parado",2000,1000)+MIN(N(M64),500)+N(F64)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G64="",O64="Aprovado",O64="Recusado",O64="Sem retorno"),0,IF(O64="Parado",2,1)*1E+13+MIN(N(M64),500)*1E+10+MIN(ROUND(N(F64),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -6412,7 +6412,7 @@
         <v/>
       </c>
       <c r="Q65" s="40">
-        <f>IF(OR(G65="",O65="Aprovado",O65="Recusado",O65="Sem retorno"),0,IF(O65="Parado",2000,1000)+MIN(N(M65),500)+N(F65)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G65="",O65="Aprovado",O65="Recusado",O65="Sem retorno"),0,IF(O65="Parado",2,1)*1E+13+MIN(N(M65),500)*1E+10+MIN(ROUND(N(F65),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -6452,7 +6452,7 @@
         <v/>
       </c>
       <c r="Q66" s="40">
-        <f>IF(OR(G66="",O66="Aprovado",O66="Recusado",O66="Sem retorno"),0,IF(O66="Parado",2000,1000)+MIN(N(M66),500)+N(F66)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G66="",O66="Aprovado",O66="Recusado",O66="Sem retorno"),0,IF(O66="Parado",2,1)*1E+13+MIN(N(M66),500)*1E+10+MIN(ROUND(N(F66),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -6492,7 +6492,7 @@
         <v/>
       </c>
       <c r="Q67" s="40">
-        <f>IF(OR(G67="",O67="Aprovado",O67="Recusado",O67="Sem retorno"),0,IF(O67="Parado",2000,1000)+MIN(N(M67),500)+N(F67)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G67="",O67="Aprovado",O67="Recusado",O67="Sem retorno"),0,IF(O67="Parado",2,1)*1E+13+MIN(N(M67),500)*1E+10+MIN(ROUND(N(F67),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -6532,7 +6532,7 @@
         <v/>
       </c>
       <c r="Q68" s="40">
-        <f>IF(OR(G68="",O68="Aprovado",O68="Recusado",O68="Sem retorno"),0,IF(O68="Parado",2000,1000)+MIN(N(M68),500)+N(F68)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G68="",O68="Aprovado",O68="Recusado",O68="Sem retorno"),0,IF(O68="Parado",2,1)*1E+13+MIN(N(M68),500)*1E+10+MIN(ROUND(N(F68),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -6572,7 +6572,7 @@
         <v/>
       </c>
       <c r="Q69" s="40">
-        <f>IF(OR(G69="",O69="Aprovado",O69="Recusado",O69="Sem retorno"),0,IF(O69="Parado",2000,1000)+MIN(N(M69),500)+N(F69)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G69="",O69="Aprovado",O69="Recusado",O69="Sem retorno"),0,IF(O69="Parado",2,1)*1E+13+MIN(N(M69),500)*1E+10+MIN(ROUND(N(F69),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -6612,7 +6612,7 @@
         <v/>
       </c>
       <c r="Q70" s="40">
-        <f>IF(OR(G70="",O70="Aprovado",O70="Recusado",O70="Sem retorno"),0,IF(O70="Parado",2000,1000)+MIN(N(M70),500)+N(F70)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G70="",O70="Aprovado",O70="Recusado",O70="Sem retorno"),0,IF(O70="Parado",2,1)*1E+13+MIN(N(M70),500)*1E+10+MIN(ROUND(N(F70),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -6652,7 +6652,7 @@
         <v/>
       </c>
       <c r="Q71" s="40">
-        <f>IF(OR(G71="",O71="Aprovado",O71="Recusado",O71="Sem retorno"),0,IF(O71="Parado",2000,1000)+MIN(N(M71),500)+N(F71)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G71="",O71="Aprovado",O71="Recusado",O71="Sem retorno"),0,IF(O71="Parado",2,1)*1E+13+MIN(N(M71),500)*1E+10+MIN(ROUND(N(F71),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -6692,7 +6692,7 @@
         <v/>
       </c>
       <c r="Q72" s="40">
-        <f>IF(OR(G72="",O72="Aprovado",O72="Recusado",O72="Sem retorno"),0,IF(O72="Parado",2000,1000)+MIN(N(M72),500)+N(F72)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G72="",O72="Aprovado",O72="Recusado",O72="Sem retorno"),0,IF(O72="Parado",2,1)*1E+13+MIN(N(M72),500)*1E+10+MIN(ROUND(N(F72),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -6732,7 +6732,7 @@
         <v/>
       </c>
       <c r="Q73" s="40">
-        <f>IF(OR(G73="",O73="Aprovado",O73="Recusado",O73="Sem retorno"),0,IF(O73="Parado",2000,1000)+MIN(N(M73),500)+N(F73)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G73="",O73="Aprovado",O73="Recusado",O73="Sem retorno"),0,IF(O73="Parado",2,1)*1E+13+MIN(N(M73),500)*1E+10+MIN(ROUND(N(F73),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -6772,7 +6772,7 @@
         <v/>
       </c>
       <c r="Q74" s="40">
-        <f>IF(OR(G74="",O74="Aprovado",O74="Recusado",O74="Sem retorno"),0,IF(O74="Parado",2000,1000)+MIN(N(M74),500)+N(F74)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G74="",O74="Aprovado",O74="Recusado",O74="Sem retorno"),0,IF(O74="Parado",2,1)*1E+13+MIN(N(M74),500)*1E+10+MIN(ROUND(N(F74),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -6812,7 +6812,7 @@
         <v/>
       </c>
       <c r="Q75" s="40">
-        <f>IF(OR(G75="",O75="Aprovado",O75="Recusado",O75="Sem retorno"),0,IF(O75="Parado",2000,1000)+MIN(N(M75),500)+N(F75)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G75="",O75="Aprovado",O75="Recusado",O75="Sem retorno"),0,IF(O75="Parado",2,1)*1E+13+MIN(N(M75),500)*1E+10+MIN(ROUND(N(F75),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -6852,7 +6852,7 @@
         <v/>
       </c>
       <c r="Q76" s="40">
-        <f>IF(OR(G76="",O76="Aprovado",O76="Recusado",O76="Sem retorno"),0,IF(O76="Parado",2000,1000)+MIN(N(M76),500)+N(F76)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G76="",O76="Aprovado",O76="Recusado",O76="Sem retorno"),0,IF(O76="Parado",2,1)*1E+13+MIN(N(M76),500)*1E+10+MIN(ROUND(N(F76),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -6892,7 +6892,7 @@
         <v/>
       </c>
       <c r="Q77" s="40">
-        <f>IF(OR(G77="",O77="Aprovado",O77="Recusado",O77="Sem retorno"),0,IF(O77="Parado",2000,1000)+MIN(N(M77),500)+N(F77)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G77="",O77="Aprovado",O77="Recusado",O77="Sem retorno"),0,IF(O77="Parado",2,1)*1E+13+MIN(N(M77),500)*1E+10+MIN(ROUND(N(F77),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -6932,7 +6932,7 @@
         <v/>
       </c>
       <c r="Q78" s="40">
-        <f>IF(OR(G78="",O78="Aprovado",O78="Recusado",O78="Sem retorno"),0,IF(O78="Parado",2000,1000)+MIN(N(M78),500)+N(F78)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G78="",O78="Aprovado",O78="Recusado",O78="Sem retorno"),0,IF(O78="Parado",2,1)*1E+13+MIN(N(M78),500)*1E+10+MIN(ROUND(N(F78),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -6972,7 +6972,7 @@
         <v/>
       </c>
       <c r="Q79" s="40">
-        <f>IF(OR(G79="",O79="Aprovado",O79="Recusado",O79="Sem retorno"),0,IF(O79="Parado",2000,1000)+MIN(N(M79),500)+N(F79)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G79="",O79="Aprovado",O79="Recusado",O79="Sem retorno"),0,IF(O79="Parado",2,1)*1E+13+MIN(N(M79),500)*1E+10+MIN(ROUND(N(F79),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -7012,7 +7012,7 @@
         <v/>
       </c>
       <c r="Q80" s="40">
-        <f>IF(OR(G80="",O80="Aprovado",O80="Recusado",O80="Sem retorno"),0,IF(O80="Parado",2000,1000)+MIN(N(M80),500)+N(F80)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G80="",O80="Aprovado",O80="Recusado",O80="Sem retorno"),0,IF(O80="Parado",2,1)*1E+13+MIN(N(M80),500)*1E+10+MIN(ROUND(N(F80),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -7052,7 +7052,7 @@
         <v/>
       </c>
       <c r="Q81" s="40">
-        <f>IF(OR(G81="",O81="Aprovado",O81="Recusado",O81="Sem retorno"),0,IF(O81="Parado",2000,1000)+MIN(N(M81),500)+N(F81)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G81="",O81="Aprovado",O81="Recusado",O81="Sem retorno"),0,IF(O81="Parado",2,1)*1E+13+MIN(N(M81),500)*1E+10+MIN(ROUND(N(F81),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -7092,7 +7092,7 @@
         <v/>
       </c>
       <c r="Q82" s="40">
-        <f>IF(OR(G82="",O82="Aprovado",O82="Recusado",O82="Sem retorno"),0,IF(O82="Parado",2000,1000)+MIN(N(M82),500)+N(F82)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G82="",O82="Aprovado",O82="Recusado",O82="Sem retorno"),0,IF(O82="Parado",2,1)*1E+13+MIN(N(M82),500)*1E+10+MIN(ROUND(N(F82),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -7132,7 +7132,7 @@
         <v/>
       </c>
       <c r="Q83" s="40">
-        <f>IF(OR(G83="",O83="Aprovado",O83="Recusado",O83="Sem retorno"),0,IF(O83="Parado",2000,1000)+MIN(N(M83),500)+N(F83)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G83="",O83="Aprovado",O83="Recusado",O83="Sem retorno"),0,IF(O83="Parado",2,1)*1E+13+MIN(N(M83),500)*1E+10+MIN(ROUND(N(F83),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -7172,7 +7172,7 @@
         <v/>
       </c>
       <c r="Q84" s="40">
-        <f>IF(OR(G84="",O84="Aprovado",O84="Recusado",O84="Sem retorno"),0,IF(O84="Parado",2000,1000)+MIN(N(M84),500)+N(F84)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G84="",O84="Aprovado",O84="Recusado",O84="Sem retorno"),0,IF(O84="Parado",2,1)*1E+13+MIN(N(M84),500)*1E+10+MIN(ROUND(N(F84),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -7212,7 +7212,7 @@
         <v/>
       </c>
       <c r="Q85" s="40">
-        <f>IF(OR(G85="",O85="Aprovado",O85="Recusado",O85="Sem retorno"),0,IF(O85="Parado",2000,1000)+MIN(N(M85),500)+N(F85)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G85="",O85="Aprovado",O85="Recusado",O85="Sem retorno"),0,IF(O85="Parado",2,1)*1E+13+MIN(N(M85),500)*1E+10+MIN(ROUND(N(F85),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -7252,7 +7252,7 @@
         <v/>
       </c>
       <c r="Q86" s="40">
-        <f>IF(OR(G86="",O86="Aprovado",O86="Recusado",O86="Sem retorno"),0,IF(O86="Parado",2000,1000)+MIN(N(M86),500)+N(F86)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G86="",O86="Aprovado",O86="Recusado",O86="Sem retorno"),0,IF(O86="Parado",2,1)*1E+13+MIN(N(M86),500)*1E+10+MIN(ROUND(N(F86),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -7292,7 +7292,7 @@
         <v/>
       </c>
       <c r="Q87" s="40">
-        <f>IF(OR(G87="",O87="Aprovado",O87="Recusado",O87="Sem retorno"),0,IF(O87="Parado",2000,1000)+MIN(N(M87),500)+N(F87)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G87="",O87="Aprovado",O87="Recusado",O87="Sem retorno"),0,IF(O87="Parado",2,1)*1E+13+MIN(N(M87),500)*1E+10+MIN(ROUND(N(F87),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -7332,7 +7332,7 @@
         <v/>
       </c>
       <c r="Q88" s="40">
-        <f>IF(OR(G88="",O88="Aprovado",O88="Recusado",O88="Sem retorno"),0,IF(O88="Parado",2000,1000)+MIN(N(M88),500)+N(F88)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G88="",O88="Aprovado",O88="Recusado",O88="Sem retorno"),0,IF(O88="Parado",2,1)*1E+13+MIN(N(M88),500)*1E+10+MIN(ROUND(N(F88),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -7372,7 +7372,7 @@
         <v/>
       </c>
       <c r="Q89" s="40">
-        <f>IF(OR(G89="",O89="Aprovado",O89="Recusado",O89="Sem retorno"),0,IF(O89="Parado",2000,1000)+MIN(N(M89),500)+N(F89)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G89="",O89="Aprovado",O89="Recusado",O89="Sem retorno"),0,IF(O89="Parado",2,1)*1E+13+MIN(N(M89),500)*1E+10+MIN(ROUND(N(F89),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -7412,7 +7412,7 @@
         <v/>
       </c>
       <c r="Q90" s="40">
-        <f>IF(OR(G90="",O90="Aprovado",O90="Recusado",O90="Sem retorno"),0,IF(O90="Parado",2000,1000)+MIN(N(M90),500)+N(F90)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G90="",O90="Aprovado",O90="Recusado",O90="Sem retorno"),0,IF(O90="Parado",2,1)*1E+13+MIN(N(M90),500)*1E+10+MIN(ROUND(N(F90),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -7452,7 +7452,7 @@
         <v/>
       </c>
       <c r="Q91" s="40">
-        <f>IF(OR(G91="",O91="Aprovado",O91="Recusado",O91="Sem retorno"),0,IF(O91="Parado",2000,1000)+MIN(N(M91),500)+N(F91)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G91="",O91="Aprovado",O91="Recusado",O91="Sem retorno"),0,IF(O91="Parado",2,1)*1E+13+MIN(N(M91),500)*1E+10+MIN(ROUND(N(F91),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -7492,7 +7492,7 @@
         <v/>
       </c>
       <c r="Q92" s="40">
-        <f>IF(OR(G92="",O92="Aprovado",O92="Recusado",O92="Sem retorno"),0,IF(O92="Parado",2000,1000)+MIN(N(M92),500)+N(F92)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G92="",O92="Aprovado",O92="Recusado",O92="Sem retorno"),0,IF(O92="Parado",2,1)*1E+13+MIN(N(M92),500)*1E+10+MIN(ROUND(N(F92),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -7532,7 +7532,7 @@
         <v/>
       </c>
       <c r="Q93" s="40">
-        <f>IF(OR(G93="",O93="Aprovado",O93="Recusado",O93="Sem retorno"),0,IF(O93="Parado",2000,1000)+MIN(N(M93),500)+N(F93)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G93="",O93="Aprovado",O93="Recusado",O93="Sem retorno"),0,IF(O93="Parado",2,1)*1E+13+MIN(N(M93),500)*1E+10+MIN(ROUND(N(F93),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -7572,7 +7572,7 @@
         <v/>
       </c>
       <c r="Q94" s="40">
-        <f>IF(OR(G94="",O94="Aprovado",O94="Recusado",O94="Sem retorno"),0,IF(O94="Parado",2000,1000)+MIN(N(M94),500)+N(F94)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G94="",O94="Aprovado",O94="Recusado",O94="Sem retorno"),0,IF(O94="Parado",2,1)*1E+13+MIN(N(M94),500)*1E+10+MIN(ROUND(N(F94),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -7612,7 +7612,7 @@
         <v/>
       </c>
       <c r="Q95" s="40">
-        <f>IF(OR(G95="",O95="Aprovado",O95="Recusado",O95="Sem retorno"),0,IF(O95="Parado",2000,1000)+MIN(N(M95),500)+N(F95)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G95="",O95="Aprovado",O95="Recusado",O95="Sem retorno"),0,IF(O95="Parado",2,1)*1E+13+MIN(N(M95),500)*1E+10+MIN(ROUND(N(F95),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -7652,7 +7652,7 @@
         <v/>
       </c>
       <c r="Q96" s="40">
-        <f>IF(OR(G96="",O96="Aprovado",O96="Recusado",O96="Sem retorno"),0,IF(O96="Parado",2000,1000)+MIN(N(M96),500)+N(F96)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G96="",O96="Aprovado",O96="Recusado",O96="Sem retorno"),0,IF(O96="Parado",2,1)*1E+13+MIN(N(M96),500)*1E+10+MIN(ROUND(N(F96),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -7692,7 +7692,7 @@
         <v/>
       </c>
       <c r="Q97" s="40">
-        <f>IF(OR(G97="",O97="Aprovado",O97="Recusado",O97="Sem retorno"),0,IF(O97="Parado",2000,1000)+MIN(N(M97),500)+N(F97)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G97="",O97="Aprovado",O97="Recusado",O97="Sem retorno"),0,IF(O97="Parado",2,1)*1E+13+MIN(N(M97),500)*1E+10+MIN(ROUND(N(F97),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -7732,7 +7732,7 @@
         <v/>
       </c>
       <c r="Q98" s="40">
-        <f>IF(OR(G98="",O98="Aprovado",O98="Recusado",O98="Sem retorno"),0,IF(O98="Parado",2000,1000)+MIN(N(M98),500)+N(F98)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G98="",O98="Aprovado",O98="Recusado",O98="Sem retorno"),0,IF(O98="Parado",2,1)*1E+13+MIN(N(M98),500)*1E+10+MIN(ROUND(N(F98),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -7772,7 +7772,7 @@
         <v/>
       </c>
       <c r="Q99" s="40">
-        <f>IF(OR(G99="",O99="Aprovado",O99="Recusado",O99="Sem retorno"),0,IF(O99="Parado",2000,1000)+MIN(N(M99),500)+N(F99)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G99="",O99="Aprovado",O99="Recusado",O99="Sem retorno"),0,IF(O99="Parado",2,1)*1E+13+MIN(N(M99),500)*1E+10+MIN(ROUND(N(F99),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -7812,7 +7812,7 @@
         <v/>
       </c>
       <c r="Q100" s="40">
-        <f>IF(OR(G100="",O100="Aprovado",O100="Recusado",O100="Sem retorno"),0,IF(O100="Parado",2000,1000)+MIN(N(M100),500)+N(F100)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G100="",O100="Aprovado",O100="Recusado",O100="Sem retorno"),0,IF(O100="Parado",2,1)*1E+13+MIN(N(M100),500)*1E+10+MIN(ROUND(N(F100),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -7852,7 +7852,7 @@
         <v/>
       </c>
       <c r="Q101" s="40">
-        <f>IF(OR(G101="",O101="Aprovado",O101="Recusado",O101="Sem retorno"),0,IF(O101="Parado",2000,1000)+MIN(N(M101),500)+N(F101)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G101="",O101="Aprovado",O101="Recusado",O101="Sem retorno"),0,IF(O101="Parado",2,1)*1E+13+MIN(N(M101),500)*1E+10+MIN(ROUND(N(F101),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -7892,7 +7892,7 @@
         <v/>
       </c>
       <c r="Q102" s="40">
-        <f>IF(OR(G102="",O102="Aprovado",O102="Recusado",O102="Sem retorno"),0,IF(O102="Parado",2000,1000)+MIN(N(M102),500)+N(F102)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G102="",O102="Aprovado",O102="Recusado",O102="Sem retorno"),0,IF(O102="Parado",2,1)*1E+13+MIN(N(M102),500)*1E+10+MIN(ROUND(N(F102),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -7932,7 +7932,7 @@
         <v/>
       </c>
       <c r="Q103" s="40">
-        <f>IF(OR(G103="",O103="Aprovado",O103="Recusado",O103="Sem retorno"),0,IF(O103="Parado",2000,1000)+MIN(N(M103),500)+N(F103)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G103="",O103="Aprovado",O103="Recusado",O103="Sem retorno"),0,IF(O103="Parado",2,1)*1E+13+MIN(N(M103),500)*1E+10+MIN(ROUND(N(F103),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -7972,7 +7972,7 @@
         <v/>
       </c>
       <c r="Q104" s="40">
-        <f>IF(OR(G104="",O104="Aprovado",O104="Recusado",O104="Sem retorno"),0,IF(O104="Parado",2000,1000)+MIN(N(M104),500)+N(F104)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G104="",O104="Aprovado",O104="Recusado",O104="Sem retorno"),0,IF(O104="Parado",2,1)*1E+13+MIN(N(M104),500)*1E+10+MIN(ROUND(N(F104),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -8012,7 +8012,7 @@
         <v/>
       </c>
       <c r="Q105" s="40">
-        <f>IF(OR(G105="",O105="Aprovado",O105="Recusado",O105="Sem retorno"),0,IF(O105="Parado",2000,1000)+MIN(N(M105),500)+N(F105)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G105="",O105="Aprovado",O105="Recusado",O105="Sem retorno"),0,IF(O105="Parado",2,1)*1E+13+MIN(N(M105),500)*1E+10+MIN(ROUND(N(F105),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -8052,7 +8052,7 @@
         <v/>
       </c>
       <c r="Q106" s="40">
-        <f>IF(OR(G106="",O106="Aprovado",O106="Recusado",O106="Sem retorno"),0,IF(O106="Parado",2000,1000)+MIN(N(M106),500)+N(F106)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G106="",O106="Aprovado",O106="Recusado",O106="Sem retorno"),0,IF(O106="Parado",2,1)*1E+13+MIN(N(M106),500)*1E+10+MIN(ROUND(N(F106),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -8092,7 +8092,7 @@
         <v/>
       </c>
       <c r="Q107" s="40">
-        <f>IF(OR(G107="",O107="Aprovado",O107="Recusado",O107="Sem retorno"),0,IF(O107="Parado",2000,1000)+MIN(N(M107),500)+N(F107)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G107="",O107="Aprovado",O107="Recusado",O107="Sem retorno"),0,IF(O107="Parado",2,1)*1E+13+MIN(N(M107),500)*1E+10+MIN(ROUND(N(F107),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -8132,7 +8132,7 @@
         <v/>
       </c>
       <c r="Q108" s="40">
-        <f>IF(OR(G108="",O108="Aprovado",O108="Recusado",O108="Sem retorno"),0,IF(O108="Parado",2000,1000)+MIN(N(M108),500)+N(F108)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G108="",O108="Aprovado",O108="Recusado",O108="Sem retorno"),0,IF(O108="Parado",2,1)*1E+13+MIN(N(M108),500)*1E+10+MIN(ROUND(N(F108),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -8172,7 +8172,7 @@
         <v/>
       </c>
       <c r="Q109" s="40">
-        <f>IF(OR(G109="",O109="Aprovado",O109="Recusado",O109="Sem retorno"),0,IF(O109="Parado",2000,1000)+MIN(N(M109),500)+N(F109)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G109="",O109="Aprovado",O109="Recusado",O109="Sem retorno"),0,IF(O109="Parado",2,1)*1E+13+MIN(N(M109),500)*1E+10+MIN(ROUND(N(F109),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -8212,7 +8212,7 @@
         <v/>
       </c>
       <c r="Q110" s="40">
-        <f>IF(OR(G110="",O110="Aprovado",O110="Recusado",O110="Sem retorno"),0,IF(O110="Parado",2000,1000)+MIN(N(M110),500)+N(F110)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G110="",O110="Aprovado",O110="Recusado",O110="Sem retorno"),0,IF(O110="Parado",2,1)*1E+13+MIN(N(M110),500)*1E+10+MIN(ROUND(N(F110),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -8252,7 +8252,7 @@
         <v/>
       </c>
       <c r="Q111" s="40">
-        <f>IF(OR(G111="",O111="Aprovado",O111="Recusado",O111="Sem retorno"),0,IF(O111="Parado",2000,1000)+MIN(N(M111),500)+N(F111)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G111="",O111="Aprovado",O111="Recusado",O111="Sem retorno"),0,IF(O111="Parado",2,1)*1E+13+MIN(N(M111),500)*1E+10+MIN(ROUND(N(F111),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -8292,7 +8292,7 @@
         <v/>
       </c>
       <c r="Q112" s="40">
-        <f>IF(OR(G112="",O112="Aprovado",O112="Recusado",O112="Sem retorno"),0,IF(O112="Parado",2000,1000)+MIN(N(M112),500)+N(F112)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G112="",O112="Aprovado",O112="Recusado",O112="Sem retorno"),0,IF(O112="Parado",2,1)*1E+13+MIN(N(M112),500)*1E+10+MIN(ROUND(N(F112),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -8332,7 +8332,7 @@
         <v/>
       </c>
       <c r="Q113" s="40">
-        <f>IF(OR(G113="",O113="Aprovado",O113="Recusado",O113="Sem retorno"),0,IF(O113="Parado",2000,1000)+MIN(N(M113),500)+N(F113)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G113="",O113="Aprovado",O113="Recusado",O113="Sem retorno"),0,IF(O113="Parado",2,1)*1E+13+MIN(N(M113),500)*1E+10+MIN(ROUND(N(F113),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -8372,7 +8372,7 @@
         <v/>
       </c>
       <c r="Q114" s="40">
-        <f>IF(OR(G114="",O114="Aprovado",O114="Recusado",O114="Sem retorno"),0,IF(O114="Parado",2000,1000)+MIN(N(M114),500)+N(F114)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G114="",O114="Aprovado",O114="Recusado",O114="Sem retorno"),0,IF(O114="Parado",2,1)*1E+13+MIN(N(M114),500)*1E+10+MIN(ROUND(N(F114),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -8412,7 +8412,7 @@
         <v/>
       </c>
       <c r="Q115" s="40">
-        <f>IF(OR(G115="",O115="Aprovado",O115="Recusado",O115="Sem retorno"),0,IF(O115="Parado",2000,1000)+MIN(N(M115),500)+N(F115)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G115="",O115="Aprovado",O115="Recusado",O115="Sem retorno"),0,IF(O115="Parado",2,1)*1E+13+MIN(N(M115),500)*1E+10+MIN(ROUND(N(F115),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -8452,7 +8452,7 @@
         <v/>
       </c>
       <c r="Q116" s="40">
-        <f>IF(OR(G116="",O116="Aprovado",O116="Recusado",O116="Sem retorno"),0,IF(O116="Parado",2000,1000)+MIN(N(M116),500)+N(F116)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G116="",O116="Aprovado",O116="Recusado",O116="Sem retorno"),0,IF(O116="Parado",2,1)*1E+13+MIN(N(M116),500)*1E+10+MIN(ROUND(N(F116),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -8492,7 +8492,7 @@
         <v/>
       </c>
       <c r="Q117" s="40">
-        <f>IF(OR(G117="",O117="Aprovado",O117="Recusado",O117="Sem retorno"),0,IF(O117="Parado",2000,1000)+MIN(N(M117),500)+N(F117)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G117="",O117="Aprovado",O117="Recusado",O117="Sem retorno"),0,IF(O117="Parado",2,1)*1E+13+MIN(N(M117),500)*1E+10+MIN(ROUND(N(F117),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -8532,7 +8532,7 @@
         <v/>
       </c>
       <c r="Q118" s="40">
-        <f>IF(OR(G118="",O118="Aprovado",O118="Recusado",O118="Sem retorno"),0,IF(O118="Parado",2000,1000)+MIN(N(M118),500)+N(F118)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G118="",O118="Aprovado",O118="Recusado",O118="Sem retorno"),0,IF(O118="Parado",2,1)*1E+13+MIN(N(M118),500)*1E+10+MIN(ROUND(N(F118),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -8572,7 +8572,7 @@
         <v/>
       </c>
       <c r="Q119" s="40">
-        <f>IF(OR(G119="",O119="Aprovado",O119="Recusado",O119="Sem retorno"),0,IF(O119="Parado",2000,1000)+MIN(N(M119),500)+N(F119)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G119="",O119="Aprovado",O119="Recusado",O119="Sem retorno"),0,IF(O119="Parado",2,1)*1E+13+MIN(N(M119),500)*1E+10+MIN(ROUND(N(F119),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -8612,7 +8612,7 @@
         <v/>
       </c>
       <c r="Q120" s="40">
-        <f>IF(OR(G120="",O120="Aprovado",O120="Recusado",O120="Sem retorno"),0,IF(O120="Parado",2000,1000)+MIN(N(M120),500)+N(F120)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G120="",O120="Aprovado",O120="Recusado",O120="Sem retorno"),0,IF(O120="Parado",2,1)*1E+13+MIN(N(M120),500)*1E+10+MIN(ROUND(N(F120),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -8652,7 +8652,7 @@
         <v/>
       </c>
       <c r="Q121" s="40">
-        <f>IF(OR(G121="",O121="Aprovado",O121="Recusado",O121="Sem retorno"),0,IF(O121="Parado",2000,1000)+MIN(N(M121),500)+N(F121)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G121="",O121="Aprovado",O121="Recusado",O121="Sem retorno"),0,IF(O121="Parado",2,1)*1E+13+MIN(N(M121),500)*1E+10+MIN(ROUND(N(F121),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -8692,7 +8692,7 @@
         <v/>
       </c>
       <c r="Q122" s="40">
-        <f>IF(OR(G122="",O122="Aprovado",O122="Recusado",O122="Sem retorno"),0,IF(O122="Parado",2000,1000)+MIN(N(M122),500)+N(F122)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G122="",O122="Aprovado",O122="Recusado",O122="Sem retorno"),0,IF(O122="Parado",2,1)*1E+13+MIN(N(M122),500)*1E+10+MIN(ROUND(N(F122),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -8732,7 +8732,7 @@
         <v/>
       </c>
       <c r="Q123" s="40">
-        <f>IF(OR(G123="",O123="Aprovado",O123="Recusado",O123="Sem retorno"),0,IF(O123="Parado",2000,1000)+MIN(N(M123),500)+N(F123)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G123="",O123="Aprovado",O123="Recusado",O123="Sem retorno"),0,IF(O123="Parado",2,1)*1E+13+MIN(N(M123),500)*1E+10+MIN(ROUND(N(F123),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -8772,7 +8772,7 @@
         <v/>
       </c>
       <c r="Q124" s="40">
-        <f>IF(OR(G124="",O124="Aprovado",O124="Recusado",O124="Sem retorno"),0,IF(O124="Parado",2000,1000)+MIN(N(M124),500)+N(F124)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G124="",O124="Aprovado",O124="Recusado",O124="Sem retorno"),0,IF(O124="Parado",2,1)*1E+13+MIN(N(M124),500)*1E+10+MIN(ROUND(N(F124),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -8812,7 +8812,7 @@
         <v/>
       </c>
       <c r="Q125" s="40">
-        <f>IF(OR(G125="",O125="Aprovado",O125="Recusado",O125="Sem retorno"),0,IF(O125="Parado",2000,1000)+MIN(N(M125),500)+N(F125)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G125="",O125="Aprovado",O125="Recusado",O125="Sem retorno"),0,IF(O125="Parado",2,1)*1E+13+MIN(N(M125),500)*1E+10+MIN(ROUND(N(F125),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -8852,7 +8852,7 @@
         <v/>
       </c>
       <c r="Q126" s="40">
-        <f>IF(OR(G126="",O126="Aprovado",O126="Recusado",O126="Sem retorno"),0,IF(O126="Parado",2000,1000)+MIN(N(M126),500)+N(F126)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G126="",O126="Aprovado",O126="Recusado",O126="Sem retorno"),0,IF(O126="Parado",2,1)*1E+13+MIN(N(M126),500)*1E+10+MIN(ROUND(N(F126),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -8892,7 +8892,7 @@
         <v/>
       </c>
       <c r="Q127" s="40">
-        <f>IF(OR(G127="",O127="Aprovado",O127="Recusado",O127="Sem retorno"),0,IF(O127="Parado",2000,1000)+MIN(N(M127),500)+N(F127)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G127="",O127="Aprovado",O127="Recusado",O127="Sem retorno"),0,IF(O127="Parado",2,1)*1E+13+MIN(N(M127),500)*1E+10+MIN(ROUND(N(F127),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -8932,7 +8932,7 @@
         <v/>
       </c>
       <c r="Q128" s="40">
-        <f>IF(OR(G128="",O128="Aprovado",O128="Recusado",O128="Sem retorno"),0,IF(O128="Parado",2000,1000)+MIN(N(M128),500)+N(F128)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G128="",O128="Aprovado",O128="Recusado",O128="Sem retorno"),0,IF(O128="Parado",2,1)*1E+13+MIN(N(M128),500)*1E+10+MIN(ROUND(N(F128),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -8972,7 +8972,7 @@
         <v/>
       </c>
       <c r="Q129" s="40">
-        <f>IF(OR(G129="",O129="Aprovado",O129="Recusado",O129="Sem retorno"),0,IF(O129="Parado",2000,1000)+MIN(N(M129),500)+N(F129)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G129="",O129="Aprovado",O129="Recusado",O129="Sem retorno"),0,IF(O129="Parado",2,1)*1E+13+MIN(N(M129),500)*1E+10+MIN(ROUND(N(F129),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -9012,7 +9012,7 @@
         <v/>
       </c>
       <c r="Q130" s="40">
-        <f>IF(OR(G130="",O130="Aprovado",O130="Recusado",O130="Sem retorno"),0,IF(O130="Parado",2000,1000)+MIN(N(M130),500)+N(F130)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G130="",O130="Aprovado",O130="Recusado",O130="Sem retorno"),0,IF(O130="Parado",2,1)*1E+13+MIN(N(M130),500)*1E+10+MIN(ROUND(N(F130),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -9052,7 +9052,7 @@
         <v/>
       </c>
       <c r="Q131" s="40">
-        <f>IF(OR(G131="",O131="Aprovado",O131="Recusado",O131="Sem retorno"),0,IF(O131="Parado",2000,1000)+MIN(N(M131),500)+N(F131)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G131="",O131="Aprovado",O131="Recusado",O131="Sem retorno"),0,IF(O131="Parado",2,1)*1E+13+MIN(N(M131),500)*1E+10+MIN(ROUND(N(F131),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -9092,7 +9092,7 @@
         <v/>
       </c>
       <c r="Q132" s="40">
-        <f>IF(OR(G132="",O132="Aprovado",O132="Recusado",O132="Sem retorno"),0,IF(O132="Parado",2000,1000)+MIN(N(M132),500)+N(F132)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G132="",O132="Aprovado",O132="Recusado",O132="Sem retorno"),0,IF(O132="Parado",2,1)*1E+13+MIN(N(M132),500)*1E+10+MIN(ROUND(N(F132),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -9132,7 +9132,7 @@
         <v/>
       </c>
       <c r="Q133" s="40">
-        <f>IF(OR(G133="",O133="Aprovado",O133="Recusado",O133="Sem retorno"),0,IF(O133="Parado",2000,1000)+MIN(N(M133),500)+N(F133)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G133="",O133="Aprovado",O133="Recusado",O133="Sem retorno"),0,IF(O133="Parado",2,1)*1E+13+MIN(N(M133),500)*1E+10+MIN(ROUND(N(F133),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -9172,7 +9172,7 @@
         <v/>
       </c>
       <c r="Q134" s="40">
-        <f>IF(OR(G134="",O134="Aprovado",O134="Recusado",O134="Sem retorno"),0,IF(O134="Parado",2000,1000)+MIN(N(M134),500)+N(F134)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G134="",O134="Aprovado",O134="Recusado",O134="Sem retorno"),0,IF(O134="Parado",2,1)*1E+13+MIN(N(M134),500)*1E+10+MIN(ROUND(N(F134),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -9212,7 +9212,7 @@
         <v/>
       </c>
       <c r="Q135" s="40">
-        <f>IF(OR(G135="",O135="Aprovado",O135="Recusado",O135="Sem retorno"),0,IF(O135="Parado",2000,1000)+MIN(N(M135),500)+N(F135)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G135="",O135="Aprovado",O135="Recusado",O135="Sem retorno"),0,IF(O135="Parado",2,1)*1E+13+MIN(N(M135),500)*1E+10+MIN(ROUND(N(F135),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -9252,7 +9252,7 @@
         <v/>
       </c>
       <c r="Q136" s="40">
-        <f>IF(OR(G136="",O136="Aprovado",O136="Recusado",O136="Sem retorno"),0,IF(O136="Parado",2000,1000)+MIN(N(M136),500)+N(F136)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G136="",O136="Aprovado",O136="Recusado",O136="Sem retorno"),0,IF(O136="Parado",2,1)*1E+13+MIN(N(M136),500)*1E+10+MIN(ROUND(N(F136),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -9292,7 +9292,7 @@
         <v/>
       </c>
       <c r="Q137" s="40">
-        <f>IF(OR(G137="",O137="Aprovado",O137="Recusado",O137="Sem retorno"),0,IF(O137="Parado",2000,1000)+MIN(N(M137),500)+N(F137)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G137="",O137="Aprovado",O137="Recusado",O137="Sem retorno"),0,IF(O137="Parado",2,1)*1E+13+MIN(N(M137),500)*1E+10+MIN(ROUND(N(F137),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -9332,7 +9332,7 @@
         <v/>
       </c>
       <c r="Q138" s="40">
-        <f>IF(OR(G138="",O138="Aprovado",O138="Recusado",O138="Sem retorno"),0,IF(O138="Parado",2000,1000)+MIN(N(M138),500)+N(F138)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G138="",O138="Aprovado",O138="Recusado",O138="Sem retorno"),0,IF(O138="Parado",2,1)*1E+13+MIN(N(M138),500)*1E+10+MIN(ROUND(N(F138),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -9372,7 +9372,7 @@
         <v/>
       </c>
       <c r="Q139" s="40">
-        <f>IF(OR(G139="",O139="Aprovado",O139="Recusado",O139="Sem retorno"),0,IF(O139="Parado",2000,1000)+MIN(N(M139),500)+N(F139)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G139="",O139="Aprovado",O139="Recusado",O139="Sem retorno"),0,IF(O139="Parado",2,1)*1E+13+MIN(N(M139),500)*1E+10+MIN(ROUND(N(F139),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -9412,7 +9412,7 @@
         <v/>
       </c>
       <c r="Q140" s="40">
-        <f>IF(OR(G140="",O140="Aprovado",O140="Recusado",O140="Sem retorno"),0,IF(O140="Parado",2000,1000)+MIN(N(M140),500)+N(F140)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G140="",O140="Aprovado",O140="Recusado",O140="Sem retorno"),0,IF(O140="Parado",2,1)*1E+13+MIN(N(M140),500)*1E+10+MIN(ROUND(N(F140),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -9452,7 +9452,7 @@
         <v/>
       </c>
       <c r="Q141" s="40">
-        <f>IF(OR(G141="",O141="Aprovado",O141="Recusado",O141="Sem retorno"),0,IF(O141="Parado",2000,1000)+MIN(N(M141),500)+N(F141)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G141="",O141="Aprovado",O141="Recusado",O141="Sem retorno"),0,IF(O141="Parado",2,1)*1E+13+MIN(N(M141),500)*1E+10+MIN(ROUND(N(F141),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -9492,7 +9492,7 @@
         <v/>
       </c>
       <c r="Q142" s="40">
-        <f>IF(OR(G142="",O142="Aprovado",O142="Recusado",O142="Sem retorno"),0,IF(O142="Parado",2000,1000)+MIN(N(M142),500)+N(F142)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G142="",O142="Aprovado",O142="Recusado",O142="Sem retorno"),0,IF(O142="Parado",2,1)*1E+13+MIN(N(M142),500)*1E+10+MIN(ROUND(N(F142),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -9532,7 +9532,7 @@
         <v/>
       </c>
       <c r="Q143" s="40">
-        <f>IF(OR(G143="",O143="Aprovado",O143="Recusado",O143="Sem retorno"),0,IF(O143="Parado",2000,1000)+MIN(N(M143),500)+N(F143)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G143="",O143="Aprovado",O143="Recusado",O143="Sem retorno"),0,IF(O143="Parado",2,1)*1E+13+MIN(N(M143),500)*1E+10+MIN(ROUND(N(F143),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -9572,7 +9572,7 @@
         <v/>
       </c>
       <c r="Q144" s="40">
-        <f>IF(OR(G144="",O144="Aprovado",O144="Recusado",O144="Sem retorno"),0,IF(O144="Parado",2000,1000)+MIN(N(M144),500)+N(F144)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G144="",O144="Aprovado",O144="Recusado",O144="Sem retorno"),0,IF(O144="Parado",2,1)*1E+13+MIN(N(M144),500)*1E+10+MIN(ROUND(N(F144),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -9612,7 +9612,7 @@
         <v/>
       </c>
       <c r="Q145" s="40">
-        <f>IF(OR(G145="",O145="Aprovado",O145="Recusado",O145="Sem retorno"),0,IF(O145="Parado",2000,1000)+MIN(N(M145),500)+N(F145)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G145="",O145="Aprovado",O145="Recusado",O145="Sem retorno"),0,IF(O145="Parado",2,1)*1E+13+MIN(N(M145),500)*1E+10+MIN(ROUND(N(F145),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -9652,7 +9652,7 @@
         <v/>
       </c>
       <c r="Q146" s="40">
-        <f>IF(OR(G146="",O146="Aprovado",O146="Recusado",O146="Sem retorno"),0,IF(O146="Parado",2000,1000)+MIN(N(M146),500)+N(F146)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G146="",O146="Aprovado",O146="Recusado",O146="Sem retorno"),0,IF(O146="Parado",2,1)*1E+13+MIN(N(M146),500)*1E+10+MIN(ROUND(N(F146),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -9692,7 +9692,7 @@
         <v/>
       </c>
       <c r="Q147" s="40">
-        <f>IF(OR(G147="",O147="Aprovado",O147="Recusado",O147="Sem retorno"),0,IF(O147="Parado",2000,1000)+MIN(N(M147),500)+N(F147)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G147="",O147="Aprovado",O147="Recusado",O147="Sem retorno"),0,IF(O147="Parado",2,1)*1E+13+MIN(N(M147),500)*1E+10+MIN(ROUND(N(F147),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -9732,7 +9732,7 @@
         <v/>
       </c>
       <c r="Q148" s="40">
-        <f>IF(OR(G148="",O148="Aprovado",O148="Recusado",O148="Sem retorno"),0,IF(O148="Parado",2000,1000)+MIN(N(M148),500)+N(F148)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G148="",O148="Aprovado",O148="Recusado",O148="Sem retorno"),0,IF(O148="Parado",2,1)*1E+13+MIN(N(M148),500)*1E+10+MIN(ROUND(N(F148),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -9772,7 +9772,7 @@
         <v/>
       </c>
       <c r="Q149" s="40">
-        <f>IF(OR(G149="",O149="Aprovado",O149="Recusado",O149="Sem retorno"),0,IF(O149="Parado",2000,1000)+MIN(N(M149),500)+N(F149)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G149="",O149="Aprovado",O149="Recusado",O149="Sem retorno"),0,IF(O149="Parado",2,1)*1E+13+MIN(N(M149),500)*1E+10+MIN(ROUND(N(F149),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -9812,7 +9812,7 @@
         <v/>
       </c>
       <c r="Q150" s="40">
-        <f>IF(OR(G150="",O150="Aprovado",O150="Recusado",O150="Sem retorno"),0,IF(O150="Parado",2000,1000)+MIN(N(M150),500)+N(F150)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G150="",O150="Aprovado",O150="Recusado",O150="Sem retorno"),0,IF(O150="Parado",2,1)*1E+13+MIN(N(M150),500)*1E+10+MIN(ROUND(N(F150),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -9852,7 +9852,7 @@
         <v/>
       </c>
       <c r="Q151" s="40">
-        <f>IF(OR(G151="",O151="Aprovado",O151="Recusado",O151="Sem retorno"),0,IF(O151="Parado",2000,1000)+MIN(N(M151),500)+N(F151)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G151="",O151="Aprovado",O151="Recusado",O151="Sem retorno"),0,IF(O151="Parado",2,1)*1E+13+MIN(N(M151),500)*1E+10+MIN(ROUND(N(F151),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -9892,7 +9892,7 @@
         <v/>
       </c>
       <c r="Q152" s="40">
-        <f>IF(OR(G152="",O152="Aprovado",O152="Recusado",O152="Sem retorno"),0,IF(O152="Parado",2000,1000)+MIN(N(M152),500)+N(F152)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G152="",O152="Aprovado",O152="Recusado",O152="Sem retorno"),0,IF(O152="Parado",2,1)*1E+13+MIN(N(M152),500)*1E+10+MIN(ROUND(N(F152),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -9932,7 +9932,7 @@
         <v/>
       </c>
       <c r="Q153" s="40">
-        <f>IF(OR(G153="",O153="Aprovado",O153="Recusado",O153="Sem retorno"),0,IF(O153="Parado",2000,1000)+MIN(N(M153),500)+N(F153)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G153="",O153="Aprovado",O153="Recusado",O153="Sem retorno"),0,IF(O153="Parado",2,1)*1E+13+MIN(N(M153),500)*1E+10+MIN(ROUND(N(F153),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -9972,7 +9972,7 @@
         <v/>
       </c>
       <c r="Q154" s="40">
-        <f>IF(OR(G154="",O154="Aprovado",O154="Recusado",O154="Sem retorno"),0,IF(O154="Parado",2000,1000)+MIN(N(M154),500)+N(F154)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G154="",O154="Aprovado",O154="Recusado",O154="Sem retorno"),0,IF(O154="Parado",2,1)*1E+13+MIN(N(M154),500)*1E+10+MIN(ROUND(N(F154),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -10012,7 +10012,7 @@
         <v/>
       </c>
       <c r="Q155" s="40">
-        <f>IF(OR(G155="",O155="Aprovado",O155="Recusado",O155="Sem retorno"),0,IF(O155="Parado",2000,1000)+MIN(N(M155),500)+N(F155)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G155="",O155="Aprovado",O155="Recusado",O155="Sem retorno"),0,IF(O155="Parado",2,1)*1E+13+MIN(N(M155),500)*1E+10+MIN(ROUND(N(F155),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -10052,7 +10052,7 @@
         <v/>
       </c>
       <c r="Q156" s="40">
-        <f>IF(OR(G156="",O156="Aprovado",O156="Recusado",O156="Sem retorno"),0,IF(O156="Parado",2000,1000)+MIN(N(M156),500)+N(F156)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G156="",O156="Aprovado",O156="Recusado",O156="Sem retorno"),0,IF(O156="Parado",2,1)*1E+13+MIN(N(M156),500)*1E+10+MIN(ROUND(N(F156),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -10092,7 +10092,7 @@
         <v/>
       </c>
       <c r="Q157" s="40">
-        <f>IF(OR(G157="",O157="Aprovado",O157="Recusado",O157="Sem retorno"),0,IF(O157="Parado",2000,1000)+MIN(N(M157),500)+N(F157)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G157="",O157="Aprovado",O157="Recusado",O157="Sem retorno"),0,IF(O157="Parado",2,1)*1E+13+MIN(N(M157),500)*1E+10+MIN(ROUND(N(F157),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -10132,7 +10132,7 @@
         <v/>
       </c>
       <c r="Q158" s="40">
-        <f>IF(OR(G158="",O158="Aprovado",O158="Recusado",O158="Sem retorno"),0,IF(O158="Parado",2000,1000)+MIN(N(M158),500)+N(F158)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G158="",O158="Aprovado",O158="Recusado",O158="Sem retorno"),0,IF(O158="Parado",2,1)*1E+13+MIN(N(M158),500)*1E+10+MIN(ROUND(N(F158),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -10172,7 +10172,7 @@
         <v/>
       </c>
       <c r="Q159" s="40">
-        <f>IF(OR(G159="",O159="Aprovado",O159="Recusado",O159="Sem retorno"),0,IF(O159="Parado",2000,1000)+MIN(N(M159),500)+N(F159)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G159="",O159="Aprovado",O159="Recusado",O159="Sem retorno"),0,IF(O159="Parado",2,1)*1E+13+MIN(N(M159),500)*1E+10+MIN(ROUND(N(F159),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -10212,7 +10212,7 @@
         <v/>
       </c>
       <c r="Q160" s="40">
-        <f>IF(OR(G160="",O160="Aprovado",O160="Recusado",O160="Sem retorno"),0,IF(O160="Parado",2000,1000)+MIN(N(M160),500)+N(F160)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G160="",O160="Aprovado",O160="Recusado",O160="Sem retorno"),0,IF(O160="Parado",2,1)*1E+13+MIN(N(M160),500)*1E+10+MIN(ROUND(N(F160),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -10252,7 +10252,7 @@
         <v/>
       </c>
       <c r="Q161" s="40">
-        <f>IF(OR(G161="",O161="Aprovado",O161="Recusado",O161="Sem retorno"),0,IF(O161="Parado",2000,1000)+MIN(N(M161),500)+N(F161)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G161="",O161="Aprovado",O161="Recusado",O161="Sem retorno"),0,IF(O161="Parado",2,1)*1E+13+MIN(N(M161),500)*1E+10+MIN(ROUND(N(F161),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -10292,7 +10292,7 @@
         <v/>
       </c>
       <c r="Q162" s="40">
-        <f>IF(OR(G162="",O162="Aprovado",O162="Recusado",O162="Sem retorno"),0,IF(O162="Parado",2000,1000)+MIN(N(M162),500)+N(F162)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G162="",O162="Aprovado",O162="Recusado",O162="Sem retorno"),0,IF(O162="Parado",2,1)*1E+13+MIN(N(M162),500)*1E+10+MIN(ROUND(N(F162),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -10332,7 +10332,7 @@
         <v/>
       </c>
       <c r="Q163" s="40">
-        <f>IF(OR(G163="",O163="Aprovado",O163="Recusado",O163="Sem retorno"),0,IF(O163="Parado",2000,1000)+MIN(N(M163),500)+N(F163)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G163="",O163="Aprovado",O163="Recusado",O163="Sem retorno"),0,IF(O163="Parado",2,1)*1E+13+MIN(N(M163),500)*1E+10+MIN(ROUND(N(F163),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -10372,7 +10372,7 @@
         <v/>
       </c>
       <c r="Q164" s="40">
-        <f>IF(OR(G164="",O164="Aprovado",O164="Recusado",O164="Sem retorno"),0,IF(O164="Parado",2000,1000)+MIN(N(M164),500)+N(F164)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G164="",O164="Aprovado",O164="Recusado",O164="Sem retorno"),0,IF(O164="Parado",2,1)*1E+13+MIN(N(M164),500)*1E+10+MIN(ROUND(N(F164),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -10412,7 +10412,7 @@
         <v/>
       </c>
       <c r="Q165" s="40">
-        <f>IF(OR(G165="",O165="Aprovado",O165="Recusado",O165="Sem retorno"),0,IF(O165="Parado",2000,1000)+MIN(N(M165),500)+N(F165)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G165="",O165="Aprovado",O165="Recusado",O165="Sem retorno"),0,IF(O165="Parado",2,1)*1E+13+MIN(N(M165),500)*1E+10+MIN(ROUND(N(F165),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -10452,7 +10452,7 @@
         <v/>
       </c>
       <c r="Q166" s="40">
-        <f>IF(OR(G166="",O166="Aprovado",O166="Recusado",O166="Sem retorno"),0,IF(O166="Parado",2000,1000)+MIN(N(M166),500)+N(F166)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G166="",O166="Aprovado",O166="Recusado",O166="Sem retorno"),0,IF(O166="Parado",2,1)*1E+13+MIN(N(M166),500)*1E+10+MIN(ROUND(N(F166),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -10492,7 +10492,7 @@
         <v/>
       </c>
       <c r="Q167" s="40">
-        <f>IF(OR(G167="",O167="Aprovado",O167="Recusado",O167="Sem retorno"),0,IF(O167="Parado",2000,1000)+MIN(N(M167),500)+N(F167)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G167="",O167="Aprovado",O167="Recusado",O167="Sem retorno"),0,IF(O167="Parado",2,1)*1E+13+MIN(N(M167),500)*1E+10+MIN(ROUND(N(F167),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -10532,7 +10532,7 @@
         <v/>
       </c>
       <c r="Q168" s="40">
-        <f>IF(OR(G168="",O168="Aprovado",O168="Recusado",O168="Sem retorno"),0,IF(O168="Parado",2000,1000)+MIN(N(M168),500)+N(F168)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G168="",O168="Aprovado",O168="Recusado",O168="Sem retorno"),0,IF(O168="Parado",2,1)*1E+13+MIN(N(M168),500)*1E+10+MIN(ROUND(N(F168),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -10572,7 +10572,7 @@
         <v/>
       </c>
       <c r="Q169" s="40">
-        <f>IF(OR(G169="",O169="Aprovado",O169="Recusado",O169="Sem retorno"),0,IF(O169="Parado",2000,1000)+MIN(N(M169),500)+N(F169)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G169="",O169="Aprovado",O169="Recusado",O169="Sem retorno"),0,IF(O169="Parado",2,1)*1E+13+MIN(N(M169),500)*1E+10+MIN(ROUND(N(F169),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -10612,7 +10612,7 @@
         <v/>
       </c>
       <c r="Q170" s="40">
-        <f>IF(OR(G170="",O170="Aprovado",O170="Recusado",O170="Sem retorno"),0,IF(O170="Parado",2000,1000)+MIN(N(M170),500)+N(F170)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G170="",O170="Aprovado",O170="Recusado",O170="Sem retorno"),0,IF(O170="Parado",2,1)*1E+13+MIN(N(M170),500)*1E+10+MIN(ROUND(N(F170),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -10652,7 +10652,7 @@
         <v/>
       </c>
       <c r="Q171" s="40">
-        <f>IF(OR(G171="",O171="Aprovado",O171="Recusado",O171="Sem retorno"),0,IF(O171="Parado",2000,1000)+MIN(N(M171),500)+N(F171)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G171="",O171="Aprovado",O171="Recusado",O171="Sem retorno"),0,IF(O171="Parado",2,1)*1E+13+MIN(N(M171),500)*1E+10+MIN(ROUND(N(F171),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -10692,7 +10692,7 @@
         <v/>
       </c>
       <c r="Q172" s="40">
-        <f>IF(OR(G172="",O172="Aprovado",O172="Recusado",O172="Sem retorno"),0,IF(O172="Parado",2000,1000)+MIN(N(M172),500)+N(F172)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G172="",O172="Aprovado",O172="Recusado",O172="Sem retorno"),0,IF(O172="Parado",2,1)*1E+13+MIN(N(M172),500)*1E+10+MIN(ROUND(N(F172),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -10732,7 +10732,7 @@
         <v/>
       </c>
       <c r="Q173" s="40">
-        <f>IF(OR(G173="",O173="Aprovado",O173="Recusado",O173="Sem retorno"),0,IF(O173="Parado",2000,1000)+MIN(N(M173),500)+N(F173)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G173="",O173="Aprovado",O173="Recusado",O173="Sem retorno"),0,IF(O173="Parado",2,1)*1E+13+MIN(N(M173),500)*1E+10+MIN(ROUND(N(F173),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -10772,7 +10772,7 @@
         <v/>
       </c>
       <c r="Q174" s="40">
-        <f>IF(OR(G174="",O174="Aprovado",O174="Recusado",O174="Sem retorno"),0,IF(O174="Parado",2000,1000)+MIN(N(M174),500)+N(F174)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G174="",O174="Aprovado",O174="Recusado",O174="Sem retorno"),0,IF(O174="Parado",2,1)*1E+13+MIN(N(M174),500)*1E+10+MIN(ROUND(N(F174),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -10812,7 +10812,7 @@
         <v/>
       </c>
       <c r="Q175" s="40">
-        <f>IF(OR(G175="",O175="Aprovado",O175="Recusado",O175="Sem retorno"),0,IF(O175="Parado",2000,1000)+MIN(N(M175),500)+N(F175)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G175="",O175="Aprovado",O175="Recusado",O175="Sem retorno"),0,IF(O175="Parado",2,1)*1E+13+MIN(N(M175),500)*1E+10+MIN(ROUND(N(F175),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -10852,7 +10852,7 @@
         <v/>
       </c>
       <c r="Q176" s="40">
-        <f>IF(OR(G176="",O176="Aprovado",O176="Recusado",O176="Sem retorno"),0,IF(O176="Parado",2000,1000)+MIN(N(M176),500)+N(F176)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G176="",O176="Aprovado",O176="Recusado",O176="Sem retorno"),0,IF(O176="Parado",2,1)*1E+13+MIN(N(M176),500)*1E+10+MIN(ROUND(N(F176),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -10892,7 +10892,7 @@
         <v/>
       </c>
       <c r="Q177" s="40">
-        <f>IF(OR(G177="",O177="Aprovado",O177="Recusado",O177="Sem retorno"),0,IF(O177="Parado",2000,1000)+MIN(N(M177),500)+N(F177)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G177="",O177="Aprovado",O177="Recusado",O177="Sem retorno"),0,IF(O177="Parado",2,1)*1E+13+MIN(N(M177),500)*1E+10+MIN(ROUND(N(F177),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -10932,7 +10932,7 @@
         <v/>
       </c>
       <c r="Q178" s="40">
-        <f>IF(OR(G178="",O178="Aprovado",O178="Recusado",O178="Sem retorno"),0,IF(O178="Parado",2000,1000)+MIN(N(M178),500)+N(F178)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G178="",O178="Aprovado",O178="Recusado",O178="Sem retorno"),0,IF(O178="Parado",2,1)*1E+13+MIN(N(M178),500)*1E+10+MIN(ROUND(N(F178),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -10972,7 +10972,7 @@
         <v/>
       </c>
       <c r="Q179" s="40">
-        <f>IF(OR(G179="",O179="Aprovado",O179="Recusado",O179="Sem retorno"),0,IF(O179="Parado",2000,1000)+MIN(N(M179),500)+N(F179)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G179="",O179="Aprovado",O179="Recusado",O179="Sem retorno"),0,IF(O179="Parado",2,1)*1E+13+MIN(N(M179),500)*1E+10+MIN(ROUND(N(F179),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -11012,7 +11012,7 @@
         <v/>
       </c>
       <c r="Q180" s="40">
-        <f>IF(OR(G180="",O180="Aprovado",O180="Recusado",O180="Sem retorno"),0,IF(O180="Parado",2000,1000)+MIN(N(M180),500)+N(F180)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G180="",O180="Aprovado",O180="Recusado",O180="Sem retorno"),0,IF(O180="Parado",2,1)*1E+13+MIN(N(M180),500)*1E+10+MIN(ROUND(N(F180),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -11052,7 +11052,7 @@
         <v/>
       </c>
       <c r="Q181" s="40">
-        <f>IF(OR(G181="",O181="Aprovado",O181="Recusado",O181="Sem retorno"),0,IF(O181="Parado",2000,1000)+MIN(N(M181),500)+N(F181)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G181="",O181="Aprovado",O181="Recusado",O181="Sem retorno"),0,IF(O181="Parado",2,1)*1E+13+MIN(N(M181),500)*1E+10+MIN(ROUND(N(F181),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -11092,7 +11092,7 @@
         <v/>
       </c>
       <c r="Q182" s="40">
-        <f>IF(OR(G182="",O182="Aprovado",O182="Recusado",O182="Sem retorno"),0,IF(O182="Parado",2000,1000)+MIN(N(M182),500)+N(F182)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G182="",O182="Aprovado",O182="Recusado",O182="Sem retorno"),0,IF(O182="Parado",2,1)*1E+13+MIN(N(M182),500)*1E+10+MIN(ROUND(N(F182),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -11132,7 +11132,7 @@
         <v/>
       </c>
       <c r="Q183" s="40">
-        <f>IF(OR(G183="",O183="Aprovado",O183="Recusado",O183="Sem retorno"),0,IF(O183="Parado",2000,1000)+MIN(N(M183),500)+N(F183)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G183="",O183="Aprovado",O183="Recusado",O183="Sem retorno"),0,IF(O183="Parado",2,1)*1E+13+MIN(N(M183),500)*1E+10+MIN(ROUND(N(F183),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -11172,7 +11172,7 @@
         <v/>
       </c>
       <c r="Q184" s="40">
-        <f>IF(OR(G184="",O184="Aprovado",O184="Recusado",O184="Sem retorno"),0,IF(O184="Parado",2000,1000)+MIN(N(M184),500)+N(F184)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G184="",O184="Aprovado",O184="Recusado",O184="Sem retorno"),0,IF(O184="Parado",2,1)*1E+13+MIN(N(M184),500)*1E+10+MIN(ROUND(N(F184),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -11212,7 +11212,7 @@
         <v/>
       </c>
       <c r="Q185" s="40">
-        <f>IF(OR(G185="",O185="Aprovado",O185="Recusado",O185="Sem retorno"),0,IF(O185="Parado",2000,1000)+MIN(N(M185),500)+N(F185)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G185="",O185="Aprovado",O185="Recusado",O185="Sem retorno"),0,IF(O185="Parado",2,1)*1E+13+MIN(N(M185),500)*1E+10+MIN(ROUND(N(F185),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -11252,7 +11252,7 @@
         <v/>
       </c>
       <c r="Q186" s="40">
-        <f>IF(OR(G186="",O186="Aprovado",O186="Recusado",O186="Sem retorno"),0,IF(O186="Parado",2000,1000)+MIN(N(M186),500)+N(F186)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G186="",O186="Aprovado",O186="Recusado",O186="Sem retorno"),0,IF(O186="Parado",2,1)*1E+13+MIN(N(M186),500)*1E+10+MIN(ROUND(N(F186),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -11292,7 +11292,7 @@
         <v/>
       </c>
       <c r="Q187" s="40">
-        <f>IF(OR(G187="",O187="Aprovado",O187="Recusado",O187="Sem retorno"),0,IF(O187="Parado",2000,1000)+MIN(N(M187),500)+N(F187)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G187="",O187="Aprovado",O187="Recusado",O187="Sem retorno"),0,IF(O187="Parado",2,1)*1E+13+MIN(N(M187),500)*1E+10+MIN(ROUND(N(F187),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -11332,7 +11332,7 @@
         <v/>
       </c>
       <c r="Q188" s="40">
-        <f>IF(OR(G188="",O188="Aprovado",O188="Recusado",O188="Sem retorno"),0,IF(O188="Parado",2000,1000)+MIN(N(M188),500)+N(F188)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G188="",O188="Aprovado",O188="Recusado",O188="Sem retorno"),0,IF(O188="Parado",2,1)*1E+13+MIN(N(M188),500)*1E+10+MIN(ROUND(N(F188),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -11372,7 +11372,7 @@
         <v/>
       </c>
       <c r="Q189" s="40">
-        <f>IF(OR(G189="",O189="Aprovado",O189="Recusado",O189="Sem retorno"),0,IF(O189="Parado",2000,1000)+MIN(N(M189),500)+N(F189)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G189="",O189="Aprovado",O189="Recusado",O189="Sem retorno"),0,IF(O189="Parado",2,1)*1E+13+MIN(N(M189),500)*1E+10+MIN(ROUND(N(F189),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -11412,7 +11412,7 @@
         <v/>
       </c>
       <c r="Q190" s="40">
-        <f>IF(OR(G190="",O190="Aprovado",O190="Recusado",O190="Sem retorno"),0,IF(O190="Parado",2000,1000)+MIN(N(M190),500)+N(F190)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G190="",O190="Aprovado",O190="Recusado",O190="Sem retorno"),0,IF(O190="Parado",2,1)*1E+13+MIN(N(M190),500)*1E+10+MIN(ROUND(N(F190),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -11452,7 +11452,7 @@
         <v/>
       </c>
       <c r="Q191" s="40">
-        <f>IF(OR(G191="",O191="Aprovado",O191="Recusado",O191="Sem retorno"),0,IF(O191="Parado",2000,1000)+MIN(N(M191),500)+N(F191)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G191="",O191="Aprovado",O191="Recusado",O191="Sem retorno"),0,IF(O191="Parado",2,1)*1E+13+MIN(N(M191),500)*1E+10+MIN(ROUND(N(F191),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -11492,7 +11492,7 @@
         <v/>
       </c>
       <c r="Q192" s="40">
-        <f>IF(OR(G192="",O192="Aprovado",O192="Recusado",O192="Sem retorno"),0,IF(O192="Parado",2000,1000)+MIN(N(M192),500)+N(F192)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G192="",O192="Aprovado",O192="Recusado",O192="Sem retorno"),0,IF(O192="Parado",2,1)*1E+13+MIN(N(M192),500)*1E+10+MIN(ROUND(N(F192),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -11532,7 +11532,7 @@
         <v/>
       </c>
       <c r="Q193" s="40">
-        <f>IF(OR(G193="",O193="Aprovado",O193="Recusado",O193="Sem retorno"),0,IF(O193="Parado",2000,1000)+MIN(N(M193),500)+N(F193)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G193="",O193="Aprovado",O193="Recusado",O193="Sem retorno"),0,IF(O193="Parado",2,1)*1E+13+MIN(N(M193),500)*1E+10+MIN(ROUND(N(F193),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -11572,7 +11572,7 @@
         <v/>
       </c>
       <c r="Q194" s="40">
-        <f>IF(OR(G194="",O194="Aprovado",O194="Recusado",O194="Sem retorno"),0,IF(O194="Parado",2000,1000)+MIN(N(M194),500)+N(F194)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G194="",O194="Aprovado",O194="Recusado",O194="Sem retorno"),0,IF(O194="Parado",2,1)*1E+13+MIN(N(M194),500)*1E+10+MIN(ROUND(N(F194),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -11612,7 +11612,7 @@
         <v/>
       </c>
       <c r="Q195" s="40">
-        <f>IF(OR(G195="",O195="Aprovado",O195="Recusado",O195="Sem retorno"),0,IF(O195="Parado",2000,1000)+MIN(N(M195),500)+N(F195)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G195="",O195="Aprovado",O195="Recusado",O195="Sem retorno"),0,IF(O195="Parado",2,1)*1E+13+MIN(N(M195),500)*1E+10+MIN(ROUND(N(F195),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -11652,7 +11652,7 @@
         <v/>
       </c>
       <c r="Q196" s="40">
-        <f>IF(OR(G196="",O196="Aprovado",O196="Recusado",O196="Sem retorno"),0,IF(O196="Parado",2000,1000)+MIN(N(M196),500)+N(F196)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G196="",O196="Aprovado",O196="Recusado",O196="Sem retorno"),0,IF(O196="Parado",2,1)*1E+13+MIN(N(M196),500)*1E+10+MIN(ROUND(N(F196),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -11692,7 +11692,7 @@
         <v/>
       </c>
       <c r="Q197" s="40">
-        <f>IF(OR(G197="",O197="Aprovado",O197="Recusado",O197="Sem retorno"),0,IF(O197="Parado",2000,1000)+MIN(N(M197),500)+N(F197)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G197="",O197="Aprovado",O197="Recusado",O197="Sem retorno"),0,IF(O197="Parado",2,1)*1E+13+MIN(N(M197),500)*1E+10+MIN(ROUND(N(F197),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -11732,7 +11732,7 @@
         <v/>
       </c>
       <c r="Q198" s="40">
-        <f>IF(OR(G198="",O198="Aprovado",O198="Recusado",O198="Sem retorno"),0,IF(O198="Parado",2000,1000)+MIN(N(M198),500)+N(F198)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G198="",O198="Aprovado",O198="Recusado",O198="Sem retorno"),0,IF(O198="Parado",2,1)*1E+13+MIN(N(M198),500)*1E+10+MIN(ROUND(N(F198),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -11772,7 +11772,7 @@
         <v/>
       </c>
       <c r="Q199" s="40">
-        <f>IF(OR(G199="",O199="Aprovado",O199="Recusado",O199="Sem retorno"),0,IF(O199="Parado",2000,1000)+MIN(N(M199),500)+N(F199)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G199="",O199="Aprovado",O199="Recusado",O199="Sem retorno"),0,IF(O199="Parado",2,1)*1E+13+MIN(N(M199),500)*1E+10+MIN(ROUND(N(F199),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -11812,7 +11812,7 @@
         <v/>
       </c>
       <c r="Q200" s="40">
-        <f>IF(OR(G200="",O200="Aprovado",O200="Recusado",O200="Sem retorno"),0,IF(O200="Parado",2000,1000)+MIN(N(M200),500)+N(F200)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G200="",O200="Aprovado",O200="Recusado",O200="Sem retorno"),0,IF(O200="Parado",2,1)*1E+13+MIN(N(M200),500)*1E+10+MIN(ROUND(N(F200),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -11852,7 +11852,7 @@
         <v/>
       </c>
       <c r="Q201" s="40">
-        <f>IF(OR(G201="",O201="Aprovado",O201="Recusado",O201="Sem retorno"),0,IF(O201="Parado",2000,1000)+MIN(N(M201),500)+N(F201)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G201="",O201="Aprovado",O201="Recusado",O201="Sem retorno"),0,IF(O201="Parado",2,1)*1E+13+MIN(N(M201),500)*1E+10+MIN(ROUND(N(F201),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -11892,7 +11892,7 @@
         <v/>
       </c>
       <c r="Q202" s="40">
-        <f>IF(OR(G202="",O202="Aprovado",O202="Recusado",O202="Sem retorno"),0,IF(O202="Parado",2000,1000)+MIN(N(M202),500)+N(F202)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G202="",O202="Aprovado",O202="Recusado",O202="Sem retorno"),0,IF(O202="Parado",2,1)*1E+13+MIN(N(M202),500)*1E+10+MIN(ROUND(N(F202),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -11932,7 +11932,7 @@
         <v/>
       </c>
       <c r="Q203" s="40">
-        <f>IF(OR(G203="",O203="Aprovado",O203="Recusado",O203="Sem retorno"),0,IF(O203="Parado",2000,1000)+MIN(N(M203),500)+N(F203)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G203="",O203="Aprovado",O203="Recusado",O203="Sem retorno"),0,IF(O203="Parado",2,1)*1E+13+MIN(N(M203),500)*1E+10+MIN(ROUND(N(F203),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -11972,7 +11972,7 @@
         <v/>
       </c>
       <c r="Q204" s="40">
-        <f>IF(OR(G204="",O204="Aprovado",O204="Recusado",O204="Sem retorno"),0,IF(O204="Parado",2000,1000)+MIN(N(M204),500)+N(F204)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G204="",O204="Aprovado",O204="Recusado",O204="Sem retorno"),0,IF(O204="Parado",2,1)*1E+13+MIN(N(M204),500)*1E+10+MIN(ROUND(N(F204),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -12012,7 +12012,7 @@
         <v/>
       </c>
       <c r="Q205" s="40">
-        <f>IF(OR(G205="",O205="Aprovado",O205="Recusado",O205="Sem retorno"),0,IF(O205="Parado",2000,1000)+MIN(N(M205),500)+N(F205)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G205="",O205="Aprovado",O205="Recusado",O205="Sem retorno"),0,IF(O205="Parado",2,1)*1E+13+MIN(N(M205),500)*1E+10+MIN(ROUND(N(F205),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -12052,7 +12052,7 @@
         <v/>
       </c>
       <c r="Q206" s="40">
-        <f>IF(OR(G206="",O206="Aprovado",O206="Recusado",O206="Sem retorno"),0,IF(O206="Parado",2000,1000)+MIN(N(M206),500)+N(F206)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G206="",O206="Aprovado",O206="Recusado",O206="Sem retorno"),0,IF(O206="Parado",2,1)*1E+13+MIN(N(M206),500)*1E+10+MIN(ROUND(N(F206),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -12092,7 +12092,7 @@
         <v/>
       </c>
       <c r="Q207" s="40">
-        <f>IF(OR(G207="",O207="Aprovado",O207="Recusado",O207="Sem retorno"),0,IF(O207="Parado",2000,1000)+MIN(N(M207),500)+N(F207)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G207="",O207="Aprovado",O207="Recusado",O207="Sem retorno"),0,IF(O207="Parado",2,1)*1E+13+MIN(N(M207),500)*1E+10+MIN(ROUND(N(F207),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -12132,7 +12132,7 @@
         <v/>
       </c>
       <c r="Q208" s="40">
-        <f>IF(OR(G208="",O208="Aprovado",O208="Recusado",O208="Sem retorno"),0,IF(O208="Parado",2000,1000)+MIN(N(M208),500)+N(F208)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G208="",O208="Aprovado",O208="Recusado",O208="Sem retorno"),0,IF(O208="Parado",2,1)*1E+13+MIN(N(M208),500)*1E+10+MIN(ROUND(N(F208),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -12172,7 +12172,7 @@
         <v/>
       </c>
       <c r="Q209" s="40">
-        <f>IF(OR(G209="",O209="Aprovado",O209="Recusado",O209="Sem retorno"),0,IF(O209="Parado",2000,1000)+MIN(N(M209),500)+N(F209)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G209="",O209="Aprovado",O209="Recusado",O209="Sem retorno"),0,IF(O209="Parado",2,1)*1E+13+MIN(N(M209),500)*1E+10+MIN(ROUND(N(F209),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -12212,7 +12212,7 @@
         <v/>
       </c>
       <c r="Q210" s="40">
-        <f>IF(OR(G210="",O210="Aprovado",O210="Recusado",O210="Sem retorno"),0,IF(O210="Parado",2000,1000)+MIN(N(M210),500)+N(F210)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G210="",O210="Aprovado",O210="Recusado",O210="Sem retorno"),0,IF(O210="Parado",2,1)*1E+13+MIN(N(M210),500)*1E+10+MIN(ROUND(N(F210),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -12252,7 +12252,7 @@
         <v/>
       </c>
       <c r="Q211" s="40">
-        <f>IF(OR(G211="",O211="Aprovado",O211="Recusado",O211="Sem retorno"),0,IF(O211="Parado",2000,1000)+MIN(N(M211),500)+N(F211)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G211="",O211="Aprovado",O211="Recusado",O211="Sem retorno"),0,IF(O211="Parado",2,1)*1E+13+MIN(N(M211),500)*1E+10+MIN(ROUND(N(F211),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -12292,7 +12292,7 @@
         <v/>
       </c>
       <c r="Q212" s="40">
-        <f>IF(OR(G212="",O212="Aprovado",O212="Recusado",O212="Sem retorno"),0,IF(O212="Parado",2000,1000)+MIN(N(M212),500)+N(F212)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G212="",O212="Aprovado",O212="Recusado",O212="Sem retorno"),0,IF(O212="Parado",2,1)*1E+13+MIN(N(M212),500)*1E+10+MIN(ROUND(N(F212),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -12332,7 +12332,7 @@
         <v/>
       </c>
       <c r="Q213" s="40">
-        <f>IF(OR(G213="",O213="Aprovado",O213="Recusado",O213="Sem retorno"),0,IF(O213="Parado",2000,1000)+MIN(N(M213),500)+N(F213)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G213="",O213="Aprovado",O213="Recusado",O213="Sem retorno"),0,IF(O213="Parado",2,1)*1E+13+MIN(N(M213),500)*1E+10+MIN(ROUND(N(F213),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -12372,7 +12372,7 @@
         <v/>
       </c>
       <c r="Q214" s="40">
-        <f>IF(OR(G214="",O214="Aprovado",O214="Recusado",O214="Sem retorno"),0,IF(O214="Parado",2000,1000)+MIN(N(M214),500)+N(F214)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G214="",O214="Aprovado",O214="Recusado",O214="Sem retorno"),0,IF(O214="Parado",2,1)*1E+13+MIN(N(M214),500)*1E+10+MIN(ROUND(N(F214),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -12412,7 +12412,7 @@
         <v/>
       </c>
       <c r="Q215" s="40">
-        <f>IF(OR(G215="",O215="Aprovado",O215="Recusado",O215="Sem retorno"),0,IF(O215="Parado",2000,1000)+MIN(N(M215),500)+N(F215)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G215="",O215="Aprovado",O215="Recusado",O215="Sem retorno"),0,IF(O215="Parado",2,1)*1E+13+MIN(N(M215),500)*1E+10+MIN(ROUND(N(F215),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -12452,7 +12452,7 @@
         <v/>
       </c>
       <c r="Q216" s="40">
-        <f>IF(OR(G216="",O216="Aprovado",O216="Recusado",O216="Sem retorno"),0,IF(O216="Parado",2000,1000)+MIN(N(M216),500)+N(F216)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G216="",O216="Aprovado",O216="Recusado",O216="Sem retorno"),0,IF(O216="Parado",2,1)*1E+13+MIN(N(M216),500)*1E+10+MIN(ROUND(N(F216),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -12492,7 +12492,7 @@
         <v/>
       </c>
       <c r="Q217" s="40">
-        <f>IF(OR(G217="",O217="Aprovado",O217="Recusado",O217="Sem retorno"),0,IF(O217="Parado",2000,1000)+MIN(N(M217),500)+N(F217)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G217="",O217="Aprovado",O217="Recusado",O217="Sem retorno"),0,IF(O217="Parado",2,1)*1E+13+MIN(N(M217),500)*1E+10+MIN(ROUND(N(F217),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -12532,7 +12532,7 @@
         <v/>
       </c>
       <c r="Q218" s="40">
-        <f>IF(OR(G218="",O218="Aprovado",O218="Recusado",O218="Sem retorno"),0,IF(O218="Parado",2000,1000)+MIN(N(M218),500)+N(F218)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G218="",O218="Aprovado",O218="Recusado",O218="Sem retorno"),0,IF(O218="Parado",2,1)*1E+13+MIN(N(M218),500)*1E+10+MIN(ROUND(N(F218),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -12572,7 +12572,7 @@
         <v/>
       </c>
       <c r="Q219" s="40">
-        <f>IF(OR(G219="",O219="Aprovado",O219="Recusado",O219="Sem retorno"),0,IF(O219="Parado",2000,1000)+MIN(N(M219),500)+N(F219)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G219="",O219="Aprovado",O219="Recusado",O219="Sem retorno"),0,IF(O219="Parado",2,1)*1E+13+MIN(N(M219),500)*1E+10+MIN(ROUND(N(F219),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -12612,7 +12612,7 @@
         <v/>
       </c>
       <c r="Q220" s="40">
-        <f>IF(OR(G220="",O220="Aprovado",O220="Recusado",O220="Sem retorno"),0,IF(O220="Parado",2000,1000)+MIN(N(M220),500)+N(F220)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G220="",O220="Aprovado",O220="Recusado",O220="Sem retorno"),0,IF(O220="Parado",2,1)*1E+13+MIN(N(M220),500)*1E+10+MIN(ROUND(N(F220),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -12652,7 +12652,7 @@
         <v/>
       </c>
       <c r="Q221" s="40">
-        <f>IF(OR(G221="",O221="Aprovado",O221="Recusado",O221="Sem retorno"),0,IF(O221="Parado",2000,1000)+MIN(N(M221),500)+N(F221)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G221="",O221="Aprovado",O221="Recusado",O221="Sem retorno"),0,IF(O221="Parado",2,1)*1E+13+MIN(N(M221),500)*1E+10+MIN(ROUND(N(F221),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -12692,7 +12692,7 @@
         <v/>
       </c>
       <c r="Q222" s="40">
-        <f>IF(OR(G222="",O222="Aprovado",O222="Recusado",O222="Sem retorno"),0,IF(O222="Parado",2000,1000)+MIN(N(M222),500)+N(F222)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G222="",O222="Aprovado",O222="Recusado",O222="Sem retorno"),0,IF(O222="Parado",2,1)*1E+13+MIN(N(M222),500)*1E+10+MIN(ROUND(N(F222),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -12732,7 +12732,7 @@
         <v/>
       </c>
       <c r="Q223" s="40">
-        <f>IF(OR(G223="",O223="Aprovado",O223="Recusado",O223="Sem retorno"),0,IF(O223="Parado",2000,1000)+MIN(N(M223),500)+N(F223)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G223="",O223="Aprovado",O223="Recusado",O223="Sem retorno"),0,IF(O223="Parado",2,1)*1E+13+MIN(N(M223),500)*1E+10+MIN(ROUND(N(F223),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -12772,7 +12772,7 @@
         <v/>
       </c>
       <c r="Q224" s="40">
-        <f>IF(OR(G224="",O224="Aprovado",O224="Recusado",O224="Sem retorno"),0,IF(O224="Parado",2000,1000)+MIN(N(M224),500)+N(F224)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G224="",O224="Aprovado",O224="Recusado",O224="Sem retorno"),0,IF(O224="Parado",2,1)*1E+13+MIN(N(M224),500)*1E+10+MIN(ROUND(N(F224),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -12812,7 +12812,7 @@
         <v/>
       </c>
       <c r="Q225" s="40">
-        <f>IF(OR(G225="",O225="Aprovado",O225="Recusado",O225="Sem retorno"),0,IF(O225="Parado",2000,1000)+MIN(N(M225),500)+N(F225)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G225="",O225="Aprovado",O225="Recusado",O225="Sem retorno"),0,IF(O225="Parado",2,1)*1E+13+MIN(N(M225),500)*1E+10+MIN(ROUND(N(F225),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -12852,7 +12852,7 @@
         <v/>
       </c>
       <c r="Q226" s="40">
-        <f>IF(OR(G226="",O226="Aprovado",O226="Recusado",O226="Sem retorno"),0,IF(O226="Parado",2000,1000)+MIN(N(M226),500)+N(F226)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G226="",O226="Aprovado",O226="Recusado",O226="Sem retorno"),0,IF(O226="Parado",2,1)*1E+13+MIN(N(M226),500)*1E+10+MIN(ROUND(N(F226),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -12892,7 +12892,7 @@
         <v/>
       </c>
       <c r="Q227" s="40">
-        <f>IF(OR(G227="",O227="Aprovado",O227="Recusado",O227="Sem retorno"),0,IF(O227="Parado",2000,1000)+MIN(N(M227),500)+N(F227)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G227="",O227="Aprovado",O227="Recusado",O227="Sem retorno"),0,IF(O227="Parado",2,1)*1E+13+MIN(N(M227),500)*1E+10+MIN(ROUND(N(F227),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -12932,7 +12932,7 @@
         <v/>
       </c>
       <c r="Q228" s="40">
-        <f>IF(OR(G228="",O228="Aprovado",O228="Recusado",O228="Sem retorno"),0,IF(O228="Parado",2000,1000)+MIN(N(M228),500)+N(F228)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G228="",O228="Aprovado",O228="Recusado",O228="Sem retorno"),0,IF(O228="Parado",2,1)*1E+13+MIN(N(M228),500)*1E+10+MIN(ROUND(N(F228),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -12972,7 +12972,7 @@
         <v/>
       </c>
       <c r="Q229" s="40">
-        <f>IF(OR(G229="",O229="Aprovado",O229="Recusado",O229="Sem retorno"),0,IF(O229="Parado",2000,1000)+MIN(N(M229),500)+N(F229)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G229="",O229="Aprovado",O229="Recusado",O229="Sem retorno"),0,IF(O229="Parado",2,1)*1E+13+MIN(N(M229),500)*1E+10+MIN(ROUND(N(F229),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -13012,7 +13012,7 @@
         <v/>
       </c>
       <c r="Q230" s="40">
-        <f>IF(OR(G230="",O230="Aprovado",O230="Recusado",O230="Sem retorno"),0,IF(O230="Parado",2000,1000)+MIN(N(M230),500)+N(F230)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G230="",O230="Aprovado",O230="Recusado",O230="Sem retorno"),0,IF(O230="Parado",2,1)*1E+13+MIN(N(M230),500)*1E+10+MIN(ROUND(N(F230),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -13052,7 +13052,7 @@
         <v/>
       </c>
       <c r="Q231" s="40">
-        <f>IF(OR(G231="",O231="Aprovado",O231="Recusado",O231="Sem retorno"),0,IF(O231="Parado",2000,1000)+MIN(N(M231),500)+N(F231)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G231="",O231="Aprovado",O231="Recusado",O231="Sem retorno"),0,IF(O231="Parado",2,1)*1E+13+MIN(N(M231),500)*1E+10+MIN(ROUND(N(F231),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -13092,7 +13092,7 @@
         <v/>
       </c>
       <c r="Q232" s="40">
-        <f>IF(OR(G232="",O232="Aprovado",O232="Recusado",O232="Sem retorno"),0,IF(O232="Parado",2000,1000)+MIN(N(M232),500)+N(F232)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G232="",O232="Aprovado",O232="Recusado",O232="Sem retorno"),0,IF(O232="Parado",2,1)*1E+13+MIN(N(M232),500)*1E+10+MIN(ROUND(N(F232),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -13132,7 +13132,7 @@
         <v/>
       </c>
       <c r="Q233" s="40">
-        <f>IF(OR(G233="",O233="Aprovado",O233="Recusado",O233="Sem retorno"),0,IF(O233="Parado",2000,1000)+MIN(N(M233),500)+N(F233)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G233="",O233="Aprovado",O233="Recusado",O233="Sem retorno"),0,IF(O233="Parado",2,1)*1E+13+MIN(N(M233),500)*1E+10+MIN(ROUND(N(F233),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -13172,7 +13172,7 @@
         <v/>
       </c>
       <c r="Q234" s="40">
-        <f>IF(OR(G234="",O234="Aprovado",O234="Recusado",O234="Sem retorno"),0,IF(O234="Parado",2000,1000)+MIN(N(M234),500)+N(F234)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G234="",O234="Aprovado",O234="Recusado",O234="Sem retorno"),0,IF(O234="Parado",2,1)*1E+13+MIN(N(M234),500)*1E+10+MIN(ROUND(N(F234),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -13212,7 +13212,7 @@
         <v/>
       </c>
       <c r="Q235" s="40">
-        <f>IF(OR(G235="",O235="Aprovado",O235="Recusado",O235="Sem retorno"),0,IF(O235="Parado",2000,1000)+MIN(N(M235),500)+N(F235)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G235="",O235="Aprovado",O235="Recusado",O235="Sem retorno"),0,IF(O235="Parado",2,1)*1E+13+MIN(N(M235),500)*1E+10+MIN(ROUND(N(F235),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -13252,7 +13252,7 @@
         <v/>
       </c>
       <c r="Q236" s="40">
-        <f>IF(OR(G236="",O236="Aprovado",O236="Recusado",O236="Sem retorno"),0,IF(O236="Parado",2000,1000)+MIN(N(M236),500)+N(F236)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G236="",O236="Aprovado",O236="Recusado",O236="Sem retorno"),0,IF(O236="Parado",2,1)*1E+13+MIN(N(M236),500)*1E+10+MIN(ROUND(N(F236),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -13292,7 +13292,7 @@
         <v/>
       </c>
       <c r="Q237" s="40">
-        <f>IF(OR(G237="",O237="Aprovado",O237="Recusado",O237="Sem retorno"),0,IF(O237="Parado",2000,1000)+MIN(N(M237),500)+N(F237)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G237="",O237="Aprovado",O237="Recusado",O237="Sem retorno"),0,IF(O237="Parado",2,1)*1E+13+MIN(N(M237),500)*1E+10+MIN(ROUND(N(F237),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -13332,7 +13332,7 @@
         <v/>
       </c>
       <c r="Q238" s="40">
-        <f>IF(OR(G238="",O238="Aprovado",O238="Recusado",O238="Sem retorno"),0,IF(O238="Parado",2000,1000)+MIN(N(M238),500)+N(F238)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G238="",O238="Aprovado",O238="Recusado",O238="Sem retorno"),0,IF(O238="Parado",2,1)*1E+13+MIN(N(M238),500)*1E+10+MIN(ROUND(N(F238),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -13372,7 +13372,7 @@
         <v/>
       </c>
       <c r="Q239" s="40">
-        <f>IF(OR(G239="",O239="Aprovado",O239="Recusado",O239="Sem retorno"),0,IF(O239="Parado",2000,1000)+MIN(N(M239),500)+N(F239)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G239="",O239="Aprovado",O239="Recusado",O239="Sem retorno"),0,IF(O239="Parado",2,1)*1E+13+MIN(N(M239),500)*1E+10+MIN(ROUND(N(F239),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -13412,7 +13412,7 @@
         <v/>
       </c>
       <c r="Q240" s="40">
-        <f>IF(OR(G240="",O240="Aprovado",O240="Recusado",O240="Sem retorno"),0,IF(O240="Parado",2000,1000)+MIN(N(M240),500)+N(F240)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G240="",O240="Aprovado",O240="Recusado",O240="Sem retorno"),0,IF(O240="Parado",2,1)*1E+13+MIN(N(M240),500)*1E+10+MIN(ROUND(N(F240),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -13452,7 +13452,7 @@
         <v/>
       </c>
       <c r="Q241" s="40">
-        <f>IF(OR(G241="",O241="Aprovado",O241="Recusado",O241="Sem retorno"),0,IF(O241="Parado",2000,1000)+MIN(N(M241),500)+N(F241)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G241="",O241="Aprovado",O241="Recusado",O241="Sem retorno"),0,IF(O241="Parado",2,1)*1E+13+MIN(N(M241),500)*1E+10+MIN(ROUND(N(F241),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -13492,7 +13492,7 @@
         <v/>
       </c>
       <c r="Q242" s="40">
-        <f>IF(OR(G242="",O242="Aprovado",O242="Recusado",O242="Sem retorno"),0,IF(O242="Parado",2000,1000)+MIN(N(M242),500)+N(F242)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G242="",O242="Aprovado",O242="Recusado",O242="Sem retorno"),0,IF(O242="Parado",2,1)*1E+13+MIN(N(M242),500)*1E+10+MIN(ROUND(N(F242),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -13532,7 +13532,7 @@
         <v/>
       </c>
       <c r="Q243" s="40">
-        <f>IF(OR(G243="",O243="Aprovado",O243="Recusado",O243="Sem retorno"),0,IF(O243="Parado",2000,1000)+MIN(N(M243),500)+N(F243)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G243="",O243="Aprovado",O243="Recusado",O243="Sem retorno"),0,IF(O243="Parado",2,1)*1E+13+MIN(N(M243),500)*1E+10+MIN(ROUND(N(F243),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -13572,7 +13572,7 @@
         <v/>
       </c>
       <c r="Q244" s="40">
-        <f>IF(OR(G244="",O244="Aprovado",O244="Recusado",O244="Sem retorno"),0,IF(O244="Parado",2000,1000)+MIN(N(M244),500)+N(F244)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G244="",O244="Aprovado",O244="Recusado",O244="Sem retorno"),0,IF(O244="Parado",2,1)*1E+13+MIN(N(M244),500)*1E+10+MIN(ROUND(N(F244),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -13612,7 +13612,7 @@
         <v/>
       </c>
       <c r="Q245" s="40">
-        <f>IF(OR(G245="",O245="Aprovado",O245="Recusado",O245="Sem retorno"),0,IF(O245="Parado",2000,1000)+MIN(N(M245),500)+N(F245)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G245="",O245="Aprovado",O245="Recusado",O245="Sem retorno"),0,IF(O245="Parado",2,1)*1E+13+MIN(N(M245),500)*1E+10+MIN(ROUND(N(F245),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -13652,7 +13652,7 @@
         <v/>
       </c>
       <c r="Q246" s="40">
-        <f>IF(OR(G246="",O246="Aprovado",O246="Recusado",O246="Sem retorno"),0,IF(O246="Parado",2000,1000)+MIN(N(M246),500)+N(F246)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G246="",O246="Aprovado",O246="Recusado",O246="Sem retorno"),0,IF(O246="Parado",2,1)*1E+13+MIN(N(M246),500)*1E+10+MIN(ROUND(N(F246),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -13692,7 +13692,7 @@
         <v/>
       </c>
       <c r="Q247" s="40">
-        <f>IF(OR(G247="",O247="Aprovado",O247="Recusado",O247="Sem retorno"),0,IF(O247="Parado",2000,1000)+MIN(N(M247),500)+N(F247)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G247="",O247="Aprovado",O247="Recusado",O247="Sem retorno"),0,IF(O247="Parado",2,1)*1E+13+MIN(N(M247),500)*1E+10+MIN(ROUND(N(F247),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -13732,7 +13732,7 @@
         <v/>
       </c>
       <c r="Q248" s="40">
-        <f>IF(OR(G248="",O248="Aprovado",O248="Recusado",O248="Sem retorno"),0,IF(O248="Parado",2000,1000)+MIN(N(M248),500)+N(F248)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G248="",O248="Aprovado",O248="Recusado",O248="Sem retorno"),0,IF(O248="Parado",2,1)*1E+13+MIN(N(M248),500)*1E+10+MIN(ROUND(N(F248),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -13772,7 +13772,7 @@
         <v/>
       </c>
       <c r="Q249" s="40">
-        <f>IF(OR(G249="",O249="Aprovado",O249="Recusado",O249="Sem retorno"),0,IF(O249="Parado",2000,1000)+MIN(N(M249),500)+N(F249)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G249="",O249="Aprovado",O249="Recusado",O249="Sem retorno"),0,IF(O249="Parado",2,1)*1E+13+MIN(N(M249),500)*1E+10+MIN(ROUND(N(F249),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -13812,7 +13812,7 @@
         <v/>
       </c>
       <c r="Q250" s="40">
-        <f>IF(OR(G250="",O250="Aprovado",O250="Recusado",O250="Sem retorno"),0,IF(O250="Parado",2000,1000)+MIN(N(M250),500)+N(F250)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G250="",O250="Aprovado",O250="Recusado",O250="Sem retorno"),0,IF(O250="Parado",2,1)*1E+13+MIN(N(M250),500)*1E+10+MIN(ROUND(N(F250),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -13852,7 +13852,7 @@
         <v/>
       </c>
       <c r="Q251" s="40">
-        <f>IF(OR(G251="",O251="Aprovado",O251="Recusado",O251="Sem retorno"),0,IF(O251="Parado",2000,1000)+MIN(N(M251),500)+N(F251)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G251="",O251="Aprovado",O251="Recusado",O251="Sem retorno"),0,IF(O251="Parado",2,1)*1E+13+MIN(N(M251),500)*1E+10+MIN(ROUND(N(F251),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -13892,7 +13892,7 @@
         <v/>
       </c>
       <c r="Q252" s="40">
-        <f>IF(OR(G252="",O252="Aprovado",O252="Recusado",O252="Sem retorno"),0,IF(O252="Parado",2000,1000)+MIN(N(M252),500)+N(F252)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G252="",O252="Aprovado",O252="Recusado",O252="Sem retorno"),0,IF(O252="Parado",2,1)*1E+13+MIN(N(M252),500)*1E+10+MIN(ROUND(N(F252),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -13932,7 +13932,7 @@
         <v/>
       </c>
       <c r="Q253" s="40">
-        <f>IF(OR(G253="",O253="Aprovado",O253="Recusado",O253="Sem retorno"),0,IF(O253="Parado",2000,1000)+MIN(N(M253),500)+N(F253)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G253="",O253="Aprovado",O253="Recusado",O253="Sem retorno"),0,IF(O253="Parado",2,1)*1E+13+MIN(N(M253),500)*1E+10+MIN(ROUND(N(F253),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -13972,7 +13972,7 @@
         <v/>
       </c>
       <c r="Q254" s="40">
-        <f>IF(OR(G254="",O254="Aprovado",O254="Recusado",O254="Sem retorno"),0,IF(O254="Parado",2000,1000)+MIN(N(M254),500)+N(F254)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G254="",O254="Aprovado",O254="Recusado",O254="Sem retorno"),0,IF(O254="Parado",2,1)*1E+13+MIN(N(M254),500)*1E+10+MIN(ROUND(N(F254),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -14012,7 +14012,7 @@
         <v/>
       </c>
       <c r="Q255" s="40">
-        <f>IF(OR(G255="",O255="Aprovado",O255="Recusado",O255="Sem retorno"),0,IF(O255="Parado",2000,1000)+MIN(N(M255),500)+N(F255)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G255="",O255="Aprovado",O255="Recusado",O255="Sem retorno"),0,IF(O255="Parado",2,1)*1E+13+MIN(N(M255),500)*1E+10+MIN(ROUND(N(F255),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -14052,7 +14052,7 @@
         <v/>
       </c>
       <c r="Q256" s="40">
-        <f>IF(OR(G256="",O256="Aprovado",O256="Recusado",O256="Sem retorno"),0,IF(O256="Parado",2000,1000)+MIN(N(M256),500)+N(F256)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G256="",O256="Aprovado",O256="Recusado",O256="Sem retorno"),0,IF(O256="Parado",2,1)*1E+13+MIN(N(M256),500)*1E+10+MIN(ROUND(N(F256),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -14092,7 +14092,7 @@
         <v/>
       </c>
       <c r="Q257" s="40">
-        <f>IF(OR(G257="",O257="Aprovado",O257="Recusado",O257="Sem retorno"),0,IF(O257="Parado",2000,1000)+MIN(N(M257),500)+N(F257)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G257="",O257="Aprovado",O257="Recusado",O257="Sem retorno"),0,IF(O257="Parado",2,1)*1E+13+MIN(N(M257),500)*1E+10+MIN(ROUND(N(F257),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -14132,7 +14132,7 @@
         <v/>
       </c>
       <c r="Q258" s="40">
-        <f>IF(OR(G258="",O258="Aprovado",O258="Recusado",O258="Sem retorno"),0,IF(O258="Parado",2000,1000)+MIN(N(M258),500)+N(F258)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G258="",O258="Aprovado",O258="Recusado",O258="Sem retorno"),0,IF(O258="Parado",2,1)*1E+13+MIN(N(M258),500)*1E+10+MIN(ROUND(N(F258),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -14172,7 +14172,7 @@
         <v/>
       </c>
       <c r="Q259" s="40">
-        <f>IF(OR(G259="",O259="Aprovado",O259="Recusado",O259="Sem retorno"),0,IF(O259="Parado",2000,1000)+MIN(N(M259),500)+N(F259)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G259="",O259="Aprovado",O259="Recusado",O259="Sem retorno"),0,IF(O259="Parado",2,1)*1E+13+MIN(N(M259),500)*1E+10+MIN(ROUND(N(F259),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -14212,7 +14212,7 @@
         <v/>
       </c>
       <c r="Q260" s="40">
-        <f>IF(OR(G260="",O260="Aprovado",O260="Recusado",O260="Sem retorno"),0,IF(O260="Parado",2000,1000)+MIN(N(M260),500)+N(F260)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G260="",O260="Aprovado",O260="Recusado",O260="Sem retorno"),0,IF(O260="Parado",2,1)*1E+13+MIN(N(M260),500)*1E+10+MIN(ROUND(N(F260),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -14252,7 +14252,7 @@
         <v/>
       </c>
       <c r="Q261" s="40">
-        <f>IF(OR(G261="",O261="Aprovado",O261="Recusado",O261="Sem retorno"),0,IF(O261="Parado",2000,1000)+MIN(N(M261),500)+N(F261)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G261="",O261="Aprovado",O261="Recusado",O261="Sem retorno"),0,IF(O261="Parado",2,1)*1E+13+MIN(N(M261),500)*1E+10+MIN(ROUND(N(F261),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -14292,7 +14292,7 @@
         <v/>
       </c>
       <c r="Q262" s="40">
-        <f>IF(OR(G262="",O262="Aprovado",O262="Recusado",O262="Sem retorno"),0,IF(O262="Parado",2000,1000)+MIN(N(M262),500)+N(F262)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G262="",O262="Aprovado",O262="Recusado",O262="Sem retorno"),0,IF(O262="Parado",2,1)*1E+13+MIN(N(M262),500)*1E+10+MIN(ROUND(N(F262),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -14332,7 +14332,7 @@
         <v/>
       </c>
       <c r="Q263" s="40">
-        <f>IF(OR(G263="",O263="Aprovado",O263="Recusado",O263="Sem retorno"),0,IF(O263="Parado",2000,1000)+MIN(N(M263),500)+N(F263)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G263="",O263="Aprovado",O263="Recusado",O263="Sem retorno"),0,IF(O263="Parado",2,1)*1E+13+MIN(N(M263),500)*1E+10+MIN(ROUND(N(F263),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -14372,7 +14372,7 @@
         <v/>
       </c>
       <c r="Q264" s="40">
-        <f>IF(OR(G264="",O264="Aprovado",O264="Recusado",O264="Sem retorno"),0,IF(O264="Parado",2000,1000)+MIN(N(M264),500)+N(F264)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G264="",O264="Aprovado",O264="Recusado",O264="Sem retorno"),0,IF(O264="Parado",2,1)*1E+13+MIN(N(M264),500)*1E+10+MIN(ROUND(N(F264),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -14412,7 +14412,7 @@
         <v/>
       </c>
       <c r="Q265" s="40">
-        <f>IF(OR(G265="",O265="Aprovado",O265="Recusado",O265="Sem retorno"),0,IF(O265="Parado",2000,1000)+MIN(N(M265),500)+N(F265)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G265="",O265="Aprovado",O265="Recusado",O265="Sem retorno"),0,IF(O265="Parado",2,1)*1E+13+MIN(N(M265),500)*1E+10+MIN(ROUND(N(F265),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -14452,7 +14452,7 @@
         <v/>
       </c>
       <c r="Q266" s="40">
-        <f>IF(OR(G266="",O266="Aprovado",O266="Recusado",O266="Sem retorno"),0,IF(O266="Parado",2000,1000)+MIN(N(M266),500)+N(F266)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G266="",O266="Aprovado",O266="Recusado",O266="Sem retorno"),0,IF(O266="Parado",2,1)*1E+13+MIN(N(M266),500)*1E+10+MIN(ROUND(N(F266),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -14492,7 +14492,7 @@
         <v/>
       </c>
       <c r="Q267" s="40">
-        <f>IF(OR(G267="",O267="Aprovado",O267="Recusado",O267="Sem retorno"),0,IF(O267="Parado",2000,1000)+MIN(N(M267),500)+N(F267)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G267="",O267="Aprovado",O267="Recusado",O267="Sem retorno"),0,IF(O267="Parado",2,1)*1E+13+MIN(N(M267),500)*1E+10+MIN(ROUND(N(F267),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -14532,7 +14532,7 @@
         <v/>
       </c>
       <c r="Q268" s="40">
-        <f>IF(OR(G268="",O268="Aprovado",O268="Recusado",O268="Sem retorno"),0,IF(O268="Parado",2000,1000)+MIN(N(M268),500)+N(F268)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G268="",O268="Aprovado",O268="Recusado",O268="Sem retorno"),0,IF(O268="Parado",2,1)*1E+13+MIN(N(M268),500)*1E+10+MIN(ROUND(N(F268),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -14572,7 +14572,7 @@
         <v/>
       </c>
       <c r="Q269" s="40">
-        <f>IF(OR(G269="",O269="Aprovado",O269="Recusado",O269="Sem retorno"),0,IF(O269="Parado",2000,1000)+MIN(N(M269),500)+N(F269)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G269="",O269="Aprovado",O269="Recusado",O269="Sem retorno"),0,IF(O269="Parado",2,1)*1E+13+MIN(N(M269),500)*1E+10+MIN(ROUND(N(F269),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -14612,7 +14612,7 @@
         <v/>
       </c>
       <c r="Q270" s="40">
-        <f>IF(OR(G270="",O270="Aprovado",O270="Recusado",O270="Sem retorno"),0,IF(O270="Parado",2000,1000)+MIN(N(M270),500)+N(F270)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G270="",O270="Aprovado",O270="Recusado",O270="Sem retorno"),0,IF(O270="Parado",2,1)*1E+13+MIN(N(M270),500)*1E+10+MIN(ROUND(N(F270),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -14652,7 +14652,7 @@
         <v/>
       </c>
       <c r="Q271" s="40">
-        <f>IF(OR(G271="",O271="Aprovado",O271="Recusado",O271="Sem retorno"),0,IF(O271="Parado",2000,1000)+MIN(N(M271),500)+N(F271)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G271="",O271="Aprovado",O271="Recusado",O271="Sem retorno"),0,IF(O271="Parado",2,1)*1E+13+MIN(N(M271),500)*1E+10+MIN(ROUND(N(F271),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -14692,7 +14692,7 @@
         <v/>
       </c>
       <c r="Q272" s="40">
-        <f>IF(OR(G272="",O272="Aprovado",O272="Recusado",O272="Sem retorno"),0,IF(O272="Parado",2000,1000)+MIN(N(M272),500)+N(F272)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G272="",O272="Aprovado",O272="Recusado",O272="Sem retorno"),0,IF(O272="Parado",2,1)*1E+13+MIN(N(M272),500)*1E+10+MIN(ROUND(N(F272),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -14732,7 +14732,7 @@
         <v/>
       </c>
       <c r="Q273" s="40">
-        <f>IF(OR(G273="",O273="Aprovado",O273="Recusado",O273="Sem retorno"),0,IF(O273="Parado",2000,1000)+MIN(N(M273),500)+N(F273)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G273="",O273="Aprovado",O273="Recusado",O273="Sem retorno"),0,IF(O273="Parado",2,1)*1E+13+MIN(N(M273),500)*1E+10+MIN(ROUND(N(F273),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -14772,7 +14772,7 @@
         <v/>
       </c>
       <c r="Q274" s="40">
-        <f>IF(OR(G274="",O274="Aprovado",O274="Recusado",O274="Sem retorno"),0,IF(O274="Parado",2000,1000)+MIN(N(M274),500)+N(F274)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G274="",O274="Aprovado",O274="Recusado",O274="Sem retorno"),0,IF(O274="Parado",2,1)*1E+13+MIN(N(M274),500)*1E+10+MIN(ROUND(N(F274),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -14812,7 +14812,7 @@
         <v/>
       </c>
       <c r="Q275" s="40">
-        <f>IF(OR(G275="",O275="Aprovado",O275="Recusado",O275="Sem retorno"),0,IF(O275="Parado",2000,1000)+MIN(N(M275),500)+N(F275)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G275="",O275="Aprovado",O275="Recusado",O275="Sem retorno"),0,IF(O275="Parado",2,1)*1E+13+MIN(N(M275),500)*1E+10+MIN(ROUND(N(F275),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -14852,7 +14852,7 @@
         <v/>
       </c>
       <c r="Q276" s="40">
-        <f>IF(OR(G276="",O276="Aprovado",O276="Recusado",O276="Sem retorno"),0,IF(O276="Parado",2000,1000)+MIN(N(M276),500)+N(F276)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G276="",O276="Aprovado",O276="Recusado",O276="Sem retorno"),0,IF(O276="Parado",2,1)*1E+13+MIN(N(M276),500)*1E+10+MIN(ROUND(N(F276),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -14892,7 +14892,7 @@
         <v/>
       </c>
       <c r="Q277" s="40">
-        <f>IF(OR(G277="",O277="Aprovado",O277="Recusado",O277="Sem retorno"),0,IF(O277="Parado",2000,1000)+MIN(N(M277),500)+N(F277)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G277="",O277="Aprovado",O277="Recusado",O277="Sem retorno"),0,IF(O277="Parado",2,1)*1E+13+MIN(N(M277),500)*1E+10+MIN(ROUND(N(F277),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -14932,7 +14932,7 @@
         <v/>
       </c>
       <c r="Q278" s="40">
-        <f>IF(OR(G278="",O278="Aprovado",O278="Recusado",O278="Sem retorno"),0,IF(O278="Parado",2000,1000)+MIN(N(M278),500)+N(F278)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G278="",O278="Aprovado",O278="Recusado",O278="Sem retorno"),0,IF(O278="Parado",2,1)*1E+13+MIN(N(M278),500)*1E+10+MIN(ROUND(N(F278),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -14972,7 +14972,7 @@
         <v/>
       </c>
       <c r="Q279" s="40">
-        <f>IF(OR(G279="",O279="Aprovado",O279="Recusado",O279="Sem retorno"),0,IF(O279="Parado",2000,1000)+MIN(N(M279),500)+N(F279)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G279="",O279="Aprovado",O279="Recusado",O279="Sem retorno"),0,IF(O279="Parado",2,1)*1E+13+MIN(N(M279),500)*1E+10+MIN(ROUND(N(F279),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -15012,7 +15012,7 @@
         <v/>
       </c>
       <c r="Q280" s="40">
-        <f>IF(OR(G280="",O280="Aprovado",O280="Recusado",O280="Sem retorno"),0,IF(O280="Parado",2000,1000)+MIN(N(M280),500)+N(F280)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G280="",O280="Aprovado",O280="Recusado",O280="Sem retorno"),0,IF(O280="Parado",2,1)*1E+13+MIN(N(M280),500)*1E+10+MIN(ROUND(N(F280),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -15052,7 +15052,7 @@
         <v/>
       </c>
       <c r="Q281" s="40">
-        <f>IF(OR(G281="",O281="Aprovado",O281="Recusado",O281="Sem retorno"),0,IF(O281="Parado",2000,1000)+MIN(N(M281),500)+N(F281)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G281="",O281="Aprovado",O281="Recusado",O281="Sem retorno"),0,IF(O281="Parado",2,1)*1E+13+MIN(N(M281),500)*1E+10+MIN(ROUND(N(F281),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -15092,7 +15092,7 @@
         <v/>
       </c>
       <c r="Q282" s="40">
-        <f>IF(OR(G282="",O282="Aprovado",O282="Recusado",O282="Sem retorno"),0,IF(O282="Parado",2000,1000)+MIN(N(M282),500)+N(F282)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G282="",O282="Aprovado",O282="Recusado",O282="Sem retorno"),0,IF(O282="Parado",2,1)*1E+13+MIN(N(M282),500)*1E+10+MIN(ROUND(N(F282),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -15132,7 +15132,7 @@
         <v/>
       </c>
       <c r="Q283" s="40">
-        <f>IF(OR(G283="",O283="Aprovado",O283="Recusado",O283="Sem retorno"),0,IF(O283="Parado",2000,1000)+MIN(N(M283),500)+N(F283)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G283="",O283="Aprovado",O283="Recusado",O283="Sem retorno"),0,IF(O283="Parado",2,1)*1E+13+MIN(N(M283),500)*1E+10+MIN(ROUND(N(F283),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -15172,7 +15172,7 @@
         <v/>
       </c>
       <c r="Q284" s="40">
-        <f>IF(OR(G284="",O284="Aprovado",O284="Recusado",O284="Sem retorno"),0,IF(O284="Parado",2000,1000)+MIN(N(M284),500)+N(F284)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G284="",O284="Aprovado",O284="Recusado",O284="Sem retorno"),0,IF(O284="Parado",2,1)*1E+13+MIN(N(M284),500)*1E+10+MIN(ROUND(N(F284),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -15212,7 +15212,7 @@
         <v/>
       </c>
       <c r="Q285" s="40">
-        <f>IF(OR(G285="",O285="Aprovado",O285="Recusado",O285="Sem retorno"),0,IF(O285="Parado",2000,1000)+MIN(N(M285),500)+N(F285)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G285="",O285="Aprovado",O285="Recusado",O285="Sem retorno"),0,IF(O285="Parado",2,1)*1E+13+MIN(N(M285),500)*1E+10+MIN(ROUND(N(F285),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -15252,7 +15252,7 @@
         <v/>
       </c>
       <c r="Q286" s="40">
-        <f>IF(OR(G286="",O286="Aprovado",O286="Recusado",O286="Sem retorno"),0,IF(O286="Parado",2000,1000)+MIN(N(M286),500)+N(F286)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G286="",O286="Aprovado",O286="Recusado",O286="Sem retorno"),0,IF(O286="Parado",2,1)*1E+13+MIN(N(M286),500)*1E+10+MIN(ROUND(N(F286),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -15292,7 +15292,7 @@
         <v/>
       </c>
       <c r="Q287" s="40">
-        <f>IF(OR(G287="",O287="Aprovado",O287="Recusado",O287="Sem retorno"),0,IF(O287="Parado",2000,1000)+MIN(N(M287),500)+N(F287)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G287="",O287="Aprovado",O287="Recusado",O287="Sem retorno"),0,IF(O287="Parado",2,1)*1E+13+MIN(N(M287),500)*1E+10+MIN(ROUND(N(F287),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -15332,7 +15332,7 @@
         <v/>
       </c>
       <c r="Q288" s="40">
-        <f>IF(OR(G288="",O288="Aprovado",O288="Recusado",O288="Sem retorno"),0,IF(O288="Parado",2000,1000)+MIN(N(M288),500)+N(F288)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G288="",O288="Aprovado",O288="Recusado",O288="Sem retorno"),0,IF(O288="Parado",2,1)*1E+13+MIN(N(M288),500)*1E+10+MIN(ROUND(N(F288),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -15372,7 +15372,7 @@
         <v/>
       </c>
       <c r="Q289" s="40">
-        <f>IF(OR(G289="",O289="Aprovado",O289="Recusado",O289="Sem retorno"),0,IF(O289="Parado",2000,1000)+MIN(N(M289),500)+N(F289)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G289="",O289="Aprovado",O289="Recusado",O289="Sem retorno"),0,IF(O289="Parado",2,1)*1E+13+MIN(N(M289),500)*1E+10+MIN(ROUND(N(F289),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -15412,7 +15412,7 @@
         <v/>
       </c>
       <c r="Q290" s="40">
-        <f>IF(OR(G290="",O290="Aprovado",O290="Recusado",O290="Sem retorno"),0,IF(O290="Parado",2000,1000)+MIN(N(M290),500)+N(F290)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G290="",O290="Aprovado",O290="Recusado",O290="Sem retorno"),0,IF(O290="Parado",2,1)*1E+13+MIN(N(M290),500)*1E+10+MIN(ROUND(N(F290),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -15452,7 +15452,7 @@
         <v/>
       </c>
       <c r="Q291" s="40">
-        <f>IF(OR(G291="",O291="Aprovado",O291="Recusado",O291="Sem retorno"),0,IF(O291="Parado",2000,1000)+MIN(N(M291),500)+N(F291)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G291="",O291="Aprovado",O291="Recusado",O291="Sem retorno"),0,IF(O291="Parado",2,1)*1E+13+MIN(N(M291),500)*1E+10+MIN(ROUND(N(F291),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -15492,7 +15492,7 @@
         <v/>
       </c>
       <c r="Q292" s="40">
-        <f>IF(OR(G292="",O292="Aprovado",O292="Recusado",O292="Sem retorno"),0,IF(O292="Parado",2000,1000)+MIN(N(M292),500)+N(F292)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G292="",O292="Aprovado",O292="Recusado",O292="Sem retorno"),0,IF(O292="Parado",2,1)*1E+13+MIN(N(M292),500)*1E+10+MIN(ROUND(N(F292),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -15532,7 +15532,7 @@
         <v/>
       </c>
       <c r="Q293" s="40">
-        <f>IF(OR(G293="",O293="Aprovado",O293="Recusado",O293="Sem retorno"),0,IF(O293="Parado",2000,1000)+MIN(N(M293),500)+N(F293)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G293="",O293="Aprovado",O293="Recusado",O293="Sem retorno"),0,IF(O293="Parado",2,1)*1E+13+MIN(N(M293),500)*1E+10+MIN(ROUND(N(F293),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -15572,7 +15572,7 @@
         <v/>
       </c>
       <c r="Q294" s="40">
-        <f>IF(OR(G294="",O294="Aprovado",O294="Recusado",O294="Sem retorno"),0,IF(O294="Parado",2000,1000)+MIN(N(M294),500)+N(F294)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G294="",O294="Aprovado",O294="Recusado",O294="Sem retorno"),0,IF(O294="Parado",2,1)*1E+13+MIN(N(M294),500)*1E+10+MIN(ROUND(N(F294),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -15612,7 +15612,7 @@
         <v/>
       </c>
       <c r="Q295" s="40">
-        <f>IF(OR(G295="",O295="Aprovado",O295="Recusado",O295="Sem retorno"),0,IF(O295="Parado",2000,1000)+MIN(N(M295),500)+N(F295)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G295="",O295="Aprovado",O295="Recusado",O295="Sem retorno"),0,IF(O295="Parado",2,1)*1E+13+MIN(N(M295),500)*1E+10+MIN(ROUND(N(F295),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -15652,7 +15652,7 @@
         <v/>
       </c>
       <c r="Q296" s="40">
-        <f>IF(OR(G296="",O296="Aprovado",O296="Recusado",O296="Sem retorno"),0,IF(O296="Parado",2000,1000)+MIN(N(M296),500)+N(F296)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G296="",O296="Aprovado",O296="Recusado",O296="Sem retorno"),0,IF(O296="Parado",2,1)*1E+13+MIN(N(M296),500)*1E+10+MIN(ROUND(N(F296),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -15692,7 +15692,7 @@
         <v/>
       </c>
       <c r="Q297" s="40">
-        <f>IF(OR(G297="",O297="Aprovado",O297="Recusado",O297="Sem retorno"),0,IF(O297="Parado",2000,1000)+MIN(N(M297),500)+N(F297)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G297="",O297="Aprovado",O297="Recusado",O297="Sem retorno"),0,IF(O297="Parado",2,1)*1E+13+MIN(N(M297),500)*1E+10+MIN(ROUND(N(F297),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -15732,7 +15732,7 @@
         <v/>
       </c>
       <c r="Q298" s="40">
-        <f>IF(OR(G298="",O298="Aprovado",O298="Recusado",O298="Sem retorno"),0,IF(O298="Parado",2000,1000)+MIN(N(M298),500)+N(F298)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G298="",O298="Aprovado",O298="Recusado",O298="Sem retorno"),0,IF(O298="Parado",2,1)*1E+13+MIN(N(M298),500)*1E+10+MIN(ROUND(N(F298),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -15772,7 +15772,7 @@
         <v/>
       </c>
       <c r="Q299" s="40">
-        <f>IF(OR(G299="",O299="Aprovado",O299="Recusado",O299="Sem retorno"),0,IF(O299="Parado",2000,1000)+MIN(N(M299),500)+N(F299)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G299="",O299="Aprovado",O299="Recusado",O299="Sem retorno"),0,IF(O299="Parado",2,1)*1E+13+MIN(N(M299),500)*1E+10+MIN(ROUND(N(F299),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -15812,7 +15812,7 @@
         <v/>
       </c>
       <c r="Q300" s="40">
-        <f>IF(OR(G300="",O300="Aprovado",O300="Recusado",O300="Sem retorno"),0,IF(O300="Parado",2000,1000)+MIN(N(M300),500)+N(F300)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G300="",O300="Aprovado",O300="Recusado",O300="Sem retorno"),0,IF(O300="Parado",2,1)*1E+13+MIN(N(M300),500)*1E+10+MIN(ROUND(N(F300),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -15852,7 +15852,7 @@
         <v/>
       </c>
       <c r="Q301" s="40">
-        <f>IF(OR(G301="",O301="Aprovado",O301="Recusado",O301="Sem retorno"),0,IF(O301="Parado",2000,1000)+MIN(N(M301),500)+N(F301)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G301="",O301="Aprovado",O301="Recusado",O301="Sem retorno"),0,IF(O301="Parado",2,1)*1E+13+MIN(N(M301),500)*1E+10+MIN(ROUND(N(F301),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -15892,7 +15892,7 @@
         <v/>
       </c>
       <c r="Q302" s="40">
-        <f>IF(OR(G302="",O302="Aprovado",O302="Recusado",O302="Sem retorno"),0,IF(O302="Parado",2000,1000)+MIN(N(M302),500)+N(F302)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G302="",O302="Aprovado",O302="Recusado",O302="Sem retorno"),0,IF(O302="Parado",2,1)*1E+13+MIN(N(M302),500)*1E+10+MIN(ROUND(N(F302),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -15932,7 +15932,7 @@
         <v/>
       </c>
       <c r="Q303" s="40">
-        <f>IF(OR(G303="",O303="Aprovado",O303="Recusado",O303="Sem retorno"),0,IF(O303="Parado",2000,1000)+MIN(N(M303),500)+N(F303)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G303="",O303="Aprovado",O303="Recusado",O303="Sem retorno"),0,IF(O303="Parado",2,1)*1E+13+MIN(N(M303),500)*1E+10+MIN(ROUND(N(F303),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -15972,7 +15972,7 @@
         <v/>
       </c>
       <c r="Q304" s="40">
-        <f>IF(OR(G304="",O304="Aprovado",O304="Recusado",O304="Sem retorno"),0,IF(O304="Parado",2000,1000)+MIN(N(M304),500)+N(F304)/1000000-ROW()/100000)</f>
+        <f>IF(OR(G304="",O304="Aprovado",O304="Recusado",O304="Sem retorno"),0,IF(O304="Parado",2,1)*1E+13+MIN(N(M304),500)*1E+10+MIN(ROUND(N(F304),0),999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>

--- a/projetos/gestao-ia-planilhas/produto/kit-medicos/15-orcamentos.xlsx
+++ b/projetos/gestao-ia-planilhas/produto/kit-medicos/15-orcamentos.xlsx
@@ -2998,7 +2998,7 @@
         <v>46174.0</v>
       </c>
       <c r="Q5" s="40">
-        <f>IF(OR(G5="",O5="Aprovado",O5="Recusado",O5="Sem retorno"),0,IF(O5="Parado",2,1)*1E+13+MIN(N(M5),500)*1E+10+MIN(ROUND(N(F5),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G5="",O5="Aprovado",O5="Recusado",O5="Sem retorno"),0,IF(O5="Parado",2,1)*1E+15+MIN(N(M5),500)*1E+12+MIN(ROUND(N(F5)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
         <v>46174.0</v>
       </c>
       <c r="Q6" s="40">
-        <f>IF(OR(G6="",O6="Aprovado",O6="Recusado",O6="Sem retorno"),0,IF(O6="Parado",2,1)*1E+13+MIN(N(M6),500)*1E+10+MIN(ROUND(N(F6),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G6="",O6="Aprovado",O6="Recusado",O6="Sem retorno"),0,IF(O6="Parado",2,1)*1E+15+MIN(N(M6),500)*1E+12+MIN(ROUND(N(F6)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
         <v>46204.0</v>
       </c>
       <c r="Q7" s="40">
-        <f>IF(OR(G7="",O7="Aprovado",O7="Recusado",O7="Sem retorno"),0,IF(O7="Parado",2,1)*1E+13+MIN(N(M7),500)*1E+10+MIN(ROUND(N(F7),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G7="",O7="Aprovado",O7="Recusado",O7="Sem retorno"),0,IF(O7="Parado",2,1)*1E+15+MIN(N(M7),500)*1E+12+MIN(ROUND(N(F7)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
         <v>46204.0</v>
       </c>
       <c r="Q8" s="40">
-        <f>IF(OR(G8="",O8="Aprovado",O8="Recusado",O8="Sem retorno"),0,IF(O8="Parado",2,1)*1E+13+MIN(N(M8),500)*1E+10+MIN(ROUND(N(F8),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G8="",O8="Aprovado",O8="Recusado",O8="Sem retorno"),0,IF(O8="Parado",2,1)*1E+15+MIN(N(M8),500)*1E+12+MIN(ROUND(N(F8)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
         <v>46204.0</v>
       </c>
       <c r="Q9" s="40">
-        <f>IF(OR(G9="",O9="Aprovado",O9="Recusado",O9="Sem retorno"),0,IF(O9="Parado",2,1)*1E+13+MIN(N(M9),500)*1E+10+MIN(ROUND(N(F9),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G9="",O9="Aprovado",O9="Recusado",O9="Sem retorno"),0,IF(O9="Parado",2,1)*1E+15+MIN(N(M9),500)*1E+12+MIN(ROUND(N(F9)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
         <v>46204.0</v>
       </c>
       <c r="Q10" s="40">
-        <f>IF(OR(G10="",O10="Aprovado",O10="Recusado",O10="Sem retorno"),0,IF(O10="Parado",2,1)*1E+13+MIN(N(M10),500)*1E+10+MIN(ROUND(N(F10),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G10="",O10="Aprovado",O10="Recusado",O10="Sem retorno"),0,IF(O10="Parado",2,1)*1E+15+MIN(N(M10),500)*1E+12+MIN(ROUND(N(F10)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
         <v>46204.0</v>
       </c>
       <c r="Q11" s="40">
-        <f>IF(OR(G11="",O11="Aprovado",O11="Recusado",O11="Sem retorno"),0,IF(O11="Parado",2,1)*1E+13+MIN(N(M11),500)*1E+10+MIN(ROUND(N(F11),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G11="",O11="Aprovado",O11="Recusado",O11="Sem retorno"),0,IF(O11="Parado",2,1)*1E+15+MIN(N(M11),500)*1E+12+MIN(ROUND(N(F11)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
         <v>46204.0</v>
       </c>
       <c r="Q12" s="40">
-        <f>IF(OR(G12="",O12="Aprovado",O12="Recusado",O12="Sem retorno"),0,IF(O12="Parado",2,1)*1E+13+MIN(N(M12),500)*1E+10+MIN(ROUND(N(F12),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G12="",O12="Aprovado",O12="Recusado",O12="Sem retorno"),0,IF(O12="Parado",2,1)*1E+15+MIN(N(M12),500)*1E+12+MIN(ROUND(N(F12)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
         <v>46204.0</v>
       </c>
       <c r="Q13" s="40">
-        <f>IF(OR(G13="",O13="Aprovado",O13="Recusado",O13="Sem retorno"),0,IF(O13="Parado",2,1)*1E+13+MIN(N(M13),500)*1E+10+MIN(ROUND(N(F13),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G13="",O13="Aprovado",O13="Recusado",O13="Sem retorno"),0,IF(O13="Parado",2,1)*1E+15+MIN(N(M13),500)*1E+12+MIN(ROUND(N(F13)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -3628,7 +3628,7 @@
         <v>46204.0</v>
       </c>
       <c r="Q14" s="40">
-        <f>IF(OR(G14="",O14="Aprovado",O14="Recusado",O14="Sem retorno"),0,IF(O14="Parado",2,1)*1E+13+MIN(N(M14),500)*1E+10+MIN(ROUND(N(F14),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G14="",O14="Aprovado",O14="Recusado",O14="Sem retorno"),0,IF(O14="Parado",2,1)*1E+15+MIN(N(M14),500)*1E+12+MIN(ROUND(N(F14)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -3698,7 +3698,7 @@
         <v>46204.0</v>
       </c>
       <c r="Q15" s="40">
-        <f>IF(OR(G15="",O15="Aprovado",O15="Recusado",O15="Sem retorno"),0,IF(O15="Parado",2,1)*1E+13+MIN(N(M15),500)*1E+10+MIN(ROUND(N(F15),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G15="",O15="Aprovado",O15="Recusado",O15="Sem retorno"),0,IF(O15="Parado",2,1)*1E+15+MIN(N(M15),500)*1E+12+MIN(ROUND(N(F15)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
         <v>46235.0</v>
       </c>
       <c r="Q16" s="40">
-        <f>IF(OR(G16="",O16="Aprovado",O16="Recusado",O16="Sem retorno"),0,IF(O16="Parado",2,1)*1E+13+MIN(N(M16),500)*1E+10+MIN(ROUND(N(F16),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G16="",O16="Aprovado",O16="Recusado",O16="Sem retorno"),0,IF(O16="Parado",2,1)*1E+15+MIN(N(M16),500)*1E+12+MIN(ROUND(N(F16)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -3838,7 +3838,7 @@
         <v>46235.0</v>
       </c>
       <c r="Q17" s="40">
-        <f>IF(OR(G17="",O17="Aprovado",O17="Recusado",O17="Sem retorno"),0,IF(O17="Parado",2,1)*1E+13+MIN(N(M17),500)*1E+10+MIN(ROUND(N(F17),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G17="",O17="Aprovado",O17="Recusado",O17="Sem retorno"),0,IF(O17="Parado",2,1)*1E+15+MIN(N(M17),500)*1E+12+MIN(ROUND(N(F17)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -3908,7 +3908,7 @@
         <v>46235.0</v>
       </c>
       <c r="Q18" s="40">
-        <f>IF(OR(G18="",O18="Aprovado",O18="Recusado",O18="Sem retorno"),0,IF(O18="Parado",2,1)*1E+13+MIN(N(M18),500)*1E+10+MIN(ROUND(N(F18),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G18="",O18="Aprovado",O18="Recusado",O18="Sem retorno"),0,IF(O18="Parado",2,1)*1E+15+MIN(N(M18),500)*1E+12+MIN(ROUND(N(F18)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
         <v>46235.0</v>
       </c>
       <c r="Q19" s="40">
-        <f>IF(OR(G19="",O19="Aprovado",O19="Recusado",O19="Sem retorno"),0,IF(O19="Parado",2,1)*1E+13+MIN(N(M19),500)*1E+10+MIN(ROUND(N(F19),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G19="",O19="Aprovado",O19="Recusado",O19="Sem retorno"),0,IF(O19="Parado",2,1)*1E+15+MIN(N(M19),500)*1E+12+MIN(ROUND(N(F19)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -4048,7 +4048,7 @@
         <v>46235.0</v>
       </c>
       <c r="Q20" s="40">
-        <f>IF(OR(G20="",O20="Aprovado",O20="Recusado",O20="Sem retorno"),0,IF(O20="Parado",2,1)*1E+13+MIN(N(M20),500)*1E+10+MIN(ROUND(N(F20),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G20="",O20="Aprovado",O20="Recusado",O20="Sem retorno"),0,IF(O20="Parado",2,1)*1E+15+MIN(N(M20),500)*1E+12+MIN(ROUND(N(F20)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -4118,7 +4118,7 @@
         <v>46235.0</v>
       </c>
       <c r="Q21" s="40">
-        <f>IF(OR(G21="",O21="Aprovado",O21="Recusado",O21="Sem retorno"),0,IF(O21="Parado",2,1)*1E+13+MIN(N(M21),500)*1E+10+MIN(ROUND(N(F21),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G21="",O21="Aprovado",O21="Recusado",O21="Sem retorno"),0,IF(O21="Parado",2,1)*1E+15+MIN(N(M21),500)*1E+12+MIN(ROUND(N(F21)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
         <v>46235.0</v>
       </c>
       <c r="Q22" s="40">
-        <f>IF(OR(G22="",O22="Aprovado",O22="Recusado",O22="Sem retorno"),0,IF(O22="Parado",2,1)*1E+13+MIN(N(M22),500)*1E+10+MIN(ROUND(N(F22),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G22="",O22="Aprovado",O22="Recusado",O22="Sem retorno"),0,IF(O22="Parado",2,1)*1E+15+MIN(N(M22),500)*1E+12+MIN(ROUND(N(F22)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -4258,7 +4258,7 @@
         <v>46235.0</v>
       </c>
       <c r="Q23" s="40">
-        <f>IF(OR(G23="",O23="Aprovado",O23="Recusado",O23="Sem retorno"),0,IF(O23="Parado",2,1)*1E+13+MIN(N(M23),500)*1E+10+MIN(ROUND(N(F23),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G23="",O23="Aprovado",O23="Recusado",O23="Sem retorno"),0,IF(O23="Parado",2,1)*1E+15+MIN(N(M23),500)*1E+12+MIN(ROUND(N(F23)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -4328,7 +4328,7 @@
         <v>46235.0</v>
       </c>
       <c r="Q24" s="40">
-        <f>IF(OR(G24="",O24="Aprovado",O24="Recusado",O24="Sem retorno"),0,IF(O24="Parado",2,1)*1E+13+MIN(N(M24),500)*1E+10+MIN(ROUND(N(F24),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G24="",O24="Aprovado",O24="Recusado",O24="Sem retorno"),0,IF(O24="Parado",2,1)*1E+15+MIN(N(M24),500)*1E+12+MIN(ROUND(N(F24)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
         <v>46235.0</v>
       </c>
       <c r="Q25" s="40">
-        <f>IF(OR(G25="",O25="Aprovado",O25="Recusado",O25="Sem retorno"),0,IF(O25="Parado",2,1)*1E+13+MIN(N(M25),500)*1E+10+MIN(ROUND(N(F25),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G25="",O25="Aprovado",O25="Recusado",O25="Sem retorno"),0,IF(O25="Parado",2,1)*1E+15+MIN(N(M25),500)*1E+12+MIN(ROUND(N(F25)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -4468,7 +4468,7 @@
         <v>46235.0</v>
       </c>
       <c r="Q26" s="40">
-        <f>IF(OR(G26="",O26="Aprovado",O26="Recusado",O26="Sem retorno"),0,IF(O26="Parado",2,1)*1E+13+MIN(N(M26),500)*1E+10+MIN(ROUND(N(F26),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G26="",O26="Aprovado",O26="Recusado",O26="Sem retorno"),0,IF(O26="Parado",2,1)*1E+15+MIN(N(M26),500)*1E+12+MIN(ROUND(N(F26)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -4538,7 +4538,7 @@
         <v>46235.0</v>
       </c>
       <c r="Q27" s="40">
-        <f>IF(OR(G27="",O27="Aprovado",O27="Recusado",O27="Sem retorno"),0,IF(O27="Parado",2,1)*1E+13+MIN(N(M27),500)*1E+10+MIN(ROUND(N(F27),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G27="",O27="Aprovado",O27="Recusado",O27="Sem retorno"),0,IF(O27="Parado",2,1)*1E+15+MIN(N(M27),500)*1E+12+MIN(ROUND(N(F27)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -4608,7 +4608,7 @@
         <v>46235.0</v>
       </c>
       <c r="Q28" s="40">
-        <f>IF(OR(G28="",O28="Aprovado",O28="Recusado",O28="Sem retorno"),0,IF(O28="Parado",2,1)*1E+13+MIN(N(M28),500)*1E+10+MIN(ROUND(N(F28),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G28="",O28="Aprovado",O28="Recusado",O28="Sem retorno"),0,IF(O28="Parado",2,1)*1E+15+MIN(N(M28),500)*1E+12+MIN(ROUND(N(F28)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -4678,7 +4678,7 @@
         <v>46235.0</v>
       </c>
       <c r="Q29" s="40">
-        <f>IF(OR(G29="",O29="Aprovado",O29="Recusado",O29="Sem retorno"),0,IF(O29="Parado",2,1)*1E+13+MIN(N(M29),500)*1E+10+MIN(ROUND(N(F29),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G29="",O29="Aprovado",O29="Recusado",O29="Sem retorno"),0,IF(O29="Parado",2,1)*1E+15+MIN(N(M29),500)*1E+12+MIN(ROUND(N(F29)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -4748,7 +4748,7 @@
         <v>46235.0</v>
       </c>
       <c r="Q30" s="40">
-        <f>IF(OR(G30="",O30="Aprovado",O30="Recusado",O30="Sem retorno"),0,IF(O30="Parado",2,1)*1E+13+MIN(N(M30),500)*1E+10+MIN(ROUND(N(F30),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G30="",O30="Aprovado",O30="Recusado",O30="Sem retorno"),0,IF(O30="Parado",2,1)*1E+15+MIN(N(M30),500)*1E+12+MIN(ROUND(N(F30)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -4818,7 +4818,7 @@
         <v>46235.0</v>
       </c>
       <c r="Q31" s="40">
-        <f>IF(OR(G31="",O31="Aprovado",O31="Recusado",O31="Sem retorno"),0,IF(O31="Parado",2,1)*1E+13+MIN(N(M31),500)*1E+10+MIN(ROUND(N(F31),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G31="",O31="Aprovado",O31="Recusado",O31="Sem retorno"),0,IF(O31="Parado",2,1)*1E+15+MIN(N(M31),500)*1E+12+MIN(ROUND(N(F31)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -4888,7 +4888,7 @@
         <v>46235.0</v>
       </c>
       <c r="Q32" s="40">
-        <f>IF(OR(G32="",O32="Aprovado",O32="Recusado",O32="Sem retorno"),0,IF(O32="Parado",2,1)*1E+13+MIN(N(M32),500)*1E+10+MIN(ROUND(N(F32),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G32="",O32="Aprovado",O32="Recusado",O32="Sem retorno"),0,IF(O32="Parado",2,1)*1E+15+MIN(N(M32),500)*1E+12+MIN(ROUND(N(F32)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -4958,7 +4958,7 @@
         <v>46266.0</v>
       </c>
       <c r="Q33" s="40">
-        <f>IF(OR(G33="",O33="Aprovado",O33="Recusado",O33="Sem retorno"),0,IF(O33="Parado",2,1)*1E+13+MIN(N(M33),500)*1E+10+MIN(ROUND(N(F33),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G33="",O33="Aprovado",O33="Recusado",O33="Sem retorno"),0,IF(O33="Parado",2,1)*1E+15+MIN(N(M33),500)*1E+12+MIN(ROUND(N(F33)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -5022,8 +5022,8 @@
         <v>46266.0</v>
       </c>
       <c r="Q34" s="40">
-        <f>IF(OR(G34="",O34="Aprovado",O34="Recusado",O34="Sem retorno"),0,IF(O34="Parado",2,1)*1E+13+MIN(N(M34),500)*1E+10+MIN(ROUND(N(F34),0),999999)*1E+4+(304+1-ROW()))</f>
-        <v>20120006500271</v>
+        <f>IF(OR(G34="",O34="Aprovado",O34="Recusado",O34="Sem retorno"),0,IF(O34="Parado",2,1)*1E+15+MIN(N(M34),500)*1E+12+MIN(ROUND(N(F34)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
+        <v>2012000650000271</v>
       </c>
     </row>
     <row r="35">
@@ -5092,7 +5092,7 @@
         <v>46266.0</v>
       </c>
       <c r="Q35" s="40">
-        <f>IF(OR(G35="",O35="Aprovado",O35="Recusado",O35="Sem retorno"),0,IF(O35="Parado",2,1)*1E+13+MIN(N(M35),500)*1E+10+MIN(ROUND(N(F35),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G35="",O35="Aprovado",O35="Recusado",O35="Sem retorno"),0,IF(O35="Parado",2,1)*1E+15+MIN(N(M35),500)*1E+12+MIN(ROUND(N(F35)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -5156,8 +5156,8 @@
         <v>46266.0</v>
       </c>
       <c r="Q36" s="40">
-        <f>IF(OR(G36="",O36="Aprovado",O36="Recusado",O36="Sem retorno"),0,IF(O36="Parado",2,1)*1E+13+MIN(N(M36),500)*1E+10+MIN(ROUND(N(F36),0),999999)*1E+4+(304+1-ROW()))</f>
-        <v>20090004000269</v>
+        <f>IF(OR(G36="",O36="Aprovado",O36="Recusado",O36="Sem retorno"),0,IF(O36="Parado",2,1)*1E+15+MIN(N(M36),500)*1E+12+MIN(ROUND(N(F36)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
+        <v>2009000400000269</v>
       </c>
     </row>
     <row r="37">
@@ -5220,8 +5220,8 @@
         <v>46266.0</v>
       </c>
       <c r="Q37" s="40">
-        <f>IF(OR(G37="",O37="Aprovado",O37="Recusado",O37="Sem retorno"),0,IF(O37="Parado",2,1)*1E+13+MIN(N(M37),500)*1E+10+MIN(ROUND(N(F37),0),999999)*1E+4+(304+1-ROW()))</f>
-        <v>10060003500268</v>
+        <f>IF(OR(G37="",O37="Aprovado",O37="Recusado",O37="Sem retorno"),0,IF(O37="Parado",2,1)*1E+15+MIN(N(M37),500)*1E+12+MIN(ROUND(N(F37)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
+        <v>1006000350000268</v>
       </c>
     </row>
     <row r="38">
@@ -5284,8 +5284,8 @@
         <v>46266.0</v>
       </c>
       <c r="Q38" s="40">
-        <f>IF(OR(G38="",O38="Aprovado",O38="Recusado",O38="Sem retorno"),0,IF(O38="Parado",2,1)*1E+13+MIN(N(M38),500)*1E+10+MIN(ROUND(N(F38),0),999999)*1E+4+(304+1-ROW()))</f>
-        <v>10030009600267</v>
+        <f>IF(OR(G38="",O38="Aprovado",O38="Recusado",O38="Sem retorno"),0,IF(O38="Parado",2,1)*1E+15+MIN(N(M38),500)*1E+12+MIN(ROUND(N(F38)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
+        <v>1003000960000267</v>
       </c>
     </row>
     <row r="39">
@@ -5348,8 +5348,8 @@
         <v>46266.0</v>
       </c>
       <c r="Q39" s="40">
-        <f>IF(OR(G39="",O39="Aprovado",O39="Recusado",O39="Sem retorno"),0,IF(O39="Parado",2,1)*1E+13+MIN(N(M39),500)*1E+10+MIN(ROUND(N(F39),0),999999)*1E+4+(304+1-ROW()))</f>
-        <v>10010004500266</v>
+        <f>IF(OR(G39="",O39="Aprovado",O39="Recusado",O39="Sem retorno"),0,IF(O39="Parado",2,1)*1E+15+MIN(N(M39),500)*1E+12+MIN(ROUND(N(F39)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
+        <v>1001000450000266</v>
       </c>
     </row>
     <row r="40">
@@ -5412,8 +5412,8 @@
         <v>46266.0</v>
       </c>
       <c r="Q40" s="40">
-        <f>IF(OR(G40="",O40="Aprovado",O40="Recusado",O40="Sem retorno"),0,IF(O40="Parado",2,1)*1E+13+MIN(N(M40),500)*1E+10+MIN(ROUND(N(F40),0),999999)*1E+4+(304+1-ROW()))</f>
-        <v>10000006500265</v>
+        <f>IF(OR(G40="",O40="Aprovado",O40="Recusado",O40="Sem retorno"),0,IF(O40="Parado",2,1)*1E+15+MIN(N(M40),500)*1E+12+MIN(ROUND(N(F40)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
+        <v>1000000650000265</v>
       </c>
     </row>
     <row r="41">
@@ -5452,7 +5452,7 @@
         <v/>
       </c>
       <c r="Q41" s="40">
-        <f>IF(OR(G41="",O41="Aprovado",O41="Recusado",O41="Sem retorno"),0,IF(O41="Parado",2,1)*1E+13+MIN(N(M41),500)*1E+10+MIN(ROUND(N(F41),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G41="",O41="Aprovado",O41="Recusado",O41="Sem retorno"),0,IF(O41="Parado",2,1)*1E+15+MIN(N(M41),500)*1E+12+MIN(ROUND(N(F41)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -5492,7 +5492,7 @@
         <v/>
       </c>
       <c r="Q42" s="40">
-        <f>IF(OR(G42="",O42="Aprovado",O42="Recusado",O42="Sem retorno"),0,IF(O42="Parado",2,1)*1E+13+MIN(N(M42),500)*1E+10+MIN(ROUND(N(F42),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G42="",O42="Aprovado",O42="Recusado",O42="Sem retorno"),0,IF(O42="Parado",2,1)*1E+15+MIN(N(M42),500)*1E+12+MIN(ROUND(N(F42)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -5532,7 +5532,7 @@
         <v/>
       </c>
       <c r="Q43" s="40">
-        <f>IF(OR(G43="",O43="Aprovado",O43="Recusado",O43="Sem retorno"),0,IF(O43="Parado",2,1)*1E+13+MIN(N(M43),500)*1E+10+MIN(ROUND(N(F43),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G43="",O43="Aprovado",O43="Recusado",O43="Sem retorno"),0,IF(O43="Parado",2,1)*1E+15+MIN(N(M43),500)*1E+12+MIN(ROUND(N(F43)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -5572,7 +5572,7 @@
         <v/>
       </c>
       <c r="Q44" s="40">
-        <f>IF(OR(G44="",O44="Aprovado",O44="Recusado",O44="Sem retorno"),0,IF(O44="Parado",2,1)*1E+13+MIN(N(M44),500)*1E+10+MIN(ROUND(N(F44),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G44="",O44="Aprovado",O44="Recusado",O44="Sem retorno"),0,IF(O44="Parado",2,1)*1E+15+MIN(N(M44),500)*1E+12+MIN(ROUND(N(F44)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -5612,7 +5612,7 @@
         <v/>
       </c>
       <c r="Q45" s="40">
-        <f>IF(OR(G45="",O45="Aprovado",O45="Recusado",O45="Sem retorno"),0,IF(O45="Parado",2,1)*1E+13+MIN(N(M45),500)*1E+10+MIN(ROUND(N(F45),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G45="",O45="Aprovado",O45="Recusado",O45="Sem retorno"),0,IF(O45="Parado",2,1)*1E+15+MIN(N(M45),500)*1E+12+MIN(ROUND(N(F45)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -5652,7 +5652,7 @@
         <v/>
       </c>
       <c r="Q46" s="40">
-        <f>IF(OR(G46="",O46="Aprovado",O46="Recusado",O46="Sem retorno"),0,IF(O46="Parado",2,1)*1E+13+MIN(N(M46),500)*1E+10+MIN(ROUND(N(F46),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G46="",O46="Aprovado",O46="Recusado",O46="Sem retorno"),0,IF(O46="Parado",2,1)*1E+15+MIN(N(M46),500)*1E+12+MIN(ROUND(N(F46)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -5692,7 +5692,7 @@
         <v/>
       </c>
       <c r="Q47" s="40">
-        <f>IF(OR(G47="",O47="Aprovado",O47="Recusado",O47="Sem retorno"),0,IF(O47="Parado",2,1)*1E+13+MIN(N(M47),500)*1E+10+MIN(ROUND(N(F47),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G47="",O47="Aprovado",O47="Recusado",O47="Sem retorno"),0,IF(O47="Parado",2,1)*1E+15+MIN(N(M47),500)*1E+12+MIN(ROUND(N(F47)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -5732,7 +5732,7 @@
         <v/>
       </c>
       <c r="Q48" s="40">
-        <f>IF(OR(G48="",O48="Aprovado",O48="Recusado",O48="Sem retorno"),0,IF(O48="Parado",2,1)*1E+13+MIN(N(M48),500)*1E+10+MIN(ROUND(N(F48),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G48="",O48="Aprovado",O48="Recusado",O48="Sem retorno"),0,IF(O48="Parado",2,1)*1E+15+MIN(N(M48),500)*1E+12+MIN(ROUND(N(F48)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -5772,7 +5772,7 @@
         <v/>
       </c>
       <c r="Q49" s="40">
-        <f>IF(OR(G49="",O49="Aprovado",O49="Recusado",O49="Sem retorno"),0,IF(O49="Parado",2,1)*1E+13+MIN(N(M49),500)*1E+10+MIN(ROUND(N(F49),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G49="",O49="Aprovado",O49="Recusado",O49="Sem retorno"),0,IF(O49="Parado",2,1)*1E+15+MIN(N(M49),500)*1E+12+MIN(ROUND(N(F49)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -5812,7 +5812,7 @@
         <v/>
       </c>
       <c r="Q50" s="40">
-        <f>IF(OR(G50="",O50="Aprovado",O50="Recusado",O50="Sem retorno"),0,IF(O50="Parado",2,1)*1E+13+MIN(N(M50),500)*1E+10+MIN(ROUND(N(F50),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G50="",O50="Aprovado",O50="Recusado",O50="Sem retorno"),0,IF(O50="Parado",2,1)*1E+15+MIN(N(M50),500)*1E+12+MIN(ROUND(N(F50)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -5852,7 +5852,7 @@
         <v/>
       </c>
       <c r="Q51" s="40">
-        <f>IF(OR(G51="",O51="Aprovado",O51="Recusado",O51="Sem retorno"),0,IF(O51="Parado",2,1)*1E+13+MIN(N(M51),500)*1E+10+MIN(ROUND(N(F51),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G51="",O51="Aprovado",O51="Recusado",O51="Sem retorno"),0,IF(O51="Parado",2,1)*1E+15+MIN(N(M51),500)*1E+12+MIN(ROUND(N(F51)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -5892,7 +5892,7 @@
         <v/>
       </c>
       <c r="Q52" s="40">
-        <f>IF(OR(G52="",O52="Aprovado",O52="Recusado",O52="Sem retorno"),0,IF(O52="Parado",2,1)*1E+13+MIN(N(M52),500)*1E+10+MIN(ROUND(N(F52),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G52="",O52="Aprovado",O52="Recusado",O52="Sem retorno"),0,IF(O52="Parado",2,1)*1E+15+MIN(N(M52),500)*1E+12+MIN(ROUND(N(F52)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -5932,7 +5932,7 @@
         <v/>
       </c>
       <c r="Q53" s="40">
-        <f>IF(OR(G53="",O53="Aprovado",O53="Recusado",O53="Sem retorno"),0,IF(O53="Parado",2,1)*1E+13+MIN(N(M53),500)*1E+10+MIN(ROUND(N(F53),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G53="",O53="Aprovado",O53="Recusado",O53="Sem retorno"),0,IF(O53="Parado",2,1)*1E+15+MIN(N(M53),500)*1E+12+MIN(ROUND(N(F53)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -5972,7 +5972,7 @@
         <v/>
       </c>
       <c r="Q54" s="40">
-        <f>IF(OR(G54="",O54="Aprovado",O54="Recusado",O54="Sem retorno"),0,IF(O54="Parado",2,1)*1E+13+MIN(N(M54),500)*1E+10+MIN(ROUND(N(F54),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G54="",O54="Aprovado",O54="Recusado",O54="Sem retorno"),0,IF(O54="Parado",2,1)*1E+15+MIN(N(M54),500)*1E+12+MIN(ROUND(N(F54)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -6012,7 +6012,7 @@
         <v/>
       </c>
       <c r="Q55" s="40">
-        <f>IF(OR(G55="",O55="Aprovado",O55="Recusado",O55="Sem retorno"),0,IF(O55="Parado",2,1)*1E+13+MIN(N(M55),500)*1E+10+MIN(ROUND(N(F55),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G55="",O55="Aprovado",O55="Recusado",O55="Sem retorno"),0,IF(O55="Parado",2,1)*1E+15+MIN(N(M55),500)*1E+12+MIN(ROUND(N(F55)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -6052,7 +6052,7 @@
         <v/>
       </c>
       <c r="Q56" s="40">
-        <f>IF(OR(G56="",O56="Aprovado",O56="Recusado",O56="Sem retorno"),0,IF(O56="Parado",2,1)*1E+13+MIN(N(M56),500)*1E+10+MIN(ROUND(N(F56),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G56="",O56="Aprovado",O56="Recusado",O56="Sem retorno"),0,IF(O56="Parado",2,1)*1E+15+MIN(N(M56),500)*1E+12+MIN(ROUND(N(F56)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -6092,7 +6092,7 @@
         <v/>
       </c>
       <c r="Q57" s="40">
-        <f>IF(OR(G57="",O57="Aprovado",O57="Recusado",O57="Sem retorno"),0,IF(O57="Parado",2,1)*1E+13+MIN(N(M57),500)*1E+10+MIN(ROUND(N(F57),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G57="",O57="Aprovado",O57="Recusado",O57="Sem retorno"),0,IF(O57="Parado",2,1)*1E+15+MIN(N(M57),500)*1E+12+MIN(ROUND(N(F57)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -6132,7 +6132,7 @@
         <v/>
       </c>
       <c r="Q58" s="40">
-        <f>IF(OR(G58="",O58="Aprovado",O58="Recusado",O58="Sem retorno"),0,IF(O58="Parado",2,1)*1E+13+MIN(N(M58),500)*1E+10+MIN(ROUND(N(F58),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G58="",O58="Aprovado",O58="Recusado",O58="Sem retorno"),0,IF(O58="Parado",2,1)*1E+15+MIN(N(M58),500)*1E+12+MIN(ROUND(N(F58)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -6172,7 +6172,7 @@
         <v/>
       </c>
       <c r="Q59" s="40">
-        <f>IF(OR(G59="",O59="Aprovado",O59="Recusado",O59="Sem retorno"),0,IF(O59="Parado",2,1)*1E+13+MIN(N(M59),500)*1E+10+MIN(ROUND(N(F59),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G59="",O59="Aprovado",O59="Recusado",O59="Sem retorno"),0,IF(O59="Parado",2,1)*1E+15+MIN(N(M59),500)*1E+12+MIN(ROUND(N(F59)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -6212,7 +6212,7 @@
         <v/>
       </c>
       <c r="Q60" s="40">
-        <f>IF(OR(G60="",O60="Aprovado",O60="Recusado",O60="Sem retorno"),0,IF(O60="Parado",2,1)*1E+13+MIN(N(M60),500)*1E+10+MIN(ROUND(N(F60),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G60="",O60="Aprovado",O60="Recusado",O60="Sem retorno"),0,IF(O60="Parado",2,1)*1E+15+MIN(N(M60),500)*1E+12+MIN(ROUND(N(F60)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -6252,7 +6252,7 @@
         <v/>
       </c>
       <c r="Q61" s="40">
-        <f>IF(OR(G61="",O61="Aprovado",O61="Recusado",O61="Sem retorno"),0,IF(O61="Parado",2,1)*1E+13+MIN(N(M61),500)*1E+10+MIN(ROUND(N(F61),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G61="",O61="Aprovado",O61="Recusado",O61="Sem retorno"),0,IF(O61="Parado",2,1)*1E+15+MIN(N(M61),500)*1E+12+MIN(ROUND(N(F61)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -6292,7 +6292,7 @@
         <v/>
       </c>
       <c r="Q62" s="40">
-        <f>IF(OR(G62="",O62="Aprovado",O62="Recusado",O62="Sem retorno"),0,IF(O62="Parado",2,1)*1E+13+MIN(N(M62),500)*1E+10+MIN(ROUND(N(F62),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G62="",O62="Aprovado",O62="Recusado",O62="Sem retorno"),0,IF(O62="Parado",2,1)*1E+15+MIN(N(M62),500)*1E+12+MIN(ROUND(N(F62)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -6332,7 +6332,7 @@
         <v/>
       </c>
       <c r="Q63" s="40">
-        <f>IF(OR(G63="",O63="Aprovado",O63="Recusado",O63="Sem retorno"),0,IF(O63="Parado",2,1)*1E+13+MIN(N(M63),500)*1E+10+MIN(ROUND(N(F63),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G63="",O63="Aprovado",O63="Recusado",O63="Sem retorno"),0,IF(O63="Parado",2,1)*1E+15+MIN(N(M63),500)*1E+12+MIN(ROUND(N(F63)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -6372,7 +6372,7 @@
         <v/>
       </c>
       <c r="Q64" s="40">
-        <f>IF(OR(G64="",O64="Aprovado",O64="Recusado",O64="Sem retorno"),0,IF(O64="Parado",2,1)*1E+13+MIN(N(M64),500)*1E+10+MIN(ROUND(N(F64),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G64="",O64="Aprovado",O64="Recusado",O64="Sem retorno"),0,IF(O64="Parado",2,1)*1E+15+MIN(N(M64),500)*1E+12+MIN(ROUND(N(F64)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -6412,7 +6412,7 @@
         <v/>
       </c>
       <c r="Q65" s="40">
-        <f>IF(OR(G65="",O65="Aprovado",O65="Recusado",O65="Sem retorno"),0,IF(O65="Parado",2,1)*1E+13+MIN(N(M65),500)*1E+10+MIN(ROUND(N(F65),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G65="",O65="Aprovado",O65="Recusado",O65="Sem retorno"),0,IF(O65="Parado",2,1)*1E+15+MIN(N(M65),500)*1E+12+MIN(ROUND(N(F65)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -6452,7 +6452,7 @@
         <v/>
       </c>
       <c r="Q66" s="40">
-        <f>IF(OR(G66="",O66="Aprovado",O66="Recusado",O66="Sem retorno"),0,IF(O66="Parado",2,1)*1E+13+MIN(N(M66),500)*1E+10+MIN(ROUND(N(F66),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G66="",O66="Aprovado",O66="Recusado",O66="Sem retorno"),0,IF(O66="Parado",2,1)*1E+15+MIN(N(M66),500)*1E+12+MIN(ROUND(N(F66)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -6492,7 +6492,7 @@
         <v/>
       </c>
       <c r="Q67" s="40">
-        <f>IF(OR(G67="",O67="Aprovado",O67="Recusado",O67="Sem retorno"),0,IF(O67="Parado",2,1)*1E+13+MIN(N(M67),500)*1E+10+MIN(ROUND(N(F67),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G67="",O67="Aprovado",O67="Recusado",O67="Sem retorno"),0,IF(O67="Parado",2,1)*1E+15+MIN(N(M67),500)*1E+12+MIN(ROUND(N(F67)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -6532,7 +6532,7 @@
         <v/>
       </c>
       <c r="Q68" s="40">
-        <f>IF(OR(G68="",O68="Aprovado",O68="Recusado",O68="Sem retorno"),0,IF(O68="Parado",2,1)*1E+13+MIN(N(M68),500)*1E+10+MIN(ROUND(N(F68),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G68="",O68="Aprovado",O68="Recusado",O68="Sem retorno"),0,IF(O68="Parado",2,1)*1E+15+MIN(N(M68),500)*1E+12+MIN(ROUND(N(F68)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -6572,7 +6572,7 @@
         <v/>
       </c>
       <c r="Q69" s="40">
-        <f>IF(OR(G69="",O69="Aprovado",O69="Recusado",O69="Sem retorno"),0,IF(O69="Parado",2,1)*1E+13+MIN(N(M69),500)*1E+10+MIN(ROUND(N(F69),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G69="",O69="Aprovado",O69="Recusado",O69="Sem retorno"),0,IF(O69="Parado",2,1)*1E+15+MIN(N(M69),500)*1E+12+MIN(ROUND(N(F69)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -6612,7 +6612,7 @@
         <v/>
       </c>
       <c r="Q70" s="40">
-        <f>IF(OR(G70="",O70="Aprovado",O70="Recusado",O70="Sem retorno"),0,IF(O70="Parado",2,1)*1E+13+MIN(N(M70),500)*1E+10+MIN(ROUND(N(F70),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G70="",O70="Aprovado",O70="Recusado",O70="Sem retorno"),0,IF(O70="Parado",2,1)*1E+15+MIN(N(M70),500)*1E+12+MIN(ROUND(N(F70)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -6652,7 +6652,7 @@
         <v/>
       </c>
       <c r="Q71" s="40">
-        <f>IF(OR(G71="",O71="Aprovado",O71="Recusado",O71="Sem retorno"),0,IF(O71="Parado",2,1)*1E+13+MIN(N(M71),500)*1E+10+MIN(ROUND(N(F71),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G71="",O71="Aprovado",O71="Recusado",O71="Sem retorno"),0,IF(O71="Parado",2,1)*1E+15+MIN(N(M71),500)*1E+12+MIN(ROUND(N(F71)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -6692,7 +6692,7 @@
         <v/>
       </c>
       <c r="Q72" s="40">
-        <f>IF(OR(G72="",O72="Aprovado",O72="Recusado",O72="Sem retorno"),0,IF(O72="Parado",2,1)*1E+13+MIN(N(M72),500)*1E+10+MIN(ROUND(N(F72),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G72="",O72="Aprovado",O72="Recusado",O72="Sem retorno"),0,IF(O72="Parado",2,1)*1E+15+MIN(N(M72),500)*1E+12+MIN(ROUND(N(F72)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -6732,7 +6732,7 @@
         <v/>
       </c>
       <c r="Q73" s="40">
-        <f>IF(OR(G73="",O73="Aprovado",O73="Recusado",O73="Sem retorno"),0,IF(O73="Parado",2,1)*1E+13+MIN(N(M73),500)*1E+10+MIN(ROUND(N(F73),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G73="",O73="Aprovado",O73="Recusado",O73="Sem retorno"),0,IF(O73="Parado",2,1)*1E+15+MIN(N(M73),500)*1E+12+MIN(ROUND(N(F73)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -6772,7 +6772,7 @@
         <v/>
       </c>
       <c r="Q74" s="40">
-        <f>IF(OR(G74="",O74="Aprovado",O74="Recusado",O74="Sem retorno"),0,IF(O74="Parado",2,1)*1E+13+MIN(N(M74),500)*1E+10+MIN(ROUND(N(F74),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G74="",O74="Aprovado",O74="Recusado",O74="Sem retorno"),0,IF(O74="Parado",2,1)*1E+15+MIN(N(M74),500)*1E+12+MIN(ROUND(N(F74)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -6812,7 +6812,7 @@
         <v/>
       </c>
       <c r="Q75" s="40">
-        <f>IF(OR(G75="",O75="Aprovado",O75="Recusado",O75="Sem retorno"),0,IF(O75="Parado",2,1)*1E+13+MIN(N(M75),500)*1E+10+MIN(ROUND(N(F75),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G75="",O75="Aprovado",O75="Recusado",O75="Sem retorno"),0,IF(O75="Parado",2,1)*1E+15+MIN(N(M75),500)*1E+12+MIN(ROUND(N(F75)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -6852,7 +6852,7 @@
         <v/>
       </c>
       <c r="Q76" s="40">
-        <f>IF(OR(G76="",O76="Aprovado",O76="Recusado",O76="Sem retorno"),0,IF(O76="Parado",2,1)*1E+13+MIN(N(M76),500)*1E+10+MIN(ROUND(N(F76),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G76="",O76="Aprovado",O76="Recusado",O76="Sem retorno"),0,IF(O76="Parado",2,1)*1E+15+MIN(N(M76),500)*1E+12+MIN(ROUND(N(F76)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -6892,7 +6892,7 @@
         <v/>
       </c>
       <c r="Q77" s="40">
-        <f>IF(OR(G77="",O77="Aprovado",O77="Recusado",O77="Sem retorno"),0,IF(O77="Parado",2,1)*1E+13+MIN(N(M77),500)*1E+10+MIN(ROUND(N(F77),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G77="",O77="Aprovado",O77="Recusado",O77="Sem retorno"),0,IF(O77="Parado",2,1)*1E+15+MIN(N(M77),500)*1E+12+MIN(ROUND(N(F77)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -6932,7 +6932,7 @@
         <v/>
       </c>
       <c r="Q78" s="40">
-        <f>IF(OR(G78="",O78="Aprovado",O78="Recusado",O78="Sem retorno"),0,IF(O78="Parado",2,1)*1E+13+MIN(N(M78),500)*1E+10+MIN(ROUND(N(F78),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G78="",O78="Aprovado",O78="Recusado",O78="Sem retorno"),0,IF(O78="Parado",2,1)*1E+15+MIN(N(M78),500)*1E+12+MIN(ROUND(N(F78)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -6972,7 +6972,7 @@
         <v/>
       </c>
       <c r="Q79" s="40">
-        <f>IF(OR(G79="",O79="Aprovado",O79="Recusado",O79="Sem retorno"),0,IF(O79="Parado",2,1)*1E+13+MIN(N(M79),500)*1E+10+MIN(ROUND(N(F79),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G79="",O79="Aprovado",O79="Recusado",O79="Sem retorno"),0,IF(O79="Parado",2,1)*1E+15+MIN(N(M79),500)*1E+12+MIN(ROUND(N(F79)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -7012,7 +7012,7 @@
         <v/>
       </c>
       <c r="Q80" s="40">
-        <f>IF(OR(G80="",O80="Aprovado",O80="Recusado",O80="Sem retorno"),0,IF(O80="Parado",2,1)*1E+13+MIN(N(M80),500)*1E+10+MIN(ROUND(N(F80),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G80="",O80="Aprovado",O80="Recusado",O80="Sem retorno"),0,IF(O80="Parado",2,1)*1E+15+MIN(N(M80),500)*1E+12+MIN(ROUND(N(F80)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -7052,7 +7052,7 @@
         <v/>
       </c>
       <c r="Q81" s="40">
-        <f>IF(OR(G81="",O81="Aprovado",O81="Recusado",O81="Sem retorno"),0,IF(O81="Parado",2,1)*1E+13+MIN(N(M81),500)*1E+10+MIN(ROUND(N(F81),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G81="",O81="Aprovado",O81="Recusado",O81="Sem retorno"),0,IF(O81="Parado",2,1)*1E+15+MIN(N(M81),500)*1E+12+MIN(ROUND(N(F81)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -7092,7 +7092,7 @@
         <v/>
       </c>
       <c r="Q82" s="40">
-        <f>IF(OR(G82="",O82="Aprovado",O82="Recusado",O82="Sem retorno"),0,IF(O82="Parado",2,1)*1E+13+MIN(N(M82),500)*1E+10+MIN(ROUND(N(F82),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G82="",O82="Aprovado",O82="Recusado",O82="Sem retorno"),0,IF(O82="Parado",2,1)*1E+15+MIN(N(M82),500)*1E+12+MIN(ROUND(N(F82)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -7132,7 +7132,7 @@
         <v/>
       </c>
       <c r="Q83" s="40">
-        <f>IF(OR(G83="",O83="Aprovado",O83="Recusado",O83="Sem retorno"),0,IF(O83="Parado",2,1)*1E+13+MIN(N(M83),500)*1E+10+MIN(ROUND(N(F83),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G83="",O83="Aprovado",O83="Recusado",O83="Sem retorno"),0,IF(O83="Parado",2,1)*1E+15+MIN(N(M83),500)*1E+12+MIN(ROUND(N(F83)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -7172,7 +7172,7 @@
         <v/>
       </c>
       <c r="Q84" s="40">
-        <f>IF(OR(G84="",O84="Aprovado",O84="Recusado",O84="Sem retorno"),0,IF(O84="Parado",2,1)*1E+13+MIN(N(M84),500)*1E+10+MIN(ROUND(N(F84),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G84="",O84="Aprovado",O84="Recusado",O84="Sem retorno"),0,IF(O84="Parado",2,1)*1E+15+MIN(N(M84),500)*1E+12+MIN(ROUND(N(F84)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -7212,7 +7212,7 @@
         <v/>
       </c>
       <c r="Q85" s="40">
-        <f>IF(OR(G85="",O85="Aprovado",O85="Recusado",O85="Sem retorno"),0,IF(O85="Parado",2,1)*1E+13+MIN(N(M85),500)*1E+10+MIN(ROUND(N(F85),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G85="",O85="Aprovado",O85="Recusado",O85="Sem retorno"),0,IF(O85="Parado",2,1)*1E+15+MIN(N(M85),500)*1E+12+MIN(ROUND(N(F85)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -7252,7 +7252,7 @@
         <v/>
       </c>
       <c r="Q86" s="40">
-        <f>IF(OR(G86="",O86="Aprovado",O86="Recusado",O86="Sem retorno"),0,IF(O86="Parado",2,1)*1E+13+MIN(N(M86),500)*1E+10+MIN(ROUND(N(F86),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G86="",O86="Aprovado",O86="Recusado",O86="Sem retorno"),0,IF(O86="Parado",2,1)*1E+15+MIN(N(M86),500)*1E+12+MIN(ROUND(N(F86)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -7292,7 +7292,7 @@
         <v/>
       </c>
       <c r="Q87" s="40">
-        <f>IF(OR(G87="",O87="Aprovado",O87="Recusado",O87="Sem retorno"),0,IF(O87="Parado",2,1)*1E+13+MIN(N(M87),500)*1E+10+MIN(ROUND(N(F87),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G87="",O87="Aprovado",O87="Recusado",O87="Sem retorno"),0,IF(O87="Parado",2,1)*1E+15+MIN(N(M87),500)*1E+12+MIN(ROUND(N(F87)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -7332,7 +7332,7 @@
         <v/>
       </c>
       <c r="Q88" s="40">
-        <f>IF(OR(G88="",O88="Aprovado",O88="Recusado",O88="Sem retorno"),0,IF(O88="Parado",2,1)*1E+13+MIN(N(M88),500)*1E+10+MIN(ROUND(N(F88),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G88="",O88="Aprovado",O88="Recusado",O88="Sem retorno"),0,IF(O88="Parado",2,1)*1E+15+MIN(N(M88),500)*1E+12+MIN(ROUND(N(F88)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -7372,7 +7372,7 @@
         <v/>
       </c>
       <c r="Q89" s="40">
-        <f>IF(OR(G89="",O89="Aprovado",O89="Recusado",O89="Sem retorno"),0,IF(O89="Parado",2,1)*1E+13+MIN(N(M89),500)*1E+10+MIN(ROUND(N(F89),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G89="",O89="Aprovado",O89="Recusado",O89="Sem retorno"),0,IF(O89="Parado",2,1)*1E+15+MIN(N(M89),500)*1E+12+MIN(ROUND(N(F89)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -7412,7 +7412,7 @@
         <v/>
       </c>
       <c r="Q90" s="40">
-        <f>IF(OR(G90="",O90="Aprovado",O90="Recusado",O90="Sem retorno"),0,IF(O90="Parado",2,1)*1E+13+MIN(N(M90),500)*1E+10+MIN(ROUND(N(F90),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G90="",O90="Aprovado",O90="Recusado",O90="Sem retorno"),0,IF(O90="Parado",2,1)*1E+15+MIN(N(M90),500)*1E+12+MIN(ROUND(N(F90)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -7452,7 +7452,7 @@
         <v/>
       </c>
       <c r="Q91" s="40">
-        <f>IF(OR(G91="",O91="Aprovado",O91="Recusado",O91="Sem retorno"),0,IF(O91="Parado",2,1)*1E+13+MIN(N(M91),500)*1E+10+MIN(ROUND(N(F91),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G91="",O91="Aprovado",O91="Recusado",O91="Sem retorno"),0,IF(O91="Parado",2,1)*1E+15+MIN(N(M91),500)*1E+12+MIN(ROUND(N(F91)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -7492,7 +7492,7 @@
         <v/>
       </c>
       <c r="Q92" s="40">
-        <f>IF(OR(G92="",O92="Aprovado",O92="Recusado",O92="Sem retorno"),0,IF(O92="Parado",2,1)*1E+13+MIN(N(M92),500)*1E+10+MIN(ROUND(N(F92),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G92="",O92="Aprovado",O92="Recusado",O92="Sem retorno"),0,IF(O92="Parado",2,1)*1E+15+MIN(N(M92),500)*1E+12+MIN(ROUND(N(F92)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -7532,7 +7532,7 @@
         <v/>
       </c>
       <c r="Q93" s="40">
-        <f>IF(OR(G93="",O93="Aprovado",O93="Recusado",O93="Sem retorno"),0,IF(O93="Parado",2,1)*1E+13+MIN(N(M93),500)*1E+10+MIN(ROUND(N(F93),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G93="",O93="Aprovado",O93="Recusado",O93="Sem retorno"),0,IF(O93="Parado",2,1)*1E+15+MIN(N(M93),500)*1E+12+MIN(ROUND(N(F93)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -7572,7 +7572,7 @@
         <v/>
       </c>
       <c r="Q94" s="40">
-        <f>IF(OR(G94="",O94="Aprovado",O94="Recusado",O94="Sem retorno"),0,IF(O94="Parado",2,1)*1E+13+MIN(N(M94),500)*1E+10+MIN(ROUND(N(F94),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G94="",O94="Aprovado",O94="Recusado",O94="Sem retorno"),0,IF(O94="Parado",2,1)*1E+15+MIN(N(M94),500)*1E+12+MIN(ROUND(N(F94)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -7612,7 +7612,7 @@
         <v/>
       </c>
       <c r="Q95" s="40">
-        <f>IF(OR(G95="",O95="Aprovado",O95="Recusado",O95="Sem retorno"),0,IF(O95="Parado",2,1)*1E+13+MIN(N(M95),500)*1E+10+MIN(ROUND(N(F95),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G95="",O95="Aprovado",O95="Recusado",O95="Sem retorno"),0,IF(O95="Parado",2,1)*1E+15+MIN(N(M95),500)*1E+12+MIN(ROUND(N(F95)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -7652,7 +7652,7 @@
         <v/>
       </c>
       <c r="Q96" s="40">
-        <f>IF(OR(G96="",O96="Aprovado",O96="Recusado",O96="Sem retorno"),0,IF(O96="Parado",2,1)*1E+13+MIN(N(M96),500)*1E+10+MIN(ROUND(N(F96),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G96="",O96="Aprovado",O96="Recusado",O96="Sem retorno"),0,IF(O96="Parado",2,1)*1E+15+MIN(N(M96),500)*1E+12+MIN(ROUND(N(F96)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -7692,7 +7692,7 @@
         <v/>
       </c>
       <c r="Q97" s="40">
-        <f>IF(OR(G97="",O97="Aprovado",O97="Recusado",O97="Sem retorno"),0,IF(O97="Parado",2,1)*1E+13+MIN(N(M97),500)*1E+10+MIN(ROUND(N(F97),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G97="",O97="Aprovado",O97="Recusado",O97="Sem retorno"),0,IF(O97="Parado",2,1)*1E+15+MIN(N(M97),500)*1E+12+MIN(ROUND(N(F97)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -7732,7 +7732,7 @@
         <v/>
       </c>
       <c r="Q98" s="40">
-        <f>IF(OR(G98="",O98="Aprovado",O98="Recusado",O98="Sem retorno"),0,IF(O98="Parado",2,1)*1E+13+MIN(N(M98),500)*1E+10+MIN(ROUND(N(F98),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G98="",O98="Aprovado",O98="Recusado",O98="Sem retorno"),0,IF(O98="Parado",2,1)*1E+15+MIN(N(M98),500)*1E+12+MIN(ROUND(N(F98)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -7772,7 +7772,7 @@
         <v/>
       </c>
       <c r="Q99" s="40">
-        <f>IF(OR(G99="",O99="Aprovado",O99="Recusado",O99="Sem retorno"),0,IF(O99="Parado",2,1)*1E+13+MIN(N(M99),500)*1E+10+MIN(ROUND(N(F99),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G99="",O99="Aprovado",O99="Recusado",O99="Sem retorno"),0,IF(O99="Parado",2,1)*1E+15+MIN(N(M99),500)*1E+12+MIN(ROUND(N(F99)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -7812,7 +7812,7 @@
         <v/>
       </c>
       <c r="Q100" s="40">
-        <f>IF(OR(G100="",O100="Aprovado",O100="Recusado",O100="Sem retorno"),0,IF(O100="Parado",2,1)*1E+13+MIN(N(M100),500)*1E+10+MIN(ROUND(N(F100),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G100="",O100="Aprovado",O100="Recusado",O100="Sem retorno"),0,IF(O100="Parado",2,1)*1E+15+MIN(N(M100),500)*1E+12+MIN(ROUND(N(F100)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -7852,7 +7852,7 @@
         <v/>
       </c>
       <c r="Q101" s="40">
-        <f>IF(OR(G101="",O101="Aprovado",O101="Recusado",O101="Sem retorno"),0,IF(O101="Parado",2,1)*1E+13+MIN(N(M101),500)*1E+10+MIN(ROUND(N(F101),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G101="",O101="Aprovado",O101="Recusado",O101="Sem retorno"),0,IF(O101="Parado",2,1)*1E+15+MIN(N(M101),500)*1E+12+MIN(ROUND(N(F101)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -7892,7 +7892,7 @@
         <v/>
       </c>
       <c r="Q102" s="40">
-        <f>IF(OR(G102="",O102="Aprovado",O102="Recusado",O102="Sem retorno"),0,IF(O102="Parado",2,1)*1E+13+MIN(N(M102),500)*1E+10+MIN(ROUND(N(F102),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G102="",O102="Aprovado",O102="Recusado",O102="Sem retorno"),0,IF(O102="Parado",2,1)*1E+15+MIN(N(M102),500)*1E+12+MIN(ROUND(N(F102)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -7932,7 +7932,7 @@
         <v/>
       </c>
       <c r="Q103" s="40">
-        <f>IF(OR(G103="",O103="Aprovado",O103="Recusado",O103="Sem retorno"),0,IF(O103="Parado",2,1)*1E+13+MIN(N(M103),500)*1E+10+MIN(ROUND(N(F103),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G103="",O103="Aprovado",O103="Recusado",O103="Sem retorno"),0,IF(O103="Parado",2,1)*1E+15+MIN(N(M103),500)*1E+12+MIN(ROUND(N(F103)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -7972,7 +7972,7 @@
         <v/>
       </c>
       <c r="Q104" s="40">
-        <f>IF(OR(G104="",O104="Aprovado",O104="Recusado",O104="Sem retorno"),0,IF(O104="Parado",2,1)*1E+13+MIN(N(M104),500)*1E+10+MIN(ROUND(N(F104),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G104="",O104="Aprovado",O104="Recusado",O104="Sem retorno"),0,IF(O104="Parado",2,1)*1E+15+MIN(N(M104),500)*1E+12+MIN(ROUND(N(F104)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -8012,7 +8012,7 @@
         <v/>
       </c>
       <c r="Q105" s="40">
-        <f>IF(OR(G105="",O105="Aprovado",O105="Recusado",O105="Sem retorno"),0,IF(O105="Parado",2,1)*1E+13+MIN(N(M105),500)*1E+10+MIN(ROUND(N(F105),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G105="",O105="Aprovado",O105="Recusado",O105="Sem retorno"),0,IF(O105="Parado",2,1)*1E+15+MIN(N(M105),500)*1E+12+MIN(ROUND(N(F105)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -8052,7 +8052,7 @@
         <v/>
       </c>
       <c r="Q106" s="40">
-        <f>IF(OR(G106="",O106="Aprovado",O106="Recusado",O106="Sem retorno"),0,IF(O106="Parado",2,1)*1E+13+MIN(N(M106),500)*1E+10+MIN(ROUND(N(F106),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G106="",O106="Aprovado",O106="Recusado",O106="Sem retorno"),0,IF(O106="Parado",2,1)*1E+15+MIN(N(M106),500)*1E+12+MIN(ROUND(N(F106)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -8092,7 +8092,7 @@
         <v/>
       </c>
       <c r="Q107" s="40">
-        <f>IF(OR(G107="",O107="Aprovado",O107="Recusado",O107="Sem retorno"),0,IF(O107="Parado",2,1)*1E+13+MIN(N(M107),500)*1E+10+MIN(ROUND(N(F107),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G107="",O107="Aprovado",O107="Recusado",O107="Sem retorno"),0,IF(O107="Parado",2,1)*1E+15+MIN(N(M107),500)*1E+12+MIN(ROUND(N(F107)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -8132,7 +8132,7 @@
         <v/>
       </c>
       <c r="Q108" s="40">
-        <f>IF(OR(G108="",O108="Aprovado",O108="Recusado",O108="Sem retorno"),0,IF(O108="Parado",2,1)*1E+13+MIN(N(M108),500)*1E+10+MIN(ROUND(N(F108),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G108="",O108="Aprovado",O108="Recusado",O108="Sem retorno"),0,IF(O108="Parado",2,1)*1E+15+MIN(N(M108),500)*1E+12+MIN(ROUND(N(F108)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -8172,7 +8172,7 @@
         <v/>
       </c>
       <c r="Q109" s="40">
-        <f>IF(OR(G109="",O109="Aprovado",O109="Recusado",O109="Sem retorno"),0,IF(O109="Parado",2,1)*1E+13+MIN(N(M109),500)*1E+10+MIN(ROUND(N(F109),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G109="",O109="Aprovado",O109="Recusado",O109="Sem retorno"),0,IF(O109="Parado",2,1)*1E+15+MIN(N(M109),500)*1E+12+MIN(ROUND(N(F109)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -8212,7 +8212,7 @@
         <v/>
       </c>
       <c r="Q110" s="40">
-        <f>IF(OR(G110="",O110="Aprovado",O110="Recusado",O110="Sem retorno"),0,IF(O110="Parado",2,1)*1E+13+MIN(N(M110),500)*1E+10+MIN(ROUND(N(F110),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G110="",O110="Aprovado",O110="Recusado",O110="Sem retorno"),0,IF(O110="Parado",2,1)*1E+15+MIN(N(M110),500)*1E+12+MIN(ROUND(N(F110)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -8252,7 +8252,7 @@
         <v/>
       </c>
       <c r="Q111" s="40">
-        <f>IF(OR(G111="",O111="Aprovado",O111="Recusado",O111="Sem retorno"),0,IF(O111="Parado",2,1)*1E+13+MIN(N(M111),500)*1E+10+MIN(ROUND(N(F111),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G111="",O111="Aprovado",O111="Recusado",O111="Sem retorno"),0,IF(O111="Parado",2,1)*1E+15+MIN(N(M111),500)*1E+12+MIN(ROUND(N(F111)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -8292,7 +8292,7 @@
         <v/>
       </c>
       <c r="Q112" s="40">
-        <f>IF(OR(G112="",O112="Aprovado",O112="Recusado",O112="Sem retorno"),0,IF(O112="Parado",2,1)*1E+13+MIN(N(M112),500)*1E+10+MIN(ROUND(N(F112),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G112="",O112="Aprovado",O112="Recusado",O112="Sem retorno"),0,IF(O112="Parado",2,1)*1E+15+MIN(N(M112),500)*1E+12+MIN(ROUND(N(F112)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -8332,7 +8332,7 @@
         <v/>
       </c>
       <c r="Q113" s="40">
-        <f>IF(OR(G113="",O113="Aprovado",O113="Recusado",O113="Sem retorno"),0,IF(O113="Parado",2,1)*1E+13+MIN(N(M113),500)*1E+10+MIN(ROUND(N(F113),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G113="",O113="Aprovado",O113="Recusado",O113="Sem retorno"),0,IF(O113="Parado",2,1)*1E+15+MIN(N(M113),500)*1E+12+MIN(ROUND(N(F113)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -8372,7 +8372,7 @@
         <v/>
       </c>
       <c r="Q114" s="40">
-        <f>IF(OR(G114="",O114="Aprovado",O114="Recusado",O114="Sem retorno"),0,IF(O114="Parado",2,1)*1E+13+MIN(N(M114),500)*1E+10+MIN(ROUND(N(F114),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G114="",O114="Aprovado",O114="Recusado",O114="Sem retorno"),0,IF(O114="Parado",2,1)*1E+15+MIN(N(M114),500)*1E+12+MIN(ROUND(N(F114)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -8412,7 +8412,7 @@
         <v/>
       </c>
       <c r="Q115" s="40">
-        <f>IF(OR(G115="",O115="Aprovado",O115="Recusado",O115="Sem retorno"),0,IF(O115="Parado",2,1)*1E+13+MIN(N(M115),500)*1E+10+MIN(ROUND(N(F115),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G115="",O115="Aprovado",O115="Recusado",O115="Sem retorno"),0,IF(O115="Parado",2,1)*1E+15+MIN(N(M115),500)*1E+12+MIN(ROUND(N(F115)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -8452,7 +8452,7 @@
         <v/>
       </c>
       <c r="Q116" s="40">
-        <f>IF(OR(G116="",O116="Aprovado",O116="Recusado",O116="Sem retorno"),0,IF(O116="Parado",2,1)*1E+13+MIN(N(M116),500)*1E+10+MIN(ROUND(N(F116),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G116="",O116="Aprovado",O116="Recusado",O116="Sem retorno"),0,IF(O116="Parado",2,1)*1E+15+MIN(N(M116),500)*1E+12+MIN(ROUND(N(F116)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -8492,7 +8492,7 @@
         <v/>
       </c>
       <c r="Q117" s="40">
-        <f>IF(OR(G117="",O117="Aprovado",O117="Recusado",O117="Sem retorno"),0,IF(O117="Parado",2,1)*1E+13+MIN(N(M117),500)*1E+10+MIN(ROUND(N(F117),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G117="",O117="Aprovado",O117="Recusado",O117="Sem retorno"),0,IF(O117="Parado",2,1)*1E+15+MIN(N(M117),500)*1E+12+MIN(ROUND(N(F117)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -8532,7 +8532,7 @@
         <v/>
       </c>
       <c r="Q118" s="40">
-        <f>IF(OR(G118="",O118="Aprovado",O118="Recusado",O118="Sem retorno"),0,IF(O118="Parado",2,1)*1E+13+MIN(N(M118),500)*1E+10+MIN(ROUND(N(F118),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G118="",O118="Aprovado",O118="Recusado",O118="Sem retorno"),0,IF(O118="Parado",2,1)*1E+15+MIN(N(M118),500)*1E+12+MIN(ROUND(N(F118)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -8572,7 +8572,7 @@
         <v/>
       </c>
       <c r="Q119" s="40">
-        <f>IF(OR(G119="",O119="Aprovado",O119="Recusado",O119="Sem retorno"),0,IF(O119="Parado",2,1)*1E+13+MIN(N(M119),500)*1E+10+MIN(ROUND(N(F119),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G119="",O119="Aprovado",O119="Recusado",O119="Sem retorno"),0,IF(O119="Parado",2,1)*1E+15+MIN(N(M119),500)*1E+12+MIN(ROUND(N(F119)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -8612,7 +8612,7 @@
         <v/>
       </c>
       <c r="Q120" s="40">
-        <f>IF(OR(G120="",O120="Aprovado",O120="Recusado",O120="Sem retorno"),0,IF(O120="Parado",2,1)*1E+13+MIN(N(M120),500)*1E+10+MIN(ROUND(N(F120),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G120="",O120="Aprovado",O120="Recusado",O120="Sem retorno"),0,IF(O120="Parado",2,1)*1E+15+MIN(N(M120),500)*1E+12+MIN(ROUND(N(F120)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -8652,7 +8652,7 @@
         <v/>
       </c>
       <c r="Q121" s="40">
-        <f>IF(OR(G121="",O121="Aprovado",O121="Recusado",O121="Sem retorno"),0,IF(O121="Parado",2,1)*1E+13+MIN(N(M121),500)*1E+10+MIN(ROUND(N(F121),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G121="",O121="Aprovado",O121="Recusado",O121="Sem retorno"),0,IF(O121="Parado",2,1)*1E+15+MIN(N(M121),500)*1E+12+MIN(ROUND(N(F121)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -8692,7 +8692,7 @@
         <v/>
       </c>
       <c r="Q122" s="40">
-        <f>IF(OR(G122="",O122="Aprovado",O122="Recusado",O122="Sem retorno"),0,IF(O122="Parado",2,1)*1E+13+MIN(N(M122),500)*1E+10+MIN(ROUND(N(F122),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G122="",O122="Aprovado",O122="Recusado",O122="Sem retorno"),0,IF(O122="Parado",2,1)*1E+15+MIN(N(M122),500)*1E+12+MIN(ROUND(N(F122)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -8732,7 +8732,7 @@
         <v/>
       </c>
       <c r="Q123" s="40">
-        <f>IF(OR(G123="",O123="Aprovado",O123="Recusado",O123="Sem retorno"),0,IF(O123="Parado",2,1)*1E+13+MIN(N(M123),500)*1E+10+MIN(ROUND(N(F123),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G123="",O123="Aprovado",O123="Recusado",O123="Sem retorno"),0,IF(O123="Parado",2,1)*1E+15+MIN(N(M123),500)*1E+12+MIN(ROUND(N(F123)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -8772,7 +8772,7 @@
         <v/>
       </c>
       <c r="Q124" s="40">
-        <f>IF(OR(G124="",O124="Aprovado",O124="Recusado",O124="Sem retorno"),0,IF(O124="Parado",2,1)*1E+13+MIN(N(M124),500)*1E+10+MIN(ROUND(N(F124),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G124="",O124="Aprovado",O124="Recusado",O124="Sem retorno"),0,IF(O124="Parado",2,1)*1E+15+MIN(N(M124),500)*1E+12+MIN(ROUND(N(F124)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -8812,7 +8812,7 @@
         <v/>
       </c>
       <c r="Q125" s="40">
-        <f>IF(OR(G125="",O125="Aprovado",O125="Recusado",O125="Sem retorno"),0,IF(O125="Parado",2,1)*1E+13+MIN(N(M125),500)*1E+10+MIN(ROUND(N(F125),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G125="",O125="Aprovado",O125="Recusado",O125="Sem retorno"),0,IF(O125="Parado",2,1)*1E+15+MIN(N(M125),500)*1E+12+MIN(ROUND(N(F125)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -8852,7 +8852,7 @@
         <v/>
       </c>
       <c r="Q126" s="40">
-        <f>IF(OR(G126="",O126="Aprovado",O126="Recusado",O126="Sem retorno"),0,IF(O126="Parado",2,1)*1E+13+MIN(N(M126),500)*1E+10+MIN(ROUND(N(F126),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G126="",O126="Aprovado",O126="Recusado",O126="Sem retorno"),0,IF(O126="Parado",2,1)*1E+15+MIN(N(M126),500)*1E+12+MIN(ROUND(N(F126)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -8892,7 +8892,7 @@
         <v/>
       </c>
       <c r="Q127" s="40">
-        <f>IF(OR(G127="",O127="Aprovado",O127="Recusado",O127="Sem retorno"),0,IF(O127="Parado",2,1)*1E+13+MIN(N(M127),500)*1E+10+MIN(ROUND(N(F127),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G127="",O127="Aprovado",O127="Recusado",O127="Sem retorno"),0,IF(O127="Parado",2,1)*1E+15+MIN(N(M127),500)*1E+12+MIN(ROUND(N(F127)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -8932,7 +8932,7 @@
         <v/>
       </c>
       <c r="Q128" s="40">
-        <f>IF(OR(G128="",O128="Aprovado",O128="Recusado",O128="Sem retorno"),0,IF(O128="Parado",2,1)*1E+13+MIN(N(M128),500)*1E+10+MIN(ROUND(N(F128),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G128="",O128="Aprovado",O128="Recusado",O128="Sem retorno"),0,IF(O128="Parado",2,1)*1E+15+MIN(N(M128),500)*1E+12+MIN(ROUND(N(F128)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -8972,7 +8972,7 @@
         <v/>
       </c>
       <c r="Q129" s="40">
-        <f>IF(OR(G129="",O129="Aprovado",O129="Recusado",O129="Sem retorno"),0,IF(O129="Parado",2,1)*1E+13+MIN(N(M129),500)*1E+10+MIN(ROUND(N(F129),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G129="",O129="Aprovado",O129="Recusado",O129="Sem retorno"),0,IF(O129="Parado",2,1)*1E+15+MIN(N(M129),500)*1E+12+MIN(ROUND(N(F129)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -9012,7 +9012,7 @@
         <v/>
       </c>
       <c r="Q130" s="40">
-        <f>IF(OR(G130="",O130="Aprovado",O130="Recusado",O130="Sem retorno"),0,IF(O130="Parado",2,1)*1E+13+MIN(N(M130),500)*1E+10+MIN(ROUND(N(F130),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G130="",O130="Aprovado",O130="Recusado",O130="Sem retorno"),0,IF(O130="Parado",2,1)*1E+15+MIN(N(M130),500)*1E+12+MIN(ROUND(N(F130)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -9052,7 +9052,7 @@
         <v/>
       </c>
       <c r="Q131" s="40">
-        <f>IF(OR(G131="",O131="Aprovado",O131="Recusado",O131="Sem retorno"),0,IF(O131="Parado",2,1)*1E+13+MIN(N(M131),500)*1E+10+MIN(ROUND(N(F131),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G131="",O131="Aprovado",O131="Recusado",O131="Sem retorno"),0,IF(O131="Parado",2,1)*1E+15+MIN(N(M131),500)*1E+12+MIN(ROUND(N(F131)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -9092,7 +9092,7 @@
         <v/>
       </c>
       <c r="Q132" s="40">
-        <f>IF(OR(G132="",O132="Aprovado",O132="Recusado",O132="Sem retorno"),0,IF(O132="Parado",2,1)*1E+13+MIN(N(M132),500)*1E+10+MIN(ROUND(N(F132),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G132="",O132="Aprovado",O132="Recusado",O132="Sem retorno"),0,IF(O132="Parado",2,1)*1E+15+MIN(N(M132),500)*1E+12+MIN(ROUND(N(F132)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -9132,7 +9132,7 @@
         <v/>
       </c>
       <c r="Q133" s="40">
-        <f>IF(OR(G133="",O133="Aprovado",O133="Recusado",O133="Sem retorno"),0,IF(O133="Parado",2,1)*1E+13+MIN(N(M133),500)*1E+10+MIN(ROUND(N(F133),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G133="",O133="Aprovado",O133="Recusado",O133="Sem retorno"),0,IF(O133="Parado",2,1)*1E+15+MIN(N(M133),500)*1E+12+MIN(ROUND(N(F133)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -9172,7 +9172,7 @@
         <v/>
       </c>
       <c r="Q134" s="40">
-        <f>IF(OR(G134="",O134="Aprovado",O134="Recusado",O134="Sem retorno"),0,IF(O134="Parado",2,1)*1E+13+MIN(N(M134),500)*1E+10+MIN(ROUND(N(F134),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G134="",O134="Aprovado",O134="Recusado",O134="Sem retorno"),0,IF(O134="Parado",2,1)*1E+15+MIN(N(M134),500)*1E+12+MIN(ROUND(N(F134)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -9212,7 +9212,7 @@
         <v/>
       </c>
       <c r="Q135" s="40">
-        <f>IF(OR(G135="",O135="Aprovado",O135="Recusado",O135="Sem retorno"),0,IF(O135="Parado",2,1)*1E+13+MIN(N(M135),500)*1E+10+MIN(ROUND(N(F135),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G135="",O135="Aprovado",O135="Recusado",O135="Sem retorno"),0,IF(O135="Parado",2,1)*1E+15+MIN(N(M135),500)*1E+12+MIN(ROUND(N(F135)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -9252,7 +9252,7 @@
         <v/>
       </c>
       <c r="Q136" s="40">
-        <f>IF(OR(G136="",O136="Aprovado",O136="Recusado",O136="Sem retorno"),0,IF(O136="Parado",2,1)*1E+13+MIN(N(M136),500)*1E+10+MIN(ROUND(N(F136),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G136="",O136="Aprovado",O136="Recusado",O136="Sem retorno"),0,IF(O136="Parado",2,1)*1E+15+MIN(N(M136),500)*1E+12+MIN(ROUND(N(F136)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -9292,7 +9292,7 @@
         <v/>
       </c>
       <c r="Q137" s="40">
-        <f>IF(OR(G137="",O137="Aprovado",O137="Recusado",O137="Sem retorno"),0,IF(O137="Parado",2,1)*1E+13+MIN(N(M137),500)*1E+10+MIN(ROUND(N(F137),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G137="",O137="Aprovado",O137="Recusado",O137="Sem retorno"),0,IF(O137="Parado",2,1)*1E+15+MIN(N(M137),500)*1E+12+MIN(ROUND(N(F137)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -9332,7 +9332,7 @@
         <v/>
       </c>
       <c r="Q138" s="40">
-        <f>IF(OR(G138="",O138="Aprovado",O138="Recusado",O138="Sem retorno"),0,IF(O138="Parado",2,1)*1E+13+MIN(N(M138),500)*1E+10+MIN(ROUND(N(F138),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G138="",O138="Aprovado",O138="Recusado",O138="Sem retorno"),0,IF(O138="Parado",2,1)*1E+15+MIN(N(M138),500)*1E+12+MIN(ROUND(N(F138)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -9372,7 +9372,7 @@
         <v/>
       </c>
       <c r="Q139" s="40">
-        <f>IF(OR(G139="",O139="Aprovado",O139="Recusado",O139="Sem retorno"),0,IF(O139="Parado",2,1)*1E+13+MIN(N(M139),500)*1E+10+MIN(ROUND(N(F139),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G139="",O139="Aprovado",O139="Recusado",O139="Sem retorno"),0,IF(O139="Parado",2,1)*1E+15+MIN(N(M139),500)*1E+12+MIN(ROUND(N(F139)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -9412,7 +9412,7 @@
         <v/>
       </c>
       <c r="Q140" s="40">
-        <f>IF(OR(G140="",O140="Aprovado",O140="Recusado",O140="Sem retorno"),0,IF(O140="Parado",2,1)*1E+13+MIN(N(M140),500)*1E+10+MIN(ROUND(N(F140),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G140="",O140="Aprovado",O140="Recusado",O140="Sem retorno"),0,IF(O140="Parado",2,1)*1E+15+MIN(N(M140),500)*1E+12+MIN(ROUND(N(F140)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -9452,7 +9452,7 @@
         <v/>
       </c>
       <c r="Q141" s="40">
-        <f>IF(OR(G141="",O141="Aprovado",O141="Recusado",O141="Sem retorno"),0,IF(O141="Parado",2,1)*1E+13+MIN(N(M141),500)*1E+10+MIN(ROUND(N(F141),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G141="",O141="Aprovado",O141="Recusado",O141="Sem retorno"),0,IF(O141="Parado",2,1)*1E+15+MIN(N(M141),500)*1E+12+MIN(ROUND(N(F141)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -9492,7 +9492,7 @@
         <v/>
       </c>
       <c r="Q142" s="40">
-        <f>IF(OR(G142="",O142="Aprovado",O142="Recusado",O142="Sem retorno"),0,IF(O142="Parado",2,1)*1E+13+MIN(N(M142),500)*1E+10+MIN(ROUND(N(F142),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G142="",O142="Aprovado",O142="Recusado",O142="Sem retorno"),0,IF(O142="Parado",2,1)*1E+15+MIN(N(M142),500)*1E+12+MIN(ROUND(N(F142)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -9532,7 +9532,7 @@
         <v/>
       </c>
       <c r="Q143" s="40">
-        <f>IF(OR(G143="",O143="Aprovado",O143="Recusado",O143="Sem retorno"),0,IF(O143="Parado",2,1)*1E+13+MIN(N(M143),500)*1E+10+MIN(ROUND(N(F143),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G143="",O143="Aprovado",O143="Recusado",O143="Sem retorno"),0,IF(O143="Parado",2,1)*1E+15+MIN(N(M143),500)*1E+12+MIN(ROUND(N(F143)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -9572,7 +9572,7 @@
         <v/>
       </c>
       <c r="Q144" s="40">
-        <f>IF(OR(G144="",O144="Aprovado",O144="Recusado",O144="Sem retorno"),0,IF(O144="Parado",2,1)*1E+13+MIN(N(M144),500)*1E+10+MIN(ROUND(N(F144),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G144="",O144="Aprovado",O144="Recusado",O144="Sem retorno"),0,IF(O144="Parado",2,1)*1E+15+MIN(N(M144),500)*1E+12+MIN(ROUND(N(F144)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -9612,7 +9612,7 @@
         <v/>
       </c>
       <c r="Q145" s="40">
-        <f>IF(OR(G145="",O145="Aprovado",O145="Recusado",O145="Sem retorno"),0,IF(O145="Parado",2,1)*1E+13+MIN(N(M145),500)*1E+10+MIN(ROUND(N(F145),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G145="",O145="Aprovado",O145="Recusado",O145="Sem retorno"),0,IF(O145="Parado",2,1)*1E+15+MIN(N(M145),500)*1E+12+MIN(ROUND(N(F145)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -9652,7 +9652,7 @@
         <v/>
       </c>
       <c r="Q146" s="40">
-        <f>IF(OR(G146="",O146="Aprovado",O146="Recusado",O146="Sem retorno"),0,IF(O146="Parado",2,1)*1E+13+MIN(N(M146),500)*1E+10+MIN(ROUND(N(F146),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G146="",O146="Aprovado",O146="Recusado",O146="Sem retorno"),0,IF(O146="Parado",2,1)*1E+15+MIN(N(M146),500)*1E+12+MIN(ROUND(N(F146)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -9692,7 +9692,7 @@
         <v/>
       </c>
       <c r="Q147" s="40">
-        <f>IF(OR(G147="",O147="Aprovado",O147="Recusado",O147="Sem retorno"),0,IF(O147="Parado",2,1)*1E+13+MIN(N(M147),500)*1E+10+MIN(ROUND(N(F147),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G147="",O147="Aprovado",O147="Recusado",O147="Sem retorno"),0,IF(O147="Parado",2,1)*1E+15+MIN(N(M147),500)*1E+12+MIN(ROUND(N(F147)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -9732,7 +9732,7 @@
         <v/>
       </c>
       <c r="Q148" s="40">
-        <f>IF(OR(G148="",O148="Aprovado",O148="Recusado",O148="Sem retorno"),0,IF(O148="Parado",2,1)*1E+13+MIN(N(M148),500)*1E+10+MIN(ROUND(N(F148),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G148="",O148="Aprovado",O148="Recusado",O148="Sem retorno"),0,IF(O148="Parado",2,1)*1E+15+MIN(N(M148),500)*1E+12+MIN(ROUND(N(F148)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -9772,7 +9772,7 @@
         <v/>
       </c>
       <c r="Q149" s="40">
-        <f>IF(OR(G149="",O149="Aprovado",O149="Recusado",O149="Sem retorno"),0,IF(O149="Parado",2,1)*1E+13+MIN(N(M149),500)*1E+10+MIN(ROUND(N(F149),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G149="",O149="Aprovado",O149="Recusado",O149="Sem retorno"),0,IF(O149="Parado",2,1)*1E+15+MIN(N(M149),500)*1E+12+MIN(ROUND(N(F149)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -9812,7 +9812,7 @@
         <v/>
       </c>
       <c r="Q150" s="40">
-        <f>IF(OR(G150="",O150="Aprovado",O150="Recusado",O150="Sem retorno"),0,IF(O150="Parado",2,1)*1E+13+MIN(N(M150),500)*1E+10+MIN(ROUND(N(F150),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G150="",O150="Aprovado",O150="Recusado",O150="Sem retorno"),0,IF(O150="Parado",2,1)*1E+15+MIN(N(M150),500)*1E+12+MIN(ROUND(N(F150)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -9852,7 +9852,7 @@
         <v/>
       </c>
       <c r="Q151" s="40">
-        <f>IF(OR(G151="",O151="Aprovado",O151="Recusado",O151="Sem retorno"),0,IF(O151="Parado",2,1)*1E+13+MIN(N(M151),500)*1E+10+MIN(ROUND(N(F151),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G151="",O151="Aprovado",O151="Recusado",O151="Sem retorno"),0,IF(O151="Parado",2,1)*1E+15+MIN(N(M151),500)*1E+12+MIN(ROUND(N(F151)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -9892,7 +9892,7 @@
         <v/>
       </c>
       <c r="Q152" s="40">
-        <f>IF(OR(G152="",O152="Aprovado",O152="Recusado",O152="Sem retorno"),0,IF(O152="Parado",2,1)*1E+13+MIN(N(M152),500)*1E+10+MIN(ROUND(N(F152),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G152="",O152="Aprovado",O152="Recusado",O152="Sem retorno"),0,IF(O152="Parado",2,1)*1E+15+MIN(N(M152),500)*1E+12+MIN(ROUND(N(F152)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -9932,7 +9932,7 @@
         <v/>
       </c>
       <c r="Q153" s="40">
-        <f>IF(OR(G153="",O153="Aprovado",O153="Recusado",O153="Sem retorno"),0,IF(O153="Parado",2,1)*1E+13+MIN(N(M153),500)*1E+10+MIN(ROUND(N(F153),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G153="",O153="Aprovado",O153="Recusado",O153="Sem retorno"),0,IF(O153="Parado",2,1)*1E+15+MIN(N(M153),500)*1E+12+MIN(ROUND(N(F153)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -9972,7 +9972,7 @@
         <v/>
       </c>
       <c r="Q154" s="40">
-        <f>IF(OR(G154="",O154="Aprovado",O154="Recusado",O154="Sem retorno"),0,IF(O154="Parado",2,1)*1E+13+MIN(N(M154),500)*1E+10+MIN(ROUND(N(F154),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G154="",O154="Aprovado",O154="Recusado",O154="Sem retorno"),0,IF(O154="Parado",2,1)*1E+15+MIN(N(M154),500)*1E+12+MIN(ROUND(N(F154)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -10012,7 +10012,7 @@
         <v/>
       </c>
       <c r="Q155" s="40">
-        <f>IF(OR(G155="",O155="Aprovado",O155="Recusado",O155="Sem retorno"),0,IF(O155="Parado",2,1)*1E+13+MIN(N(M155),500)*1E+10+MIN(ROUND(N(F155),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G155="",O155="Aprovado",O155="Recusado",O155="Sem retorno"),0,IF(O155="Parado",2,1)*1E+15+MIN(N(M155),500)*1E+12+MIN(ROUND(N(F155)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -10052,7 +10052,7 @@
         <v/>
       </c>
       <c r="Q156" s="40">
-        <f>IF(OR(G156="",O156="Aprovado",O156="Recusado",O156="Sem retorno"),0,IF(O156="Parado",2,1)*1E+13+MIN(N(M156),500)*1E+10+MIN(ROUND(N(F156),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G156="",O156="Aprovado",O156="Recusado",O156="Sem retorno"),0,IF(O156="Parado",2,1)*1E+15+MIN(N(M156),500)*1E+12+MIN(ROUND(N(F156)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -10092,7 +10092,7 @@
         <v/>
       </c>
       <c r="Q157" s="40">
-        <f>IF(OR(G157="",O157="Aprovado",O157="Recusado",O157="Sem retorno"),0,IF(O157="Parado",2,1)*1E+13+MIN(N(M157),500)*1E+10+MIN(ROUND(N(F157),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G157="",O157="Aprovado",O157="Recusado",O157="Sem retorno"),0,IF(O157="Parado",2,1)*1E+15+MIN(N(M157),500)*1E+12+MIN(ROUND(N(F157)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -10132,7 +10132,7 @@
         <v/>
       </c>
       <c r="Q158" s="40">
-        <f>IF(OR(G158="",O158="Aprovado",O158="Recusado",O158="Sem retorno"),0,IF(O158="Parado",2,1)*1E+13+MIN(N(M158),500)*1E+10+MIN(ROUND(N(F158),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G158="",O158="Aprovado",O158="Recusado",O158="Sem retorno"),0,IF(O158="Parado",2,1)*1E+15+MIN(N(M158),500)*1E+12+MIN(ROUND(N(F158)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -10172,7 +10172,7 @@
         <v/>
       </c>
       <c r="Q159" s="40">
-        <f>IF(OR(G159="",O159="Aprovado",O159="Recusado",O159="Sem retorno"),0,IF(O159="Parado",2,1)*1E+13+MIN(N(M159),500)*1E+10+MIN(ROUND(N(F159),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G159="",O159="Aprovado",O159="Recusado",O159="Sem retorno"),0,IF(O159="Parado",2,1)*1E+15+MIN(N(M159),500)*1E+12+MIN(ROUND(N(F159)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -10212,7 +10212,7 @@
         <v/>
       </c>
       <c r="Q160" s="40">
-        <f>IF(OR(G160="",O160="Aprovado",O160="Recusado",O160="Sem retorno"),0,IF(O160="Parado",2,1)*1E+13+MIN(N(M160),500)*1E+10+MIN(ROUND(N(F160),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G160="",O160="Aprovado",O160="Recusado",O160="Sem retorno"),0,IF(O160="Parado",2,1)*1E+15+MIN(N(M160),500)*1E+12+MIN(ROUND(N(F160)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -10252,7 +10252,7 @@
         <v/>
       </c>
       <c r="Q161" s="40">
-        <f>IF(OR(G161="",O161="Aprovado",O161="Recusado",O161="Sem retorno"),0,IF(O161="Parado",2,1)*1E+13+MIN(N(M161),500)*1E+10+MIN(ROUND(N(F161),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G161="",O161="Aprovado",O161="Recusado",O161="Sem retorno"),0,IF(O161="Parado",2,1)*1E+15+MIN(N(M161),500)*1E+12+MIN(ROUND(N(F161)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -10292,7 +10292,7 @@
         <v/>
       </c>
       <c r="Q162" s="40">
-        <f>IF(OR(G162="",O162="Aprovado",O162="Recusado",O162="Sem retorno"),0,IF(O162="Parado",2,1)*1E+13+MIN(N(M162),500)*1E+10+MIN(ROUND(N(F162),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G162="",O162="Aprovado",O162="Recusado",O162="Sem retorno"),0,IF(O162="Parado",2,1)*1E+15+MIN(N(M162),500)*1E+12+MIN(ROUND(N(F162)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -10332,7 +10332,7 @@
         <v/>
       </c>
       <c r="Q163" s="40">
-        <f>IF(OR(G163="",O163="Aprovado",O163="Recusado",O163="Sem retorno"),0,IF(O163="Parado",2,1)*1E+13+MIN(N(M163),500)*1E+10+MIN(ROUND(N(F163),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G163="",O163="Aprovado",O163="Recusado",O163="Sem retorno"),0,IF(O163="Parado",2,1)*1E+15+MIN(N(M163),500)*1E+12+MIN(ROUND(N(F163)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -10372,7 +10372,7 @@
         <v/>
       </c>
       <c r="Q164" s="40">
-        <f>IF(OR(G164="",O164="Aprovado",O164="Recusado",O164="Sem retorno"),0,IF(O164="Parado",2,1)*1E+13+MIN(N(M164),500)*1E+10+MIN(ROUND(N(F164),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G164="",O164="Aprovado",O164="Recusado",O164="Sem retorno"),0,IF(O164="Parado",2,1)*1E+15+MIN(N(M164),500)*1E+12+MIN(ROUND(N(F164)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -10412,7 +10412,7 @@
         <v/>
       </c>
       <c r="Q165" s="40">
-        <f>IF(OR(G165="",O165="Aprovado",O165="Recusado",O165="Sem retorno"),0,IF(O165="Parado",2,1)*1E+13+MIN(N(M165),500)*1E+10+MIN(ROUND(N(F165),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G165="",O165="Aprovado",O165="Recusado",O165="Sem retorno"),0,IF(O165="Parado",2,1)*1E+15+MIN(N(M165),500)*1E+12+MIN(ROUND(N(F165)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -10452,7 +10452,7 @@
         <v/>
       </c>
       <c r="Q166" s="40">
-        <f>IF(OR(G166="",O166="Aprovado",O166="Recusado",O166="Sem retorno"),0,IF(O166="Parado",2,1)*1E+13+MIN(N(M166),500)*1E+10+MIN(ROUND(N(F166),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G166="",O166="Aprovado",O166="Recusado",O166="Sem retorno"),0,IF(O166="Parado",2,1)*1E+15+MIN(N(M166),500)*1E+12+MIN(ROUND(N(F166)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -10492,7 +10492,7 @@
         <v/>
       </c>
       <c r="Q167" s="40">
-        <f>IF(OR(G167="",O167="Aprovado",O167="Recusado",O167="Sem retorno"),0,IF(O167="Parado",2,1)*1E+13+MIN(N(M167),500)*1E+10+MIN(ROUND(N(F167),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G167="",O167="Aprovado",O167="Recusado",O167="Sem retorno"),0,IF(O167="Parado",2,1)*1E+15+MIN(N(M167),500)*1E+12+MIN(ROUND(N(F167)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -10532,7 +10532,7 @@
         <v/>
       </c>
       <c r="Q168" s="40">
-        <f>IF(OR(G168="",O168="Aprovado",O168="Recusado",O168="Sem retorno"),0,IF(O168="Parado",2,1)*1E+13+MIN(N(M168),500)*1E+10+MIN(ROUND(N(F168),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G168="",O168="Aprovado",O168="Recusado",O168="Sem retorno"),0,IF(O168="Parado",2,1)*1E+15+MIN(N(M168),500)*1E+12+MIN(ROUND(N(F168)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -10572,7 +10572,7 @@
         <v/>
       </c>
       <c r="Q169" s="40">
-        <f>IF(OR(G169="",O169="Aprovado",O169="Recusado",O169="Sem retorno"),0,IF(O169="Parado",2,1)*1E+13+MIN(N(M169),500)*1E+10+MIN(ROUND(N(F169),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G169="",O169="Aprovado",O169="Recusado",O169="Sem retorno"),0,IF(O169="Parado",2,1)*1E+15+MIN(N(M169),500)*1E+12+MIN(ROUND(N(F169)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -10612,7 +10612,7 @@
         <v/>
       </c>
       <c r="Q170" s="40">
-        <f>IF(OR(G170="",O170="Aprovado",O170="Recusado",O170="Sem retorno"),0,IF(O170="Parado",2,1)*1E+13+MIN(N(M170),500)*1E+10+MIN(ROUND(N(F170),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G170="",O170="Aprovado",O170="Recusado",O170="Sem retorno"),0,IF(O170="Parado",2,1)*1E+15+MIN(N(M170),500)*1E+12+MIN(ROUND(N(F170)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -10652,7 +10652,7 @@
         <v/>
       </c>
       <c r="Q171" s="40">
-        <f>IF(OR(G171="",O171="Aprovado",O171="Recusado",O171="Sem retorno"),0,IF(O171="Parado",2,1)*1E+13+MIN(N(M171),500)*1E+10+MIN(ROUND(N(F171),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G171="",O171="Aprovado",O171="Recusado",O171="Sem retorno"),0,IF(O171="Parado",2,1)*1E+15+MIN(N(M171),500)*1E+12+MIN(ROUND(N(F171)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -10692,7 +10692,7 @@
         <v/>
       </c>
       <c r="Q172" s="40">
-        <f>IF(OR(G172="",O172="Aprovado",O172="Recusado",O172="Sem retorno"),0,IF(O172="Parado",2,1)*1E+13+MIN(N(M172),500)*1E+10+MIN(ROUND(N(F172),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G172="",O172="Aprovado",O172="Recusado",O172="Sem retorno"),0,IF(O172="Parado",2,1)*1E+15+MIN(N(M172),500)*1E+12+MIN(ROUND(N(F172)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -10732,7 +10732,7 @@
         <v/>
       </c>
       <c r="Q173" s="40">
-        <f>IF(OR(G173="",O173="Aprovado",O173="Recusado",O173="Sem retorno"),0,IF(O173="Parado",2,1)*1E+13+MIN(N(M173),500)*1E+10+MIN(ROUND(N(F173),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G173="",O173="Aprovado",O173="Recusado",O173="Sem retorno"),0,IF(O173="Parado",2,1)*1E+15+MIN(N(M173),500)*1E+12+MIN(ROUND(N(F173)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -10772,7 +10772,7 @@
         <v/>
       </c>
       <c r="Q174" s="40">
-        <f>IF(OR(G174="",O174="Aprovado",O174="Recusado",O174="Sem retorno"),0,IF(O174="Parado",2,1)*1E+13+MIN(N(M174),500)*1E+10+MIN(ROUND(N(F174),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G174="",O174="Aprovado",O174="Recusado",O174="Sem retorno"),0,IF(O174="Parado",2,1)*1E+15+MIN(N(M174),500)*1E+12+MIN(ROUND(N(F174)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -10812,7 +10812,7 @@
         <v/>
       </c>
       <c r="Q175" s="40">
-        <f>IF(OR(G175="",O175="Aprovado",O175="Recusado",O175="Sem retorno"),0,IF(O175="Parado",2,1)*1E+13+MIN(N(M175),500)*1E+10+MIN(ROUND(N(F175),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G175="",O175="Aprovado",O175="Recusado",O175="Sem retorno"),0,IF(O175="Parado",2,1)*1E+15+MIN(N(M175),500)*1E+12+MIN(ROUND(N(F175)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -10852,7 +10852,7 @@
         <v/>
       </c>
       <c r="Q176" s="40">
-        <f>IF(OR(G176="",O176="Aprovado",O176="Recusado",O176="Sem retorno"),0,IF(O176="Parado",2,1)*1E+13+MIN(N(M176),500)*1E+10+MIN(ROUND(N(F176),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G176="",O176="Aprovado",O176="Recusado",O176="Sem retorno"),0,IF(O176="Parado",2,1)*1E+15+MIN(N(M176),500)*1E+12+MIN(ROUND(N(F176)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -10892,7 +10892,7 @@
         <v/>
       </c>
       <c r="Q177" s="40">
-        <f>IF(OR(G177="",O177="Aprovado",O177="Recusado",O177="Sem retorno"),0,IF(O177="Parado",2,1)*1E+13+MIN(N(M177),500)*1E+10+MIN(ROUND(N(F177),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G177="",O177="Aprovado",O177="Recusado",O177="Sem retorno"),0,IF(O177="Parado",2,1)*1E+15+MIN(N(M177),500)*1E+12+MIN(ROUND(N(F177)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -10932,7 +10932,7 @@
         <v/>
       </c>
       <c r="Q178" s="40">
-        <f>IF(OR(G178="",O178="Aprovado",O178="Recusado",O178="Sem retorno"),0,IF(O178="Parado",2,1)*1E+13+MIN(N(M178),500)*1E+10+MIN(ROUND(N(F178),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G178="",O178="Aprovado",O178="Recusado",O178="Sem retorno"),0,IF(O178="Parado",2,1)*1E+15+MIN(N(M178),500)*1E+12+MIN(ROUND(N(F178)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -10972,7 +10972,7 @@
         <v/>
       </c>
       <c r="Q179" s="40">
-        <f>IF(OR(G179="",O179="Aprovado",O179="Recusado",O179="Sem retorno"),0,IF(O179="Parado",2,1)*1E+13+MIN(N(M179),500)*1E+10+MIN(ROUND(N(F179),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G179="",O179="Aprovado",O179="Recusado",O179="Sem retorno"),0,IF(O179="Parado",2,1)*1E+15+MIN(N(M179),500)*1E+12+MIN(ROUND(N(F179)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -11012,7 +11012,7 @@
         <v/>
       </c>
       <c r="Q180" s="40">
-        <f>IF(OR(G180="",O180="Aprovado",O180="Recusado",O180="Sem retorno"),0,IF(O180="Parado",2,1)*1E+13+MIN(N(M180),500)*1E+10+MIN(ROUND(N(F180),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G180="",O180="Aprovado",O180="Recusado",O180="Sem retorno"),0,IF(O180="Parado",2,1)*1E+15+MIN(N(M180),500)*1E+12+MIN(ROUND(N(F180)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -11052,7 +11052,7 @@
         <v/>
       </c>
       <c r="Q181" s="40">
-        <f>IF(OR(G181="",O181="Aprovado",O181="Recusado",O181="Sem retorno"),0,IF(O181="Parado",2,1)*1E+13+MIN(N(M181),500)*1E+10+MIN(ROUND(N(F181),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G181="",O181="Aprovado",O181="Recusado",O181="Sem retorno"),0,IF(O181="Parado",2,1)*1E+15+MIN(N(M181),500)*1E+12+MIN(ROUND(N(F181)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -11092,7 +11092,7 @@
         <v/>
       </c>
       <c r="Q182" s="40">
-        <f>IF(OR(G182="",O182="Aprovado",O182="Recusado",O182="Sem retorno"),0,IF(O182="Parado",2,1)*1E+13+MIN(N(M182),500)*1E+10+MIN(ROUND(N(F182),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G182="",O182="Aprovado",O182="Recusado",O182="Sem retorno"),0,IF(O182="Parado",2,1)*1E+15+MIN(N(M182),500)*1E+12+MIN(ROUND(N(F182)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -11132,7 +11132,7 @@
         <v/>
       </c>
       <c r="Q183" s="40">
-        <f>IF(OR(G183="",O183="Aprovado",O183="Recusado",O183="Sem retorno"),0,IF(O183="Parado",2,1)*1E+13+MIN(N(M183),500)*1E+10+MIN(ROUND(N(F183),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G183="",O183="Aprovado",O183="Recusado",O183="Sem retorno"),0,IF(O183="Parado",2,1)*1E+15+MIN(N(M183),500)*1E+12+MIN(ROUND(N(F183)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -11172,7 +11172,7 @@
         <v/>
       </c>
       <c r="Q184" s="40">
-        <f>IF(OR(G184="",O184="Aprovado",O184="Recusado",O184="Sem retorno"),0,IF(O184="Parado",2,1)*1E+13+MIN(N(M184),500)*1E+10+MIN(ROUND(N(F184),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G184="",O184="Aprovado",O184="Recusado",O184="Sem retorno"),0,IF(O184="Parado",2,1)*1E+15+MIN(N(M184),500)*1E+12+MIN(ROUND(N(F184)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -11212,7 +11212,7 @@
         <v/>
       </c>
       <c r="Q185" s="40">
-        <f>IF(OR(G185="",O185="Aprovado",O185="Recusado",O185="Sem retorno"),0,IF(O185="Parado",2,1)*1E+13+MIN(N(M185),500)*1E+10+MIN(ROUND(N(F185),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G185="",O185="Aprovado",O185="Recusado",O185="Sem retorno"),0,IF(O185="Parado",2,1)*1E+15+MIN(N(M185),500)*1E+12+MIN(ROUND(N(F185)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -11252,7 +11252,7 @@
         <v/>
       </c>
       <c r="Q186" s="40">
-        <f>IF(OR(G186="",O186="Aprovado",O186="Recusado",O186="Sem retorno"),0,IF(O186="Parado",2,1)*1E+13+MIN(N(M186),500)*1E+10+MIN(ROUND(N(F186),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G186="",O186="Aprovado",O186="Recusado",O186="Sem retorno"),0,IF(O186="Parado",2,1)*1E+15+MIN(N(M186),500)*1E+12+MIN(ROUND(N(F186)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -11292,7 +11292,7 @@
         <v/>
       </c>
       <c r="Q187" s="40">
-        <f>IF(OR(G187="",O187="Aprovado",O187="Recusado",O187="Sem retorno"),0,IF(O187="Parado",2,1)*1E+13+MIN(N(M187),500)*1E+10+MIN(ROUND(N(F187),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G187="",O187="Aprovado",O187="Recusado",O187="Sem retorno"),0,IF(O187="Parado",2,1)*1E+15+MIN(N(M187),500)*1E+12+MIN(ROUND(N(F187)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -11332,7 +11332,7 @@
         <v/>
       </c>
       <c r="Q188" s="40">
-        <f>IF(OR(G188="",O188="Aprovado",O188="Recusado",O188="Sem retorno"),0,IF(O188="Parado",2,1)*1E+13+MIN(N(M188),500)*1E+10+MIN(ROUND(N(F188),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G188="",O188="Aprovado",O188="Recusado",O188="Sem retorno"),0,IF(O188="Parado",2,1)*1E+15+MIN(N(M188),500)*1E+12+MIN(ROUND(N(F188)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -11372,7 +11372,7 @@
         <v/>
       </c>
       <c r="Q189" s="40">
-        <f>IF(OR(G189="",O189="Aprovado",O189="Recusado",O189="Sem retorno"),0,IF(O189="Parado",2,1)*1E+13+MIN(N(M189),500)*1E+10+MIN(ROUND(N(F189),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G189="",O189="Aprovado",O189="Recusado",O189="Sem retorno"),0,IF(O189="Parado",2,1)*1E+15+MIN(N(M189),500)*1E+12+MIN(ROUND(N(F189)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -11412,7 +11412,7 @@
         <v/>
       </c>
       <c r="Q190" s="40">
-        <f>IF(OR(G190="",O190="Aprovado",O190="Recusado",O190="Sem retorno"),0,IF(O190="Parado",2,1)*1E+13+MIN(N(M190),500)*1E+10+MIN(ROUND(N(F190),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G190="",O190="Aprovado",O190="Recusado",O190="Sem retorno"),0,IF(O190="Parado",2,1)*1E+15+MIN(N(M190),500)*1E+12+MIN(ROUND(N(F190)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -11452,7 +11452,7 @@
         <v/>
       </c>
       <c r="Q191" s="40">
-        <f>IF(OR(G191="",O191="Aprovado",O191="Recusado",O191="Sem retorno"),0,IF(O191="Parado",2,1)*1E+13+MIN(N(M191),500)*1E+10+MIN(ROUND(N(F191),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G191="",O191="Aprovado",O191="Recusado",O191="Sem retorno"),0,IF(O191="Parado",2,1)*1E+15+MIN(N(M191),500)*1E+12+MIN(ROUND(N(F191)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -11492,7 +11492,7 @@
         <v/>
       </c>
       <c r="Q192" s="40">
-        <f>IF(OR(G192="",O192="Aprovado",O192="Recusado",O192="Sem retorno"),0,IF(O192="Parado",2,1)*1E+13+MIN(N(M192),500)*1E+10+MIN(ROUND(N(F192),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G192="",O192="Aprovado",O192="Recusado",O192="Sem retorno"),0,IF(O192="Parado",2,1)*1E+15+MIN(N(M192),500)*1E+12+MIN(ROUND(N(F192)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -11532,7 +11532,7 @@
         <v/>
       </c>
       <c r="Q193" s="40">
-        <f>IF(OR(G193="",O193="Aprovado",O193="Recusado",O193="Sem retorno"),0,IF(O193="Parado",2,1)*1E+13+MIN(N(M193),500)*1E+10+MIN(ROUND(N(F193),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G193="",O193="Aprovado",O193="Recusado",O193="Sem retorno"),0,IF(O193="Parado",2,1)*1E+15+MIN(N(M193),500)*1E+12+MIN(ROUND(N(F193)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -11572,7 +11572,7 @@
         <v/>
       </c>
       <c r="Q194" s="40">
-        <f>IF(OR(G194="",O194="Aprovado",O194="Recusado",O194="Sem retorno"),0,IF(O194="Parado",2,1)*1E+13+MIN(N(M194),500)*1E+10+MIN(ROUND(N(F194),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G194="",O194="Aprovado",O194="Recusado",O194="Sem retorno"),0,IF(O194="Parado",2,1)*1E+15+MIN(N(M194),500)*1E+12+MIN(ROUND(N(F194)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -11612,7 +11612,7 @@
         <v/>
       </c>
       <c r="Q195" s="40">
-        <f>IF(OR(G195="",O195="Aprovado",O195="Recusado",O195="Sem retorno"),0,IF(O195="Parado",2,1)*1E+13+MIN(N(M195),500)*1E+10+MIN(ROUND(N(F195),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G195="",O195="Aprovado",O195="Recusado",O195="Sem retorno"),0,IF(O195="Parado",2,1)*1E+15+MIN(N(M195),500)*1E+12+MIN(ROUND(N(F195)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -11652,7 +11652,7 @@
         <v/>
       </c>
       <c r="Q196" s="40">
-        <f>IF(OR(G196="",O196="Aprovado",O196="Recusado",O196="Sem retorno"),0,IF(O196="Parado",2,1)*1E+13+MIN(N(M196),500)*1E+10+MIN(ROUND(N(F196),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G196="",O196="Aprovado",O196="Recusado",O196="Sem retorno"),0,IF(O196="Parado",2,1)*1E+15+MIN(N(M196),500)*1E+12+MIN(ROUND(N(F196)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -11692,7 +11692,7 @@
         <v/>
       </c>
       <c r="Q197" s="40">
-        <f>IF(OR(G197="",O197="Aprovado",O197="Recusado",O197="Sem retorno"),0,IF(O197="Parado",2,1)*1E+13+MIN(N(M197),500)*1E+10+MIN(ROUND(N(F197),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G197="",O197="Aprovado",O197="Recusado",O197="Sem retorno"),0,IF(O197="Parado",2,1)*1E+15+MIN(N(M197),500)*1E+12+MIN(ROUND(N(F197)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -11732,7 +11732,7 @@
         <v/>
       </c>
       <c r="Q198" s="40">
-        <f>IF(OR(G198="",O198="Aprovado",O198="Recusado",O198="Sem retorno"),0,IF(O198="Parado",2,1)*1E+13+MIN(N(M198),500)*1E+10+MIN(ROUND(N(F198),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G198="",O198="Aprovado",O198="Recusado",O198="Sem retorno"),0,IF(O198="Parado",2,1)*1E+15+MIN(N(M198),500)*1E+12+MIN(ROUND(N(F198)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -11772,7 +11772,7 @@
         <v/>
       </c>
       <c r="Q199" s="40">
-        <f>IF(OR(G199="",O199="Aprovado",O199="Recusado",O199="Sem retorno"),0,IF(O199="Parado",2,1)*1E+13+MIN(N(M199),500)*1E+10+MIN(ROUND(N(F199),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G199="",O199="Aprovado",O199="Recusado",O199="Sem retorno"),0,IF(O199="Parado",2,1)*1E+15+MIN(N(M199),500)*1E+12+MIN(ROUND(N(F199)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -11812,7 +11812,7 @@
         <v/>
       </c>
       <c r="Q200" s="40">
-        <f>IF(OR(G200="",O200="Aprovado",O200="Recusado",O200="Sem retorno"),0,IF(O200="Parado",2,1)*1E+13+MIN(N(M200),500)*1E+10+MIN(ROUND(N(F200),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G200="",O200="Aprovado",O200="Recusado",O200="Sem retorno"),0,IF(O200="Parado",2,1)*1E+15+MIN(N(M200),500)*1E+12+MIN(ROUND(N(F200)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -11852,7 +11852,7 @@
         <v/>
       </c>
       <c r="Q201" s="40">
-        <f>IF(OR(G201="",O201="Aprovado",O201="Recusado",O201="Sem retorno"),0,IF(O201="Parado",2,1)*1E+13+MIN(N(M201),500)*1E+10+MIN(ROUND(N(F201),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G201="",O201="Aprovado",O201="Recusado",O201="Sem retorno"),0,IF(O201="Parado",2,1)*1E+15+MIN(N(M201),500)*1E+12+MIN(ROUND(N(F201)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -11892,7 +11892,7 @@
         <v/>
       </c>
       <c r="Q202" s="40">
-        <f>IF(OR(G202="",O202="Aprovado",O202="Recusado",O202="Sem retorno"),0,IF(O202="Parado",2,1)*1E+13+MIN(N(M202),500)*1E+10+MIN(ROUND(N(F202),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G202="",O202="Aprovado",O202="Recusado",O202="Sem retorno"),0,IF(O202="Parado",2,1)*1E+15+MIN(N(M202),500)*1E+12+MIN(ROUND(N(F202)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -11932,7 +11932,7 @@
         <v/>
       </c>
       <c r="Q203" s="40">
-        <f>IF(OR(G203="",O203="Aprovado",O203="Recusado",O203="Sem retorno"),0,IF(O203="Parado",2,1)*1E+13+MIN(N(M203),500)*1E+10+MIN(ROUND(N(F203),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G203="",O203="Aprovado",O203="Recusado",O203="Sem retorno"),0,IF(O203="Parado",2,1)*1E+15+MIN(N(M203),500)*1E+12+MIN(ROUND(N(F203)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -11972,7 +11972,7 @@
         <v/>
       </c>
       <c r="Q204" s="40">
-        <f>IF(OR(G204="",O204="Aprovado",O204="Recusado",O204="Sem retorno"),0,IF(O204="Parado",2,1)*1E+13+MIN(N(M204),500)*1E+10+MIN(ROUND(N(F204),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G204="",O204="Aprovado",O204="Recusado",O204="Sem retorno"),0,IF(O204="Parado",2,1)*1E+15+MIN(N(M204),500)*1E+12+MIN(ROUND(N(F204)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -12012,7 +12012,7 @@
         <v/>
       </c>
       <c r="Q205" s="40">
-        <f>IF(OR(G205="",O205="Aprovado",O205="Recusado",O205="Sem retorno"),0,IF(O205="Parado",2,1)*1E+13+MIN(N(M205),500)*1E+10+MIN(ROUND(N(F205),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G205="",O205="Aprovado",O205="Recusado",O205="Sem retorno"),0,IF(O205="Parado",2,1)*1E+15+MIN(N(M205),500)*1E+12+MIN(ROUND(N(F205)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -12052,7 +12052,7 @@
         <v/>
       </c>
       <c r="Q206" s="40">
-        <f>IF(OR(G206="",O206="Aprovado",O206="Recusado",O206="Sem retorno"),0,IF(O206="Parado",2,1)*1E+13+MIN(N(M206),500)*1E+10+MIN(ROUND(N(F206),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G206="",O206="Aprovado",O206="Recusado",O206="Sem retorno"),0,IF(O206="Parado",2,1)*1E+15+MIN(N(M206),500)*1E+12+MIN(ROUND(N(F206)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -12092,7 +12092,7 @@
         <v/>
       </c>
       <c r="Q207" s="40">
-        <f>IF(OR(G207="",O207="Aprovado",O207="Recusado",O207="Sem retorno"),0,IF(O207="Parado",2,1)*1E+13+MIN(N(M207),500)*1E+10+MIN(ROUND(N(F207),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G207="",O207="Aprovado",O207="Recusado",O207="Sem retorno"),0,IF(O207="Parado",2,1)*1E+15+MIN(N(M207),500)*1E+12+MIN(ROUND(N(F207)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -12132,7 +12132,7 @@
         <v/>
       </c>
       <c r="Q208" s="40">
-        <f>IF(OR(G208="",O208="Aprovado",O208="Recusado",O208="Sem retorno"),0,IF(O208="Parado",2,1)*1E+13+MIN(N(M208),500)*1E+10+MIN(ROUND(N(F208),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G208="",O208="Aprovado",O208="Recusado",O208="Sem retorno"),0,IF(O208="Parado",2,1)*1E+15+MIN(N(M208),500)*1E+12+MIN(ROUND(N(F208)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -12172,7 +12172,7 @@
         <v/>
       </c>
       <c r="Q209" s="40">
-        <f>IF(OR(G209="",O209="Aprovado",O209="Recusado",O209="Sem retorno"),0,IF(O209="Parado",2,1)*1E+13+MIN(N(M209),500)*1E+10+MIN(ROUND(N(F209),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G209="",O209="Aprovado",O209="Recusado",O209="Sem retorno"),0,IF(O209="Parado",2,1)*1E+15+MIN(N(M209),500)*1E+12+MIN(ROUND(N(F209)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -12212,7 +12212,7 @@
         <v/>
       </c>
       <c r="Q210" s="40">
-        <f>IF(OR(G210="",O210="Aprovado",O210="Recusado",O210="Sem retorno"),0,IF(O210="Parado",2,1)*1E+13+MIN(N(M210),500)*1E+10+MIN(ROUND(N(F210),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G210="",O210="Aprovado",O210="Recusado",O210="Sem retorno"),0,IF(O210="Parado",2,1)*1E+15+MIN(N(M210),500)*1E+12+MIN(ROUND(N(F210)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -12252,7 +12252,7 @@
         <v/>
       </c>
       <c r="Q211" s="40">
-        <f>IF(OR(G211="",O211="Aprovado",O211="Recusado",O211="Sem retorno"),0,IF(O211="Parado",2,1)*1E+13+MIN(N(M211),500)*1E+10+MIN(ROUND(N(F211),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G211="",O211="Aprovado",O211="Recusado",O211="Sem retorno"),0,IF(O211="Parado",2,1)*1E+15+MIN(N(M211),500)*1E+12+MIN(ROUND(N(F211)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -12292,7 +12292,7 @@
         <v/>
       </c>
       <c r="Q212" s="40">
-        <f>IF(OR(G212="",O212="Aprovado",O212="Recusado",O212="Sem retorno"),0,IF(O212="Parado",2,1)*1E+13+MIN(N(M212),500)*1E+10+MIN(ROUND(N(F212),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G212="",O212="Aprovado",O212="Recusado",O212="Sem retorno"),0,IF(O212="Parado",2,1)*1E+15+MIN(N(M212),500)*1E+12+MIN(ROUND(N(F212)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -12332,7 +12332,7 @@
         <v/>
       </c>
       <c r="Q213" s="40">
-        <f>IF(OR(G213="",O213="Aprovado",O213="Recusado",O213="Sem retorno"),0,IF(O213="Parado",2,1)*1E+13+MIN(N(M213),500)*1E+10+MIN(ROUND(N(F213),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G213="",O213="Aprovado",O213="Recusado",O213="Sem retorno"),0,IF(O213="Parado",2,1)*1E+15+MIN(N(M213),500)*1E+12+MIN(ROUND(N(F213)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -12372,7 +12372,7 @@
         <v/>
       </c>
       <c r="Q214" s="40">
-        <f>IF(OR(G214="",O214="Aprovado",O214="Recusado",O214="Sem retorno"),0,IF(O214="Parado",2,1)*1E+13+MIN(N(M214),500)*1E+10+MIN(ROUND(N(F214),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G214="",O214="Aprovado",O214="Recusado",O214="Sem retorno"),0,IF(O214="Parado",2,1)*1E+15+MIN(N(M214),500)*1E+12+MIN(ROUND(N(F214)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -12412,7 +12412,7 @@
         <v/>
       </c>
       <c r="Q215" s="40">
-        <f>IF(OR(G215="",O215="Aprovado",O215="Recusado",O215="Sem retorno"),0,IF(O215="Parado",2,1)*1E+13+MIN(N(M215),500)*1E+10+MIN(ROUND(N(F215),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G215="",O215="Aprovado",O215="Recusado",O215="Sem retorno"),0,IF(O215="Parado",2,1)*1E+15+MIN(N(M215),500)*1E+12+MIN(ROUND(N(F215)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -12452,7 +12452,7 @@
         <v/>
       </c>
       <c r="Q216" s="40">
-        <f>IF(OR(G216="",O216="Aprovado",O216="Recusado",O216="Sem retorno"),0,IF(O216="Parado",2,1)*1E+13+MIN(N(M216),500)*1E+10+MIN(ROUND(N(F216),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G216="",O216="Aprovado",O216="Recusado",O216="Sem retorno"),0,IF(O216="Parado",2,1)*1E+15+MIN(N(M216),500)*1E+12+MIN(ROUND(N(F216)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -12492,7 +12492,7 @@
         <v/>
       </c>
       <c r="Q217" s="40">
-        <f>IF(OR(G217="",O217="Aprovado",O217="Recusado",O217="Sem retorno"),0,IF(O217="Parado",2,1)*1E+13+MIN(N(M217),500)*1E+10+MIN(ROUND(N(F217),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G217="",O217="Aprovado",O217="Recusado",O217="Sem retorno"),0,IF(O217="Parado",2,1)*1E+15+MIN(N(M217),500)*1E+12+MIN(ROUND(N(F217)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -12532,7 +12532,7 @@
         <v/>
       </c>
       <c r="Q218" s="40">
-        <f>IF(OR(G218="",O218="Aprovado",O218="Recusado",O218="Sem retorno"),0,IF(O218="Parado",2,1)*1E+13+MIN(N(M218),500)*1E+10+MIN(ROUND(N(F218),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G218="",O218="Aprovado",O218="Recusado",O218="Sem retorno"),0,IF(O218="Parado",2,1)*1E+15+MIN(N(M218),500)*1E+12+MIN(ROUND(N(F218)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -12572,7 +12572,7 @@
         <v/>
       </c>
       <c r="Q219" s="40">
-        <f>IF(OR(G219="",O219="Aprovado",O219="Recusado",O219="Sem retorno"),0,IF(O219="Parado",2,1)*1E+13+MIN(N(M219),500)*1E+10+MIN(ROUND(N(F219),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G219="",O219="Aprovado",O219="Recusado",O219="Sem retorno"),0,IF(O219="Parado",2,1)*1E+15+MIN(N(M219),500)*1E+12+MIN(ROUND(N(F219)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -12612,7 +12612,7 @@
         <v/>
       </c>
       <c r="Q220" s="40">
-        <f>IF(OR(G220="",O220="Aprovado",O220="Recusado",O220="Sem retorno"),0,IF(O220="Parado",2,1)*1E+13+MIN(N(M220),500)*1E+10+MIN(ROUND(N(F220),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G220="",O220="Aprovado",O220="Recusado",O220="Sem retorno"),0,IF(O220="Parado",2,1)*1E+15+MIN(N(M220),500)*1E+12+MIN(ROUND(N(F220)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -12652,7 +12652,7 @@
         <v/>
       </c>
       <c r="Q221" s="40">
-        <f>IF(OR(G221="",O221="Aprovado",O221="Recusado",O221="Sem retorno"),0,IF(O221="Parado",2,1)*1E+13+MIN(N(M221),500)*1E+10+MIN(ROUND(N(F221),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G221="",O221="Aprovado",O221="Recusado",O221="Sem retorno"),0,IF(O221="Parado",2,1)*1E+15+MIN(N(M221),500)*1E+12+MIN(ROUND(N(F221)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -12692,7 +12692,7 @@
         <v/>
       </c>
       <c r="Q222" s="40">
-        <f>IF(OR(G222="",O222="Aprovado",O222="Recusado",O222="Sem retorno"),0,IF(O222="Parado",2,1)*1E+13+MIN(N(M222),500)*1E+10+MIN(ROUND(N(F222),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G222="",O222="Aprovado",O222="Recusado",O222="Sem retorno"),0,IF(O222="Parado",2,1)*1E+15+MIN(N(M222),500)*1E+12+MIN(ROUND(N(F222)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -12732,7 +12732,7 @@
         <v/>
       </c>
       <c r="Q223" s="40">
-        <f>IF(OR(G223="",O223="Aprovado",O223="Recusado",O223="Sem retorno"),0,IF(O223="Parado",2,1)*1E+13+MIN(N(M223),500)*1E+10+MIN(ROUND(N(F223),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G223="",O223="Aprovado",O223="Recusado",O223="Sem retorno"),0,IF(O223="Parado",2,1)*1E+15+MIN(N(M223),500)*1E+12+MIN(ROUND(N(F223)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -12772,7 +12772,7 @@
         <v/>
       </c>
       <c r="Q224" s="40">
-        <f>IF(OR(G224="",O224="Aprovado",O224="Recusado",O224="Sem retorno"),0,IF(O224="Parado",2,1)*1E+13+MIN(N(M224),500)*1E+10+MIN(ROUND(N(F224),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G224="",O224="Aprovado",O224="Recusado",O224="Sem retorno"),0,IF(O224="Parado",2,1)*1E+15+MIN(N(M224),500)*1E+12+MIN(ROUND(N(F224)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -12812,7 +12812,7 @@
         <v/>
       </c>
       <c r="Q225" s="40">
-        <f>IF(OR(G225="",O225="Aprovado",O225="Recusado",O225="Sem retorno"),0,IF(O225="Parado",2,1)*1E+13+MIN(N(M225),500)*1E+10+MIN(ROUND(N(F225),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G225="",O225="Aprovado",O225="Recusado",O225="Sem retorno"),0,IF(O225="Parado",2,1)*1E+15+MIN(N(M225),500)*1E+12+MIN(ROUND(N(F225)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -12852,7 +12852,7 @@
         <v/>
       </c>
       <c r="Q226" s="40">
-        <f>IF(OR(G226="",O226="Aprovado",O226="Recusado",O226="Sem retorno"),0,IF(O226="Parado",2,1)*1E+13+MIN(N(M226),500)*1E+10+MIN(ROUND(N(F226),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G226="",O226="Aprovado",O226="Recusado",O226="Sem retorno"),0,IF(O226="Parado",2,1)*1E+15+MIN(N(M226),500)*1E+12+MIN(ROUND(N(F226)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -12892,7 +12892,7 @@
         <v/>
       </c>
       <c r="Q227" s="40">
-        <f>IF(OR(G227="",O227="Aprovado",O227="Recusado",O227="Sem retorno"),0,IF(O227="Parado",2,1)*1E+13+MIN(N(M227),500)*1E+10+MIN(ROUND(N(F227),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G227="",O227="Aprovado",O227="Recusado",O227="Sem retorno"),0,IF(O227="Parado",2,1)*1E+15+MIN(N(M227),500)*1E+12+MIN(ROUND(N(F227)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -12932,7 +12932,7 @@
         <v/>
       </c>
       <c r="Q228" s="40">
-        <f>IF(OR(G228="",O228="Aprovado",O228="Recusado",O228="Sem retorno"),0,IF(O228="Parado",2,1)*1E+13+MIN(N(M228),500)*1E+10+MIN(ROUND(N(F228),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G228="",O228="Aprovado",O228="Recusado",O228="Sem retorno"),0,IF(O228="Parado",2,1)*1E+15+MIN(N(M228),500)*1E+12+MIN(ROUND(N(F228)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -12972,7 +12972,7 @@
         <v/>
       </c>
       <c r="Q229" s="40">
-        <f>IF(OR(G229="",O229="Aprovado",O229="Recusado",O229="Sem retorno"),0,IF(O229="Parado",2,1)*1E+13+MIN(N(M229),500)*1E+10+MIN(ROUND(N(F229),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G229="",O229="Aprovado",O229="Recusado",O229="Sem retorno"),0,IF(O229="Parado",2,1)*1E+15+MIN(N(M229),500)*1E+12+MIN(ROUND(N(F229)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -13012,7 +13012,7 @@
         <v/>
       </c>
       <c r="Q230" s="40">
-        <f>IF(OR(G230="",O230="Aprovado",O230="Recusado",O230="Sem retorno"),0,IF(O230="Parado",2,1)*1E+13+MIN(N(M230),500)*1E+10+MIN(ROUND(N(F230),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G230="",O230="Aprovado",O230="Recusado",O230="Sem retorno"),0,IF(O230="Parado",2,1)*1E+15+MIN(N(M230),500)*1E+12+MIN(ROUND(N(F230)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -13052,7 +13052,7 @@
         <v/>
       </c>
       <c r="Q231" s="40">
-        <f>IF(OR(G231="",O231="Aprovado",O231="Recusado",O231="Sem retorno"),0,IF(O231="Parado",2,1)*1E+13+MIN(N(M231),500)*1E+10+MIN(ROUND(N(F231),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G231="",O231="Aprovado",O231="Recusado",O231="Sem retorno"),0,IF(O231="Parado",2,1)*1E+15+MIN(N(M231),500)*1E+12+MIN(ROUND(N(F231)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -13092,7 +13092,7 @@
         <v/>
       </c>
       <c r="Q232" s="40">
-        <f>IF(OR(G232="",O232="Aprovado",O232="Recusado",O232="Sem retorno"),0,IF(O232="Parado",2,1)*1E+13+MIN(N(M232),500)*1E+10+MIN(ROUND(N(F232),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G232="",O232="Aprovado",O232="Recusado",O232="Sem retorno"),0,IF(O232="Parado",2,1)*1E+15+MIN(N(M232),500)*1E+12+MIN(ROUND(N(F232)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -13132,7 +13132,7 @@
         <v/>
       </c>
       <c r="Q233" s="40">
-        <f>IF(OR(G233="",O233="Aprovado",O233="Recusado",O233="Sem retorno"),0,IF(O233="Parado",2,1)*1E+13+MIN(N(M233),500)*1E+10+MIN(ROUND(N(F233),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G233="",O233="Aprovado",O233="Recusado",O233="Sem retorno"),0,IF(O233="Parado",2,1)*1E+15+MIN(N(M233),500)*1E+12+MIN(ROUND(N(F233)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -13172,7 +13172,7 @@
         <v/>
       </c>
       <c r="Q234" s="40">
-        <f>IF(OR(G234="",O234="Aprovado",O234="Recusado",O234="Sem retorno"),0,IF(O234="Parado",2,1)*1E+13+MIN(N(M234),500)*1E+10+MIN(ROUND(N(F234),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G234="",O234="Aprovado",O234="Recusado",O234="Sem retorno"),0,IF(O234="Parado",2,1)*1E+15+MIN(N(M234),500)*1E+12+MIN(ROUND(N(F234)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -13212,7 +13212,7 @@
         <v/>
       </c>
       <c r="Q235" s="40">
-        <f>IF(OR(G235="",O235="Aprovado",O235="Recusado",O235="Sem retorno"),0,IF(O235="Parado",2,1)*1E+13+MIN(N(M235),500)*1E+10+MIN(ROUND(N(F235),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G235="",O235="Aprovado",O235="Recusado",O235="Sem retorno"),0,IF(O235="Parado",2,1)*1E+15+MIN(N(M235),500)*1E+12+MIN(ROUND(N(F235)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -13252,7 +13252,7 @@
         <v/>
       </c>
       <c r="Q236" s="40">
-        <f>IF(OR(G236="",O236="Aprovado",O236="Recusado",O236="Sem retorno"),0,IF(O236="Parado",2,1)*1E+13+MIN(N(M236),500)*1E+10+MIN(ROUND(N(F236),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G236="",O236="Aprovado",O236="Recusado",O236="Sem retorno"),0,IF(O236="Parado",2,1)*1E+15+MIN(N(M236),500)*1E+12+MIN(ROUND(N(F236)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -13292,7 +13292,7 @@
         <v/>
       </c>
       <c r="Q237" s="40">
-        <f>IF(OR(G237="",O237="Aprovado",O237="Recusado",O237="Sem retorno"),0,IF(O237="Parado",2,1)*1E+13+MIN(N(M237),500)*1E+10+MIN(ROUND(N(F237),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G237="",O237="Aprovado",O237="Recusado",O237="Sem retorno"),0,IF(O237="Parado",2,1)*1E+15+MIN(N(M237),500)*1E+12+MIN(ROUND(N(F237)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -13332,7 +13332,7 @@
         <v/>
       </c>
       <c r="Q238" s="40">
-        <f>IF(OR(G238="",O238="Aprovado",O238="Recusado",O238="Sem retorno"),0,IF(O238="Parado",2,1)*1E+13+MIN(N(M238),500)*1E+10+MIN(ROUND(N(F238),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G238="",O238="Aprovado",O238="Recusado",O238="Sem retorno"),0,IF(O238="Parado",2,1)*1E+15+MIN(N(M238),500)*1E+12+MIN(ROUND(N(F238)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -13372,7 +13372,7 @@
         <v/>
       </c>
       <c r="Q239" s="40">
-        <f>IF(OR(G239="",O239="Aprovado",O239="Recusado",O239="Sem retorno"),0,IF(O239="Parado",2,1)*1E+13+MIN(N(M239),500)*1E+10+MIN(ROUND(N(F239),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G239="",O239="Aprovado",O239="Recusado",O239="Sem retorno"),0,IF(O239="Parado",2,1)*1E+15+MIN(N(M239),500)*1E+12+MIN(ROUND(N(F239)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -13412,7 +13412,7 @@
         <v/>
       </c>
       <c r="Q240" s="40">
-        <f>IF(OR(G240="",O240="Aprovado",O240="Recusado",O240="Sem retorno"),0,IF(O240="Parado",2,1)*1E+13+MIN(N(M240),500)*1E+10+MIN(ROUND(N(F240),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G240="",O240="Aprovado",O240="Recusado",O240="Sem retorno"),0,IF(O240="Parado",2,1)*1E+15+MIN(N(M240),500)*1E+12+MIN(ROUND(N(F240)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -13452,7 +13452,7 @@
         <v/>
       </c>
       <c r="Q241" s="40">
-        <f>IF(OR(G241="",O241="Aprovado",O241="Recusado",O241="Sem retorno"),0,IF(O241="Parado",2,1)*1E+13+MIN(N(M241),500)*1E+10+MIN(ROUND(N(F241),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G241="",O241="Aprovado",O241="Recusado",O241="Sem retorno"),0,IF(O241="Parado",2,1)*1E+15+MIN(N(M241),500)*1E+12+MIN(ROUND(N(F241)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -13492,7 +13492,7 @@
         <v/>
       </c>
       <c r="Q242" s="40">
-        <f>IF(OR(G242="",O242="Aprovado",O242="Recusado",O242="Sem retorno"),0,IF(O242="Parado",2,1)*1E+13+MIN(N(M242),500)*1E+10+MIN(ROUND(N(F242),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G242="",O242="Aprovado",O242="Recusado",O242="Sem retorno"),0,IF(O242="Parado",2,1)*1E+15+MIN(N(M242),500)*1E+12+MIN(ROUND(N(F242)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -13532,7 +13532,7 @@
         <v/>
       </c>
       <c r="Q243" s="40">
-        <f>IF(OR(G243="",O243="Aprovado",O243="Recusado",O243="Sem retorno"),0,IF(O243="Parado",2,1)*1E+13+MIN(N(M243),500)*1E+10+MIN(ROUND(N(F243),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G243="",O243="Aprovado",O243="Recusado",O243="Sem retorno"),0,IF(O243="Parado",2,1)*1E+15+MIN(N(M243),500)*1E+12+MIN(ROUND(N(F243)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -13572,7 +13572,7 @@
         <v/>
       </c>
       <c r="Q244" s="40">
-        <f>IF(OR(G244="",O244="Aprovado",O244="Recusado",O244="Sem retorno"),0,IF(O244="Parado",2,1)*1E+13+MIN(N(M244),500)*1E+10+MIN(ROUND(N(F244),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G244="",O244="Aprovado",O244="Recusado",O244="Sem retorno"),0,IF(O244="Parado",2,1)*1E+15+MIN(N(M244),500)*1E+12+MIN(ROUND(N(F244)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -13612,7 +13612,7 @@
         <v/>
       </c>
       <c r="Q245" s="40">
-        <f>IF(OR(G245="",O245="Aprovado",O245="Recusado",O245="Sem retorno"),0,IF(O245="Parado",2,1)*1E+13+MIN(N(M245),500)*1E+10+MIN(ROUND(N(F245),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G245="",O245="Aprovado",O245="Recusado",O245="Sem retorno"),0,IF(O245="Parado",2,1)*1E+15+MIN(N(M245),500)*1E+12+MIN(ROUND(N(F245)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -13652,7 +13652,7 @@
         <v/>
       </c>
       <c r="Q246" s="40">
-        <f>IF(OR(G246="",O246="Aprovado",O246="Recusado",O246="Sem retorno"),0,IF(O246="Parado",2,1)*1E+13+MIN(N(M246),500)*1E+10+MIN(ROUND(N(F246),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G246="",O246="Aprovado",O246="Recusado",O246="Sem retorno"),0,IF(O246="Parado",2,1)*1E+15+MIN(N(M246),500)*1E+12+MIN(ROUND(N(F246)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -13692,7 +13692,7 @@
         <v/>
       </c>
       <c r="Q247" s="40">
-        <f>IF(OR(G247="",O247="Aprovado",O247="Recusado",O247="Sem retorno"),0,IF(O247="Parado",2,1)*1E+13+MIN(N(M247),500)*1E+10+MIN(ROUND(N(F247),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G247="",O247="Aprovado",O247="Recusado",O247="Sem retorno"),0,IF(O247="Parado",2,1)*1E+15+MIN(N(M247),500)*1E+12+MIN(ROUND(N(F247)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -13732,7 +13732,7 @@
         <v/>
       </c>
       <c r="Q248" s="40">
-        <f>IF(OR(G248="",O248="Aprovado",O248="Recusado",O248="Sem retorno"),0,IF(O248="Parado",2,1)*1E+13+MIN(N(M248),500)*1E+10+MIN(ROUND(N(F248),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G248="",O248="Aprovado",O248="Recusado",O248="Sem retorno"),0,IF(O248="Parado",2,1)*1E+15+MIN(N(M248),500)*1E+12+MIN(ROUND(N(F248)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -13772,7 +13772,7 @@
         <v/>
       </c>
       <c r="Q249" s="40">
-        <f>IF(OR(G249="",O249="Aprovado",O249="Recusado",O249="Sem retorno"),0,IF(O249="Parado",2,1)*1E+13+MIN(N(M249),500)*1E+10+MIN(ROUND(N(F249),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G249="",O249="Aprovado",O249="Recusado",O249="Sem retorno"),0,IF(O249="Parado",2,1)*1E+15+MIN(N(M249),500)*1E+12+MIN(ROUND(N(F249)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -13812,7 +13812,7 @@
         <v/>
       </c>
       <c r="Q250" s="40">
-        <f>IF(OR(G250="",O250="Aprovado",O250="Recusado",O250="Sem retorno"),0,IF(O250="Parado",2,1)*1E+13+MIN(N(M250),500)*1E+10+MIN(ROUND(N(F250),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G250="",O250="Aprovado",O250="Recusado",O250="Sem retorno"),0,IF(O250="Parado",2,1)*1E+15+MIN(N(M250),500)*1E+12+MIN(ROUND(N(F250)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -13852,7 +13852,7 @@
         <v/>
       </c>
       <c r="Q251" s="40">
-        <f>IF(OR(G251="",O251="Aprovado",O251="Recusado",O251="Sem retorno"),0,IF(O251="Parado",2,1)*1E+13+MIN(N(M251),500)*1E+10+MIN(ROUND(N(F251),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G251="",O251="Aprovado",O251="Recusado",O251="Sem retorno"),0,IF(O251="Parado",2,1)*1E+15+MIN(N(M251),500)*1E+12+MIN(ROUND(N(F251)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -13892,7 +13892,7 @@
         <v/>
       </c>
       <c r="Q252" s="40">
-        <f>IF(OR(G252="",O252="Aprovado",O252="Recusado",O252="Sem retorno"),0,IF(O252="Parado",2,1)*1E+13+MIN(N(M252),500)*1E+10+MIN(ROUND(N(F252),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G252="",O252="Aprovado",O252="Recusado",O252="Sem retorno"),0,IF(O252="Parado",2,1)*1E+15+MIN(N(M252),500)*1E+12+MIN(ROUND(N(F252)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -13932,7 +13932,7 @@
         <v/>
       </c>
       <c r="Q253" s="40">
-        <f>IF(OR(G253="",O253="Aprovado",O253="Recusado",O253="Sem retorno"),0,IF(O253="Parado",2,1)*1E+13+MIN(N(M253),500)*1E+10+MIN(ROUND(N(F253),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G253="",O253="Aprovado",O253="Recusado",O253="Sem retorno"),0,IF(O253="Parado",2,1)*1E+15+MIN(N(M253),500)*1E+12+MIN(ROUND(N(F253)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -13972,7 +13972,7 @@
         <v/>
       </c>
       <c r="Q254" s="40">
-        <f>IF(OR(G254="",O254="Aprovado",O254="Recusado",O254="Sem retorno"),0,IF(O254="Parado",2,1)*1E+13+MIN(N(M254),500)*1E+10+MIN(ROUND(N(F254),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G254="",O254="Aprovado",O254="Recusado",O254="Sem retorno"),0,IF(O254="Parado",2,1)*1E+15+MIN(N(M254),500)*1E+12+MIN(ROUND(N(F254)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -14012,7 +14012,7 @@
         <v/>
       </c>
       <c r="Q255" s="40">
-        <f>IF(OR(G255="",O255="Aprovado",O255="Recusado",O255="Sem retorno"),0,IF(O255="Parado",2,1)*1E+13+MIN(N(M255),500)*1E+10+MIN(ROUND(N(F255),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G255="",O255="Aprovado",O255="Recusado",O255="Sem retorno"),0,IF(O255="Parado",2,1)*1E+15+MIN(N(M255),500)*1E+12+MIN(ROUND(N(F255)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -14052,7 +14052,7 @@
         <v/>
       </c>
       <c r="Q256" s="40">
-        <f>IF(OR(G256="",O256="Aprovado",O256="Recusado",O256="Sem retorno"),0,IF(O256="Parado",2,1)*1E+13+MIN(N(M256),500)*1E+10+MIN(ROUND(N(F256),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G256="",O256="Aprovado",O256="Recusado",O256="Sem retorno"),0,IF(O256="Parado",2,1)*1E+15+MIN(N(M256),500)*1E+12+MIN(ROUND(N(F256)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -14092,7 +14092,7 @@
         <v/>
       </c>
       <c r="Q257" s="40">
-        <f>IF(OR(G257="",O257="Aprovado",O257="Recusado",O257="Sem retorno"),0,IF(O257="Parado",2,1)*1E+13+MIN(N(M257),500)*1E+10+MIN(ROUND(N(F257),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G257="",O257="Aprovado",O257="Recusado",O257="Sem retorno"),0,IF(O257="Parado",2,1)*1E+15+MIN(N(M257),500)*1E+12+MIN(ROUND(N(F257)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -14132,7 +14132,7 @@
         <v/>
       </c>
       <c r="Q258" s="40">
-        <f>IF(OR(G258="",O258="Aprovado",O258="Recusado",O258="Sem retorno"),0,IF(O258="Parado",2,1)*1E+13+MIN(N(M258),500)*1E+10+MIN(ROUND(N(F258),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G258="",O258="Aprovado",O258="Recusado",O258="Sem retorno"),0,IF(O258="Parado",2,1)*1E+15+MIN(N(M258),500)*1E+12+MIN(ROUND(N(F258)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -14172,7 +14172,7 @@
         <v/>
       </c>
       <c r="Q259" s="40">
-        <f>IF(OR(G259="",O259="Aprovado",O259="Recusado",O259="Sem retorno"),0,IF(O259="Parado",2,1)*1E+13+MIN(N(M259),500)*1E+10+MIN(ROUND(N(F259),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G259="",O259="Aprovado",O259="Recusado",O259="Sem retorno"),0,IF(O259="Parado",2,1)*1E+15+MIN(N(M259),500)*1E+12+MIN(ROUND(N(F259)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -14212,7 +14212,7 @@
         <v/>
       </c>
       <c r="Q260" s="40">
-        <f>IF(OR(G260="",O260="Aprovado",O260="Recusado",O260="Sem retorno"),0,IF(O260="Parado",2,1)*1E+13+MIN(N(M260),500)*1E+10+MIN(ROUND(N(F260),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G260="",O260="Aprovado",O260="Recusado",O260="Sem retorno"),0,IF(O260="Parado",2,1)*1E+15+MIN(N(M260),500)*1E+12+MIN(ROUND(N(F260)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -14252,7 +14252,7 @@
         <v/>
       </c>
       <c r="Q261" s="40">
-        <f>IF(OR(G261="",O261="Aprovado",O261="Recusado",O261="Sem retorno"),0,IF(O261="Parado",2,1)*1E+13+MIN(N(M261),500)*1E+10+MIN(ROUND(N(F261),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G261="",O261="Aprovado",O261="Recusado",O261="Sem retorno"),0,IF(O261="Parado",2,1)*1E+15+MIN(N(M261),500)*1E+12+MIN(ROUND(N(F261)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -14292,7 +14292,7 @@
         <v/>
       </c>
       <c r="Q262" s="40">
-        <f>IF(OR(G262="",O262="Aprovado",O262="Recusado",O262="Sem retorno"),0,IF(O262="Parado",2,1)*1E+13+MIN(N(M262),500)*1E+10+MIN(ROUND(N(F262),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G262="",O262="Aprovado",O262="Recusado",O262="Sem retorno"),0,IF(O262="Parado",2,1)*1E+15+MIN(N(M262),500)*1E+12+MIN(ROUND(N(F262)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -14332,7 +14332,7 @@
         <v/>
       </c>
       <c r="Q263" s="40">
-        <f>IF(OR(G263="",O263="Aprovado",O263="Recusado",O263="Sem retorno"),0,IF(O263="Parado",2,1)*1E+13+MIN(N(M263),500)*1E+10+MIN(ROUND(N(F263),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G263="",O263="Aprovado",O263="Recusado",O263="Sem retorno"),0,IF(O263="Parado",2,1)*1E+15+MIN(N(M263),500)*1E+12+MIN(ROUND(N(F263)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -14372,7 +14372,7 @@
         <v/>
       </c>
       <c r="Q264" s="40">
-        <f>IF(OR(G264="",O264="Aprovado",O264="Recusado",O264="Sem retorno"),0,IF(O264="Parado",2,1)*1E+13+MIN(N(M264),500)*1E+10+MIN(ROUND(N(F264),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G264="",O264="Aprovado",O264="Recusado",O264="Sem retorno"),0,IF(O264="Parado",2,1)*1E+15+MIN(N(M264),500)*1E+12+MIN(ROUND(N(F264)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -14412,7 +14412,7 @@
         <v/>
       </c>
       <c r="Q265" s="40">
-        <f>IF(OR(G265="",O265="Aprovado",O265="Recusado",O265="Sem retorno"),0,IF(O265="Parado",2,1)*1E+13+MIN(N(M265),500)*1E+10+MIN(ROUND(N(F265),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G265="",O265="Aprovado",O265="Recusado",O265="Sem retorno"),0,IF(O265="Parado",2,1)*1E+15+MIN(N(M265),500)*1E+12+MIN(ROUND(N(F265)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -14452,7 +14452,7 @@
         <v/>
       </c>
       <c r="Q266" s="40">
-        <f>IF(OR(G266="",O266="Aprovado",O266="Recusado",O266="Sem retorno"),0,IF(O266="Parado",2,1)*1E+13+MIN(N(M266),500)*1E+10+MIN(ROUND(N(F266),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G266="",O266="Aprovado",O266="Recusado",O266="Sem retorno"),0,IF(O266="Parado",2,1)*1E+15+MIN(N(M266),500)*1E+12+MIN(ROUND(N(F266)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -14492,7 +14492,7 @@
         <v/>
       </c>
       <c r="Q267" s="40">
-        <f>IF(OR(G267="",O267="Aprovado",O267="Recusado",O267="Sem retorno"),0,IF(O267="Parado",2,1)*1E+13+MIN(N(M267),500)*1E+10+MIN(ROUND(N(F267),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G267="",O267="Aprovado",O267="Recusado",O267="Sem retorno"),0,IF(O267="Parado",2,1)*1E+15+MIN(N(M267),500)*1E+12+MIN(ROUND(N(F267)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -14532,7 +14532,7 @@
         <v/>
       </c>
       <c r="Q268" s="40">
-        <f>IF(OR(G268="",O268="Aprovado",O268="Recusado",O268="Sem retorno"),0,IF(O268="Parado",2,1)*1E+13+MIN(N(M268),500)*1E+10+MIN(ROUND(N(F268),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G268="",O268="Aprovado",O268="Recusado",O268="Sem retorno"),0,IF(O268="Parado",2,1)*1E+15+MIN(N(M268),500)*1E+12+MIN(ROUND(N(F268)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -14572,7 +14572,7 @@
         <v/>
       </c>
       <c r="Q269" s="40">
-        <f>IF(OR(G269="",O269="Aprovado",O269="Recusado",O269="Sem retorno"),0,IF(O269="Parado",2,1)*1E+13+MIN(N(M269),500)*1E+10+MIN(ROUND(N(F269),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G269="",O269="Aprovado",O269="Recusado",O269="Sem retorno"),0,IF(O269="Parado",2,1)*1E+15+MIN(N(M269),500)*1E+12+MIN(ROUND(N(F269)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -14612,7 +14612,7 @@
         <v/>
       </c>
       <c r="Q270" s="40">
-        <f>IF(OR(G270="",O270="Aprovado",O270="Recusado",O270="Sem retorno"),0,IF(O270="Parado",2,1)*1E+13+MIN(N(M270),500)*1E+10+MIN(ROUND(N(F270),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G270="",O270="Aprovado",O270="Recusado",O270="Sem retorno"),0,IF(O270="Parado",2,1)*1E+15+MIN(N(M270),500)*1E+12+MIN(ROUND(N(F270)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -14652,7 +14652,7 @@
         <v/>
       </c>
       <c r="Q271" s="40">
-        <f>IF(OR(G271="",O271="Aprovado",O271="Recusado",O271="Sem retorno"),0,IF(O271="Parado",2,1)*1E+13+MIN(N(M271),500)*1E+10+MIN(ROUND(N(F271),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G271="",O271="Aprovado",O271="Recusado",O271="Sem retorno"),0,IF(O271="Parado",2,1)*1E+15+MIN(N(M271),500)*1E+12+MIN(ROUND(N(F271)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -14692,7 +14692,7 @@
         <v/>
       </c>
       <c r="Q272" s="40">
-        <f>IF(OR(G272="",O272="Aprovado",O272="Recusado",O272="Sem retorno"),0,IF(O272="Parado",2,1)*1E+13+MIN(N(M272),500)*1E+10+MIN(ROUND(N(F272),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G272="",O272="Aprovado",O272="Recusado",O272="Sem retorno"),0,IF(O272="Parado",2,1)*1E+15+MIN(N(M272),500)*1E+12+MIN(ROUND(N(F272)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -14732,7 +14732,7 @@
         <v/>
       </c>
       <c r="Q273" s="40">
-        <f>IF(OR(G273="",O273="Aprovado",O273="Recusado",O273="Sem retorno"),0,IF(O273="Parado",2,1)*1E+13+MIN(N(M273),500)*1E+10+MIN(ROUND(N(F273),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G273="",O273="Aprovado",O273="Recusado",O273="Sem retorno"),0,IF(O273="Parado",2,1)*1E+15+MIN(N(M273),500)*1E+12+MIN(ROUND(N(F273)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -14772,7 +14772,7 @@
         <v/>
       </c>
       <c r="Q274" s="40">
-        <f>IF(OR(G274="",O274="Aprovado",O274="Recusado",O274="Sem retorno"),0,IF(O274="Parado",2,1)*1E+13+MIN(N(M274),500)*1E+10+MIN(ROUND(N(F274),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G274="",O274="Aprovado",O274="Recusado",O274="Sem retorno"),0,IF(O274="Parado",2,1)*1E+15+MIN(N(M274),500)*1E+12+MIN(ROUND(N(F274)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -14812,7 +14812,7 @@
         <v/>
       </c>
       <c r="Q275" s="40">
-        <f>IF(OR(G275="",O275="Aprovado",O275="Recusado",O275="Sem retorno"),0,IF(O275="Parado",2,1)*1E+13+MIN(N(M275),500)*1E+10+MIN(ROUND(N(F275),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G275="",O275="Aprovado",O275="Recusado",O275="Sem retorno"),0,IF(O275="Parado",2,1)*1E+15+MIN(N(M275),500)*1E+12+MIN(ROUND(N(F275)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -14852,7 +14852,7 @@
         <v/>
       </c>
       <c r="Q276" s="40">
-        <f>IF(OR(G276="",O276="Aprovado",O276="Recusado",O276="Sem retorno"),0,IF(O276="Parado",2,1)*1E+13+MIN(N(M276),500)*1E+10+MIN(ROUND(N(F276),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G276="",O276="Aprovado",O276="Recusado",O276="Sem retorno"),0,IF(O276="Parado",2,1)*1E+15+MIN(N(M276),500)*1E+12+MIN(ROUND(N(F276)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -14892,7 +14892,7 @@
         <v/>
       </c>
       <c r="Q277" s="40">
-        <f>IF(OR(G277="",O277="Aprovado",O277="Recusado",O277="Sem retorno"),0,IF(O277="Parado",2,1)*1E+13+MIN(N(M277),500)*1E+10+MIN(ROUND(N(F277),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G277="",O277="Aprovado",O277="Recusado",O277="Sem retorno"),0,IF(O277="Parado",2,1)*1E+15+MIN(N(M277),500)*1E+12+MIN(ROUND(N(F277)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -14932,7 +14932,7 @@
         <v/>
       </c>
       <c r="Q278" s="40">
-        <f>IF(OR(G278="",O278="Aprovado",O278="Recusado",O278="Sem retorno"),0,IF(O278="Parado",2,1)*1E+13+MIN(N(M278),500)*1E+10+MIN(ROUND(N(F278),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G278="",O278="Aprovado",O278="Recusado",O278="Sem retorno"),0,IF(O278="Parado",2,1)*1E+15+MIN(N(M278),500)*1E+12+MIN(ROUND(N(F278)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -14972,7 +14972,7 @@
         <v/>
       </c>
       <c r="Q279" s="40">
-        <f>IF(OR(G279="",O279="Aprovado",O279="Recusado",O279="Sem retorno"),0,IF(O279="Parado",2,1)*1E+13+MIN(N(M279),500)*1E+10+MIN(ROUND(N(F279),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G279="",O279="Aprovado",O279="Recusado",O279="Sem retorno"),0,IF(O279="Parado",2,1)*1E+15+MIN(N(M279),500)*1E+12+MIN(ROUND(N(F279)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -15012,7 +15012,7 @@
         <v/>
       </c>
       <c r="Q280" s="40">
-        <f>IF(OR(G280="",O280="Aprovado",O280="Recusado",O280="Sem retorno"),0,IF(O280="Parado",2,1)*1E+13+MIN(N(M280),500)*1E+10+MIN(ROUND(N(F280),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G280="",O280="Aprovado",O280="Recusado",O280="Sem retorno"),0,IF(O280="Parado",2,1)*1E+15+MIN(N(M280),500)*1E+12+MIN(ROUND(N(F280)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -15052,7 +15052,7 @@
         <v/>
       </c>
       <c r="Q281" s="40">
-        <f>IF(OR(G281="",O281="Aprovado",O281="Recusado",O281="Sem retorno"),0,IF(O281="Parado",2,1)*1E+13+MIN(N(M281),500)*1E+10+MIN(ROUND(N(F281),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G281="",O281="Aprovado",O281="Recusado",O281="Sem retorno"),0,IF(O281="Parado",2,1)*1E+15+MIN(N(M281),500)*1E+12+MIN(ROUND(N(F281)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -15092,7 +15092,7 @@
         <v/>
       </c>
       <c r="Q282" s="40">
-        <f>IF(OR(G282="",O282="Aprovado",O282="Recusado",O282="Sem retorno"),0,IF(O282="Parado",2,1)*1E+13+MIN(N(M282),500)*1E+10+MIN(ROUND(N(F282),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G282="",O282="Aprovado",O282="Recusado",O282="Sem retorno"),0,IF(O282="Parado",2,1)*1E+15+MIN(N(M282),500)*1E+12+MIN(ROUND(N(F282)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -15132,7 +15132,7 @@
         <v/>
       </c>
       <c r="Q283" s="40">
-        <f>IF(OR(G283="",O283="Aprovado",O283="Recusado",O283="Sem retorno"),0,IF(O283="Parado",2,1)*1E+13+MIN(N(M283),500)*1E+10+MIN(ROUND(N(F283),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G283="",O283="Aprovado",O283="Recusado",O283="Sem retorno"),0,IF(O283="Parado",2,1)*1E+15+MIN(N(M283),500)*1E+12+MIN(ROUND(N(F283)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -15172,7 +15172,7 @@
         <v/>
       </c>
       <c r="Q284" s="40">
-        <f>IF(OR(G284="",O284="Aprovado",O284="Recusado",O284="Sem retorno"),0,IF(O284="Parado",2,1)*1E+13+MIN(N(M284),500)*1E+10+MIN(ROUND(N(F284),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G284="",O284="Aprovado",O284="Recusado",O284="Sem retorno"),0,IF(O284="Parado",2,1)*1E+15+MIN(N(M284),500)*1E+12+MIN(ROUND(N(F284)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -15212,7 +15212,7 @@
         <v/>
       </c>
       <c r="Q285" s="40">
-        <f>IF(OR(G285="",O285="Aprovado",O285="Recusado",O285="Sem retorno"),0,IF(O285="Parado",2,1)*1E+13+MIN(N(M285),500)*1E+10+MIN(ROUND(N(F285),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G285="",O285="Aprovado",O285="Recusado",O285="Sem retorno"),0,IF(O285="Parado",2,1)*1E+15+MIN(N(M285),500)*1E+12+MIN(ROUND(N(F285)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -15252,7 +15252,7 @@
         <v/>
       </c>
       <c r="Q286" s="40">
-        <f>IF(OR(G286="",O286="Aprovado",O286="Recusado",O286="Sem retorno"),0,IF(O286="Parado",2,1)*1E+13+MIN(N(M286),500)*1E+10+MIN(ROUND(N(F286),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G286="",O286="Aprovado",O286="Recusado",O286="Sem retorno"),0,IF(O286="Parado",2,1)*1E+15+MIN(N(M286),500)*1E+12+MIN(ROUND(N(F286)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -15292,7 +15292,7 @@
         <v/>
       </c>
       <c r="Q287" s="40">
-        <f>IF(OR(G287="",O287="Aprovado",O287="Recusado",O287="Sem retorno"),0,IF(O287="Parado",2,1)*1E+13+MIN(N(M287),500)*1E+10+MIN(ROUND(N(F287),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G287="",O287="Aprovado",O287="Recusado",O287="Sem retorno"),0,IF(O287="Parado",2,1)*1E+15+MIN(N(M287),500)*1E+12+MIN(ROUND(N(F287)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -15332,7 +15332,7 @@
         <v/>
       </c>
       <c r="Q288" s="40">
-        <f>IF(OR(G288="",O288="Aprovado",O288="Recusado",O288="Sem retorno"),0,IF(O288="Parado",2,1)*1E+13+MIN(N(M288),500)*1E+10+MIN(ROUND(N(F288),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G288="",O288="Aprovado",O288="Recusado",O288="Sem retorno"),0,IF(O288="Parado",2,1)*1E+15+MIN(N(M288),500)*1E+12+MIN(ROUND(N(F288)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -15372,7 +15372,7 @@
         <v/>
       </c>
       <c r="Q289" s="40">
-        <f>IF(OR(G289="",O289="Aprovado",O289="Recusado",O289="Sem retorno"),0,IF(O289="Parado",2,1)*1E+13+MIN(N(M289),500)*1E+10+MIN(ROUND(N(F289),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G289="",O289="Aprovado",O289="Recusado",O289="Sem retorno"),0,IF(O289="Parado",2,1)*1E+15+MIN(N(M289),500)*1E+12+MIN(ROUND(N(F289)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -15412,7 +15412,7 @@
         <v/>
       </c>
       <c r="Q290" s="40">
-        <f>IF(OR(G290="",O290="Aprovado",O290="Recusado",O290="Sem retorno"),0,IF(O290="Parado",2,1)*1E+13+MIN(N(M290),500)*1E+10+MIN(ROUND(N(F290),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G290="",O290="Aprovado",O290="Recusado",O290="Sem retorno"),0,IF(O290="Parado",2,1)*1E+15+MIN(N(M290),500)*1E+12+MIN(ROUND(N(F290)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -15452,7 +15452,7 @@
         <v/>
       </c>
       <c r="Q291" s="40">
-        <f>IF(OR(G291="",O291="Aprovado",O291="Recusado",O291="Sem retorno"),0,IF(O291="Parado",2,1)*1E+13+MIN(N(M291),500)*1E+10+MIN(ROUND(N(F291),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G291="",O291="Aprovado",O291="Recusado",O291="Sem retorno"),0,IF(O291="Parado",2,1)*1E+15+MIN(N(M291),500)*1E+12+MIN(ROUND(N(F291)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -15492,7 +15492,7 @@
         <v/>
       </c>
       <c r="Q292" s="40">
-        <f>IF(OR(G292="",O292="Aprovado",O292="Recusado",O292="Sem retorno"),0,IF(O292="Parado",2,1)*1E+13+MIN(N(M292),500)*1E+10+MIN(ROUND(N(F292),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G292="",O292="Aprovado",O292="Recusado",O292="Sem retorno"),0,IF(O292="Parado",2,1)*1E+15+MIN(N(M292),500)*1E+12+MIN(ROUND(N(F292)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -15532,7 +15532,7 @@
         <v/>
       </c>
       <c r="Q293" s="40">
-        <f>IF(OR(G293="",O293="Aprovado",O293="Recusado",O293="Sem retorno"),0,IF(O293="Parado",2,1)*1E+13+MIN(N(M293),500)*1E+10+MIN(ROUND(N(F293),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G293="",O293="Aprovado",O293="Recusado",O293="Sem retorno"),0,IF(O293="Parado",2,1)*1E+15+MIN(N(M293),500)*1E+12+MIN(ROUND(N(F293)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -15572,7 +15572,7 @@
         <v/>
       </c>
       <c r="Q294" s="40">
-        <f>IF(OR(G294="",O294="Aprovado",O294="Recusado",O294="Sem retorno"),0,IF(O294="Parado",2,1)*1E+13+MIN(N(M294),500)*1E+10+MIN(ROUND(N(F294),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G294="",O294="Aprovado",O294="Recusado",O294="Sem retorno"),0,IF(O294="Parado",2,1)*1E+15+MIN(N(M294),500)*1E+12+MIN(ROUND(N(F294)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -15612,7 +15612,7 @@
         <v/>
       </c>
       <c r="Q295" s="40">
-        <f>IF(OR(G295="",O295="Aprovado",O295="Recusado",O295="Sem retorno"),0,IF(O295="Parado",2,1)*1E+13+MIN(N(M295),500)*1E+10+MIN(ROUND(N(F295),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G295="",O295="Aprovado",O295="Recusado",O295="Sem retorno"),0,IF(O295="Parado",2,1)*1E+15+MIN(N(M295),500)*1E+12+MIN(ROUND(N(F295)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -15652,7 +15652,7 @@
         <v/>
       </c>
       <c r="Q296" s="40">
-        <f>IF(OR(G296="",O296="Aprovado",O296="Recusado",O296="Sem retorno"),0,IF(O296="Parado",2,1)*1E+13+MIN(N(M296),500)*1E+10+MIN(ROUND(N(F296),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G296="",O296="Aprovado",O296="Recusado",O296="Sem retorno"),0,IF(O296="Parado",2,1)*1E+15+MIN(N(M296),500)*1E+12+MIN(ROUND(N(F296)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -15692,7 +15692,7 @@
         <v/>
       </c>
       <c r="Q297" s="40">
-        <f>IF(OR(G297="",O297="Aprovado",O297="Recusado",O297="Sem retorno"),0,IF(O297="Parado",2,1)*1E+13+MIN(N(M297),500)*1E+10+MIN(ROUND(N(F297),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G297="",O297="Aprovado",O297="Recusado",O297="Sem retorno"),0,IF(O297="Parado",2,1)*1E+15+MIN(N(M297),500)*1E+12+MIN(ROUND(N(F297)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -15732,7 +15732,7 @@
         <v/>
       </c>
       <c r="Q298" s="40">
-        <f>IF(OR(G298="",O298="Aprovado",O298="Recusado",O298="Sem retorno"),0,IF(O298="Parado",2,1)*1E+13+MIN(N(M298),500)*1E+10+MIN(ROUND(N(F298),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G298="",O298="Aprovado",O298="Recusado",O298="Sem retorno"),0,IF(O298="Parado",2,1)*1E+15+MIN(N(M298),500)*1E+12+MIN(ROUND(N(F298)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -15772,7 +15772,7 @@
         <v/>
       </c>
       <c r="Q299" s="40">
-        <f>IF(OR(G299="",O299="Aprovado",O299="Recusado",O299="Sem retorno"),0,IF(O299="Parado",2,1)*1E+13+MIN(N(M299),500)*1E+10+MIN(ROUND(N(F299),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G299="",O299="Aprovado",O299="Recusado",O299="Sem retorno"),0,IF(O299="Parado",2,1)*1E+15+MIN(N(M299),500)*1E+12+MIN(ROUND(N(F299)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -15812,7 +15812,7 @@
         <v/>
       </c>
       <c r="Q300" s="40">
-        <f>IF(OR(G300="",O300="Aprovado",O300="Recusado",O300="Sem retorno"),0,IF(O300="Parado",2,1)*1E+13+MIN(N(M300),500)*1E+10+MIN(ROUND(N(F300),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G300="",O300="Aprovado",O300="Recusado",O300="Sem retorno"),0,IF(O300="Parado",2,1)*1E+15+MIN(N(M300),500)*1E+12+MIN(ROUND(N(F300)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -15852,7 +15852,7 @@
         <v/>
       </c>
       <c r="Q301" s="40">
-        <f>IF(OR(G301="",O301="Aprovado",O301="Recusado",O301="Sem retorno"),0,IF(O301="Parado",2,1)*1E+13+MIN(N(M301),500)*1E+10+MIN(ROUND(N(F301),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G301="",O301="Aprovado",O301="Recusado",O301="Sem retorno"),0,IF(O301="Parado",2,1)*1E+15+MIN(N(M301),500)*1E+12+MIN(ROUND(N(F301)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -15892,7 +15892,7 @@
         <v/>
       </c>
       <c r="Q302" s="40">
-        <f>IF(OR(G302="",O302="Aprovado",O302="Recusado",O302="Sem retorno"),0,IF(O302="Parado",2,1)*1E+13+MIN(N(M302),500)*1E+10+MIN(ROUND(N(F302),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G302="",O302="Aprovado",O302="Recusado",O302="Sem retorno"),0,IF(O302="Parado",2,1)*1E+15+MIN(N(M302),500)*1E+12+MIN(ROUND(N(F302)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -15932,7 +15932,7 @@
         <v/>
       </c>
       <c r="Q303" s="40">
-        <f>IF(OR(G303="",O303="Aprovado",O303="Recusado",O303="Sem retorno"),0,IF(O303="Parado",2,1)*1E+13+MIN(N(M303),500)*1E+10+MIN(ROUND(N(F303),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G303="",O303="Aprovado",O303="Recusado",O303="Sem retorno"),0,IF(O303="Parado",2,1)*1E+15+MIN(N(M303),500)*1E+12+MIN(ROUND(N(F303)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
@@ -15972,7 +15972,7 @@
         <v/>
       </c>
       <c r="Q304" s="40">
-        <f>IF(OR(G304="",O304="Aprovado",O304="Recusado",O304="Sem retorno"),0,IF(O304="Parado",2,1)*1E+13+MIN(N(M304),500)*1E+10+MIN(ROUND(N(F304),0),999999)*1E+4+(304+1-ROW()))</f>
+        <f>IF(OR(G304="",O304="Aprovado",O304="Recusado",O304="Sem retorno"),0,IF(O304="Parado",2,1)*1E+15+MIN(N(M304),500)*1E+12+MIN(ROUND(N(F304)*100,0),99999999)*1E+4+(304+1-ROW()))</f>
         <v>0</v>
       </c>
     </row>
